--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\Brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35FD525B-14FB-4C20-BEF9-C0F745E33821}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD437C13-FF10-42DB-87DF-231A821462FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="60">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -51,325 +51,172 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>marcelly.vericimo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>claudia.magalhaes@allianz.com.br</t>
-  </si>
-  <si>
     <t>vanessa.campos@allianz.com.br</t>
   </si>
   <si>
     <t>juliana.santos@allianz.com.br</t>
   </si>
   <si>
-    <t>ana.sales@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-96211326300 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
     <t>eliana.pedroso@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12296741400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>dinah.castro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12653056200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>rosangela.silva1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-2315229910 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-2501404890 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>william.bonifacio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12644782800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>lisiane.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12655055000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>irene.rosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-33579288000150 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>rafael.petrin@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-9620651880 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>valeria.palhares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12599907100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>erica.cassandre@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12646946200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-46121588000132 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>izabela.cuba@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-71841902000107 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
     <t>fabio.lima@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12642351800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>thais.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12484233100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>daniel.iarrocheski@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12519410900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>jaciely.dias@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12652313600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>green.ferreira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12563859600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>sara.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-525035265 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12653249400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12654774600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
     <t>allan.soares@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-45438301000130 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>angela.carmo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-54000556134 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>talita.meneses@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12652520500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>isabel.cit@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-49059939972 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>carla.dalemolle@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-83883991015 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>douglas.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12654689000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>alan.peter@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-42496788000119 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>bruna.teixeira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12654425900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>andrea.duarte@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-31834393000162 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-41928626000140 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>leticia.pitkowski@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-9393835861 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>cassia.souza@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11125290633 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
     <t>geiza.vinand@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12649322600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>jonatas.lauretto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-57711313772 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-2977310762 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>stephanye.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12654223100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>rodrigo.nascimento@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-32946694968 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>samuel.martins@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-19912447972 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>izys.barreto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12652259100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>ivone.jesus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12515699600000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>lucidene.santana@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12652779800000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12654767300000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>laerte.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12531236300000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>silvia.plaza@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12654008300001 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>alessandra.souza@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-404925243 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>vanessa.almeida1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-1828866547 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>ana.santos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-2601348992 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
     <t>vanice.silva@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-2839518694 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>kelli.santos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-3064355783 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>everaldo.cordeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-5753871739 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11760321869 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>eloiza.felippe@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-29734118749 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-33926756870 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>alessandra.guedes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-51342967828 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>caroline.martins@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-89366565034 Nota 531 - Alteração ou correção dados cadastrais</t>
+    <t>gustavo.souza@allianz.com.br</t>
+  </si>
+  <si>
+    <t>janaina.rocha@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12250983000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12656554800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>diego.vasconcelos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-29414190000175 Nota 531 - Alteração ou correção dados cadastrais</t>
+  </si>
+  <si>
+    <t>luiz.inocente@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12397293400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12641009400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>sonia.nascimento@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12657597500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12652483300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>gleison.ferreira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12601582000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-26335638720 Nota 531 - Alteração ou correção dados cadastrais</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13940249831 Nota 531 - Alteração ou correção dados cadastrais</t>
+  </si>
+  <si>
+    <t>afonso.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12656914300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>rodrigo.kuguyama@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12372867400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>micael.silveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12394458000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-55472400015 Nota 531 - Alteração ou correção dados cadastrais</t>
+  </si>
+  <si>
+    <t>armando.filho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12655694000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>daiane.soares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12655707000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>rosalia.branco@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12657849300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>monica.plassa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-18526526839 Nota 531 - Alteração ou correção dados cadastrais</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-20919110000169 Nota 531 - Alteração ou correção dados cadastrais</t>
+  </si>
+  <si>
+    <t>erica.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12654682700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>fernanda.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12504941900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12654539600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>ivana.freitas@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12656773000000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>jocineia.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-29939730888 Nota 531 - Alteração ou correção dados cadastrais</t>
+  </si>
+  <si>
+    <t>aires.junior@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-926383175 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12655035400000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12569866500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>adriana.abreu@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12629752700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-19711867000183 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-48167045072 Nota 531 - Alteração ou correção dados cadastrais</t>
   </si>
 </sst>
 </file>
@@ -756,7 +603,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:C57"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr defaultColWidth="9.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="55.54296875" style="2" customWidth="1"/>
@@ -780,10 +627,10 @@
     </row>
     <row r="2" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A2" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
@@ -791,10 +638,10 @@
     </row>
     <row r="3" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>3</v>
@@ -802,10 +649,10 @@
     </row>
     <row r="4" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>3</v>
@@ -813,10 +660,10 @@
     </row>
     <row r="5" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>3</v>
@@ -824,10 +671,10 @@
     </row>
     <row r="6" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>3</v>
@@ -835,10 +682,10 @@
     </row>
     <row r="7" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>3</v>
@@ -846,7 +693,7 @@
     </row>
     <row r="8" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>22</v>
@@ -868,10 +715,10 @@
     </row>
     <row r="10" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>3</v>
@@ -879,10 +726,10 @@
     </row>
     <row r="11" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>3</v>
@@ -890,10 +737,10 @@
     </row>
     <row r="12" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>3</v>
@@ -901,10 +748,10 @@
     </row>
     <row r="13" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>3</v>
@@ -912,10 +759,10 @@
     </row>
     <row r="14" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>3</v>
@@ -923,10 +770,10 @@
     </row>
     <row r="15" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>3</v>
@@ -934,10 +781,10 @@
     </row>
     <row r="16" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>3</v>
@@ -945,10 +792,10 @@
     </row>
     <row r="17" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>3</v>
@@ -956,10 +803,10 @@
     </row>
     <row r="18" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>3</v>
@@ -967,10 +814,10 @@
     </row>
     <row r="19" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>3</v>
@@ -978,10 +825,10 @@
     </row>
     <row r="20" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>3</v>
@@ -989,10 +836,10 @@
     </row>
     <row r="21" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>3</v>
@@ -1000,10 +847,10 @@
     </row>
     <row r="22" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>3</v>
@@ -1011,7 +858,7 @@
     </row>
     <row r="23" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>47</v>
@@ -1055,10 +902,10 @@
     </row>
     <row r="27" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>55</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>3</v>
@@ -1066,10 +913,10 @@
     </row>
     <row r="28" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>3</v>
@@ -1077,10 +924,10 @@
     </row>
     <row r="29" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>3</v>
@@ -1088,10 +935,10 @@
     </row>
     <row r="30" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
-        <v>60</v>
+        <v>10</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>3</v>
@@ -1099,298 +946,12 @@
     </row>
     <row r="31" spans="1:3" ht="29" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A32" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A33" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A34" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A35" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A36" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A37" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A38" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A39" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A40" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A41" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A42" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A43" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A44" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A45" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A46" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A47" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A48" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A49" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A50" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A51" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A52" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A53" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A54" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A55" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A56" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="29" x14ac:dyDescent="0.35">
-      <c r="A57" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C57" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C92BF23B-B3CE-4B51-ACFC-DDDA11BACB36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06CABC8A-C964-47FF-81C6-E42A336F6989}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="59">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -51,175 +51,169 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>caroline.falcao@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12383775400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>rafael.petrin@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-17021257000122 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>claudia.magalhaes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12668486900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>matheus.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12652666300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>luiz.junior@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12589353500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>danillo.boem@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12678584900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>gleison.ferreira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12672620600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>allan.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12671332900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
     <t>juliana.diniz@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12651650200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12673826000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12673844800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>isabel.cit@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-3595810996 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>clarissa.cavalli@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12671777800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>jaqueline.rissi@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-66347157004 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>karla.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12313350500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>bruna.silva1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-5156008810 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12674273700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-60479400563 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>erica.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12667385700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>rafael.junior@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12650928000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>marcelo.costa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-2946678148 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>pedro.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-3529647900 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>thais.pessoto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-2875468960 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>vitor.mattos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12675110900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>maria.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-619926821 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>rodrigo.amorim@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-68979010087 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>ana.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12431528600000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>graziella.pignataro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12675219400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>renata.scarpino@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-1004580100000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-44774967000104 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>carla.valnisio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12660839300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>flavia.marcelino@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12292550500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>silvia.taschetti@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12441267800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>matheus.gomes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-40528733869 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rosangela.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12555001100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12555012800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>valeria.palhares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-18090667000198 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>fabio.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12375470000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>sonia.nascimento@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12314893000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>daniela.leal@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12579064800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>cleyciane.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12673008000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12616134400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>william.rosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12676325800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>douglas.morais@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12674250600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>eduardo.marques@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12676844700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12669430400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>douglas.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12474576300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>deise.santos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12671075400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>marcus.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12674578800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>fernanda.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12673776000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>jacqueline.mendes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12668614400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>joao.neto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12677293200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>rosemeire.faria@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12621770500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>diego.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12661508400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>juliana.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12581481300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>marlene.lopes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12654960000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>janaina.cazelato@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12675609700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>karina.vieira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12448112600000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>patricia.domingos1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12656327900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
   </si>
 </sst>
 </file>
@@ -595,7 +589,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="55.5703125" style="2" customWidth="1"/>
@@ -619,10 +613,10 @@
     </row>
     <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
@@ -630,10 +624,10 @@
     </row>
     <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>3</v>
@@ -641,10 +635,10 @@
     </row>
     <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>3</v>
@@ -652,10 +646,10 @@
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>3</v>
@@ -666,7 +660,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>3</v>
@@ -674,10 +668,10 @@
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>3</v>
@@ -685,10 +679,10 @@
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>3</v>
@@ -696,10 +690,10 @@
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>3</v>
@@ -707,10 +701,10 @@
     </row>
     <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>3</v>
@@ -718,10 +712,10 @@
     </row>
     <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>3</v>
@@ -729,10 +723,10 @@
     </row>
     <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>3</v>
@@ -740,10 +734,10 @@
     </row>
     <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>3</v>
@@ -751,10 +745,10 @@
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>3</v>
@@ -762,10 +756,10 @@
     </row>
     <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>3</v>
@@ -773,10 +767,10 @@
     </row>
     <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>3</v>
@@ -784,10 +778,10 @@
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>3</v>
@@ -795,10 +789,10 @@
     </row>
     <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>3</v>
@@ -806,10 +800,10 @@
     </row>
     <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>3</v>
@@ -817,10 +811,10 @@
     </row>
     <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>3</v>
@@ -828,10 +822,10 @@
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>3</v>
@@ -839,10 +833,10 @@
     </row>
     <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>3</v>
@@ -850,10 +844,10 @@
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>3</v>
@@ -861,10 +855,10 @@
     </row>
     <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>3</v>
@@ -872,10 +866,10 @@
     </row>
     <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>3</v>
@@ -883,10 +877,10 @@
     </row>
     <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>3</v>
@@ -894,10 +888,10 @@
     </row>
     <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>3</v>
@@ -905,10 +899,10 @@
     </row>
     <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>3</v>
@@ -916,45 +910,12 @@
     </row>
     <row r="29" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C32" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD88E379-8FF0-46C5-ABD4-BF04A70879CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39CE09C6-889D-43B2-807F-397F1EAE5076}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="71">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -51,121 +51,205 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>matheus.gomes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>karina.vieira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12304843200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>daniel.lourenco@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12677583500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>ana.arruda@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-30301106991 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>luciana.belisario@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12677467500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>talita.meneses@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12293582200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>claudia.assuncao@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12395324600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12673899500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
     <t>jonatas.lauretto@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12670574000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>carla.nascimento@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12670150200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>rafaela.jeronimo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12678942200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>filipe.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12678475000000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>daisy.marangoni@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12660815300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>rogerio.souza@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12479165900000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12612602800000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12302937300000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12340783000000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12448063500000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>ana.cunha1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12491632700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>stefani.saracho@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12527280400000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
     <t>carlos.neves@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12125148900000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12184669500000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>natalia.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12235808300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>tadeu.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12554752400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>eliana.pedroso@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12567738200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12677583500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12681226400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>rosangela.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12677417900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>irene.rosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-29442575953 Nota 531 - Alteração ou correção dados cadastrais</t>
+  </si>
+  <si>
+    <t>luiz.inocente@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-49381148015 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rafael.petrin@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12470940600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>juliano.guimaraes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12682325700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>danillo.boem@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12672392700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>flavio.cesar@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12676089200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>alessandra.araujo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-31325920720 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>jose.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12675385500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>sonia.bortoleto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12353071300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>mary.leme@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12660706000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>elisangela.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12680717600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>douglas.morais@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-8094030640 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>viviane.corbari@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12497881900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>douglas.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12588223000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>luciana.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12311161200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>karen.moraes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12677052500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>danilo.ruas@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12499310100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>gustavo.arruda@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12677015400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>alciana.carlucci@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12672635600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12678450700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>thais.pessoto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12580718700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rodrigo.amorim@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12557408500000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>viviane.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12655942300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>ana.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12673827500000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>claudenice.barbosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12677585800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>marlene.lopes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12651894200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>janaina.cazelato@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12672173100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>renata.scarpino@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11448008600000 Nota 418 - Vida - Faturamento - Proposta/DPS</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11201458900000 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -541,7 +625,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C35"/>
   <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="55.5703125" style="2" customWidth="1"/>
@@ -565,10 +649,10 @@
     </row>
     <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
@@ -576,10 +660,10 @@
     </row>
     <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>3</v>
@@ -587,10 +671,10 @@
     </row>
     <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>3</v>
@@ -598,7 +682,7 @@
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>12</v>
@@ -631,10 +715,10 @@
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>3</v>
@@ -642,10 +726,10 @@
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>3</v>
@@ -653,10 +737,10 @@
     </row>
     <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>3</v>
@@ -664,10 +748,10 @@
     </row>
     <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>3</v>
@@ -675,10 +759,10 @@
     </row>
     <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>3</v>
@@ -686,10 +770,10 @@
     </row>
     <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>3</v>
@@ -697,10 +781,10 @@
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>3</v>
@@ -708,10 +792,10 @@
     </row>
     <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>3</v>
@@ -719,10 +803,10 @@
     </row>
     <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>3</v>
@@ -730,10 +814,10 @@
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>3</v>
@@ -741,10 +825,10 @@
     </row>
     <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>3</v>
@@ -752,10 +836,10 @@
     </row>
     <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>3</v>
@@ -763,10 +847,10 @@
     </row>
     <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>3</v>
@@ -774,10 +858,10 @@
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>3</v>
@@ -785,10 +869,10 @@
     </row>
     <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>3</v>
@@ -796,12 +880,144 @@
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B2C4F5D-2CF8-43EF-80B8-A20E2D8DBC9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F5DE0BA-AAF3-4E4C-A096-4EE886753941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="54">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -54,142 +54,151 @@
     <t>marli.rocha@allianz.com.br</t>
   </si>
   <si>
-    <t>daniel.lourenco@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12648848200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>flavio.cesar@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12726693800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12738694700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>daniela.gui@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12605316100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>monica.betoni@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12490804600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
     <t>luciana.belisario@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12743536700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>talita.meneses@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-25978497834 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>alan.peter@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12616781800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>denys.antipou@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12743013400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>betina.carrasco@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12744913800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>gustavo.correa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12743292200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>lais.xavier@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12687854400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>cassia.silveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12619479600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12496064000000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12506037000000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12737851200000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>lucidene.santana@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12740456000000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>erica.santos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12729060600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12731640700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>janaina.cazelato@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12740217900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>naiara.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12679415800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>jose.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12683291100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>ana.morais@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-134958608 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
     <t>carlos.neves@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12005954600000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12140214000000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12196512800000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12216044000000 Nota 242 - Retorno Cobrança</t>
+    <t>patricia.sylos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12745897400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>luiz.inocente@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12746784900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12746785800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>otto.lopes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12428858300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>leandro.araujo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12549256500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>thais.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12414019300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12536727100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>vanessa.campos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12693744600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>alessiane.carvalho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12516103900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>caroline.wojciechowski@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12381835600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12743742300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>eliane.fernandes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-35880117812 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>luiz.santos1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-2884951000104 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>eduardo.santos1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12140086600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>patricia.carvalho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12369114800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>fernanda.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12558781000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>gabriela.logrado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12742246700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>pedro.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12357981100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>kisay.souza@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12518663700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>fabiola.caixeta@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12742222900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>ana.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12371969300000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>cristiane.lozano@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12434007600000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12738755100000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>graziella.pignataro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12741787800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-25065872848 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11989726600000 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -565,7 +574,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="55.5703125" style="2" customWidth="1"/>
@@ -589,10 +598,10 @@
     </row>
     <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>3</v>
@@ -600,10 +609,10 @@
     </row>
     <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>3</v>
@@ -611,10 +620,10 @@
     </row>
     <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>3</v>
@@ -622,10 +631,10 @@
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>3</v>
@@ -633,10 +642,10 @@
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>3</v>
@@ -644,10 +653,10 @@
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>3</v>
@@ -655,10 +664,10 @@
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>3</v>
@@ -666,10 +675,10 @@
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>3</v>
@@ -677,10 +686,10 @@
     </row>
     <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>3</v>
@@ -688,10 +697,10 @@
     </row>
     <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>3</v>
@@ -699,10 +708,10 @@
     </row>
     <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>3</v>
@@ -710,10 +719,10 @@
     </row>
     <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>3</v>
@@ -721,10 +730,10 @@
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>3</v>
@@ -732,10 +741,10 @@
     </row>
     <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>3</v>
@@ -743,10 +752,10 @@
     </row>
     <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C16" s="3" t="s">
         <v>3</v>
@@ -754,10 +763,10 @@
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C17" s="3" t="s">
         <v>3</v>
@@ -765,10 +774,10 @@
     </row>
     <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>3</v>
@@ -776,10 +785,10 @@
     </row>
     <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>3</v>
@@ -787,10 +796,10 @@
     </row>
     <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>3</v>
@@ -798,10 +807,10 @@
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>3</v>
@@ -809,10 +818,10 @@
     </row>
     <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>3</v>
@@ -820,10 +829,10 @@
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>3</v>
@@ -831,10 +840,10 @@
     </row>
     <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>3</v>
@@ -842,10 +851,10 @@
     </row>
     <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>3</v>
@@ -853,10 +862,10 @@
     </row>
     <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>3</v>
@@ -864,23 +873,12 @@
     </row>
     <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>46</v>
+        <v>7</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C28" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D32E659-FF47-4AB4-B177-E7F3AF812214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BD16095-4DCE-49FC-9906-B5DE4978B2D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="140">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -48,244 +48,7 @@
     <t>Email</t>
   </si>
   <si>
-    <t>irfelix@terra.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 125708351 - CARLA ADRIANA DE SOUZA</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 8 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>andradecorretoraseguros@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 125874214 - VANDERLY ANTONIO DA SILVA</t>
-  </si>
-  <si>
-    <t>seguros@dorconsultoria.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 125883221 - EDMILSON ALVES EVANGELISTA</t>
-  </si>
-  <si>
-    <t>norteemissao@nortecorretora.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 125887109 - SELMA MARIA DE SOUZA BARBOSA</t>
-  </si>
-  <si>
-    <t>veragomes@veracorr.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 125888994 - MERION SIQUEIRA FREITAS</t>
-  </si>
-  <si>
-    <t>contato@jpnseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126117274 - CARLOS JOSE CORDEIRO DA SILVA</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>jbonfim@jbonfimcorretora.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126184807 - RENATO SILVA</t>
-  </si>
-  <si>
-    <t>escritorioseguros@terra.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126210912 - CLAUDIO NIHUES NETO</t>
-  </si>
-  <si>
-    <t>cadastro@alexandrerenault.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126213065 - ISABELA DA CUNHA MELO</t>
-  </si>
-  <si>
-    <t>supremasegurosmuriae@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126227585 - MEKIANNE APARECIDA DE MATTOS</t>
-  </si>
-  <si>
-    <t>chsseguros@outlook.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126233995 - VANIA PAULA BERTAQUE</t>
-  </si>
-  <si>
     <t>renovacaoseguros@honda.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126245330 - RAFAEL SILVA DE JESUS</t>
-  </si>
-  <si>
-    <t>valdenicio@ponteslifeseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126247031 - LUIZ ALBERTO SAFADI</t>
-  </si>
-  <si>
-    <t>freitasbritocorretora@hotmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126347584 - SOSTENES COSTA OLIVEIRA</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 6 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>seguros@grupovia1.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126455225 - WILKA GABRIELA MANSUR DOS SANTOS SILVA</t>
-  </si>
-  <si>
-    <t>investseg.tm@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126516629 - VANESSA BERTAIOLLI</t>
-  </si>
-  <si>
-    <t>sdinamica@uol.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126516831 - JARBAS MARCAL DE QUEIROZ</t>
-  </si>
-  <si>
-    <t>suporte.vvd@vwfs.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126526090 - MARINETE DE MELO GOES</t>
-  </si>
-  <si>
-    <t>backofficecorretora@segurostoyota.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126534206 - ETIENE ALVES DA ROCHA GUSMAO</t>
-  </si>
-  <si>
-    <t>contatoseguros.adm@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126536280 - TREVISAN COMERCIO DE ALIMENTOS LTDA ME</t>
-  </si>
-  <si>
-    <t>milanoseguros@hotmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126545315 - SIMONE DAINEZI</t>
-  </si>
-  <si>
-    <t>andre.oliveira@braseg.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126545989 - NATALICIA BRITO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126559112 - RAISSA MODESTO DA COSTA</t>
-  </si>
-  <si>
-    <t>seguros@sartoricorretora.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126569336 - JENNITON BALDRAIA DA ROCHA</t>
-  </si>
-  <si>
-    <t>atendimento@miraseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126579867 - LUCIANE MARIA RODRIGUES SEIXAS</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126588520 - FABIO PINHEIRO DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>suzi@v12corretora.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126846685 - MARILIA PEREIRA DE AZEVEDO LIMA</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>naianara@lizseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126855214 - FLAVIA DIAS PRAETZEL</t>
-  </si>
-  <si>
-    <t>aferbrasil@aferbrasil.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126864149 - CAMILA ALBUQUERQUE LINHARES ROMEIRO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126866523 - CRISTINA BRONZATO BUENO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126883392 - KELLY ANTUNES</t>
-  </si>
-  <si>
-    <t>supervisor1.corretora@grupoleauto.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127113578 - PALOMA MENDES VIEIRA</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127179429 - SEMIRAMIS OLIVEIRA ROSADO DINIZ</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127212741 - JOSE DA SILVA MOTTA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127213069 - JOSE CARLOS DE MOURA</t>
-  </si>
-  <si>
-    <t>landim@landimcorretora.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127359207 - SILVIO FERREIRA GOMES JUNIOR</t>
   </si>
   <si>
     <t>Prezado(a), 
@@ -297,36 +60,6 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>faleconosco@mapma.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127386311 - GUAJARINA GUALBERTO DA SILVA</t>
-  </si>
-  <si>
-    <t>anderson@a2l2.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127459858 - FERNANDA DINIZ VASCONCELOS</t>
-  </si>
-  <si>
-    <t>adm.cor@bataglia.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127514352 - SIRLENE BORINO DOS SANTOS</t>
-  </si>
-  <si>
-    <t>irineujr@tarrafseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127519478 - MARIA APARECIDA DE ALMEIDA BARBIERI</t>
-  </si>
-  <si>
-    <t>contato@unifisaseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127699801 - GIANNY RUTH ROJAS MORALES</t>
-  </si>
-  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 2 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -339,13 +72,403 @@
     <t>allianz@redelojacorr.com.br</t>
   </si>
   <si>
-    <t>Captura de parcela rejeitada - Apólice 127842365 - VALMIR ALVES DOS SANTOS</t>
-  </si>
-  <si>
-    <t>adrianofreitas@outlook.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127857349 - MARIA DE FATIMA RIBEIRO VIEIRA</t>
+    <t>patricia.sylos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12799488800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>edirilsa.bastos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12811968500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>otto.lopes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12657891300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>claudia.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-2605763951 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>tatiany.macedo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12763782800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>saulo.santiago@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12761180600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>marco.vita@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12688972500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>aline.madeira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12812626700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>jonatas.lauretto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12824610100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>rafaela.jeronimo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12814182400022 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>gustavo.correa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12505455600008 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>thays.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-30467576890 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-96480963253 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>fabiola.caixeta@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12814071400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>viviane.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12822809400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>lucidene.santana@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12427045000000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12438313000000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>rosemeire.faria@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12812304800000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>ana.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12814071400000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>rosana.pessoa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12800647500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>wanda.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-2000320400000 Nota 742 - Prêmio</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11460231000000 Nota 742 - Prêmio</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11582435500000 Nota 742 - Prêmio</t>
+  </si>
+  <si>
+    <t>karina.vieira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11858302500000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11874934800000 Nota 742 - Prêmio</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12057461100000 Nota 742 - Prêmio</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12158274300000 Nota 742 - Prêmio</t>
+  </si>
+  <si>
+    <t>maria.ferro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12810893500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>carlos.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11442837500000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>vitorhsb@webproxy.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125945810 - CARLOS ALBERTO CORRAL JUNIOR</t>
+  </si>
+  <si>
+    <t>pivatto@pivatto.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126737419 - LIDIA IUZVIAK</t>
+  </si>
+  <si>
+    <t>emissao@maxiriscos.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127492356 - MARCOS COSSUL</t>
+  </si>
+  <si>
+    <t>wilson.gabriel@ebkseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127509587 - FABRICIO AUGUSTO MACIEL COSTA</t>
+  </si>
+  <si>
+    <t>tecnica5@ffseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127509631 - MARCO AURELIO PARAZI DOMINGOS</t>
+  </si>
+  <si>
+    <t>luizcripa@cripaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127509703 - KEILA APARECIDA CAITANO DE LIMA</t>
+  </si>
+  <si>
+    <t>cgamatriz@cgaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127509746 - MONICA ALMEIDA DE BARROS RODRIGUES</t>
+  </si>
+  <si>
+    <t>alex@elementu.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127509853 - GABRIEL TRABUCO COUTINHO</t>
+  </si>
+  <si>
+    <t>comercial.seguros@grupoprovence.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127509869 - VILMA MATRIAS FERNANDES</t>
+  </si>
+  <si>
+    <t>corretora@martinsepimenta.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127510139 - JOSE LUIZ XAVIER</t>
+  </si>
+  <si>
+    <t>kuia@uol.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127512324 - IVANILDO SILVA FERNANDES</t>
+  </si>
+  <si>
+    <t>eloisa.machado@grupoiesa.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127512570 - ROGERIO RIVA</t>
+  </si>
+  <si>
+    <t>bruna@godoicotrim.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127512709 - THIAGO TINTORI MAIA</t>
+  </si>
+  <si>
+    <t>beto@faitarone.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127513868 - VIVIANE LEIKO ISHIDA DE MATTOS</t>
+  </si>
+  <si>
+    <t>contato@3iseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127521725 - MARCIA DA PENHA MARRIEL RAMOS</t>
+  </si>
+  <si>
+    <t>christian@suaseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127521867 - ALINE DE PAULA LEAL</t>
+  </si>
+  <si>
+    <t>seguros@mmautoseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127521933 - PACFER COMERCIO DE FERRO E ACO LTDA EPP</t>
+  </si>
+  <si>
+    <t>alessandro@ferreiraromao.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127529161 - CAIRO DE JESUS SANTOS</t>
+  </si>
+  <si>
+    <t>starnews@starnewsseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127529175 - APARECIDO ZANATA</t>
+  </si>
+  <si>
+    <t>vanderson.matos@cocoonseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127529192 - LORENA FERREIRA BELGA</t>
+  </si>
+  <si>
+    <t>administrativo@gjseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127529210 - EDIMILSON ARANTES LOPES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127529215 - EDUARDO ALVES FERNANDES</t>
+  </si>
+  <si>
+    <t>administrativo@corretoradesegurosfa.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127529257 - DANIEL LUIZ OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127529505 - LEONARDO ALMEIDA ARAUJO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127529543 - MAICON ALVES SOUSA SANTANA</t>
+  </si>
+  <si>
+    <t>redebankseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127816924 - NUBIA RIBEIRO BARBOSA</t>
+  </si>
+  <si>
+    <t>zaparolli@zaparollicorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127820121 - GIRLANE HENN</t>
+  </si>
+  <si>
+    <t>rsseguros@terra.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127826120 - INDUSTRIA DE ALIMENTOS NEGRA CHICA LTDA ME</t>
+  </si>
+  <si>
+    <t>igor.back@lojacorr.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127829716 - ALUIZIO NOVACK CIA LTDA ME</t>
+  </si>
+  <si>
+    <t>bwcorretora@terra.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127831720 - EVELYN ALVES PASSOS</t>
+  </si>
+  <si>
+    <t>legitimaseguros@engeplus.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127833284 - MARCOS VALENTIM MARTINELLO</t>
+  </si>
+  <si>
+    <t>marli@pereirabuenoseguro.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127834311 - FRANCISCO CARLOS DAGA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127849670 - PATRICIA BRINGHENTI BORDIGNON RODRIGUES</t>
+  </si>
+  <si>
+    <t>contato@ricknewseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127849870 - MARCO ANTONIO DAVID DE MELO</t>
+  </si>
+  <si>
+    <t>atendimento@tenedini.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127849873 - SANDRA REGINA STRADIOTTI BIANCHIN</t>
+  </si>
+  <si>
+    <t>completa@completacorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127849883 - ANDRE LUIZ BRUNHARA</t>
+  </si>
+  <si>
+    <t>pendencia@seguralta.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127849903 - MAGDA DE OLIVEIRA CARDOSO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127849947 - HELDER ALVES DE LIMA</t>
+  </si>
+  <si>
+    <t>aryelseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127849995 - CAMILA FERREIRA</t>
+  </si>
+  <si>
+    <t>robsonseguros@uol.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127850042 - ANA CAROLINA PORTO LEMES</t>
+  </si>
+  <si>
+    <t>laysa.camargos@grupolider.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127850214 - ANTONIO FLOSINO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>marcelo@despachantefragoso.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127850254 - MELISSA LIMA OLIVEIRA REGO</t>
+  </si>
+  <si>
+    <t>mallmannseguros@mallmannseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127850309 - MARISETE MATHES</t>
+  </si>
+  <si>
+    <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
 </sst>
 </file>
@@ -721,7 +844,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:C44"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="55.5703125" style="2" customWidth="1"/>
@@ -745,475 +868,794 @@
     </row>
     <row r="2" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="B3" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="C3" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="B4" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C4" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="B5" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C5" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="B6" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="C6" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="C7" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>19</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B8" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="C8" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B9" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="C9" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B10" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="C10" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B11" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="C11" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="2" t="s">
+      <c r="B12" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="C12" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B13" t="s">
         <v>30</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="C13" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" t="s">
         <v>31</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="C14" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="B15" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="C15" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>34</v>
       </c>
-      <c r="B16" s="2" t="s">
+      <c r="B16" t="s">
         <v>35</v>
       </c>
-      <c r="C16" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="C16" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>36</v>
       </c>
-      <c r="B17" s="2" t="s">
+      <c r="B17" t="s">
         <v>37</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="C17" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="C18" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="B19" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="2" t="s">
+      <c r="C19" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
         <v>41</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="B20" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="C20" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="B21" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="2" t="s">
+      <c r="C21" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="B22" t="s">
         <v>46</v>
       </c>
-      <c r="B22" s="2" t="s">
+      <c r="C22" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" t="s">
         <v>47</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="C23" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" t="s">
         <v>48</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="C24" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>49</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="2" t="s">
+      <c r="B25" t="s">
         <v>50</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="C25" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>45</v>
+      </c>
+      <c r="B26" t="s">
         <v>51</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="C26" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" t="s">
         <v>52</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+      <c r="C27" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B28" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="2" t="s">
+      <c r="C28" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B27" s="2" t="s">
+      <c r="B29" t="s">
         <v>55</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="C29" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="2" t="s">
+      <c r="B30" t="s">
         <v>57</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C30" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+      <c r="B31" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="C31" s="2" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>27</v>
+        <v>60</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>58</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>67</v>
+        <v>4</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="C37" s="2" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>84</v>
+        <v>4</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>84</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="B44" s="2" t="s">
+      <c r="C45" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>84</v>
+      <c r="B46" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1228,31 +1670,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAzNTMxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MzAvMTIvMjAyMCAxMTo0NTo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAzMC8xMi8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41A8E509-6991-4B84-B1B5-13851E156C6A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DBFCB3-53E5-4527-B13D-DC7A854D4B55}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41A8E509-6991-4B84-B1B5-13851E156C6A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\Brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D94D300-576F-4E53-A236-ED356B3FFF7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61A5E421-58CB-4C3A-8E8B-1240CB25FEF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="27015" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -48,217 +48,127 @@
     <t>Email</t>
   </si>
   <si>
-    <t>ana.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>fernando.martins1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12815975000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>silvia.taschetti@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12702572800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12818460800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>rosangela.silva1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12813890100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12820138200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>claudia.magalhaes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-2942683082 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>sandro.francisquini@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12824483300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
     <t>flavio.cesar@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12793746500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>adriana.silveira1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12813457400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>gleison.ferreira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12819165600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>lucas.almeida@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12823088300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>juliana.diniz@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12819366900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>claudia.gomes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-32626657620 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>priscila.rubio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12492873600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>rodrigo.kuguyama@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12825356400000 Nota 741 - Inspeção veicular-exclusivo Operações</t>
-  </si>
-  <si>
-    <t>douglas.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12819941400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>alan.peter@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-18801420072 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>reginaldo.pinto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12817545800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>fernando.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12813991100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>karen.moraes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12814750200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>marcus.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12780771900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>alciana.carlucci@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12813904100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>raullison.castro@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12825929400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>michelle.araujo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12477931600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>ryan.monteiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12823726200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>daisy.marangoni@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-28455886900 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12723893400000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12811933600000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>aline.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12738516100000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>graziella.pignataro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12756211200000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12766220200000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>claudinete.machado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12774586800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12774691400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>valeria.cotrone@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12793342200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12813401000000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>janaina.mazini@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12811203600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>bruna.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12749849500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>ana.brito@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12652308000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>priscila.sousa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12575823100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>valeria.palhares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12506006800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>thais.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12465572200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12562368800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>vanessa.campos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12640923200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>mary.leme@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12825259100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>leandro.machado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12826943300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>noadia.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12466713700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>everton.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12470929400000 Nota 741 - Inspeção veicular-exclusivo Operações</t>
+  </si>
+  <si>
+    <t>rosana.teixeira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12544486000000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12821647900000 Nota 741 - Inspeção veicular-exclusivo Operações</t>
+  </si>
+  <si>
+    <t>adautina.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12800407400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>wagner.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12793042900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rafael.leite@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12819959300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>viviane.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12819111600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>marcio.kaminski@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-91625211953 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>erica.santos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12813191600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>paola.emidio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-15764060168 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>jaqueline.nicacio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-87323893100 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>sandra.mikari@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12650341900000 Nota 167 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -658,421 +568,297 @@
     </row>
     <row r="2" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" t="s">
-        <v>44</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>3</v>
-      </c>
-      <c r="B28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>3</v>
-      </c>
-      <c r="B29" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>57</v>
-      </c>
-      <c r="B30" t="s">
-        <v>58</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>59</v>
-      </c>
-      <c r="B31" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>4</v>
-      </c>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23"/>
+      <c r="B23"/>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25"/>
+      <c r="B25"/>
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26"/>
+      <c r="B26"/>
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27"/>
+      <c r="B27"/>
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28"/>
+      <c r="B28"/>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29"/>
+      <c r="B29"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30"/>
+      <c r="B30"/>
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31"/>
+      <c r="B31"/>
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C32" s="3"/>
+    </row>
+    <row r="33" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C34" s="3"/>
+    </row>
+    <row r="35" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C35" s="3"/>
+    </row>
+    <row r="36" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C36" s="3"/>
+    </row>
+    <row r="37" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C37" s="3"/>
+    </row>
+    <row r="38" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C38" s="3"/>
+    </row>
+    <row r="39" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C39" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Dados e Relatórios\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94996036-A6E6-4956-8885-6D231D39CD55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB28EBBF-9A38-4DBB-8F8A-5B2D30054D86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28800" windowHeight="14805" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="55">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -51,376 +51,157 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>noadia.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>karla.cunha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>rosangela.silva1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>juliana.diniz@allianz.com.br</t>
-  </si>
-  <si>
-    <t>priscila.rubio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>thays.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>valeria.cotrone@allianz.com.br</t>
-  </si>
-  <si>
-    <t>karina.vieira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12771871100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12867472800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12606858500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>silvia.taschetti@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12852175300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>eliana.pedroso@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12865010500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>danielle.nascimento@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12433693900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>adriano.guerra@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12783069900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>cleyciane.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11123761949 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>gisele.mazzucco@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12612623200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12862574600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>william.rosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12762280800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>claudia.gomes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12464330200000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>leandro.machado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12825678800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>angela.carmo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12839006700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-10830864000194 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-16418101000117 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>bruna.silva1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12647440700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-1588557103 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>fernando.sousa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12875692300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
     <t>rogerio.souza@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12740878800000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
     <t>laerte.silva@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12735145300000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12837180100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>juliana.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12747057500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12763439200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12858539000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12524909700000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>rodrigo.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12309741800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>fernanda.santos2@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12821213000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>ana.morais@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-5158191743 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>rodrigo.tavares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-88818221700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>carlos.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12089129000000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12233145700000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>lucidene.santana@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12838699900000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>ana.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12869467100000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>backofficeseguros@vwfs.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 125948922 - TRUBANA PAULA EDLACY DA SILVA PEIXOTO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 125948912 - TRUBANA PAULA EDLACY DA SILVA PEIXOTO</t>
-  </si>
-  <si>
-    <t>suporte.vvd@vwfs.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 125989956 - ODILON RIBEIRO DE ALBUQUERQUE FILHO</t>
-  </si>
-  <si>
-    <t>luciano@pacieloseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 125983146 - LUCIANO MACIEL PACIELO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>investseg.tm@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 125982746 - SILVIA ULLMANN JAEGER</t>
-  </si>
-  <si>
-    <t>segurosconclusiva@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126313453 - AUREA ANTONIA COSTA BRILHANTE</t>
-  </si>
-  <si>
-    <t>dalmo@dalmoseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126627209 - GISLEINE VIEIRA DE OLIVEIRA BOSQUIM</t>
-  </si>
-  <si>
-    <t>chsseguros@outlook.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126621551 - EDUARDO JUNCA</t>
-  </si>
-  <si>
-    <t>tecnico1@centrosulseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126644278 - PAULA SUELEN GUEDES DA SILVA</t>
-  </si>
-  <si>
-    <t>seguros@atuanaseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126627343 - BRUNO BRAS DIAS TORRES ESTRELA</t>
-  </si>
-  <si>
-    <t>contato@onseguroscorretora.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126965146 - ROSELI CECILIA TARANTO PUPO</t>
-  </si>
-  <si>
-    <t>anderson@martarollo.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126944438 - OSMAR VIEIRA LOPES</t>
-  </si>
-  <si>
-    <t>reginaldochaves.corretora@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126930559 - YANNE ARAGAO FELIX</t>
-  </si>
-  <si>
-    <t>contato@baccanseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127577449 - BRUNO CARRASCOSA DEZOTTI</t>
-  </si>
-  <si>
-    <t>juliana@aliancabrasileira.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127589474 - LUCAS PIMENTEL DOS SANTOS SOUZA</t>
-  </si>
-  <si>
-    <t>comercial1@aquicorretora.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127598125 - ESTRUSERV SERVICOS DE ESTRUTURA LTDA ME</t>
-  </si>
-  <si>
-    <t>backofficecorretora@segurostoyota.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127824069 - RAFAELA RIBEIRO RUIVO</t>
-  </si>
-  <si>
-    <t>emissao@idealseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127865313 - NADIR UEMA</t>
-  </si>
-  <si>
-    <t>jozeaine.novais@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128267381 - PAULA APARECIDA DE OLIVEIRA BRITO</t>
-  </si>
-  <si>
-    <t>contato@maiorseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128288605 - ANGELA REGINA DE LIMA CANAZZA CORREA</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 9 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 8 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 6 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 3 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 2 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
+    <t>maria.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12623970700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>renata.magalhaes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12877102400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>marilia.martins@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12479035600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12712753400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>lucineide.medeiros@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12866527300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>rafael.petrin@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12864944100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>claudia.magalhaes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12659471600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>otto.lopes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12866933200000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>fernando.duque@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12876482900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>ana.arruda@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12862049200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>lucas.almeida@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12879376400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>mayara.sampaio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12788650400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>saulo.santiago@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12856003500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>flavia.costa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12877872800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>nathalie.carmo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12846432800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>rafael.junior@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12673483300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>fernanda.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12858336300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>geiza.vinand@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12868695300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>pedro.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12444345500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rafael.leite@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12867795700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>izys.barreto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12720438700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12607845900000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>cristiane.lozano@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12871981000000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12818251800000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>rosana.pessoa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12853245900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>janaina.cazelato@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12875966400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
   </si>
 </sst>
 </file>
@@ -820,10 +601,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -831,10 +612,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -842,10 +623,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -853,10 +634,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -864,10 +645,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -875,10 +656,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -886,10 +667,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -897,10 +678,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -908,10 +689,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -919,10 +700,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -930,10 +711,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -941,10 +722,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -952,10 +733,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -963,10 +744,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -974,10 +755,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -985,10 +766,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -996,10 +777,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -1007,10 +788,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -1018,10 +799,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -1029,10 +810,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -1040,10 +821,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -1051,10 +832,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -1062,10 +843,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>5</v>
+        <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
@@ -1073,10 +854,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -1084,10 +865,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B26" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
@@ -1095,356 +876,160 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="B27" t="s">
-        <v>12</v>
+        <v>54</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>48</v>
-      </c>
-      <c r="B28" t="s">
-        <v>51</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A28"/>
+      <c r="B28"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>11</v>
-      </c>
-      <c r="B29" t="s">
-        <v>52</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A29"/>
+      <c r="B29"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>53</v>
-      </c>
-      <c r="B30" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A30"/>
+      <c r="B30"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A31"/>
+      <c r="B31"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>57</v>
-      </c>
-      <c r="B32" t="s">
-        <v>58</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>59</v>
-      </c>
-      <c r="B33" t="s">
-        <v>60</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>61</v>
-      </c>
-      <c r="B34" t="s">
-        <v>62</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>61</v>
-      </c>
-      <c r="B35" t="s">
-        <v>63</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>68</v>
-      </c>
-      <c r="B36" t="s">
-        <v>69</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>68</v>
-      </c>
-      <c r="B37" t="s">
-        <v>70</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>71</v>
-      </c>
-      <c r="B38" t="s">
-        <v>72</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>73</v>
-      </c>
-      <c r="B39" t="s">
-        <v>74</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>75</v>
-      </c>
-      <c r="B40" t="s">
-        <v>76</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>77</v>
-      </c>
-      <c r="B41" t="s">
-        <v>78</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>79</v>
-      </c>
-      <c r="B42" t="s">
-        <v>80</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>81</v>
-      </c>
-      <c r="B43" t="s">
-        <v>82</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>83</v>
-      </c>
-      <c r="B44" t="s">
-        <v>84</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>85</v>
-      </c>
-      <c r="B45" t="s">
-        <v>86</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>87</v>
-      </c>
-      <c r="B46" t="s">
-        <v>88</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>89</v>
-      </c>
-      <c r="B47" t="s">
-        <v>90</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>91</v>
-      </c>
-      <c r="B48" t="s">
-        <v>92</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>93</v>
-      </c>
-      <c r="B49" t="s">
-        <v>94</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>95</v>
-      </c>
-      <c r="B50" t="s">
-        <v>96</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>97</v>
-      </c>
-      <c r="B51" t="s">
-        <v>98</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>99</v>
-      </c>
-      <c r="B52" t="s">
-        <v>100</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>101</v>
-      </c>
-      <c r="B53" t="s">
-        <v>102</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>103</v>
-      </c>
-      <c r="B54" t="s">
-        <v>104</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>105</v>
-      </c>
-      <c r="B55" t="s">
-        <v>106</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32"/>
+      <c r="B32"/>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33"/>
+      <c r="B33"/>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34"/>
+      <c r="B34"/>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35"/>
+      <c r="B35"/>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36"/>
+      <c r="B36"/>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37"/>
+      <c r="B37"/>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38"/>
+      <c r="B38"/>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39"/>
+      <c r="B39"/>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40"/>
+      <c r="B40"/>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41"/>
+      <c r="B41"/>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42"/>
+      <c r="B42"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43"/>
+      <c r="B43"/>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44"/>
+      <c r="B44"/>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45"/>
+      <c r="B45"/>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46"/>
+      <c r="B46"/>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47"/>
+      <c r="B47"/>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48"/>
+      <c r="B48"/>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49"/>
+      <c r="B49"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50"/>
+      <c r="B50"/>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51"/>
+      <c r="B51"/>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52"/>
+      <c r="B52"/>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53"/>
+      <c r="B53"/>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54"/>
+      <c r="B54"/>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55"/>
+      <c r="B55"/>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56"/>
       <c r="B56"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57"/>
       <c r="B57"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58"/>
       <c r="B58"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59"/>
       <c r="B59"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60"/>
       <c r="B60"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61"/>
       <c r="B61"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62"/>
       <c r="B62"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63"/>
       <c r="B63"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64"/>
       <c r="B64"/>
     </row>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Dados e Relatórios\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB28EBBF-9A38-4DBB-8F8A-5B2D30054D86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A22DD1B1-EA34-40F8-96D6-56E05E8A1CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28800" windowHeight="14805" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="60">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -202,6 +202,21 @@
   </si>
   <si>
     <t>Retorno de GO referência-12875966400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>lucidene.santana@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12487549600000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>rosemeire.faria@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12857413400000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12861100700000 Nota 472 - Reentrada OK Produto</t>
   </si>
 </sst>
 </file>
@@ -832,10 +847,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -843,10 +858,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
@@ -854,10 +869,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>5</v>
+        <v>57</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -865,10 +880,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
@@ -876,26 +891,47 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>48</v>
+      </c>
+      <c r="B27" t="s">
+        <v>49</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" t="s">
+        <v>50</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>51</v>
+      </c>
+      <c r="B29" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>53</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B30" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28"/>
-      <c r="B28"/>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29"/>
-      <c r="B29"/>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30"/>
-      <c r="B30"/>
+      <c r="C30" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31"/>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Dados e Relatórios\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A22DD1B1-EA34-40F8-96D6-56E05E8A1CD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DD65959-5980-454B-BEAC-3B8B7393B32F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28800" windowHeight="14805" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28995" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envio Robô" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="199">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -51,172 +51,643 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>rogerio.souza@allianz.com.br</t>
-  </si>
-  <si>
-    <t>laerte.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>maria.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12623970700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>renata.magalhaes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12877102400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>marilia.martins@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12479035600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12712753400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>lucineide.medeiros@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12866527300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>rafael.petrin@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12864944100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>claudia.magalhaes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12659471600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>otto.lopes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12866933200000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>fernando.duque@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12876482900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>ana.arruda@allianz.com.br</t>
   </si>
   <si>
     <t>Retorno de GO referência-12862049200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
   </si>
   <si>
-    <t>lucas.almeida@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12879376400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>mayara.sampaio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12788650400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>saulo.santiago@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12856003500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
     <t>flavia.costa@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12877872800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>nathalie.carmo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12846432800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>rafael.junior@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12673483300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>fernanda.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12858336300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>geiza.vinand@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12868695300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>pedro.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12444345500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>rafael.leite@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12867795700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>izys.barreto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12720438700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12607845900000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>cristiane.lozano@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12871981000000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12818251800000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>rosana.pessoa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12853245900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>janaina.cazelato@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12875966400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>lucidene.santana@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12487549600000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
     <t>rosemeire.faria@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12857413400000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12861100700000 Nota 472 - Reentrada OK Produto</t>
+    <t>tadeu.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12881100000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>jessika.pazin@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-5595527854 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>samuel.martins@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12842286800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>cleyciane.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12881162200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>elisangela.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12879982500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>celso.filho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12857413400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>leandro.gonzaga@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12871102800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>vitor.mattos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12569998300000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>jheniffer.emiliano@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12849616000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>alexia.fernandes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12538223800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12783022000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>karen.moraes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12518360100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>raphael.callado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12869854500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>claudia.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12872138800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12471600300000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>ana.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12559072100000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12702330900000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12873319300000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12877965100000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>marli.rocha@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12878138700000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12879728900000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>aline.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12639491000000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12875859700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>karina.vieira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11372524300000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>carlos.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-10737729600000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11367737100000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11412163500000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>jethaseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125680058 - JORGE WASHINGTON SOUZA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 10 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>mabemseguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125981444 - ZILDA RODRIGUES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 9 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>asuzanocorretora@hotmail.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126049574 - ALINE MORELLI WIRTHMANN</t>
+  </si>
+  <si>
+    <t>contato@waseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126033194 - SARA DE TOLEDO RAINHA</t>
+  </si>
+  <si>
+    <t>luizalbertodionysio56@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126001156 - LUCIANO GONCALVES DA ROCHA</t>
+  </si>
+  <si>
+    <t>suporte.vvd@vwfs.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126350938 - GIULLBER VALENTIM DA SILVA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 8 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>faleconosco@mapma.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127326789 - SONIA REGINA BALMANT DOS SANTOS REZENDE</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>backofficecorretora@segurostoyota.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127338296 - LUCIANA FELIX GONCALVES PINTO</t>
+  </si>
+  <si>
+    <t>renovacaoseguros@honda.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127343374 - JOSEILDO DOMINGOS DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127883748 - MARCIA APARECIDA SILVA ERHARDT</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 3 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128381505 - ARTUR OLIVEIRA PIRES</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 2 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>leandro@cabreraseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125925280 - VIVIAN LACERDA DE MELO</t>
+  </si>
+  <si>
+    <t>contato@uxseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125973684 - CLARISSA KURY PINHEIRO</t>
+  </si>
+  <si>
+    <t>diretoria@lapisbellus.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126350664 - DOUGLAS SOLEDADE DA SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126674196 - ANTONIO CARLOS DE FONTES</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>sudeste@sudesteseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126704888 - TANISE RODRIGUES DA SILVA FONTES</t>
+  </si>
+  <si>
+    <t>seg.cac@terra.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126969832 - JEAN ONESIMO FERREIRA DA COSTA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 6 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126990070 - JAIRO IZIDIO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127316956 - VITORIA ALVES ROQUE DA SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127307913 - SOLANGE SOUZA ARAUJO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127325978 - CONCEICAO FERREIRA LIMA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128328841 - ALANIS ELOISA MOTA</t>
+  </si>
+  <si>
+    <t>gferreira@gferreiraseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125668133 - STAEL SOARES VIEIRA CAMPOS</t>
+  </si>
+  <si>
+    <t>colmeiacor@colmeiaseg.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125675807 - GUSTAVO ANDRE CORRADI</t>
+  </si>
+  <si>
+    <t>elittecorretora@elittecorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125670269 - DAISY VIEIRA DE ARAUJO</t>
+  </si>
+  <si>
+    <t>contato@luganocorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125960387 - EVERALDO MIRANDA</t>
+  </si>
+  <si>
+    <t>sibelesouzabaeta@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126013388 - ROSENIL OLIVEIRA MOTTA FAGUNDES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126314556 - ROBERTO JORGE FADEL</t>
+  </si>
+  <si>
+    <t>andre.oliveira@braseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126272780 - ANGELO MARIO DAS NEVES</t>
+  </si>
+  <si>
+    <t>andradecorretoraseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126288543 - VALDECI FERREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>duromarcorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126355625 - ERINALDA BATISTA ALVES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126701278 - CRISTIANE GIAVARINI MANSK</t>
+  </si>
+  <si>
+    <t>maisbrasilcor@maisbrasilcor.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126606925 - JULIETA MINORI NAKASHIMA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126985037 - CHRISELLEN DE PAULA CHAVES</t>
+  </si>
+  <si>
+    <t>amlbseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127225617 - MARGARIDA MARIA COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>seguros@trigocorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127295746 - COMBRAS 2000 COMERCIO E LOCACAO DE CONTEINERE</t>
+  </si>
+  <si>
+    <t>aprossegteresina@aprosseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127311919 - EDNA MARIA CORREIA LIMA E SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127284115 - MARIA AUGUSTA SIMONASSI ARAUJO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127530836 - BRUNA OLIVEIRA DA SILVA CARVALHO</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>contigo@contigoseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127618149 - VIRGINIA LUCIA FONSECA DA COSTA</t>
+  </si>
+  <si>
+    <t>globalpoliana@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127627304 - LUIS ANTONIO SOUTO</t>
+  </si>
+  <si>
+    <t>agenol.seguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127901020 - DANIEL DE OLIVEIRA SILVA</t>
+  </si>
+  <si>
+    <t>interweg@interweg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127895906 - ANDREA DINIZ DE MELO PAZ</t>
+  </si>
+  <si>
+    <t>aoseguros@aoseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127904056 - LUIZ ROBERTO RENZI</t>
+  </si>
+  <si>
+    <t>adm.corretora@revemar.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128094369 - LUCIVANIA BRANDAO MENDES</t>
+  </si>
+  <si>
+    <t>pendencia@seguralta.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128320407 - EDSON MENDES GONZAGA</t>
+  </si>
+  <si>
+    <t>emissao@willistowerswatson.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128184461 - AMAURY DOS SANTOS</t>
+  </si>
+  <si>
+    <t>delgadojfseguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125656379 - GIL DAYRELL SIQUEIRA</t>
+  </si>
+  <si>
+    <t>jozeaine.novais@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125664418 - DEISE LUCI CORREA BENTO</t>
+  </si>
+  <si>
+    <t>lchcorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125992576 - ANAIDE SILVA</t>
+  </si>
+  <si>
+    <t>adim@amcorretagem.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126024409 - LOURDES KARINE CUSTODIO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>confiarcorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126022143 - CLAUDIO GERALDO DA SILVA</t>
+  </si>
+  <si>
+    <t>simone@corasbeg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126016469 - FRANCISCO COELHO DA COSTA</t>
+  </si>
+  <si>
+    <t>luciana@cunhacastro.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126011684 - JEFFERSON SOUSA SILVA</t>
+  </si>
+  <si>
+    <t>jaguare@jaguareseguros.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126025037 - JULIANE MARISTELLA AGUIAR DA COSTA CARVALHO A</t>
+  </si>
+  <si>
+    <t>albacarvalho@aerocarcorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126240350 - VERA SELMA RODRIGUES CARVALHO</t>
+  </si>
+  <si>
+    <t>operacional@holdcorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126300406 - DENISE GUICHARD FREIRE</t>
+  </si>
+  <si>
+    <t>prisminas@prisminas.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126278175 - UBALDO JOSE DE CARVALHO</t>
+  </si>
+  <si>
+    <t>diamantinaseguros@diamantinaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126608530 - IZABELLA PRISCILA SANTOS SIDONIO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126681492 - MILENA DE LIMA BRAGANCA VIEIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126973352 - GISELE CANDIDO LANDI</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127265158 - ANA LUCIA BORLOT FALCAO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127282765 - VALDETE MIRANDA MARCILIO</t>
+  </si>
+  <si>
+    <t>fernandacunha@vivacorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127292767 - MARCONY GIORDANI MIRANDA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127593533 - WANESSA PARREIRA SERAFIM CARDOSO</t>
+  </si>
+  <si>
+    <t>seguecorretora.contato@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126018858 - SUPPORT TELEINFORMATICA LTDA ME</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126317599 - KELRILAYNNY FRANCISCA DE SANTANA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126247792 - CAMILA LEAL DE SOUSA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126652424 - ALDRICH HEUSER CAMARA GODEIRO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126649535 - MARIA RODRIGUES DO CARMO</t>
+  </si>
+  <si>
+    <t>eloimseguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126628892 - ANTONIO CARLOS DOS SANTOS SILVA</t>
+  </si>
+  <si>
+    <t>solange@mottacorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126623096 - ADRIANA DA SILVA FERREIRA</t>
+  </si>
+  <si>
+    <t>ikeda@ikedaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126968339 - MARIO MASSAO TAKAKI</t>
+  </si>
+  <si>
+    <t>marta@berdam.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126959902 - RITA DE CASSIA SANCHES MARQUES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126931877 - IVANILDO MEDEIROS NUNES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127276247 - MARICELMA CAVALCANTE DA SILVA</t>
+  </si>
+  <si>
+    <t>andrea@thompsonseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127244441 - ELEMENTAR CONSTRUCOES E REFORMAS LTDA ME</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127510836 - APAD APOIO EMPRESARIAL S S LTDA ME</t>
+  </si>
+  <si>
+    <t>seguradoras@dartanseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127563618 - RUI GOMARA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127607279 - FABRICIA DA SILVA ROMAO</t>
+  </si>
+  <si>
+    <t>pendencia@vilavelha.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128170050 - CELSO CUNHA GONCALVES</t>
   </si>
 </sst>
 </file>
@@ -616,10 +1087,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -627,10 +1098,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -638,10 +1109,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -649,10 +1120,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -660,10 +1131,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -671,10 +1142,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -682,10 +1153,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -693,10 +1164,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -704,10 +1175,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -715,10 +1186,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -726,10 +1197,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -737,10 +1208,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -748,10 +1219,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -759,10 +1230,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -770,10 +1241,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -781,7 +1252,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
@@ -803,10 +1274,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>37</v>
+      </c>
+      <c r="B19" t="s">
         <v>39</v>
-      </c>
-      <c r="B19" t="s">
-        <v>40</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -814,10 +1285,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -825,10 +1296,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="B21" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -836,10 +1307,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B22" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -847,10 +1318,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B23" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -858,10 +1329,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
@@ -869,10 +1340,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -880,10 +1351,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="B26" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
@@ -891,10 +1362,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B27" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -902,10 +1373,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>3</v>
@@ -913,10 +1384,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>3</v>
@@ -924,340 +1395,900 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31"/>
-      <c r="B31"/>
+      <c r="A31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" t="s">
+        <v>58</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32"/>
-      <c r="B32"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33"/>
-      <c r="B33"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34"/>
-      <c r="B34"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35"/>
-      <c r="B35"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36"/>
-      <c r="B36"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37"/>
-      <c r="B37"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38"/>
-      <c r="B38"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39"/>
-      <c r="B39"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40"/>
-      <c r="B40"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41"/>
-      <c r="B41"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42"/>
-      <c r="B42"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43"/>
-      <c r="B43"/>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44"/>
-      <c r="B44"/>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45"/>
-      <c r="B45"/>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46"/>
-      <c r="B46"/>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47"/>
-      <c r="B47"/>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48"/>
-      <c r="B48"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49"/>
-      <c r="B49"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50"/>
-      <c r="B50"/>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51"/>
-      <c r="B51"/>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52"/>
-      <c r="B52"/>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53"/>
-      <c r="B53"/>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54"/>
-      <c r="B54"/>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55"/>
-      <c r="B55"/>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56"/>
-      <c r="B56"/>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57"/>
-      <c r="B57"/>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58"/>
-      <c r="B58"/>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59"/>
-      <c r="B59"/>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60"/>
-      <c r="B60"/>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61"/>
-      <c r="B61"/>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62"/>
-      <c r="B62"/>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63"/>
-      <c r="B63"/>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64"/>
-      <c r="B64"/>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65"/>
-      <c r="B65"/>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66"/>
-      <c r="B66"/>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67"/>
-      <c r="B67"/>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68"/>
-      <c r="B68"/>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69"/>
-      <c r="B69"/>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70"/>
-      <c r="B70"/>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71"/>
-      <c r="B71"/>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72"/>
-      <c r="B72"/>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73"/>
-      <c r="B73"/>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74"/>
-      <c r="B74"/>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75"/>
-      <c r="B75"/>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76"/>
-      <c r="B76"/>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77"/>
-      <c r="B77"/>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78"/>
-      <c r="B78"/>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79"/>
-      <c r="B79"/>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80"/>
-      <c r="B80"/>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81"/>
-      <c r="B81"/>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82"/>
-      <c r="B82"/>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83"/>
-      <c r="B83"/>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84"/>
-      <c r="B84"/>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85"/>
-      <c r="B85"/>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86"/>
-      <c r="B86"/>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87"/>
-      <c r="B87"/>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88"/>
-      <c r="B88"/>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89"/>
-      <c r="B89"/>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90"/>
-      <c r="B90"/>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91"/>
-      <c r="B91"/>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92"/>
-      <c r="B92"/>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93"/>
-      <c r="B93"/>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94"/>
-      <c r="B94"/>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95"/>
-      <c r="B95"/>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96"/>
-      <c r="B96"/>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97"/>
-      <c r="B97"/>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98"/>
-      <c r="B98"/>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99"/>
-      <c r="B99"/>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100"/>
-      <c r="B100"/>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101"/>
-      <c r="B101"/>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102"/>
-      <c r="B102"/>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103"/>
-      <c r="B103"/>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104"/>
-      <c r="B104"/>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105"/>
-      <c r="B105"/>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106"/>
-      <c r="B106"/>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107"/>
-      <c r="B107"/>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108"/>
-      <c r="B108"/>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109"/>
-      <c r="B109"/>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110"/>
-      <c r="B110"/>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B32" t="s">
+        <v>61</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>62</v>
+      </c>
+      <c r="B33" t="s">
+        <v>63</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>66</v>
+      </c>
+      <c r="B35" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>69</v>
+      </c>
+      <c r="B36" t="s">
+        <v>70</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>72</v>
+      </c>
+      <c r="B37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" t="s">
+        <v>76</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>74</v>
+      </c>
+      <c r="B40" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" t="s">
+        <v>85</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>74</v>
+      </c>
+      <c r="B44" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>88</v>
+      </c>
+      <c r="B45" t="s">
+        <v>89</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>90</v>
+      </c>
+      <c r="B46" t="s">
+        <v>91</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>66</v>
+      </c>
+      <c r="B47" t="s">
+        <v>93</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>74</v>
+      </c>
+      <c r="B48" t="s">
+        <v>94</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>72</v>
+      </c>
+      <c r="B49" t="s">
+        <v>95</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>74</v>
+      </c>
+      <c r="B50" t="s">
+        <v>96</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>74</v>
+      </c>
+      <c r="B51" t="s">
+        <v>97</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>98</v>
+      </c>
+      <c r="B52" t="s">
+        <v>99</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>100</v>
+      </c>
+      <c r="B53" t="s">
+        <v>101</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>102</v>
+      </c>
+      <c r="B54" t="s">
+        <v>103</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>104</v>
+      </c>
+      <c r="B55" t="s">
+        <v>105</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>106</v>
+      </c>
+      <c r="B56" t="s">
+        <v>107</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>64</v>
+      </c>
+      <c r="B57" t="s">
+        <v>108</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>109</v>
+      </c>
+      <c r="B58" t="s">
+        <v>110</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>111</v>
+      </c>
+      <c r="B59" t="s">
+        <v>112</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>113</v>
+      </c>
+      <c r="B60" t="s">
+        <v>114</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>72</v>
+      </c>
+      <c r="B61" t="s">
+        <v>115</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>116</v>
+      </c>
+      <c r="B62" t="s">
+        <v>117</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>74</v>
+      </c>
+      <c r="B63" t="s">
+        <v>118</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>119</v>
+      </c>
+      <c r="B64" t="s">
+        <v>120</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>121</v>
+      </c>
+      <c r="B65" t="s">
+        <v>122</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>123</v>
+      </c>
+      <c r="B66" t="s">
+        <v>124</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>74</v>
+      </c>
+      <c r="B67" t="s">
+        <v>125</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>111</v>
+      </c>
+      <c r="B68" t="s">
+        <v>126</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>128</v>
+      </c>
+      <c r="B69" t="s">
+        <v>129</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>130</v>
+      </c>
+      <c r="B70" t="s">
+        <v>131</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>132</v>
+      </c>
+      <c r="B71" t="s">
+        <v>133</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>134</v>
+      </c>
+      <c r="B72" t="s">
+        <v>135</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>136</v>
+      </c>
+      <c r="B73" t="s">
+        <v>137</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>138</v>
+      </c>
+      <c r="B74" t="s">
+        <v>139</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>140</v>
+      </c>
+      <c r="B75" t="s">
+        <v>141</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>142</v>
+      </c>
+      <c r="B76" t="s">
+        <v>143</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>144</v>
+      </c>
+      <c r="B77" t="s">
+        <v>145</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>146</v>
+      </c>
+      <c r="B78" t="s">
+        <v>147</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>148</v>
+      </c>
+      <c r="B79" t="s">
+        <v>149</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>150</v>
+      </c>
+      <c r="B80" t="s">
+        <v>151</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>152</v>
+      </c>
+      <c r="B81" t="s">
+        <v>153</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>154</v>
+      </c>
+      <c r="B82" t="s">
+        <v>155</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>156</v>
+      </c>
+      <c r="B83" t="s">
+        <v>157</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>158</v>
+      </c>
+      <c r="B84" t="s">
+        <v>159</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>160</v>
+      </c>
+      <c r="B85" t="s">
+        <v>161</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>162</v>
+      </c>
+      <c r="B86" t="s">
+        <v>163</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>164</v>
+      </c>
+      <c r="B87" t="s">
+        <v>165</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>166</v>
+      </c>
+      <c r="B88" t="s">
+        <v>167</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>109</v>
+      </c>
+      <c r="B89" t="s">
+        <v>168</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>72</v>
+      </c>
+      <c r="B90" t="s">
+        <v>169</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>72</v>
+      </c>
+      <c r="B91" t="s">
+        <v>170</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>72</v>
+      </c>
+      <c r="B92" t="s">
+        <v>171</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>172</v>
+      </c>
+      <c r="B93" t="s">
+        <v>173</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>111</v>
+      </c>
+      <c r="B94" t="s">
+        <v>174</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>175</v>
+      </c>
+      <c r="B95" t="s">
+        <v>176</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>66</v>
+      </c>
+      <c r="B96" t="s">
+        <v>177</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>111</v>
+      </c>
+      <c r="B97" t="s">
+        <v>178</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>128</v>
+      </c>
+      <c r="B98" t="s">
+        <v>179</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>72</v>
+      </c>
+      <c r="B99" t="s">
+        <v>180</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>181</v>
+      </c>
+      <c r="B100" t="s">
+        <v>182</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>183</v>
+      </c>
+      <c r="B101" t="s">
+        <v>184</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>185</v>
+      </c>
+      <c r="B102" t="s">
+        <v>186</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>187</v>
+      </c>
+      <c r="B103" t="s">
+        <v>188</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>72</v>
+      </c>
+      <c r="B104" t="s">
+        <v>189</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>72</v>
+      </c>
+      <c r="B105" t="s">
+        <v>190</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>191</v>
+      </c>
+      <c r="B106" t="s">
+        <v>192</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>191</v>
+      </c>
+      <c r="B107" t="s">
+        <v>193</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>194</v>
+      </c>
+      <c r="B108" t="s">
+        <v>195</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>74</v>
+      </c>
+      <c r="B109" t="s">
+        <v>196</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>197</v>
+      </c>
+      <c r="B110" t="s">
+        <v>198</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111"/>
       <c r="B111"/>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112"/>
       <c r="B112"/>
     </row>
@@ -1322,31 +2353,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAzNTMxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MzAvMTIvMjAyMCAxMTo0NTo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAzMC8xMi8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41A8E509-6991-4B84-B1B5-13851E156C6A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DBFCB3-53E5-4527-B13D-DC7A854D4B55}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41A8E509-6991-4B84-B1B5-13851E156C6A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Dados e Relatórios\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FF22F1B-784E-4BA2-8678-1A5278C6686A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E1622BF-B7DD-4B43-8A97-59E86688801F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="102">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -51,178 +51,298 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>flavia.costa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>rosemeire.faria@allianz.com.br</t>
-  </si>
-  <si>
-    <t>cleyciane.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>carlos.neves@allianz.com.br</t>
-  </si>
-  <si>
     <t>adriano.guerra@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12883251400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
     <t>irene.rosa@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12479361400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>patricia.reis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12883630800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12884454900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>flavio.cesar@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12777283000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>juliana.almeida@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12818981300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12886060200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>douglas.morais@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12710053300000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>claudia.gomes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12883548400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
     <t>talita.meneses@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12884739100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
     <t>andrea.duarte@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12867399800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12886888300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12886891900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
     <t>dayane.oliveira@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12814649000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>rafael.junior@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12836176400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>fernanda.oliveira@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12884543500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12887816200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>adautina.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12883455700000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
     <t>lucas.monteiro@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12887999700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
     <t>dimas.soares@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12877966600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>carla.nascimento@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12483838300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>fernando.sousa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12843514400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>viviane.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12884666200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>claudenice.barbosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12843699300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12872544700000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
     <t>karla.cunha@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12847462000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>emerson.cruz@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11112900756 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>debora.santos2@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12784674000000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>alessandra.guedes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-39323399000187 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11402906800000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11468249700000 Nota 242 - Retorno Cobrança</t>
+    <t>marina.melo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12495560100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>william.bonifacio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12866060500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>lilian.sudati@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12836762600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>eliana.pedroso@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12886034600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12875110500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rubiane.bendlin@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12579545400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12887599800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>leandro.araujo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12750741300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>danillo.boem@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12879926800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>alessandra.araujo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12887197000000 Nota 595 - ERRO PDF PDF RETORNO</t>
+  </si>
+  <si>
+    <t>jose.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12888357900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>daniela.leal@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-29460018068 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>vanessa.campos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12886905900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>gleison.ferreira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-487954000170 Nota 531 - Alteração ou correção dados cadastrais</t>
+  </si>
+  <si>
+    <t>tatiany.macedo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12873520200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>andre.gouvea@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-7578211897 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>priscila.rubio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-4858609000157 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>leandro.santos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12842654300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>claudia.pires@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12866744700000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12879626900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-14592173000150 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-26060446000103 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>gustavo.correa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12436587800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>eliane.outor@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12754925900000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>vitor.mattos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12832231000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12834226600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>erineuza.monzillo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-2878879872 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>daiane.soares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12723236900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>fabio.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12883107300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12885333200000 Nota 595 - ERRO PDF PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12883320000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12834033500000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>luiz.sanchetta@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12884588000000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>alciana.carlucci@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12874816500000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12885698900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12536055800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12843699300000 Nota 595 - ERRO PDF PSF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12843699300000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>ivana.freitas@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12876239200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>thays.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12876923400001 Nota 595 - ERRO PDF PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12886764200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>joao.neto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12878140600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>marcio.kaminski@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12884129300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>lucidene.santana@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12631590800000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>ana.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12701478100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12847944900000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>nelma.xavier@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12844870700000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12850545600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>janaina.cazelato@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12866425200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12880140100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>thomaz.jesus@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12302937300000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>elvis.patez@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12879479900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>eloiza.felippe@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12884924300000 Nota 595 - ERRO PDF</t>
   </si>
 </sst>
 </file>
@@ -622,10 +742,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -633,10 +753,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -644,10 +764,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -655,10 +775,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -666,10 +786,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -677,10 +797,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -688,10 +808,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -699,10 +819,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -710,10 +830,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -721,10 +841,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -732,10 +852,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -743,10 +863,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -754,10 +874,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -765,10 +885,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -776,10 +896,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -787,10 +907,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -798,10 +918,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -809,10 +929,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -820,10 +940,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -831,10 +951,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -845,7 +965,7 @@
         <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -853,10 +973,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -864,10 +984,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
@@ -875,10 +995,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -886,10 +1006,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="B26" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
@@ -900,7 +1020,7 @@
         <v>52</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -908,10 +1028,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>3</v>
@@ -919,10 +1039,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>3</v>
@@ -930,10 +1050,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>3</v>
@@ -941,10 +1061,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="B31" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>3</v>
@@ -955,137 +1075,291 @@
         <v>7</v>
       </c>
       <c r="B32" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33"/>
-      <c r="B33"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34"/>
-      <c r="B34"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35"/>
-      <c r="B35"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36"/>
-      <c r="B36"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37"/>
-      <c r="B37"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38"/>
-      <c r="B38"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39"/>
-      <c r="B39"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40"/>
-      <c r="B40"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41"/>
-      <c r="B41"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42"/>
-      <c r="B42"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43"/>
-      <c r="B43"/>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44"/>
-      <c r="B44"/>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45"/>
-      <c r="B45"/>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46"/>
-      <c r="B46"/>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47"/>
-      <c r="B47"/>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48"/>
-      <c r="B48"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49"/>
-      <c r="B49"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50"/>
-      <c r="B50"/>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51"/>
-      <c r="B51"/>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52"/>
-      <c r="B52"/>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53"/>
-      <c r="B53"/>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54"/>
-      <c r="B54"/>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>8</v>
+      </c>
+      <c r="B33" t="s">
+        <v>67</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>68</v>
+      </c>
+      <c r="B34" t="s">
+        <v>69</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>9</v>
+      </c>
+      <c r="B36" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39" t="s">
+        <v>75</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>76</v>
+      </c>
+      <c r="B40" t="s">
+        <v>77</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>78</v>
+      </c>
+      <c r="B42" t="s">
+        <v>80</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>81</v>
+      </c>
+      <c r="B43" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>83</v>
+      </c>
+      <c r="B44" t="s">
+        <v>84</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>85</v>
+      </c>
+      <c r="B45" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>87</v>
+      </c>
+      <c r="B46" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>12</v>
+      </c>
+      <c r="B47" t="s">
+        <v>89</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>90</v>
+      </c>
+      <c r="B48" t="s">
+        <v>91</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>90</v>
+      </c>
+      <c r="B49" t="s">
+        <v>92</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>93</v>
+      </c>
+      <c r="B50" t="s">
+        <v>94</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>93</v>
+      </c>
+      <c r="B51" t="s">
+        <v>95</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>96</v>
+      </c>
+      <c r="B52" t="s">
+        <v>97</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>98</v>
+      </c>
+      <c r="B53" t="s">
+        <v>99</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>100</v>
+      </c>
+      <c r="B54" t="s">
+        <v>101</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55"/>
       <c r="B55"/>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56"/>
       <c r="B56"/>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57"/>
       <c r="B57"/>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58"/>
       <c r="B58"/>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59"/>
       <c r="B59"/>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60"/>
       <c r="B60"/>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61"/>
       <c r="B61"/>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62"/>
       <c r="B62"/>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63"/>
       <c r="B63"/>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64"/>
       <c r="B64"/>
     </row>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Dados e Relatórios\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E1622BF-B7DD-4B43-8A97-59E86688801F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3779461B-AC19-4D0B-8E55-500E26830A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28875" windowHeight="14625" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envio Robô" sheetId="2" r:id="rId1"/>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Envio Robô'!$A$1:$C$2</definedName>
   </definedNames>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="214">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -54,295 +54,685 @@
     <t>adriano.guerra@allianz.com.br</t>
   </si>
   <si>
-    <t>irene.rosa@allianz.com.br</t>
-  </si>
-  <si>
     <t>talita.meneses@allianz.com.br</t>
   </si>
   <si>
-    <t>andrea.duarte@allianz.com.br</t>
-  </si>
-  <si>
-    <t>dayane.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>fernanda.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>lucas.monteiro@allianz.com.br</t>
-  </si>
-  <si>
     <t>dimas.soares@allianz.com.br</t>
   </si>
   <si>
-    <t>karla.cunha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>marina.melo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12495560100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>william.bonifacio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12866060500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>lilian.sudati@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12836762600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>eliana.pedroso@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12886034600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12875110500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>rubiane.bendlin@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12579545400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12887599800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>leandro.araujo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12750741300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>danillo.boem@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12879926800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>alessandra.araujo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12887197000000 Nota 595 - ERRO PDF PDF RETORNO</t>
-  </si>
-  <si>
-    <t>jose.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12888357900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daniela.leal@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-29460018068 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>vanessa.campos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12886905900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>gleison.ferreira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-487954000170 Nota 531 - Alteração ou correção dados cadastrais</t>
-  </si>
-  <si>
-    <t>tatiany.macedo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12873520200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>andre.gouvea@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-7578211897 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>priscila.rubio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-4858609000157 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>leandro.santos@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12842654300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>claudia.pires@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12866744700000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12879626900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-14592173000150 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-26060446000103 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>gustavo.correa@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12436587800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>eliane.outor@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12754925900000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>vitor.mattos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12832231000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12834226600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>erineuza.monzillo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-2878879872 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daiane.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12723236900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>fabio.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12883107300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12885333200000 Nota 595 - ERRO PDF PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12883320000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12834033500000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>luiz.sanchetta@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12884588000000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>alciana.carlucci@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12874816500000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12885698900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12536055800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12843699300000 Nota 595 - ERRO PDF PSF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12843699300000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>ivana.freitas@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12876239200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
     <t>thays.silva@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12876923400001 Nota 595 - ERRO PDF PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12886764200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>joao.neto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12878140600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>marcio.kaminski@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12884129300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>lucidene.santana@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12631590800000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>ana.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12701478100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12847944900000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>nelma.xavier@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12844870700000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12850545600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>janaina.cazelato@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12866425200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12880140100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>thomaz.jesus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12302937300000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>elvis.patez@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12879479900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>eloiza.felippe@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12884924300000 Nota 595 - ERRO PDF</t>
+    <t>bruna.carneiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12879292000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>rodrigo.amorim@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12889524100000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>everton.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12889754000000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>silvia.taschetti@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12793154800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12879307300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12886034600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>lucineide.medeiros@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12843339000000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12888704800000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>lucas.almeida@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12887834700000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>fernando.martins1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12887772600000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>tatiana.monis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12879461800000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>lidiane.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12842181900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>luciana.belisario@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12679235300000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>leandro.gonzaga@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12880254400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12511190300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12776054300035 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12860417800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>monica.prates@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12818985800000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>flavia.costa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12890350700000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>diogo.junior@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12768055500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>daniele.beck@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12698880400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>jonatas.lauretto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12888423100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12885484500000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12884574600000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>daniella.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12887541000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>rafael.leite@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12890433900000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>izys.barreto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12815959300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>viviane.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12884666200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>claudenice.barbosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12881881900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12593852500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>renata.scarpino@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12876720500000 Nota 418 - Vida - Faturamento - Proposta/DPS</t>
+  </si>
+  <si>
+    <t>jeisis.arruda@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-76491269868 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>carlos.costa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12881881900000 Nota 595 - ERRO PDF ERRO PDF</t>
+  </si>
+  <si>
+    <t>jethaseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125680058 - JORGE WASHINGTON SOUZA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 10 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>mabemseguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125981444 - ZILDA RODRIGUES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 9 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>asuzanocorretora@hotmail.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126049574 - ALINE MORELLI WIRTHMANN</t>
+  </si>
+  <si>
+    <t>contato@waseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126033194 - SARA DE TOLEDO RAINHA</t>
+  </si>
+  <si>
+    <t>luizalbertodionysio56@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126001156 - LUCIANO GONCALVES DA ROCHA</t>
+  </si>
+  <si>
+    <t>suporte.vvd@vwfs.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126350938 - GIULLBER VALENTIM DA SILVA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 8 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>faleconosco@mapma.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127326789 - SONIA REGINA BALMANT DOS SANTOS REZENDE</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>backofficecorretora@segurostoyota.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127338296 - LUCIANA FELIX GONCALVES PINTO</t>
+  </si>
+  <si>
+    <t>renovacaoseguros@honda.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127343374 - JOSEILDO DOMINGOS DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127883748 - MARCIA APARECIDA SILVA ERHARDT</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 3 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128381505 - ARTUR OLIVEIRA PIRES</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 2 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>leandro@cabreraseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125925280 - VIVIAN LACERDA DE MELO</t>
+  </si>
+  <si>
+    <t>contato@uxseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125973684 - CLARISSA KURY PINHEIRO</t>
+  </si>
+  <si>
+    <t>diretoria@lapisbellus.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126350664 - DOUGLAS SOLEDADE DA SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126674196 - ANTONIO CARLOS DE FONTES</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>sudeste@sudesteseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126704888 - TANISE RODRIGUES DA SILVA FONTES</t>
+  </si>
+  <si>
+    <t>seg.cac@terra.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126969832 - JEAN ONESIMO FERREIRA DA COSTA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 6 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126990070 - JAIRO IZIDIO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127316956 - VITORIA ALVES ROQUE DA SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127307913 - SOLANGE SOUZA ARAUJO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127325978 - CONCEICAO FERREIRA LIMA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128328841 - ALANIS ELOISA MOTA</t>
+  </si>
+  <si>
+    <t>gferreira@gferreiraseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125668133 - STAEL SOARES VIEIRA CAMPOS</t>
+  </si>
+  <si>
+    <t>colmeiacor@colmeiaseg.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125675807 - GUSTAVO ANDRE CORRADI</t>
+  </si>
+  <si>
+    <t>elittecorretora@elittecorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125670269 - DAISY VIEIRA DE ARAUJO</t>
+  </si>
+  <si>
+    <t>contato@luganocorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125960387 - EVERALDO MIRANDA</t>
+  </si>
+  <si>
+    <t>sibelesouzabaeta@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126013388 - ROSENIL OLIVEIRA MOTTA FAGUNDES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126314556 - ROBERTO JORGE FADEL</t>
+  </si>
+  <si>
+    <t>andre.oliveira@braseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126272780 - ANGELO MARIO DAS NEVES</t>
+  </si>
+  <si>
+    <t>andradecorretoraseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126288543 - VALDECI FERREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>duromarcorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126355625 - ERINALDA BATISTA ALVES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126701278 - CRISTIANE GIAVARINI MANSK</t>
+  </si>
+  <si>
+    <t>maisbrasilcor@maisbrasilcor.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126606925 - JULIETA MINORI NAKASHIMA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126985037 - CHRISELLEN DE PAULA CHAVES</t>
+  </si>
+  <si>
+    <t>amlbseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127225617 - MARGARIDA MARIA COSTA BATISTA</t>
+  </si>
+  <si>
+    <t>seguros@trigocorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127295746 - COMBRAS 2000 COMERCIO E LOCACAO DE CONTEINERE</t>
+  </si>
+  <si>
+    <t>aprossegteresina@aprosseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127311919 - EDNA MARIA CORREIA LIMA E SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127284115 - MARIA AUGUSTA SIMONASSI ARAUJO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127530836 - BRUNA OLIVEIRA DA SILVA CARVALHO</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>contigo@contigoseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127618149 - VIRGINIA LUCIA FONSECA DA COSTA</t>
+  </si>
+  <si>
+    <t>globalpoliana@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127627304 - LUIS ANTONIO SOUTO</t>
+  </si>
+  <si>
+    <t>agenol.seguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127901020 - DANIEL DE OLIVEIRA SILVA</t>
+  </si>
+  <si>
+    <t>interweg@interweg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127895906 - ANDREA DINIZ DE MELO PAZ</t>
+  </si>
+  <si>
+    <t>aoseguros@aoseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127904056 - LUIZ ROBERTO RENZI</t>
+  </si>
+  <si>
+    <t>adm.corretora@revemar.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128094369 - LUCIVANIA BRANDAO MENDES</t>
+  </si>
+  <si>
+    <t>pendencia@seguralta.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128320407 - EDSON MENDES GONZAGA</t>
+  </si>
+  <si>
+    <t>emissao@willistowerswatson.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128184461 - AMAURY DOS SANTOS</t>
+  </si>
+  <si>
+    <t>delgadojfseguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125656379 - GIL DAYRELL SIQUEIRA</t>
+  </si>
+  <si>
+    <t>jozeaine.novais@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125664418 - DEISE LUCI CORREA BENTO</t>
+  </si>
+  <si>
+    <t>lchcorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125992576 - ANAIDE SILVA</t>
+  </si>
+  <si>
+    <t>adim@amcorretagem.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126024409 - LOURDES KARINE CUSTODIO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>confiarcorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126022143 - CLAUDIO GERALDO DA SILVA</t>
+  </si>
+  <si>
+    <t>simone@corasbeg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126016469 - FRANCISCO COELHO DA COSTA</t>
+  </si>
+  <si>
+    <t>luciana@cunhacastro.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126011684 - JEFFERSON SOUSA SILVA</t>
+  </si>
+  <si>
+    <t>jaguare@jaguareseguros.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126025037 - JULIANE MARISTELLA AGUIAR DA COSTA CARVALHO A</t>
+  </si>
+  <si>
+    <t>albacarvalho@aerocarcorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126240350 - VERA SELMA RODRIGUES CARVALHO</t>
+  </si>
+  <si>
+    <t>operacional@holdcorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126300406 - DENISE GUICHARD FREIRE</t>
+  </si>
+  <si>
+    <t>prisminas@prisminas.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126278175 - UBALDO JOSE DE CARVALHO</t>
+  </si>
+  <si>
+    <t>diamantinaseguros@diamantinaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126608530 - IZABELLA PRISCILA SANTOS SIDONIO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126681492 - MILENA DE LIMA BRAGANCA VIEIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126973352 - GISELE CANDIDO LANDI</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127265158 - ANA LUCIA BORLOT FALCAO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127282765 - VALDETE MIRANDA MARCILIO</t>
+  </si>
+  <si>
+    <t>fernandacunha@vivacorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127292767 - MARCONY GIORDANI MIRANDA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127593533 - WANESSA PARREIRA SERAFIM CARDOSO</t>
+  </si>
+  <si>
+    <t>seguecorretora.contato@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126018858 - SUPPORT TELEINFORMATICA LTDA ME</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126317599 - KELRILAYNNY FRANCISCA DE SANTANA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126247792 - CAMILA LEAL DE SOUSA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126652424 - ALDRICH HEUSER CAMARA GODEIRO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126649535 - MARIA RODRIGUES DO CARMO</t>
+  </si>
+  <si>
+    <t>eloimseguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126628892 - ANTONIO CARLOS DOS SANTOS SILVA</t>
+  </si>
+  <si>
+    <t>solange@mottacorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126623096 - ADRIANA DA SILVA FERREIRA</t>
+  </si>
+  <si>
+    <t>ikeda@ikedaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126968339 - MARIO MASSAO TAKAKI</t>
+  </si>
+  <si>
+    <t>marta@berdam.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126959902 - RITA DE CASSIA SANCHES MARQUES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126931877 - IVANILDO MEDEIROS NUNES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127276247 - MARICELMA CAVALCANTE DA SILVA</t>
+  </si>
+  <si>
+    <t>andrea@thompsonseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127244441 - ELEMENTAR CONSTRUCOES E REFORMAS LTDA ME</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127510836 - APAD APOIO EMPRESARIAL S S LTDA ME</t>
+  </si>
+  <si>
+    <t>seguradoras@dartanseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127563618 - RUI GOMARA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127607279 - FABRICIA DA SILVA ROMAO</t>
+  </si>
+  <si>
+    <t>pendencia@vilavelha.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128170050 - CELSO CUNHA GONCALVES</t>
   </si>
 </sst>
 </file>
@@ -742,10 +1132,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -753,10 +1143,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" t="s">
         <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -764,10 +1154,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
         <v>17</v>
-      </c>
-      <c r="B4" t="s">
-        <v>18</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -775,10 +1165,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
         <v>19</v>
-      </c>
-      <c r="B5" t="s">
-        <v>20</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -786,10 +1176,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -797,10 +1187,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -808,10 +1198,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -819,10 +1209,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -830,10 +1220,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -841,10 +1231,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -852,10 +1242,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -863,10 +1253,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -874,10 +1264,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -885,10 +1275,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -896,10 +1286,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -907,10 +1297,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -918,10 +1308,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>9</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -929,10 +1319,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -940,10 +1330,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -951,10 +1341,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>6</v>
+        <v>44</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -962,10 +1352,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B22" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -973,10 +1363,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="B23" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -984,10 +1374,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
@@ -995,10 +1385,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="B25" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -1006,10 +1396,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B26" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
@@ -1017,10 +1407,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -1028,10 +1418,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>3</v>
@@ -1039,10 +1429,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B29" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>3</v>
@@ -1050,10 +1440,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B30" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>3</v>
@@ -1061,10 +1451,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>63</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>3</v>
@@ -1072,10 +1462,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>7</v>
+        <v>63</v>
       </c>
       <c r="B32" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>3</v>
@@ -1083,10 +1473,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>8</v>
+        <v>65</v>
       </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>3</v>
@@ -1094,10 +1484,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" t="s">
         <v>68</v>
-      </c>
-      <c r="B34" t="s">
-        <v>69</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>3</v>
@@ -1105,467 +1495,894 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
+        <v>69</v>
+      </c>
+      <c r="B35" t="s">
         <v>70</v>
       </c>
-      <c r="B35" t="s">
+      <c r="C35" s="2" t="s">
         <v>71</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="B36" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>10</v>
+        <v>75</v>
       </c>
       <c r="B37" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>11</v>
+        <v>77</v>
       </c>
       <c r="B38" t="s">
+        <v>78</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="B39" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="B40" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>3</v>
+        <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="B43" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B44" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>3</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B45" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>3</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="B46" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="B47" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B48" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>3</v>
+        <v>83</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B49" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>3</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>93</v>
+        <v>103</v>
       </c>
       <c r="B50" t="s">
-        <v>94</v>
+        <v>104</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>3</v>
+        <v>102</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="B51" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>3</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="B52" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>3</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="B53" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
       <c r="B54" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>3</v>
+        <v>86</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55"/>
-      <c r="B55"/>
+      <c r="A55" t="s">
+        <v>89</v>
+      </c>
+      <c r="B55" t="s">
+        <v>111</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56"/>
-      <c r="B56"/>
+      <c r="A56" t="s">
+        <v>89</v>
+      </c>
+      <c r="B56" t="s">
+        <v>112</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57"/>
-      <c r="B57"/>
+      <c r="A57" t="s">
+        <v>113</v>
+      </c>
+      <c r="B57" t="s">
+        <v>114</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58"/>
-      <c r="B58"/>
+      <c r="A58" t="s">
+        <v>115</v>
+      </c>
+      <c r="B58" t="s">
+        <v>116</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59"/>
-      <c r="B59"/>
+      <c r="A59" t="s">
+        <v>117</v>
+      </c>
+      <c r="B59" t="s">
+        <v>118</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60"/>
-      <c r="B60"/>
+      <c r="A60" t="s">
+        <v>119</v>
+      </c>
+      <c r="B60" t="s">
+        <v>120</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61"/>
-      <c r="B61"/>
+      <c r="A61" t="s">
+        <v>121</v>
+      </c>
+      <c r="B61" t="s">
+        <v>122</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62"/>
-      <c r="B62"/>
+      <c r="A62" t="s">
+        <v>79</v>
+      </c>
+      <c r="B62" t="s">
+        <v>123</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63"/>
-      <c r="B63"/>
+      <c r="A63" t="s">
+        <v>124</v>
+      </c>
+      <c r="B63" t="s">
+        <v>125</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64"/>
-      <c r="B64"/>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65"/>
-      <c r="B65"/>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66"/>
-      <c r="B66"/>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67"/>
-      <c r="B67"/>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68"/>
-      <c r="B68"/>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69"/>
-      <c r="B69"/>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70"/>
-      <c r="B70"/>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71"/>
-      <c r="B71"/>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72"/>
-      <c r="B72"/>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73"/>
-      <c r="B73"/>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74"/>
-      <c r="B74"/>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75"/>
-      <c r="B75"/>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76"/>
-      <c r="B76"/>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77"/>
-      <c r="B77"/>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78"/>
-      <c r="B78"/>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79"/>
-      <c r="B79"/>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80"/>
-      <c r="B80"/>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81"/>
-      <c r="B81"/>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82"/>
-      <c r="B82"/>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83"/>
-      <c r="B83"/>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84"/>
-      <c r="B84"/>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85"/>
-      <c r="B85"/>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86"/>
-      <c r="B86"/>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87"/>
-      <c r="B87"/>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88"/>
-      <c r="B88"/>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89"/>
-      <c r="B89"/>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90"/>
-      <c r="B90"/>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91"/>
-      <c r="B91"/>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92"/>
-      <c r="B92"/>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93"/>
-      <c r="B93"/>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94"/>
-      <c r="B94"/>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95"/>
-      <c r="B95"/>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96"/>
-      <c r="B96"/>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97"/>
-      <c r="B97"/>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98"/>
-      <c r="B98"/>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99"/>
-      <c r="B99"/>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100"/>
-      <c r="B100"/>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101"/>
-      <c r="B101"/>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102"/>
-      <c r="B102"/>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103"/>
-      <c r="B103"/>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104"/>
-      <c r="B104"/>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105"/>
-      <c r="B105"/>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106"/>
-      <c r="B106"/>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107"/>
-      <c r="B107"/>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108"/>
-      <c r="B108"/>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109"/>
-      <c r="B109"/>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110"/>
-      <c r="B110"/>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111"/>
-      <c r="B111"/>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112"/>
-      <c r="B112"/>
+      <c r="A64" t="s">
+        <v>126</v>
+      </c>
+      <c r="B64" t="s">
+        <v>127</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>128</v>
+      </c>
+      <c r="B65" t="s">
+        <v>129</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>87</v>
+      </c>
+      <c r="B66" t="s">
+        <v>130</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>131</v>
+      </c>
+      <c r="B67" t="s">
+        <v>132</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>89</v>
+      </c>
+      <c r="B68" t="s">
+        <v>133</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>134</v>
+      </c>
+      <c r="B69" t="s">
+        <v>135</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>136</v>
+      </c>
+      <c r="B70" t="s">
+        <v>137</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>138</v>
+      </c>
+      <c r="B71" t="s">
+        <v>139</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>89</v>
+      </c>
+      <c r="B72" t="s">
+        <v>140</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>126</v>
+      </c>
+      <c r="B73" t="s">
+        <v>141</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>143</v>
+      </c>
+      <c r="B74" t="s">
+        <v>144</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>145</v>
+      </c>
+      <c r="B75" t="s">
+        <v>146</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>147</v>
+      </c>
+      <c r="B76" t="s">
+        <v>148</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>149</v>
+      </c>
+      <c r="B77" t="s">
+        <v>150</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>151</v>
+      </c>
+      <c r="B78" t="s">
+        <v>152</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>153</v>
+      </c>
+      <c r="B79" t="s">
+        <v>154</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>155</v>
+      </c>
+      <c r="B80" t="s">
+        <v>156</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>157</v>
+      </c>
+      <c r="B81" t="s">
+        <v>158</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>159</v>
+      </c>
+      <c r="B82" t="s">
+        <v>160</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>161</v>
+      </c>
+      <c r="B83" t="s">
+        <v>162</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>163</v>
+      </c>
+      <c r="B84" t="s">
+        <v>164</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>165</v>
+      </c>
+      <c r="B85" t="s">
+        <v>166</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>167</v>
+      </c>
+      <c r="B86" t="s">
+        <v>168</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>169</v>
+      </c>
+      <c r="B87" t="s">
+        <v>170</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>171</v>
+      </c>
+      <c r="B88" t="s">
+        <v>172</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>173</v>
+      </c>
+      <c r="B89" t="s">
+        <v>174</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>175</v>
+      </c>
+      <c r="B90" t="s">
+        <v>176</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>177</v>
+      </c>
+      <c r="B91" t="s">
+        <v>178</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>179</v>
+      </c>
+      <c r="B92" t="s">
+        <v>180</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>181</v>
+      </c>
+      <c r="B93" t="s">
+        <v>182</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>124</v>
+      </c>
+      <c r="B94" t="s">
+        <v>183</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>87</v>
+      </c>
+      <c r="B95" t="s">
+        <v>184</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>87</v>
+      </c>
+      <c r="B96" t="s">
+        <v>185</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>87</v>
+      </c>
+      <c r="B97" t="s">
+        <v>186</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>187</v>
+      </c>
+      <c r="B98" t="s">
+        <v>188</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>126</v>
+      </c>
+      <c r="B99" t="s">
+        <v>189</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>190</v>
+      </c>
+      <c r="B100" t="s">
+        <v>191</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>81</v>
+      </c>
+      <c r="B101" t="s">
+        <v>192</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>126</v>
+      </c>
+      <c r="B102" t="s">
+        <v>193</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>143</v>
+      </c>
+      <c r="B103" t="s">
+        <v>194</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>87</v>
+      </c>
+      <c r="B104" t="s">
+        <v>195</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>196</v>
+      </c>
+      <c r="B105" t="s">
+        <v>197</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>198</v>
+      </c>
+      <c r="B106" t="s">
+        <v>199</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>200</v>
+      </c>
+      <c r="B107" t="s">
+        <v>201</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>202</v>
+      </c>
+      <c r="B108" t="s">
+        <v>203</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>87</v>
+      </c>
+      <c r="B109" t="s">
+        <v>204</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>87</v>
+      </c>
+      <c r="B110" t="s">
+        <v>205</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>206</v>
+      </c>
+      <c r="B111" t="s">
+        <v>207</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>206</v>
+      </c>
+      <c r="B112" t="s">
+        <v>208</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113"/>
-      <c r="B113"/>
+      <c r="A113" t="s">
+        <v>209</v>
+      </c>
+      <c r="B113" t="s">
+        <v>210</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114"/>
-      <c r="B114"/>
+      <c r="A114" t="s">
+        <v>89</v>
+      </c>
+      <c r="B114" t="s">
+        <v>211</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115"/>
-      <c r="B115"/>
+      <c r="A115" t="s">
+        <v>212</v>
+      </c>
+      <c r="B115" t="s">
+        <v>213</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116"/>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Dados e Relatórios\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{196FF386-C8AE-4906-8A24-20889C5FC5A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7127128A-41B5-4DEA-8E4C-C2CAE394A92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3075" yWindow="3075" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28800" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envio Robô" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="87">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -51,211 +51,253 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>everton.silva1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>marina.melo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>crislaine.trindade@allianz.com.br</t>
-  </si>
-  <si>
-    <t>patricia.reis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>danillo.boem@allianz.com.br</t>
-  </si>
-  <si>
     <t>carlos.neves@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12211125100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12890002100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>jocineia.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-32780728809 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12811000000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>diego.vasconcelos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12532090900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>dinah.castro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12886963200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
     <t>irene.rosa@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12529562700000 Nota 595 - ERRO PDF RETORNO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12887413400000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>claudia.magalhaes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12815115000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>matheus.pereira@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12884762400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12712249800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>ana.alves1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12798431500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>jose.neves@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12843474000000 Nota 595 - ERRO PDF RETORNO PDF</t>
-  </si>
-  <si>
-    <t>fernanda.braga@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12883108000000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
     <t>caroline.wojciechowski@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12889957100000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12891277900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>andriele.pala@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12650390400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>saulo.santiago@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12863509600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>erineuza.monzillo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12816384500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>karen.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12836837300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>daiane.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12867882900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12891436800000 Nota 595 - ERRO PDF ERRO PDF</t>
-  </si>
-  <si>
-    <t>adriano.campos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12879303900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>alberto.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12884627100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>gilberto.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12881157400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>gustavo.arruda@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12891135400000 Nota 595 - ERRO PDF RETORNO PDF</t>
-  </si>
-  <si>
-    <t>luiz.pereira2@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12894303900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-20550280000119 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>dimas.soares@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12892000700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>ivone.jesus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12799000200000 Nota 167 - Retorno Cobrança op53</t>
-  </si>
-  <si>
     <t>daniella.andrade@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12889036500000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>juliana.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12809594100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>graziella.pignataro@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12885762700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>ana.carneiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-61574273000134 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>edson.jesus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12892033900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11873865600000 Nota 242 - Retorno Cobrança</t>
+    <t>noadia.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12884844600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>william.bonifacio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12755419500000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>rosangela.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12892525100000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>silvia.taschetti@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12723521200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>eliana.pedroso@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12769927400000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>tadeu.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12879515800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>luiz.inocente@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12789002200003 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12884492500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>ana.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12891358700000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12884366700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12843474000000 Nota 595 - ERRO PDF retorno PDF</t>
+  </si>
+  <si>
+    <t>fernando.martins1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12716572500000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12716572500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>vanessa.penatti@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12887040900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>sonia.bortoleto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12893533300000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>tatiana.monis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12894656200000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12894647500000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>leandro.machado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12720961200000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>leandro.gonzaga@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12889193600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>rodrigo.kuguyama@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-88818357500000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>leonardo.dache@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12771844500000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>bruna.teixeira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12893012700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>flavia.costa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12894956700000 Nota 595 - ERRO PDF Retorno PDF</t>
+  </si>
+  <si>
+    <t>rosana.teixeira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12855040400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>alciana.carlucci@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12476604100000 Nota 595 - ERRO PDF retorno pdf</t>
+  </si>
+  <si>
+    <t>marco.vita@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12892690900000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>jonatas.lauretto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12866161200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12891961200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>daniella.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-9356903000184 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>joao.neto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12635909500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>laerte.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12569248600000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12813564200000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12864385100000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>ariane.bottini@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12817416700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>anderson.menezes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12869273900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>karina.vieira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12223851200000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12302937300000 Nota 167 - Retorno Cobrança op53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12448063500000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12762122900000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12845237300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>ana.brito@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12697278900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>jamaica.saldanha@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12769715600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>ana.morais@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-38965870801 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12121449200000 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -655,10 +697,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -666,10 +708,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -677,10 +719,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -688,10 +730,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -699,10 +741,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -710,10 +752,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -721,10 +763,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -732,10 +774,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -743,10 +785,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -754,10 +796,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -765,10 +807,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -776,10 +818,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -787,10 +829,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -798,10 +840,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -809,10 +851,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -820,10 +862,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -831,10 +873,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -842,10 +884,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -853,10 +895,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -864,10 +906,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -875,10 +917,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -886,10 +928,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="B23" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -897,10 +939,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B24" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
@@ -908,10 +950,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B25" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -919,10 +961,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
@@ -930,10 +972,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="B27" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -941,10 +983,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="B28" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>3</v>
@@ -952,10 +994,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>55</v>
+        <v>9</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>3</v>
@@ -963,10 +1005,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>3</v>
@@ -974,10 +1016,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>3</v>
@@ -985,10 +1027,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>3</v>
@@ -996,10 +1038,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>10</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>3</v>
@@ -1010,7 +1052,7 @@
         <v>66</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>3</v>
@@ -1018,10 +1060,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>3</v>
@@ -1029,10 +1071,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>3</v>
@@ -1040,46 +1082,102 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>9</v>
+        <v>74</v>
       </c>
       <c r="B37" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38"/>
-      <c r="B38"/>
+      <c r="A38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" t="s">
+        <v>76</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39"/>
-      <c r="B39"/>
+      <c r="A39" t="s">
+        <v>74</v>
+      </c>
+      <c r="B39" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40"/>
-      <c r="B40"/>
+      <c r="A40" t="s">
+        <v>74</v>
+      </c>
+      <c r="B40" t="s">
+        <v>78</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41"/>
-      <c r="B41"/>
+      <c r="A41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41" t="s">
+        <v>79</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42"/>
-      <c r="B42"/>
+      <c r="A42" t="s">
+        <v>80</v>
+      </c>
+      <c r="B42" t="s">
+        <v>81</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43"/>
-      <c r="B43"/>
+      <c r="A43" t="s">
+        <v>82</v>
+      </c>
+      <c r="B43" t="s">
+        <v>83</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44"/>
-      <c r="B44"/>
+      <c r="A44" t="s">
+        <v>84</v>
+      </c>
+      <c r="B44" t="s">
+        <v>85</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45"/>
-      <c r="B45"/>
+      <c r="A45" t="s">
+        <v>4</v>
+      </c>
+      <c r="B45" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46"/>
@@ -1410,31 +1508,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAzNTMxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MzAvMTIvMjAyMCAxMTo0NTo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAzMC8xMi8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAzNTMxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MzAvMTIvMjAyMCAxMTo0NTo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAzMC8xMi8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DBFCB3-53E5-4527-B13D-DC7A854D4B55}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41A8E509-6991-4B84-B1B5-13851E156C6A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DBFCB3-53E5-4527-B13D-DC7A854D4B55}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Dados e Relatórios\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7127128A-41B5-4DEA-8E4C-C2CAE394A92F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{839B64BA-2A25-43F2-B02E-A3444C1EF60B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28800" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envio Robô" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="214">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -54,250 +54,685 @@
     <t>carlos.neves@allianz.com.br</t>
   </si>
   <si>
-    <t>irene.rosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>matheus.pereira@allianz.com.br</t>
-  </si>
-  <si>
     <t>jose.neves@allianz.com.br</t>
   </si>
   <si>
-    <t>caroline.wojciechowski@allianz.com.br</t>
-  </si>
-  <si>
-    <t>dimas.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>daniella.andrade@allianz.com.br</t>
-  </si>
-  <si>
-    <t>graziella.pignataro@allianz.com.br</t>
-  </si>
-  <si>
     <t>noadia.rodrigues@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12884844600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>william.bonifacio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12755419500000 Nota 595 - ERRO PDF RETORNO PDF</t>
-  </si>
-  <si>
-    <t>rosangela.silva1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12892525100000 Nota 595 - ERRO PDF RETORNO PDF</t>
-  </si>
-  <si>
-    <t>silvia.taschetti@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12723521200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>eliana.pedroso@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12769927400000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>tadeu.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12879515800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>luiz.inocente@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12789002200003 Nota 595 - ERRO PDF RETORNO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12884492500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>ana.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12891358700000 Nota 595 - ERRO PDF RETORNO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12884366700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12843474000000 Nota 595 - ERRO PDF retorno PDF</t>
-  </si>
-  <si>
-    <t>fernando.martins1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12716572500000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12716572500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>vanessa.penatti@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12887040900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>sonia.bortoleto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12893533300000 Nota 595 - ERRO PDF RETORNO PDF</t>
-  </si>
-  <si>
-    <t>tatiana.monis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12894656200000 Nota 595 - ERRO PDF RETORNO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12894647500000 Nota 595 - ERRO PDF RETORNO PDF</t>
-  </si>
-  <si>
-    <t>leandro.machado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12720961200000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
     <t>leandro.gonzaga@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12889193600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>rodrigo.kuguyama@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-88818357500000 Nota 595 - ERRO PDF RETORNO PDF</t>
-  </si>
-  <si>
-    <t>leonardo.dache@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12771844500000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>bruna.teixeira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12893012700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
     <t>flavia.costa@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12894956700000 Nota 595 - ERRO PDF Retorno PDF</t>
-  </si>
-  <si>
-    <t>rosana.teixeira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12855040400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>alciana.carlucci@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12476604100000 Nota 595 - ERRO PDF retorno pdf</t>
-  </si>
-  <si>
-    <t>marco.vita@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12892690900000 Nota 595 - ERRO PDF RETORNO PDF</t>
-  </si>
-  <si>
-    <t>jonatas.lauretto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12866161200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12891961200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>daniella.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-9356903000184 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>joao.neto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12635909500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
     <t>laerte.silva@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12569248600000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12813564200000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12864385100000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>ariane.bottini@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12817416700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>anderson.menezes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12869273900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>karina.vieira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12223851200000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12302937300000 Nota 167 - Retorno Cobrança op53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12448063500000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12762122900000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12845237300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>ana.brito@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12697278900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>jamaica.saldanha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12769715600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>ana.morais@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-38965870801 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12121449200000 Nota 242 - Retorno Cobrança</t>
+    <t>aline.nogueira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12848781700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>jocineia.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12813794700000 Nota 595 - ERRO PDF retorno PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12885784900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12889728500000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>eliane.fernandes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12893383800000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>everton.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-88818373100000 Nota 595 - ERRO PDF retorno PDF</t>
+  </si>
+  <si>
+    <t>matheus.gomes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12700125200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>crislaine.trindade@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12852774800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>juliano.guimaraes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12896017300000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>samuel.martins@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12613607100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>marco.schiabel@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12519387700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12598579600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>fernanda.braga@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12894125600000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>lidiane.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12593982900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>gisele.cardoso1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12893428400000 Nota 595 - ERRO PDF retorno PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12712675500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12894657800000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>talita.meneses@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12616839100000 Nota 595 - ERRO PDF Retorno PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12637657600000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>leandro.santos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12865472300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12893476600000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>fernanda.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12895661800000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>clarissa.cavalli@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12634558800000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>gustavo.correa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12783739300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>erineuza.monzillo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12842163700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>aline.carpes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12884512900000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>rosilene.nogueira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12894940400000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>itamar.junior@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12882709300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>lucas.godinho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12893910800000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12895267200000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>cristiane.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12845382500000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>adautina.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12897634000000 Nota 595 - ERRO PDF Retorno PDF</t>
+  </si>
+  <si>
+    <t>carla.nascimento@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12870921600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>thays.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12885018800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12893350200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>karinne.furtado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12787954100000 Nota 595 - ERRO PDF RETORN PDF</t>
+  </si>
+  <si>
+    <t>laila.steil@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12898622500000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>ana.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12489234200000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>marli.rocha@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12495330300000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>carolina.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12868513500000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12889654300000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12819236100000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12829583900000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>aline.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12806116400000 Nota 595 - ERRO PDF RETORNO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11253575800000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>backofficeseguros@vwfs.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125752396 - ALINE ARRUSSUL TORRES</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 10 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>andre.oliveira@braseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125770624 - ELENY MARIA DE SOUSA</t>
+  </si>
+  <si>
+    <t>atendimento@mplusseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125738837 - HENRIQUE JOSE DA SILVA</t>
+  </si>
+  <si>
+    <t>ro.seguros@yahoo.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126149269 - TASSIA HELENA DA SILVA OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 9 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>daniel@fernandocorretora.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126138334 - MARIO SERGIO SPOLADORE FILHO</t>
+  </si>
+  <si>
+    <t>operacional@holdcorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126776887 - MARIA BENVINDA DE ALMEIDA COSTA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>contato@verisseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127040934 - NEIDE PAES</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 6 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>ggr@ggrseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127083218 - FELIPE GUSTAVO BLOS</t>
+  </si>
+  <si>
+    <t>top.seguros@yahoo.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127079581 - DIEGO EMMANUELL RIBEIRO REIS</t>
+  </si>
+  <si>
+    <t>faleconosco@mapma.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127340306 - ANA CLAUDIA BASTOS CARDOSO</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>renovacaoseguros@honda.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127723934 - VANDERLAN DE MORAIS PINHEIRO</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>edilsonwb@hotmail.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125749431 - RENATA OKUBO</t>
+  </si>
+  <si>
+    <t>proteger@protegercorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125748535 - KARINE BRUNA PARISOTTO DELLA JUSTINA</t>
+  </si>
+  <si>
+    <t>marciodeoliveira@nuclearseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125912035 - MARIA DE LOURDES MELLO DA COSTA</t>
+  </si>
+  <si>
+    <t>chsseguros@outlook.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126093169 - CAROLINA DOURADO PADILHA DE FREITAS</t>
+  </si>
+  <si>
+    <t>mrlinscorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126134029 - EVALDO GOMES DE ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>marpeseguros@marpeseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126425083 - ELISIANE ROSSI POZZOBON</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 8 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>suporte.vvd@vwfs.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126443695 - FELIPE BARBOSA DO REGO BARROS</t>
+  </si>
+  <si>
+    <t>backofficecorretora@segurostoyota.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126740496 - NEILTON BARRETO SOCORRO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126684300 - ESTHER WAIHRICH QUEIROZ DE MENEZES</t>
+  </si>
+  <si>
+    <t>banseg@bansegseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127077654 - FERNANDA DE MASCENA ALVES SOUZA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127079691 - DELMA CREMONEZI LOMBARDI</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127093901 - ALBERIO ANTONIO DE LIMA</t>
+  </si>
+  <si>
+    <t>elittecorretora@elittecorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127071948 - KENIA WALERIA DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>atlantic.admseg@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127037871 - DIRLENE MARIA MOREIRA SILVA</t>
+  </si>
+  <si>
+    <t>diamantinaseguros@diamantinaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127408313 - LUCIVAN ALVES OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127412715 - LEANDRO DOS SANTOS SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127399505 - SOLANGE DE SOUZA OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127609885 - HELENO JOAO DA COSTA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127711479 - MARIO SERGIO SPOLADORE FILHO</t>
+  </si>
+  <si>
+    <t>agnseguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128065636 - CAMILA ESTEVES ALVES PEREIRA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 3 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>andrearosa.seguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128493373 - MIRIAM BUENO MARTINS CARNEIRO</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 2 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>benda@bendaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125719258 - ROSSANA GRANADO PONCE</t>
+  </si>
+  <si>
+    <t>casullo@casulloseguros.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125748124 - ALTAIR DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126058903 - ELIANE MACEDO RODRIGUES SILVA</t>
+  </si>
+  <si>
+    <t>ativa@ativaseguros.net</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126413093 - CARLA ANGELICA PICCININI CANOVA</t>
+  </si>
+  <si>
+    <t>adm@marconcinseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126412503 - AMANDA ALINE MACIEL GOMES</t>
+  </si>
+  <si>
+    <t>gaia@gaiaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127637017 - CRISTIANE CORDEIRO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128070630 - CLEOMAR COSMI DE FREITAS</t>
+  </si>
+  <si>
+    <t>contato@waseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126082035 - MARCIA MENDES VIRGINIO</t>
+  </si>
+  <si>
+    <t>marceloluizcoelho@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126369302 - VIRGINIA DA SILVA MESSINA</t>
+  </si>
+  <si>
+    <t>contate@gebramseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126405794 - ENIDE MARIA RIBEIRO ALVES</t>
+  </si>
+  <si>
+    <t>diferencialcorretora@uol.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126418362 - DENISE APARECIDA PEREIRA DE ANHAIA</t>
+  </si>
+  <si>
+    <t>simplusseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126427057 - ALDA MARIA BARCELLOS BRANDAO MAGALHAES</t>
+  </si>
+  <si>
+    <t>multilifeseguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126151448 - ALESSANDRA MACIEL MENDES BORGES</t>
+  </si>
+  <si>
+    <t>atendimento@bigbrasilseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126675393 - VIVIANE APARECIDA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>l3corretoraseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127264181 - ALINE RUBIA DE OLIVEIRA COSTA</t>
+  </si>
+  <si>
+    <t>petra@petraseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127345819 - CIDADE DA MODA FASHION LOCACOES DE BOX LTDA</t>
+  </si>
+  <si>
+    <t>klimaseguros@klimaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127659911 - ODETTE MINOZZO DE MATTOS</t>
+  </si>
+  <si>
+    <t>aliancadowsley@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127714653 - MARISA CLEA MORAES EUSEBIO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127718928 - WESLEI BATISTA ALMEIDA</t>
+  </si>
+  <si>
+    <t>contato@cellenceseguros.net.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126202132 - PAULO RONALDO RAMOS DE MACEDO</t>
+  </si>
+  <si>
+    <t>3pcorretora.seguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125694192 - JOSUE ALMEIDA DE SOUZA JUNIOR</t>
+  </si>
+  <si>
+    <t>contato@luganocorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125740033 - REGINA HELENA CALMON SILVA PEREIRA VAQUERO</t>
+  </si>
+  <si>
+    <t>atendimento@metacorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125918499 - JULIA FIGUEIRA MARTINS</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126098641 - RINALDO GOMES DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126084541 - RODOLPHO DE PAIVA FELIPPE</t>
+  </si>
+  <si>
+    <t>aricorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126403872 - ANA LUCIA ALMEIDA PIRES</t>
+  </si>
+  <si>
+    <t>oestefozseguros@oestefoz.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126412471 - TELMA TERESINHA FERREIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126416187 - ANTONIO EDEGLEIR FARIAS DA CRUZ</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126751425 - JOYCE HOLANDA PINHEIRO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127027395 - TERESA LOSADA VALLE</t>
+  </si>
+  <si>
+    <t>3c@seguros3c.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127336128 - SIMONE FRANCO LOBATO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127376918 - MARXSUEL ARAUJO DA SILVA</t>
+  </si>
+  <si>
+    <t>pc@lojacorr.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127837062 - BRUNO ROBERTO DA SILVA</t>
+  </si>
+  <si>
+    <t>contato@hlseguroscorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128344086 - KAMILLA RAQUEL SILVA</t>
+  </si>
+  <si>
+    <t>parvicorretorama@parvicorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128419156 - JOSE MARCELO DE OLIVEIRA</t>
   </si>
 </sst>
 </file>
@@ -678,7 +1113,7 @@
   <cols>
     <col min="1" max="1" width="55.5703125" style="2" customWidth="1"/>
     <col min="2" max="2" width="101.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="97.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="255.7109375" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="9.42578125" style="2"/>
     <col min="7" max="7" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9.42578125" style="2"/>
@@ -697,10 +1132,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -708,10 +1143,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -719,10 +1154,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -730,10 +1165,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -741,10 +1176,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -752,10 +1187,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -763,10 +1198,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -774,10 +1209,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -785,10 +1220,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -796,10 +1231,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -807,10 +1242,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -818,10 +1253,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -832,7 +1267,7 @@
         <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -840,10 +1275,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B15" t="s">
         <v>34</v>
-      </c>
-      <c r="B15" t="s">
-        <v>35</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -851,10 +1286,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>35</v>
+      </c>
+      <c r="B16" t="s">
         <v>36</v>
-      </c>
-      <c r="B16" t="s">
-        <v>37</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -862,10 +1297,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -873,10 +1308,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -884,10 +1319,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -895,10 +1330,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -906,10 +1341,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -917,10 +1352,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -928,10 +1363,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -939,10 +1374,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B24" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
@@ -950,10 +1385,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B25" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -961,10 +1396,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B26" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
@@ -972,10 +1407,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B27" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -983,10 +1418,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="B28" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>3</v>
@@ -994,10 +1429,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="B29" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>3</v>
@@ -1005,10 +1440,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="B30" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>3</v>
@@ -1016,10 +1451,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>64</v>
+        <v>8</v>
       </c>
       <c r="B31" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>3</v>
@@ -1027,10 +1462,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B32" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>3</v>
@@ -1038,10 +1473,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>10</v>
+        <v>64</v>
       </c>
       <c r="B33" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>3</v>
@@ -1052,7 +1487,7 @@
         <v>66</v>
       </c>
       <c r="B34" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>3</v>
@@ -1060,10 +1495,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>3</v>
@@ -1071,10 +1506,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>3</v>
@@ -1082,10 +1517,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B37" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>3</v>
@@ -1093,10 +1528,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>73</v>
+      </c>
+      <c r="B38" t="s">
         <v>74</v>
-      </c>
-      <c r="B38" t="s">
-        <v>76</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>3</v>
@@ -1104,10 +1539,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B39" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>3</v>
@@ -1115,7 +1550,7 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B40" t="s">
         <v>78</v>
@@ -1126,10 +1561,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>11</v>
+        <v>79</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>3</v>
@@ -1137,7 +1572,7 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="B42" t="s">
         <v>81</v>
@@ -1148,10 +1583,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>9</v>
+      </c>
+      <c r="B43" t="s">
         <v>82</v>
-      </c>
-      <c r="B43" t="s">
-        <v>83</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>3</v>
@@ -1159,10 +1594,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>84</v>
+        <v>9</v>
       </c>
       <c r="B44" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>3</v>
@@ -1170,286 +1605,762 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>84</v>
+      </c>
+      <c r="B45" t="s">
+        <v>85</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>4</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B46" t="s">
         <v>86</v>
       </c>
-      <c r="C45" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46"/>
-      <c r="B46"/>
+      <c r="C46" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47"/>
-      <c r="B47"/>
+      <c r="A47" t="s">
+        <v>87</v>
+      </c>
+      <c r="B47" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48"/>
-      <c r="B48"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49"/>
-      <c r="B49"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50"/>
-      <c r="B50"/>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51"/>
-      <c r="B51"/>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52"/>
-      <c r="B52"/>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53"/>
-      <c r="B53"/>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54"/>
-      <c r="B54"/>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55"/>
-      <c r="B55"/>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56"/>
-      <c r="B56"/>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57"/>
-      <c r="B57"/>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58"/>
-      <c r="B58"/>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59"/>
-      <c r="B59"/>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60"/>
-      <c r="B60"/>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61"/>
-      <c r="B61"/>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62"/>
-      <c r="B62"/>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63"/>
-      <c r="B63"/>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64"/>
-      <c r="B64"/>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65"/>
-      <c r="B65"/>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66"/>
-      <c r="B66"/>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67"/>
-      <c r="B67"/>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68"/>
-      <c r="B68"/>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69"/>
-      <c r="B69"/>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70"/>
-      <c r="B70"/>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71"/>
-      <c r="B71"/>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72"/>
-      <c r="B72"/>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73"/>
-      <c r="B73"/>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74"/>
-      <c r="B74"/>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75"/>
-      <c r="B75"/>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76"/>
-      <c r="B76"/>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77"/>
-      <c r="B77"/>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78"/>
-      <c r="B78"/>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79"/>
-      <c r="B79"/>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80"/>
-      <c r="B80"/>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81"/>
-      <c r="B81"/>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82"/>
-      <c r="B82"/>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83"/>
-      <c r="B83"/>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84"/>
-      <c r="B84"/>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85"/>
-      <c r="B85"/>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86"/>
-      <c r="B86"/>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87"/>
-      <c r="B87"/>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88"/>
-      <c r="B88"/>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89"/>
-      <c r="B89"/>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90"/>
-      <c r="B90"/>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91"/>
-      <c r="B91"/>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92"/>
-      <c r="B92"/>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93"/>
-      <c r="B93"/>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94"/>
-      <c r="B94"/>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95"/>
-      <c r="B95"/>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96"/>
-      <c r="B96"/>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97"/>
-      <c r="B97"/>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98"/>
-      <c r="B98"/>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99"/>
-      <c r="B99"/>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100"/>
-      <c r="B100"/>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101"/>
-      <c r="B101"/>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102"/>
-      <c r="B102"/>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103"/>
-      <c r="B103"/>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104"/>
-      <c r="B104"/>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105"/>
-      <c r="B105"/>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106"/>
-      <c r="B106"/>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107"/>
-      <c r="B107"/>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108"/>
-      <c r="B108"/>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109"/>
-      <c r="B109"/>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110"/>
-      <c r="B110"/>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111"/>
-      <c r="B111"/>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112"/>
-      <c r="B112"/>
+      <c r="A48" t="s">
+        <v>90</v>
+      </c>
+      <c r="B48" t="s">
+        <v>91</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>92</v>
+      </c>
+      <c r="B49" t="s">
+        <v>93</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>94</v>
+      </c>
+      <c r="B50" t="s">
+        <v>95</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>97</v>
+      </c>
+      <c r="B51" t="s">
+        <v>98</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>99</v>
+      </c>
+      <c r="B52" t="s">
+        <v>100</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>102</v>
+      </c>
+      <c r="B53" t="s">
+        <v>103</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>105</v>
+      </c>
+      <c r="B54" t="s">
+        <v>106</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>107</v>
+      </c>
+      <c r="B55" t="s">
+        <v>108</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>109</v>
+      </c>
+      <c r="B56" t="s">
+        <v>110</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>112</v>
+      </c>
+      <c r="B57" t="s">
+        <v>113</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>115</v>
+      </c>
+      <c r="B58" t="s">
+        <v>116</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>117</v>
+      </c>
+      <c r="B59" t="s">
+        <v>118</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>119</v>
+      </c>
+      <c r="B60" t="s">
+        <v>120</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>121</v>
+      </c>
+      <c r="B61" t="s">
+        <v>122</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>123</v>
+      </c>
+      <c r="B62" t="s">
+        <v>124</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>125</v>
+      </c>
+      <c r="B63" t="s">
+        <v>126</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>128</v>
+      </c>
+      <c r="B64" t="s">
+        <v>129</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>130</v>
+      </c>
+      <c r="B65" t="s">
+        <v>131</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>130</v>
+      </c>
+      <c r="B66" t="s">
+        <v>132</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>133</v>
+      </c>
+      <c r="B67" t="s">
+        <v>134</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>112</v>
+      </c>
+      <c r="B68" t="s">
+        <v>135</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>112</v>
+      </c>
+      <c r="B69" t="s">
+        <v>136</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>137</v>
+      </c>
+      <c r="B70" t="s">
+        <v>138</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>139</v>
+      </c>
+      <c r="B71" t="s">
+        <v>140</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>141</v>
+      </c>
+      <c r="B72" t="s">
+        <v>142</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>112</v>
+      </c>
+      <c r="B73" t="s">
+        <v>143</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>128</v>
+      </c>
+      <c r="B74" t="s">
+        <v>144</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>112</v>
+      </c>
+      <c r="B75" t="s">
+        <v>145</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>97</v>
+      </c>
+      <c r="B76" t="s">
+        <v>146</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>147</v>
+      </c>
+      <c r="B77" t="s">
+        <v>148</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>150</v>
+      </c>
+      <c r="B78" t="s">
+        <v>151</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>153</v>
+      </c>
+      <c r="B79" t="s">
+        <v>154</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>155</v>
+      </c>
+      <c r="B80" t="s">
+        <v>156</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>128</v>
+      </c>
+      <c r="B81" t="s">
+        <v>157</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>158</v>
+      </c>
+      <c r="B82" t="s">
+        <v>159</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>160</v>
+      </c>
+      <c r="B83" t="s">
+        <v>161</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>162</v>
+      </c>
+      <c r="B84" t="s">
+        <v>163</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>112</v>
+      </c>
+      <c r="B85" t="s">
+        <v>164</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>165</v>
+      </c>
+      <c r="B86" t="s">
+        <v>166</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>167</v>
+      </c>
+      <c r="B87" t="s">
+        <v>168</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>169</v>
+      </c>
+      <c r="B88" t="s">
+        <v>170</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>171</v>
+      </c>
+      <c r="B89" t="s">
+        <v>172</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>173</v>
+      </c>
+      <c r="B90" t="s">
+        <v>174</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>175</v>
+      </c>
+      <c r="B91" t="s">
+        <v>176</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>177</v>
+      </c>
+      <c r="B92" t="s">
+        <v>178</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>179</v>
+      </c>
+      <c r="B93" t="s">
+        <v>180</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>181</v>
+      </c>
+      <c r="B94" t="s">
+        <v>182</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>183</v>
+      </c>
+      <c r="B95" t="s">
+        <v>184</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>185</v>
+      </c>
+      <c r="B96" t="s">
+        <v>186</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>112</v>
+      </c>
+      <c r="B97" t="s">
+        <v>187</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>188</v>
+      </c>
+      <c r="B98" t="s">
+        <v>189</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>190</v>
+      </c>
+      <c r="B99" t="s">
+        <v>191</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>192</v>
+      </c>
+      <c r="B100" t="s">
+        <v>193</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>194</v>
+      </c>
+      <c r="B101" t="s">
+        <v>195</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>128</v>
+      </c>
+      <c r="B102" t="s">
+        <v>196</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>94</v>
+      </c>
+      <c r="B103" t="s">
+        <v>197</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>198</v>
+      </c>
+      <c r="B104" t="s">
+        <v>199</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>200</v>
+      </c>
+      <c r="B105" t="s">
+        <v>201</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>112</v>
+      </c>
+      <c r="B106" t="s">
+        <v>202</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>112</v>
+      </c>
+      <c r="B107" t="s">
+        <v>203</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>130</v>
+      </c>
+      <c r="B108" t="s">
+        <v>204</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>205</v>
+      </c>
+      <c r="B109" t="s">
+        <v>206</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>112</v>
+      </c>
+      <c r="B110" t="s">
+        <v>207</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>208</v>
+      </c>
+      <c r="B111" t="s">
+        <v>209</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>210</v>
+      </c>
+      <c r="B112" t="s">
+        <v>211</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113"/>
-      <c r="B113"/>
+      <c r="A113" t="s">
+        <v>212</v>
+      </c>
+      <c r="B113" t="s">
+        <v>213</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114"/>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Dados e Relatórios\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74D38BFE-917F-42B7-9069-110A38CBD6DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB6FC12B-5A2E-4342-A5ED-923B847168E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28950" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envio Robô" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="162">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -51,241 +51,532 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>carlos.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>daniel.lourenco@allianz.com.br</t>
-  </si>
-  <si>
     <t>patricia.reis@allianz.com.br</t>
   </si>
   <si>
-    <t>fabio.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>rosangela.silva1@allianz.com.br</t>
-  </si>
-  <si>
     <t>rodrigo.kuguyama@allianz.com.br</t>
   </si>
   <si>
-    <t>marcus.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>fernanda.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>rafaela.jeronimo@allianz.com.br</t>
-  </si>
-  <si>
     <t>weldja.bozi@allianz.com.br</t>
   </si>
   <si>
-    <t>rodrigo.amorim@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12861590000000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12900938700000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12752055500000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12899842100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12901885100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>valeria.palhares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12852509600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>matheus.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12869393700000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>alex.grabowski@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12895698800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>kaue.medeiros@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12898558200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>renata.matheus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12896344100000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>carla.ventura@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12838260500000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>douglas.morais@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12894191900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12805702883 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>priscila.rubio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12889621500000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>claudia.pires@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12899319700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-88818389400000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>fernanda.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12677159800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12900693900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>rodrigo.deus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12897246700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
     <t>itamar.junior@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12421966400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12844478300000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>josiane.vilarinho@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12886468100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>flavia.costa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12771115400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12898940200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>rosana.teixeira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12887929200000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>monica.plassa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12896660200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>deise.santos@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12727025800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12821741700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>alciana.carlucci@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12669859600000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12904458600000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>carla.nascimento@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12870921600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>jacqueline.mendes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12502731500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12806453500000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12842698100000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>joao.neto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-6457314554 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>rosemeire.faria@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12692446600000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12841995400000 Nota 167 - Retorno Cobrança op53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12885341200000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>marcos.penachioni@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12880289000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>aline.lima@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12638555800000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12866053400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>guilherme.teodoro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12883776600000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12512484500000 Nota 242 - Retorno Cobrança</t>
+    <t>kaue.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12901555900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>adriano.guerra@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12895866100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12637016700000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12898460800000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12902046100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12904693100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>renata.vidigal@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12661508600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>juliano.guimaraes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12899973200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>eduardo.olicshevis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12877363800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>fausto.reis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12877334900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>ana.sales@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12899633700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>bruno.castro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12655536600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>vanessa.penatti@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12876247100077 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>gisele.cardoso1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-7983903000189 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12901990700000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>leandro.gonzaga@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12902407800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12730980000005 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>leandro.santos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12904378300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-88818417500000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>andreia.brixner@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12903534700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>leonardo.dache@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12907173500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>vitor.mattos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12717455400000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>gustavo.correa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12805129700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>ana.guanais@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12899634100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>bruno.rosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12887272300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>andreia.cardias@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12904732400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12615997700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>renato.faillace@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12696791800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12798012300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>lucas.godinho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-88818412700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12897400300000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12902930800000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>raullison.castro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12776424900000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>karinne.furtado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12906410700000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>viviane.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-60485825015 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12875635400000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>ana.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12901744100000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12905839300000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>daniella.andrade@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12858402100000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12837689300000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12866009000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>antonio.rodrigues1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12839908200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>vanessa.almeida1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-5886051902 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>carla.valnisio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12725981500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>grandevitoria@gvcorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125859162 - ANDRE BARBOSA DE SOUZA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 10 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>diana@diamanteseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125866804 - JOSE JOAO EUFRASIO</t>
+  </si>
+  <si>
+    <t>fabio@milaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126148685 - DENIS CARREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 9 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>renovacaoseguros@honda.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126234530 - OLAVO GONZAGA DE OLIVEIRA JUNIOR</t>
+  </si>
+  <si>
+    <t>thomaz@thomaz.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126471989 - MARIA BETHANIA BARBALHO DE AZEVEDO RODRIGUES</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 8 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>suporte.vvd@vwfs.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126526090 - MARINETE DE MELO GOES</t>
+  </si>
+  <si>
+    <t>patricia@djseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126533548 - ISABELLA FIORETTI ACHITTI</t>
+  </si>
+  <si>
+    <t>backofficecorretora@segurostoyota.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126534203 - ARIELE AURORA ALMEIDA MOREIRA DA ROSA</t>
+  </si>
+  <si>
+    <t>atendimento@projacseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126745981 - FERNANDA VIANA DE ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127176386 - NATALIA RIBEIRO DOREA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 6 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>corretora@costaecarminati.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127159306 - FABIO FOLLADOR MURTA</t>
+  </si>
+  <si>
+    <t>faleconosco@mapma.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127386311 - GUAJARINA GUALBERTO DA SILVA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>administrativo@g4c.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127455371 - JOAO BOSCO NASCIMENTO DE SOUZA SANTOS</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127494722 - JOAO JANUARIO DE SOUZA</t>
+  </si>
+  <si>
+    <t>contato@valdirenecorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128189464 - LORENA RABARCHI GRACIANO</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 3 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>paulo.macedo@macedoseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125764548 - JOSIBERTO CARLOS MELO DE FIGUEIREDO</t>
+  </si>
+  <si>
+    <t>contato@ricknewseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125823505 - VIRGINIA GONCALVES CAMARGOS RIBEIRO</t>
+  </si>
+  <si>
+    <t>ermaria.gomes@theodoroseguros.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126146211 - MAGNO ROSAS CARNEIRO</t>
+  </si>
+  <si>
+    <t>cfseguros1@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126204743 - CLOVES FERNANDES DA SILVA</t>
+  </si>
+  <si>
+    <t>ivoneide@caraibaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126220796 - MARCONE DA SILVA LOPES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126523060 - ANTONIO FLAVIO RODRIGUES DE AZEVEDO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126520536 - GUILHERME HENRIQUE NEUMANN</t>
+  </si>
+  <si>
+    <t>gislene@cvseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126530735 - AE YOUNG HAN</t>
+  </si>
+  <si>
+    <t>adm@segurotranquilo.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126766500 - NADIA MARCELLINO CANDIDO</t>
+  </si>
+  <si>
+    <t>karen@schneidseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126789863 - KAREN BORGES SCHNEID</t>
+  </si>
+  <si>
+    <t>ultimoseguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126833179 - FABIANA HERNANDES MERIGHI PREZA</t>
+  </si>
+  <si>
+    <t>diamantinaseguros@diamantinaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126810122 - GISLAINE APARECIDA DA CRUZ OLIVEIRA</t>
+  </si>
+  <si>
+    <t>backoffice.corretora@yamaha-motor.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127164862 - ISAQUE GALDINO DE CARVALHO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127146764 - PAULO AUGUSTO DO NASCIMENTO LIMA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127232755 - LUDMILLA DA SILVA CAMARAO CABRAL</t>
+  </si>
+  <si>
+    <t>alliancaseguros1@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127442123 - RAFAELA DANTAS DINIZ MORAES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127464677 - CPMX CONSULTORIA IMOBILIARIA LTDA ME</t>
+  </si>
+  <si>
+    <t>npseguros@uol.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127498372 - SILVIA MARIA MAGALHAES DE SOUZA</t>
+  </si>
+  <si>
+    <t>atendimento@wacor.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127791365 - FLAVIA MARIA DE LIMA CAVALCANTE</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>camilo@riosegon.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127946229 - JOSE LUIS BUENO DE CAMPOS</t>
+  </si>
+  <si>
+    <t>contato@foster.seg.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127968835 - ROSA LIANE KLEIN STANKOWSKI</t>
+  </si>
+  <si>
+    <t>bhrseguros@bhr.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128080004 - ROSEMEIRE APARECIDA PICORELI DE SOUZA</t>
+  </si>
+  <si>
+    <t>renovacao@volantseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128588263 - NEYRISLAINE LOURES FERREIRA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 2 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
   </si>
 </sst>
 </file>
@@ -685,10 +976,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -696,10 +987,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" t="s">
         <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -707,10 +998,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -718,10 +1009,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -729,10 +1020,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -740,10 +1031,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -751,10 +1042,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -762,10 +1053,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -773,10 +1064,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -784,10 +1075,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -795,10 +1086,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -806,10 +1097,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -817,10 +1108,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -828,10 +1119,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -839,10 +1130,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -850,10 +1141,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -861,10 +1152,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -872,10 +1163,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" t="s">
         <v>40</v>
-      </c>
-      <c r="B19" t="s">
-        <v>42</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -883,10 +1174,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -894,10 +1185,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -905,10 +1196,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>7</v>
+        <v>44</v>
       </c>
       <c r="B22" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -916,10 +1207,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -927,10 +1218,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B24" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
@@ -941,7 +1232,7 @@
         <v>50</v>
       </c>
       <c r="B25" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -949,10 +1240,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" t="s">
         <v>53</v>
-      </c>
-      <c r="B26" t="s">
-        <v>54</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
@@ -960,10 +1251,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>54</v>
+      </c>
+      <c r="B27" t="s">
         <v>55</v>
-      </c>
-      <c r="B27" t="s">
-        <v>56</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -971,10 +1262,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>57</v>
+        <v>7</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>3</v>
@@ -982,10 +1273,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>57</v>
       </c>
       <c r="B29" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>3</v>
@@ -993,10 +1284,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B30" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>3</v>
@@ -1004,10 +1295,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="B31" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>3</v>
@@ -1015,10 +1306,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>63</v>
+        <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>3</v>
@@ -1026,10 +1317,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>65</v>
+        <v>8</v>
       </c>
       <c r="B33" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>3</v>
@@ -1037,10 +1328,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>3</v>
@@ -1048,10 +1339,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="B35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>3</v>
@@ -1059,10 +1350,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" t="s">
         <v>69</v>
-      </c>
-      <c r="B36" t="s">
-        <v>70</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>3</v>
@@ -1070,10 +1361,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="B37" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>3</v>
@@ -1081,10 +1372,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="B38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>3</v>
@@ -1092,10 +1383,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>71</v>
+        <v>9</v>
       </c>
       <c r="B39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>3</v>
@@ -1103,10 +1394,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>74</v>
+      </c>
+      <c r="B40" t="s">
         <v>75</v>
-      </c>
-      <c r="B40" t="s">
-        <v>76</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>3</v>
@@ -1114,10 +1405,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>77</v>
+        <v>10</v>
       </c>
       <c r="B41" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>3</v>
@@ -1125,10 +1416,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42" t="s">
         <v>77</v>
-      </c>
-      <c r="B42" t="s">
-        <v>79</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>3</v>
@@ -1136,10 +1427,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B43" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>3</v>
@@ -1147,220 +1438,493 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="B44" t="s">
+        <v>81</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>82</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45"/>
-      <c r="B45"/>
+      <c r="B45" t="s">
+        <v>83</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46"/>
-      <c r="B46"/>
+      <c r="A46" t="s">
+        <v>84</v>
+      </c>
+      <c r="B46" t="s">
+        <v>85</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47"/>
-      <c r="B47"/>
+      <c r="A47" t="s">
+        <v>87</v>
+      </c>
+      <c r="B47" t="s">
+        <v>88</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48"/>
-      <c r="B48"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49"/>
-      <c r="B49"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50"/>
-      <c r="B50"/>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51"/>
-      <c r="B51"/>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52"/>
-      <c r="B52"/>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53"/>
-      <c r="B53"/>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54"/>
-      <c r="B54"/>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55"/>
-      <c r="B55"/>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56"/>
-      <c r="B56"/>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57"/>
-      <c r="B57"/>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58"/>
-      <c r="B58"/>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59"/>
-      <c r="B59"/>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60"/>
-      <c r="B60"/>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61"/>
-      <c r="B61"/>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62"/>
-      <c r="B62"/>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63"/>
-      <c r="B63"/>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64"/>
-      <c r="B64"/>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65"/>
-      <c r="B65"/>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66"/>
-      <c r="B66"/>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67"/>
-      <c r="B67"/>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68"/>
-      <c r="B68"/>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69"/>
-      <c r="B69"/>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70"/>
-      <c r="B70"/>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71"/>
-      <c r="B71"/>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72"/>
-      <c r="B72"/>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73"/>
-      <c r="B73"/>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74"/>
-      <c r="B74"/>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75"/>
-      <c r="B75"/>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76"/>
-      <c r="B76"/>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77"/>
-      <c r="B77"/>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78"/>
-      <c r="B78"/>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79"/>
-      <c r="B79"/>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80"/>
-      <c r="B80"/>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81"/>
-      <c r="B81"/>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82"/>
-      <c r="B82"/>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83"/>
-      <c r="B83"/>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>89</v>
+      </c>
+      <c r="B48" t="s">
+        <v>90</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>92</v>
+      </c>
+      <c r="B49" t="s">
+        <v>93</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>94</v>
+      </c>
+      <c r="B50" t="s">
+        <v>95</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>97</v>
+      </c>
+      <c r="B51" t="s">
+        <v>98</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>99</v>
+      </c>
+      <c r="B52" t="s">
+        <v>100</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>101</v>
+      </c>
+      <c r="B53" t="s">
+        <v>102</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>103</v>
+      </c>
+      <c r="B54" t="s">
+        <v>104</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>101</v>
+      </c>
+      <c r="B55" t="s">
+        <v>106</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>108</v>
+      </c>
+      <c r="B56" t="s">
+        <v>109</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>110</v>
+      </c>
+      <c r="B57" t="s">
+        <v>111</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>113</v>
+      </c>
+      <c r="B58" t="s">
+        <v>114</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>103</v>
+      </c>
+      <c r="B59" t="s">
+        <v>115</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>116</v>
+      </c>
+      <c r="B60" t="s">
+        <v>117</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>119</v>
+      </c>
+      <c r="B61" t="s">
+        <v>120</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>121</v>
+      </c>
+      <c r="B62" t="s">
+        <v>122</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>123</v>
+      </c>
+      <c r="B63" t="s">
+        <v>124</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>125</v>
+      </c>
+      <c r="B64" t="s">
+        <v>126</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>127</v>
+      </c>
+      <c r="B65" t="s">
+        <v>128</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>97</v>
+      </c>
+      <c r="B66" t="s">
+        <v>129</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>101</v>
+      </c>
+      <c r="B67" t="s">
+        <v>130</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>131</v>
+      </c>
+      <c r="B68" t="s">
+        <v>132</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>133</v>
+      </c>
+      <c r="B69" t="s">
+        <v>134</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>135</v>
+      </c>
+      <c r="B70" t="s">
+        <v>136</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>137</v>
+      </c>
+      <c r="B71" t="s">
+        <v>138</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>139</v>
+      </c>
+      <c r="B72" t="s">
+        <v>140</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>141</v>
+      </c>
+      <c r="B73" t="s">
+        <v>142</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>141</v>
+      </c>
+      <c r="B74" t="s">
+        <v>143</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>92</v>
+      </c>
+      <c r="B75" t="s">
+        <v>144</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>145</v>
+      </c>
+      <c r="B76" t="s">
+        <v>146</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>101</v>
+      </c>
+      <c r="B77" t="s">
+        <v>147</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>148</v>
+      </c>
+      <c r="B78" t="s">
+        <v>149</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>150</v>
+      </c>
+      <c r="B79" t="s">
+        <v>151</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>153</v>
+      </c>
+      <c r="B80" t="s">
+        <v>154</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>155</v>
+      </c>
+      <c r="B81" t="s">
+        <v>156</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>157</v>
+      </c>
+      <c r="B82" t="s">
+        <v>158</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>159</v>
+      </c>
+      <c r="B83" t="s">
+        <v>160</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84"/>
       <c r="B84"/>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85"/>
       <c r="B85"/>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86"/>
       <c r="B86"/>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87"/>
       <c r="B87"/>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88"/>
       <c r="B88"/>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89"/>
       <c r="B89"/>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90"/>
       <c r="B90"/>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91"/>
       <c r="B91"/>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92"/>
       <c r="B92"/>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93"/>
       <c r="B93"/>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94"/>
       <c r="B94"/>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95"/>
       <c r="B95"/>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96"/>
       <c r="B96"/>
     </row>
@@ -1489,31 +2053,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAzNTMxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MzAvMTIvMjAyMCAxMTo0NTo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAzMC8xMi8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41A8E509-6991-4B84-B1B5-13851E156C6A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DBFCB3-53E5-4527-B13D-DC7A854D4B55}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41A8E509-6991-4B84-B1B5-13851E156C6A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Dados e Relatórios\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46096B8-854C-4BCD-8DA5-EC6F50A50619}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB6298A9-78C9-449B-A42D-BC3828B446DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28800" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envio Robô" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="214">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -54,460 +54,685 @@
     <t>patricia.reis@allianz.com.br</t>
   </si>
   <si>
-    <t>weldja.bozi@allianz.com.br</t>
-  </si>
-  <si>
     <t>rosemeire.faria@allianz.com.br</t>
   </si>
   <si>
-    <t>kaue.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>juliano.guimaraes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>vanessa.penatti@allianz.com.br</t>
-  </si>
-  <si>
     <t>gisele.cardoso1@allianz.com.br</t>
   </si>
   <si>
-    <t>ana.guanais@allianz.com.br</t>
-  </si>
-  <si>
     <t>viviane.silva@allianz.com.br</t>
   </si>
   <si>
-    <t>daniella.andrade@allianz.com.br</t>
-  </si>
-  <si>
-    <t>aparecida.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12616292900000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>rodrigo.amorim@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12904161000000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>luciana.mayer@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12904859600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12905951500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>rosiane.honorato@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12907276000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12908695500000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>daniel.lourenco@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12898352500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>tadeu.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12907762000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>lucineide.medeiros@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12893722100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>rubiane.bendlin@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12895841800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12819236100000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12902046100000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>caroline.falcao@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12907405400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12907423500000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12907427400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12907433400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12907440400000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12906004600000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12907702300000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
     <t>fernando.duque@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12898492900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>rosalia.branco@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12908709500000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>claudia.malaggi@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-88818425600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>raquel.sech@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12768863700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daniel.iarrocheski@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12909813700000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>flavio.cesar@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12787855500000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
     <t>daniela.leal@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12908684400000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>adriana.silveira1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12908923400000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>karina.barros@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12897795200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12904712600000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
     <t>vanessa.campos@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12907375200000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12907494600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>yuri.santos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12657966200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>adriana.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12906391300000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>priscila.sousa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12906569100000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>fernando.martins1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12908684900000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
     <t>Retorno de GO referência-12863435100000 Nota 7022 - Help Desk</t>
   </si>
   <si>
-    <t>priscila.santana@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12907146000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12907666500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>tatiana.monis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12908439200000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>gisele.mazzucco@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12906947400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12685049800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12908988500000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
     <t>leandro.machado@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12904533800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
     <t>mayara.sampaio@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12908141500000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>isabel.cit@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12697066600000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12907899900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
     <t>armando.filho@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12906565900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12907681500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>daiane.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12898654100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12898685100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12905791000000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>laiane.martins@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12908262500000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>andrea.duarte@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12638718000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>claudia.assuncao@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12904881000000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>danilo.ruas@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12880009200000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>cassia.souza@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12745489200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12671171100000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12896989400000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12905599500000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12906311800000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12907337000000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12907924300000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>lucas.monteiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12537057900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>geiza.vinand@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12909146200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>leticia.bezerra@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12907062500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
     <t>thays.silva@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12908299200000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>fabiola.caixeta@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12909024200000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12909100200000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>enriete.saucedo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12854184600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12895876100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12902730700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12545329700000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>lucidene.santana@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12562235000000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
     <t>ivone.jesus@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12620132800000 Nota 167 - Retorno Cobrança op53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12738137800000 Nota 167 - Retorno Cobrança op53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12790595700000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
     <t>rogerio.souza@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12824456700000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12833037000000 Nota 167 - Retorno Cobrança op53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12842080500000 Nota 167 - Retorno Cobrança op53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12844156700000 Nota 167 - Retorno Cobrança op53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12881981300000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12884130000000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12898990700000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>cristiane.lozano@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12899824000000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>marli.rocha@allianz.com.br</t>
-  </si>
-  <si>
     <t>Retorno de GO referência-12901476400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12901933200000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12903687700000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12904170000000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12473197100000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>danieli.ferreira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12891422700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>graziella.pignataro@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12903630100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>juliana.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12904856400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>rosangela.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-9225402848 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12911708400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>matheus.gomes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12894946700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>adriano.guerra@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12806184500000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>irene.rosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12899637300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12907974100000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>valeria.palhares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12492088100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12899201900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>edirilsa.bastos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12908393400000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>danillo.boem@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12875972200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12909028800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12906751800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12911351000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12911486700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>allan.soares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12601568800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>sonia.bortoleto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12910283500000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>renata.matheus@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12747978800000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>elisangela.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12910399800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>caroline.wojciechowski@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12907991800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12908212000000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12908267100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12909522400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12909544800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12910283000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12909549400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>andriele.pala@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12905242600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12905260000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12906359500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12907528400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12907529600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12908753500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>alan.peter@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12896443400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>viviane.corbari@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12906762900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>vitor.mattos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12909084200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12910659900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>bruno.rosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12893962000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>aline.carpes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12910157900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>alexia.fernandes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12906347700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>fabio.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12910653800000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>flavia.costa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12579010900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>raphael.callado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12801284000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>raullison.castro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12911952300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12723354000000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12895552700000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12899245600000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12901246300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12905278200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12906278200000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12906507800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12906918800000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12907615200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12907623200000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12907770800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12908485100000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12908576800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12908641700000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12908949300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12909308100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12911191700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>cristiane.konrad@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12439446900000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12911839900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12908809500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12910618400000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>ana.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12487590800000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12643145400000 Nota 167 - Retorno Cobrança op53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12663108800000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12836163700000 Nota 167 - Retorno Cobrança op53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12896380800000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12896443400000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>carolina.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12897747300000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>claudenice.barbosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12899245600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12906347700000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12909473100000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>karla.cunha@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12861402800000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12861450900000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12862170400000 Nota 167 - Retorno Cobrança op53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12862236800000 Nota 167 - Retorno Cobrança op53</t>
+  </si>
+  <si>
+    <t>laerte.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12875780600000 Nota 167 - Retorno Cobrança op53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12907829600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>karina.vieira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12302937300000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12340783000000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12792564300000 Nota 167 - Retorno Cobrança op53</t>
+  </si>
+  <si>
+    <t>ana.costa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12911223000000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>carla.valnisio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12794339400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>contato@jpnseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126117274 - CARLOS JOSE CORDEIRO DA SILVA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 9 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>escritorioseguros@terra.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126210912 - CLAUDIO NIHUES NETO</t>
+  </si>
+  <si>
+    <t>pacelli_seguros@yahoo.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126240198 - FLAVIO REIS DA SILVA</t>
+  </si>
+  <si>
+    <t>wnfernandes2@yahoo.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126199319 - ROBERTO PINHO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>freitasbritocorretora@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126347584 - SOSTENES COSTA OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 8 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>contatoseguros.adm@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126536280 - TREVISAN COMERCIO DE ALIMENTOS LTDA ME</t>
+  </si>
+  <si>
+    <t>luizalbertodionysio56@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126538894 - ADRIANO FREIRE DIONYSIO</t>
+  </si>
+  <si>
+    <t>renovacaoseguros@honda.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126883392 - KELLY ANTUNES</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126861536 - MARIA DAS GRACAS ZENI DE SOUZA</t>
+  </si>
+  <si>
+    <t>backofficecorretora@segurostoyota.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127163191 - MIRELLA ALBUQUERQUE SOUSA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 6 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>protecta@protectaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127161511 - RAYZA OLIVEIRA ECHEVERRIA</t>
+  </si>
+  <si>
+    <t>suporte.vvd@vwfs.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127158524 - MIRIAM YAMAZAKI PEZZOTTA</t>
+  </si>
+  <si>
+    <t>qualities.seguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127500888 - DANIEL DE ANDRADE FERNANDES</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>allianz@redelojacorr.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127824531 - LUCIA RODRIGUES TOMAZ</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>contate@gebramseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127811818 - RODRIGO MUKAI DE ANDRADE ROSA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128209743 - LUANA DOS SANTOS SILVA NOGUEIRA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 3 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>reinaldo.alves@carmais.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128210020 - DARIO GOMES DE CASTRO</t>
+  </si>
+  <si>
+    <t>barralife.contato@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126548932 - MARIA DE OLIVEIRA CASTRO</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 2 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>valencioseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125867654 - ROGERIO FERREIRA TERRA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 10 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>veragomes@veracorr.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125888994 - MERION SIQUEIRA FREITAS</t>
+  </si>
+  <si>
+    <t>degasperi@mhnet.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126203764 - DUETTO MODAS CONFECCOES E CALCADOS LTDA EPP</t>
+  </si>
+  <si>
+    <t>cadastro@alexandrerenault.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126213065 - ISABELA DA CUNHA MELO</t>
+  </si>
+  <si>
+    <t>chsseguros@outlook.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126233995 - VANIA PAULA BERTAQUE</t>
+  </si>
+  <si>
+    <t>adm.cotraseg@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126231092 - LORRANY THALINE SOARES MAMAO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126239178 - ANA SORAIA ALVES NOBREGA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126245330 - RAFAEL SILVA DE JESUS</t>
+  </si>
+  <si>
+    <t>valdenicio@ponteslifeseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126247031 - LUIZ ALBERTO SAFADI</t>
+  </si>
+  <si>
+    <t>supremasegurosmuriae@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126227585 - MEKIANNE APARECIDA DE MATTOS</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126534206 - ETIENE ALVES DA ROCHA GUSMAO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126866523 - CRISTINA BRONZATO BUENO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127176963 - HUELIGTON PEREIRA DE MELO</t>
+  </si>
+  <si>
+    <t>rogerio@bw4seguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127173235 - DAYANE DA SILVA RODRIGUES DAMACENO</t>
+  </si>
+  <si>
+    <t>jeferson.beltran@beltrancorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127276115 - MARIA DA GRACA GOMES VAZ</t>
+  </si>
+  <si>
+    <t>pendencias@rbmseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127480986 - VALMIR BARZAN</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127499979 - ALBERTO GONCALVES BRASIL FILHO</t>
+  </si>
+  <si>
+    <t>tecnico1@centrosulseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127797733 - LEODECIO BRAZ DA SILVA SEGUNDO</t>
+  </si>
+  <si>
+    <t>jethaseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127816669 - LAIS LIMA DE ANDRADE</t>
+  </si>
+  <si>
+    <t>suzi@v12corretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128202610 - JULIO CESAR FERREIRA</t>
   </si>
 </sst>
 </file>
@@ -883,7 +1108,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:C124"/>
+  <dimension ref="A1:C126"/>
   <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="55.5703125" style="2" customWidth="1"/>
@@ -907,10 +1132,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -918,10 +1143,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -929,10 +1154,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -940,10 +1165,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -951,10 +1176,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -962,10 +1187,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -973,10 +1198,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -984,10 +1209,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -995,10 +1220,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -1006,10 +1231,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -1017,10 +1242,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>36</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -1028,10 +1253,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -1039,10 +1264,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -1050,10 +1275,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -1061,10 +1286,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -1072,10 +1297,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -1083,10 +1308,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -1094,10 +1319,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -1105,10 +1330,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -1116,10 +1341,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -1127,10 +1352,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="B22" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -1138,10 +1363,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -1149,10 +1374,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B24" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
@@ -1163,7 +1388,7 @@
         <v>50</v>
       </c>
       <c r="B25" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -1171,10 +1396,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="B26" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
@@ -1182,10 +1407,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>54</v>
+        <v>12</v>
       </c>
       <c r="B27" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -1193,7 +1418,7 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s">
         <v>57</v>
@@ -1226,10 +1451,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>58</v>
+      </c>
+      <c r="B31" t="s">
         <v>61</v>
-      </c>
-      <c r="B31" t="s">
-        <v>62</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>3</v>
@@ -1237,10 +1462,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>3</v>
@@ -1248,10 +1473,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B33" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>3</v>
@@ -1259,10 +1484,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="B34" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>3</v>
@@ -1270,10 +1495,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B35" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>3</v>
@@ -1281,10 +1506,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="B36" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>3</v>
@@ -1292,10 +1517,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="B37" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>3</v>
@@ -1303,10 +1528,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="B38" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>3</v>
@@ -1314,10 +1539,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>72</v>
+      </c>
+      <c r="B39" t="s">
         <v>73</v>
-      </c>
-      <c r="B39" t="s">
-        <v>75</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>3</v>
@@ -1325,10 +1550,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B40" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>3</v>
@@ -1336,10 +1561,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B41" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>3</v>
@@ -1347,10 +1572,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>10</v>
+        <v>78</v>
       </c>
       <c r="B42" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>3</v>
@@ -1358,7 +1583,7 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>10</v>
+        <v>80</v>
       </c>
       <c r="B43" t="s">
         <v>81</v>
@@ -1391,10 +1616,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
         <v>86</v>
-      </c>
-      <c r="B46" t="s">
-        <v>87</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>3</v>
@@ -1402,10 +1627,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>86</v>
+        <v>15</v>
       </c>
       <c r="B47" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>3</v>
@@ -1413,10 +1638,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="B48" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>3</v>
@@ -1424,10 +1649,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B49" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>3</v>
@@ -1435,10 +1660,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="B50" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>3</v>
@@ -1446,10 +1671,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>92</v>
+        <v>15</v>
       </c>
       <c r="B51" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>3</v>
@@ -1457,10 +1682,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
         <v>92</v>
-      </c>
-      <c r="B52" t="s">
-        <v>95</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>3</v>
@@ -1468,10 +1693,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>96</v>
+        <v>15</v>
       </c>
       <c r="B53" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>3</v>
@@ -1479,10 +1704,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>98</v>
+        <v>15</v>
       </c>
       <c r="B54" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>3</v>
@@ -1490,10 +1715,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="B55" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>3</v>
@@ -1501,10 +1726,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>102</v>
+        <v>15</v>
       </c>
       <c r="B56" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>3</v>
@@ -1512,10 +1737,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>104</v>
+        <v>15</v>
       </c>
       <c r="B57" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>3</v>
@@ -1523,10 +1748,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>106</v>
+        <v>15</v>
       </c>
       <c r="B58" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>3</v>
@@ -1534,10 +1759,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>106</v>
+        <v>15</v>
       </c>
       <c r="B59" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>3</v>
@@ -1545,10 +1770,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>106</v>
+        <v>15</v>
       </c>
       <c r="B60" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>3</v>
@@ -1556,10 +1781,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>106</v>
+        <v>15</v>
       </c>
       <c r="B61" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C61" s="2" t="s">
         <v>3</v>
@@ -1567,10 +1792,10 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>106</v>
+        <v>15</v>
       </c>
       <c r="B62" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>3</v>
@@ -1578,10 +1803,10 @@
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B63" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>3</v>
@@ -1589,10 +1814,10 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>113</v>
+        <v>16</v>
       </c>
       <c r="B64" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>3</v>
@@ -1600,10 +1825,10 @@
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>115</v>
+        <v>7</v>
       </c>
       <c r="B65" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>3</v>
@@ -1611,10 +1836,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>117</v>
+        <v>7</v>
       </c>
       <c r="B66" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>3</v>
@@ -1622,10 +1847,10 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="B67" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>3</v>
@@ -1633,10 +1858,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>121</v>
+        <v>17</v>
       </c>
       <c r="B68" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>3</v>
@@ -1644,10 +1869,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>121</v>
+        <v>17</v>
       </c>
       <c r="B69" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>3</v>
@@ -1655,10 +1880,10 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
       <c r="B70" t="s">
-        <v>125</v>
+        <v>112</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>3</v>
@@ -1666,10 +1891,10 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>12</v>
+        <v>108</v>
       </c>
       <c r="B71" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>3</v>
@@ -1677,10 +1902,10 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B72" t="s">
-        <v>127</v>
+        <v>114</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>3</v>
@@ -1688,10 +1913,10 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>6</v>
+        <v>115</v>
       </c>
       <c r="B73" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>3</v>
@@ -1699,10 +1924,10 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="B74" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>3</v>
@@ -1710,10 +1935,10 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>131</v>
+        <v>5</v>
       </c>
       <c r="B75" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>3</v>
@@ -1721,10 +1946,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>5</v>
+        <v>115</v>
       </c>
       <c r="B76" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>3</v>
@@ -1732,10 +1957,10 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B77" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>3</v>
@@ -1743,10 +1968,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>135</v>
+        <v>121</v>
       </c>
       <c r="B78" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>3</v>
@@ -1754,10 +1979,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B79" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>3</v>
@@ -1765,10 +1990,10 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>5</v>
+        <v>121</v>
       </c>
       <c r="B80" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>3</v>
@@ -1776,10 +2001,10 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="B81" t="s">
-        <v>139</v>
+        <v>11</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>3</v>
@@ -1787,10 +2012,10 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="B82" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>3</v>
@@ -1798,10 +2023,10 @@
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>129</v>
+        <v>20</v>
       </c>
       <c r="B83" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="C83" s="2" t="s">
         <v>3</v>
@@ -1812,7 +2037,7 @@
         <v>129</v>
       </c>
       <c r="B84" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>3</v>
@@ -1820,10 +2045,10 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="B85" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>3</v>
@@ -1831,10 +2056,10 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>145</v>
+        <v>129</v>
       </c>
       <c r="B86" t="s">
-        <v>146</v>
+        <v>132</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>3</v>
@@ -1842,10 +2067,10 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B87" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>3</v>
@@ -1853,10 +2078,10 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B88" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>3</v>
@@ -1864,183 +2089,421 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>6</v>
+        <v>137</v>
       </c>
       <c r="B89" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>3</v>
+        <v>139</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>13</v>
+        <v>140</v>
       </c>
       <c r="B90" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>3</v>
+        <v>139</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="B91" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>3</v>
+        <v>139</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>153</v>
+        <v>144</v>
       </c>
       <c r="B92" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>3</v>
+        <v>139</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>146</v>
+      </c>
+      <c r="B93" t="s">
+        <v>147</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>149</v>
+      </c>
+      <c r="B94" t="s">
+        <v>150</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>151</v>
+      </c>
+      <c r="B95" t="s">
+        <v>152</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>153</v>
+      </c>
+      <c r="B96" t="s">
+        <v>154</v>
+      </c>
+      <c r="C96" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="B93" t="s">
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>153</v>
+      </c>
+      <c r="B97" t="s">
         <v>156</v>
       </c>
-      <c r="C93" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94"/>
-      <c r="B94"/>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95"/>
-      <c r="B95"/>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96"/>
-      <c r="B96"/>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97"/>
-      <c r="B97"/>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98"/>
-      <c r="B98"/>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99"/>
-      <c r="B99"/>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100"/>
-      <c r="B100"/>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101"/>
-      <c r="B101"/>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102"/>
-      <c r="B102"/>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103"/>
-      <c r="B103"/>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104"/>
-      <c r="B104"/>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105"/>
-      <c r="B105"/>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106"/>
-      <c r="B106"/>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107"/>
-      <c r="B107"/>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108"/>
-      <c r="B108"/>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109"/>
-      <c r="B109"/>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110"/>
-      <c r="B110"/>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111"/>
-      <c r="B111"/>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112"/>
-      <c r="B112"/>
+      <c r="C97" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>157</v>
+      </c>
+      <c r="B98" t="s">
+        <v>158</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>160</v>
+      </c>
+      <c r="B99" t="s">
+        <v>161</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>162</v>
+      </c>
+      <c r="B100" t="s">
+        <v>163</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>164</v>
+      </c>
+      <c r="B101" t="s">
+        <v>165</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>167</v>
+      </c>
+      <c r="B102" t="s">
+        <v>168</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>170</v>
+      </c>
+      <c r="B103" t="s">
+        <v>171</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>153</v>
+      </c>
+      <c r="B104" t="s">
+        <v>172</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>174</v>
+      </c>
+      <c r="B105" t="s">
+        <v>175</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>176</v>
+      </c>
+      <c r="B106" t="s">
+        <v>177</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>179</v>
+      </c>
+      <c r="B107" t="s">
+        <v>180</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>182</v>
+      </c>
+      <c r="B108" t="s">
+        <v>183</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>184</v>
+      </c>
+      <c r="B109" t="s">
+        <v>185</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>186</v>
+      </c>
+      <c r="B110" t="s">
+        <v>187</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>188</v>
+      </c>
+      <c r="B111" t="s">
+        <v>189</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>190</v>
+      </c>
+      <c r="B112" t="s">
+        <v>191</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113"/>
-      <c r="B113"/>
+      <c r="A113" t="s">
+        <v>153</v>
+      </c>
+      <c r="B113" t="s">
+        <v>192</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114"/>
-      <c r="B114"/>
+      <c r="A114" t="s">
+        <v>153</v>
+      </c>
+      <c r="B114" t="s">
+        <v>193</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115"/>
-      <c r="B115"/>
+      <c r="A115" t="s">
+        <v>194</v>
+      </c>
+      <c r="B115" t="s">
+        <v>195</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116"/>
-      <c r="B116"/>
+      <c r="A116" t="s">
+        <v>196</v>
+      </c>
+      <c r="B116" t="s">
+        <v>197</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117"/>
-      <c r="B117"/>
+      <c r="A117" t="s">
+        <v>157</v>
+      </c>
+      <c r="B117" t="s">
+        <v>198</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>148</v>
+      </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118"/>
-      <c r="B118"/>
+      <c r="A118" t="s">
+        <v>157</v>
+      </c>
+      <c r="B118" t="s">
+        <v>199</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>155</v>
+      </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119"/>
-      <c r="B119"/>
+      <c r="A119" t="s">
+        <v>157</v>
+      </c>
+      <c r="B119" t="s">
+        <v>200</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120"/>
-      <c r="B120"/>
+      <c r="A120" t="s">
+        <v>201</v>
+      </c>
+      <c r="B120" t="s">
+        <v>202</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>159</v>
+      </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121"/>
-      <c r="B121"/>
+      <c r="A121" t="s">
+        <v>203</v>
+      </c>
+      <c r="B121" t="s">
+        <v>204</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122"/>
-      <c r="B122"/>
+      <c r="A122" t="s">
+        <v>205</v>
+      </c>
+      <c r="B122" t="s">
+        <v>206</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>166</v>
+      </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123"/>
-      <c r="B123"/>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124"/>
-      <c r="B124"/>
-      <c r="C124" s="3"/>
+      <c r="A123" t="s">
+        <v>162</v>
+      </c>
+      <c r="B123" t="s">
+        <v>207</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" ht="180" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>208</v>
+      </c>
+      <c r="B124" t="s">
+        <v>209</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>173</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Dados e Relatórios\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0B9AA1C-3E3E-4AD2-B97A-E5C7B027188D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2562E1AB-F834-40A7-A4CF-C9DFD22C1481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28800" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envio Robô" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="154">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -51,426 +51,24 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>gisele.cardoso1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>thays.silva@allianz.com.br</t>
-  </si>
-  <si>
     <t>ivone.jesus@allianz.com.br</t>
   </si>
   <si>
     <t>rogerio.souza@allianz.com.br</t>
   </si>
   <si>
-    <t>allan.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>renata.matheus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>ana.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>carla.valnisio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 9 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 8 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
     <t>renovacaoseguros@honda.com.br</t>
   </si>
   <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
     <t>backofficecorretora@segurostoyota.com.br</t>
   </si>
   <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 6 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>suporte.vvd@vwfs.com</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 3 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 2 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 10 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>andreia.carvalhais@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12456100600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>eduardo.marques@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12781521800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>tadeu.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12530602400000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>eliana.pedroso@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12902622400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>mary.fernandes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12742168600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>rafael.petrin@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12452355200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>eduardo.olicshevis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12833930000000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>william.bichet@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12861600800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>fausto.reis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12877334900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>yuri.santos@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12911930600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>priscila.santana@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12836745200000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12849099600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12582922700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12914036300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>angela.carmo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12888096700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>leandro.gonzaga@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12913864000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>talita.meneses@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12616839100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>andreia.brixner@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12912767800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>daniel.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12913715800000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>dayane.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12833487400000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>fernanda.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12913435800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>betina.carrasco@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12758850900000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>ivana.freitas@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12583130800000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12861564600001 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>leticia.bezerra@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12889956800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>rafael.leite@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12910421900000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
     <t>leinny.amorim@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12913123400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12642803100000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12739258800000 Nota 167 - Retorno Cobrança op53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12769769600000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12784169700000 Nota 167 - Retorno Cobrança op53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12813858100000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>diego.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12904459100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12904459100000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>daniella.andrade@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12889036500000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>nelma.xavier@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12906563600000 Nota 167 - Retorno Cobrança op53</t>
-  </si>
-  <si>
-    <t>renata.souza1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12870336300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12834978300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>sandra.mikari@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12650341900000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>seguros@dorconsultoria.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 125883221 - EDMILSON ALVES EVANGELISTA</t>
-  </si>
-  <si>
-    <t>grandevitoria@gvcorretora.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 125840741 - TAMIRIS VIANA CAMPOREZ CARREIRO</t>
-  </si>
-  <si>
-    <t>andre.oliveira@braseg.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126545989 - NATALICIA BRITO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>seguros@sartoricorretora.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126569336 - JENNITON BALDRAIA DA ROCHA</t>
-  </si>
-  <si>
-    <t>atendimento@miraseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126579867 - LUCIANE MARIA RODRIGUES SEIXAS</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126592387 - LIEUTIENE KELIA VIEIRA DOS PASSOS</t>
-  </si>
-  <si>
-    <t>bacellarseguros@bacellarseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126591116 - ANA PAULA FRANCA ARAUJO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126588520 - FABIO PINHEIRO DE MEDEIROS</t>
-  </si>
-  <si>
-    <t>vbsegs@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126844850 - LUIS CLAUDIO MATOS DA MOTA</t>
-  </si>
-  <si>
-    <t>aferbrasil@aferbrasil.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126864149 - CAMILA ALBUQUERQUE LINHARES ROMEIRO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127212741 - JOSE DA SILVA MOTTA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127214571 - FLAVIO WAKED DE MORAES REGO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127216564 - SOLARCHIO PARTICIPACOES LTDA</t>
-  </si>
-  <si>
-    <t>info@plataformaseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127216197 - BRUNO SOARES DA SILVA</t>
-  </si>
-  <si>
-    <t>tecnica@perspectivaseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127766570 - ADEMILSON GONCALVES PEREIRA COELHO</t>
-  </si>
-  <si>
-    <t>renova@procede.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127784824 - RODOLFO POLCARO SAENZ</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128198489 - RAQUEL RODRIGUES DE PAIVA LEITE</t>
-  </si>
-  <si>
-    <t>diamantinaseguros@diamantinaseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128222524 - GEILSON BARBOSA SILVEIRA</t>
-  </si>
-  <si>
-    <t>jbonfim@jbonfimcorretora.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126184807 - RENATO SILVA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126532909 - ISIS DE MELO VILACA</t>
-  </si>
-  <si>
-    <t>ademirseguros@ademirseguros.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126562237 - LEONARDO DIAS SANTOS</t>
-  </si>
-  <si>
     <t>Captura de parcela rejeitada - Apólice 126559112 - RAISSA MODESTO DA COSTA</t>
   </si>
   <si>
@@ -586,6 +184,321 @@
   </si>
   <si>
     <t>Captura de parcela rejeitada - Apólice 127519478 - MARIA APARECIDA DE ALMEIDA BARBIERI</t>
+  </si>
+  <si>
+    <t>marina.melo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12618285700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>marilia.martins@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12915255100000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>daniel.lourenco@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12916278900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>patricia.reis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12543461300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-19925517745 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>juliano.guimaraes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12914357600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>claudia.malaggi@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12718925300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>daniel.iarrocheski@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12915139900000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>jose.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12915732800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>lucas.almeida@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12916407000000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>fernanda.braga@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12916430600000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-88818467800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>fernando.martins1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12914442800000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>bruno.castro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12916424400000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>vanessa.penatti@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12917940100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>william.rosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12916429400000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>viviane.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12792256800000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>douglas.morais@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12905850400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>mayara.sampaio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12531128900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12912935200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>afonso.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12913270500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12914339600000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>claudia.pires@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12913315300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>francieli.becker@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12909188300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>jaqueline.rissi@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12843461100000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12843938600000 Nota 595 - ERRO PDF retorno RETORNO</t>
+  </si>
+  <si>
+    <t>viviane.corbari@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12913004800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>gustavo.correa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12760365200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>jheniffer.emiliano@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12832617800000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>eliane.outor@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12916530000000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>erineuza.monzillo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12909201200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12909976400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>daiane.soares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12876238600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>lucas.godinho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12906686700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>renato.faillace@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12907299100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>claudia.assuncao@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12536868500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>nathalie.carmo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12916573300000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>rosana.teixeira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12913339900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>gustavo.arruda@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12914732800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>rafael.junior@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12915469000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>geiza.vinand@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12524099700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>cristiane.konrad@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12809415200000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>daniella.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12912843100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>wagner.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12914893400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12915312600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12915558400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12915564700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>karinne.furtado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-8658128000159 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12749130900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>daisy.marangoni@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-585693919 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12611779600000 Nota 167 - Retorno Cobrança op53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12893722100000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>laerte.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12439446900000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12819236100000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12873635400000 Nota 167 - Retorno Cobrança op53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12892442900000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>valeria.cotrone@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12694752300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>janaina.cazelato@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12903461600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>graziella.pignataro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12907829600000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>carlos.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12184400300000 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -985,10 +898,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -996,10 +909,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -1007,10 +920,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -1018,10 +931,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="B5" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -1029,10 +942,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -1040,10 +953,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -1051,10 +964,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="B8" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -1062,10 +975,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="B9" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -1073,10 +986,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -1084,10 +997,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -1095,10 +1008,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="B12" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -1109,7 +1022,7 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -1117,10 +1030,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>72</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -1128,10 +1041,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>4</v>
+        <v>73</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -1139,10 +1052,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -1150,10 +1063,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="B17" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -1161,10 +1074,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -1172,10 +1085,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="B19" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -1183,10 +1096,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="B20" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -1194,10 +1107,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>59</v>
+        <v>83</v>
       </c>
       <c r="B21" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -1205,10 +1118,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>61</v>
+        <v>86</v>
       </c>
       <c r="B22" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -1216,10 +1129,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="B23" t="s">
-        <v>64</v>
+        <v>88</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -1227,10 +1140,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="B24" t="s">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
@@ -1238,10 +1151,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>5</v>
+        <v>91</v>
       </c>
       <c r="B25" t="s">
-        <v>67</v>
+        <v>92</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -1249,10 +1162,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="B26" t="s">
-        <v>69</v>
+        <v>94</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
@@ -1260,10 +1173,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="B27" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -1271,10 +1184,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="B28" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>3</v>
@@ -1282,10 +1195,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>7</v>
+        <v>98</v>
       </c>
       <c r="B29" t="s">
-        <v>74</v>
+        <v>99</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>3</v>
@@ -1293,10 +1206,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>6</v>
+        <v>100</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>3</v>
@@ -1304,10 +1217,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>7</v>
+        <v>102</v>
       </c>
       <c r="B31" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>3</v>
@@ -1315,10 +1228,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>7</v>
+        <v>104</v>
       </c>
       <c r="B32" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>3</v>
@@ -1326,10 +1239,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>6</v>
+        <v>104</v>
       </c>
       <c r="B33" t="s">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>3</v>
@@ -1337,10 +1250,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="B34" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>3</v>
@@ -1348,10 +1261,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>10</v>
+        <v>109</v>
       </c>
       <c r="B35" t="s">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>3</v>
@@ -1359,10 +1272,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="B36" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>3</v>
@@ -1370,10 +1283,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="B37" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>3</v>
@@ -1381,10 +1294,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="B38" t="s">
-        <v>87</v>
+        <v>116</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>3</v>
@@ -1392,10 +1305,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>11</v>
+        <v>117</v>
       </c>
       <c r="B39" t="s">
-        <v>88</v>
+        <v>118</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>3</v>
@@ -1403,10 +1316,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="B40" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>3</v>
@@ -1414,475 +1327,475 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>91</v>
+        <v>121</v>
       </c>
       <c r="B41" t="s">
-        <v>92</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>23</v>
+        <v>122</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>93</v>
+        <v>123</v>
       </c>
       <c r="B42" t="s">
-        <v>94</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>23</v>
+        <v>124</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="B43" t="s">
-        <v>96</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>13</v>
+        <v>126</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="B44" t="s">
-        <v>98</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>13</v>
+        <v>128</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>99</v>
+        <v>129</v>
       </c>
       <c r="B45" t="s">
-        <v>100</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>13</v>
+        <v>130</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>14</v>
+        <v>127</v>
       </c>
       <c r="B46" t="s">
-        <v>101</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>13</v>
+        <v>131</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="B47" t="s">
-        <v>103</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>13</v>
+        <v>132</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>14</v>
+        <v>129</v>
       </c>
       <c r="B48" t="s">
-        <v>104</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>13</v>
+        <v>133</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>105</v>
+        <v>134</v>
       </c>
       <c r="B49" t="s">
-        <v>106</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>15</v>
+        <v>135</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>107</v>
+        <v>9</v>
       </c>
       <c r="B50" t="s">
-        <v>108</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>15</v>
+        <v>136</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>16</v>
+        <v>137</v>
       </c>
       <c r="B51" t="s">
-        <v>109</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>17</v>
+        <v>138</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B52" t="s">
-        <v>110</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>17</v>
+        <v>139</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="B53" t="s">
-        <v>111</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>17</v>
+        <v>140</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="B54" t="s">
-        <v>113</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>17</v>
+        <v>142</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>114</v>
+        <v>141</v>
       </c>
       <c r="B55" t="s">
-        <v>115</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>20</v>
+        <v>143</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>116</v>
+        <v>141</v>
       </c>
       <c r="B56" t="s">
-        <v>117</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>20</v>
+        <v>144</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>16</v>
+        <v>141</v>
       </c>
       <c r="B57" t="s">
-        <v>118</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>21</v>
+        <v>145</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>119</v>
+        <v>146</v>
       </c>
       <c r="B58" t="s">
-        <v>120</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>21</v>
+        <v>147</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>121</v>
+        <v>148</v>
       </c>
       <c r="B59" t="s">
-        <v>122</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>12</v>
+        <v>149</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>18</v>
+        <v>150</v>
       </c>
       <c r="B60" t="s">
-        <v>123</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>13</v>
+        <v>151</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="B61" t="s">
-        <v>125</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>13</v>
+        <v>153</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B62" t="s">
-        <v>126</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>13</v>
+        <v>10</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>127</v>
+        <v>11</v>
       </c>
       <c r="B63" t="s">
-        <v>128</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>129</v>
+        <v>13</v>
       </c>
       <c r="B64" t="s">
-        <v>130</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>131</v>
+        <v>15</v>
       </c>
       <c r="B65" t="s">
-        <v>132</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>133</v>
+        <v>17</v>
       </c>
       <c r="B66" t="s">
-        <v>134</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>135</v>
+        <v>19</v>
       </c>
       <c r="B67" t="s">
-        <v>136</v>
-      </c>
-      <c r="C67" s="3" t="s">
         <v>20</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B68" t="s">
-        <v>137</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>138</v>
+        <v>22</v>
       </c>
       <c r="B69" t="s">
-        <v>139</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>140</v>
+        <v>24</v>
       </c>
       <c r="B70" t="s">
-        <v>141</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>22</v>
+        <v>25</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>142</v>
+        <v>26</v>
       </c>
       <c r="B71" t="s">
-        <v>143</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>22</v>
+        <v>27</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>144</v>
+        <v>28</v>
       </c>
       <c r="B72" t="s">
-        <v>145</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>140</v>
+        <v>24</v>
       </c>
       <c r="B73" t="s">
-        <v>146</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>23</v>
+        <v>30</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>147</v>
+        <v>31</v>
       </c>
       <c r="B74" t="s">
-        <v>148</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>23</v>
+        <v>32</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>149</v>
+        <v>33</v>
       </c>
       <c r="B75" t="s">
-        <v>150</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>23</v>
+        <v>34</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>149</v>
+        <v>33</v>
       </c>
       <c r="B76" t="s">
-        <v>151</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>23</v>
+        <v>35</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>152</v>
+        <v>36</v>
       </c>
       <c r="B77" t="s">
-        <v>153</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>13</v>
+        <v>37</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>154</v>
+        <v>38</v>
       </c>
       <c r="B78" t="s">
-        <v>155</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>13</v>
+        <v>39</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>156</v>
+        <v>40</v>
       </c>
       <c r="B79" t="s">
-        <v>157</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>13</v>
+        <v>41</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B80" t="s">
-        <v>158</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>17</v>
+        <v>42</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>159</v>
+        <v>43</v>
       </c>
       <c r="B81" t="s">
-        <v>160</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>19</v>
+        <v>44</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>161</v>
+        <v>45</v>
       </c>
       <c r="B82" t="s">
-        <v>162</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>19</v>
+        <v>46</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>163</v>
+        <v>47</v>
       </c>
       <c r="B83" t="s">
-        <v>164</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>19</v>
+        <v>48</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Dados e Relatórios\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0CA247B-D055-4132-9AB5-DAD10FC088A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD59F52-E2B7-461F-BD42-C6EACA210DDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29010" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="89">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -57,21 +57,9 @@
     <t>rogerio.souza@allianz.com.br</t>
   </si>
   <si>
-    <t>mayara.sampaio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>priscila.rubio@allianz.com.br</t>
-  </si>
-  <si>
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
-    <t>rafael.leite@allianz.com.br</t>
-  </si>
-  <si>
-    <t>irene.rosa@allianz.com.br</t>
-  </si>
-  <si>
     <t>juliano.guimaraes@allianz.com.br</t>
   </si>
   <si>
@@ -84,226 +72,238 @@
     <t>raphael.callado@allianz.com.br</t>
   </si>
   <si>
-    <t>nicole.demori@allianz.com.br</t>
-  </si>
-  <si>
-    <t>laila.steil@allianz.com.br</t>
-  </si>
-  <si>
-    <t>ana.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>rosangela.silva1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12729708700000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>matheus.gomes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12923325400000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12613250600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>claudia.magalhaes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12893824100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12520793000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12545793700000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>rosthiane.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12873142300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daniel.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12719808900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>daniela.leal@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-37884212072 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>vanessa.campos@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12920902100000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>carla.ventura@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12846281900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>leandro.machado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12920483900000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12729137300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12920138500000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12537379200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>talita.meneses@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12898518000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-17082930000134 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-17803113000128 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12918969700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
     <t>monica.plassa@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12920663200000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>daniele.beck@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12922317100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-73292621887 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12920459400000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12920591700000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12921624800000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>lucas.monteiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12916608300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12840224000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12924899500000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>wagner.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-15441681000109 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>fabiola.caixeta@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12922381400000 Nota 741 - Inspeção veicular-exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-512177082 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>viviane.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12912761900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-88818465300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12712279700000 Nota 167 - Retorno Cobrança op53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12827560900000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12851878000000 Nota 167 - Retorno Cobrança op53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12890533500000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12917626100000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>karla.cunha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12845997900000 Nota 167 - Retorno Cobrança op53</t>
-  </si>
-  <si>
     <t>anderson.menezes@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-11317709500000 Nota 742 - Prêmio</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11421879500001 Nota 742 - Prêmio</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12089129000001 Nota 742 - Prêmio</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12184669500000 Nota 742 - Prêmio</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12226005200000 Nota 742 - Prêmio</t>
-  </si>
-  <si>
-    <t>luciana.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12872256800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>karina.vieira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12464160200000 Nota 167 - Retorno Cobrança op53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12464330200000 Nota 167 - Retorno Cobrança op53</t>
-  </si>
-  <si>
-    <t>barbara.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12660189900000 Nota 167 - Retorno Cobrança op53</t>
-  </si>
-  <si>
-    <t>viviane.costa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12784973200000 Nota 167 - Retorno Cobrança op53</t>
+    <t>everton.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12920907500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>patricia.sylos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12876599600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>renato.lopes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12918087800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>matheus.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12907085600000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12925145200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12797657100000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>danillo.boem@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12917157100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>marcia.castelo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-21669327892 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>juliana.almeida@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12924313900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12913582400000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>gleison.ferreira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12923625000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>monica.betoni@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12840688200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>claudia.gomes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12916995500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>andriele.pala@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12923519400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>vitor.mattos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12780346300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>eliane.outor@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-26313634772 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>ana.guanais@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12744946200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>erineuza.monzillo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12909201200000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12919908200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>daiane.soares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12712309500000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12868799400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12911500600000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12911500600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>adriano.campos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12900831000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>ana.cunha@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12916909800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>rosana.teixeira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-10138417800000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12921462800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12771367100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12919352300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12919352300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>cristiane.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12921987300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12925600800000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12925608600000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>jacqueline.mendes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12779450600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>daisy.marangoni@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12919200700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12763274700000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12841918500000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12842080500000 Nota 167 - Retorno Cobrança op53</t>
+  </si>
+  <si>
+    <t>claudenice.barbosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12845382500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12894954600000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12911500600000 Nota 595 - ERRO PDF RTORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12681442500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>janaina.cazelato@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12906891800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>graziella.pignataro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12913939700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>ana.morais@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-7986013613 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-31209101807 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-35950309820 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>carlos.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-10739609900000 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -703,10 +703,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -714,10 +714,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -725,10 +725,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -736,10 +736,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -747,10 +747,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -758,10 +758,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -769,10 +769,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -780,10 +780,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -791,10 +791,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -802,10 +802,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -813,10 +813,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -824,10 +824,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -835,10 +835,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -846,10 +846,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -857,10 +857,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -868,10 +868,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" t="s">
         <v>42</v>
-      </c>
-      <c r="B17" t="s">
-        <v>43</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
         <v>44</v>
@@ -890,10 +890,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -901,10 +901,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="B20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -912,10 +912,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B21" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -923,7 +923,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B22" t="s">
         <v>50</v>
@@ -934,7 +934,7 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B23" t="s">
         <v>51</v>
@@ -945,7 +945,7 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B24" t="s">
         <v>52</v>
@@ -956,10 +956,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -967,10 +967,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>8</v>
+        <v>55</v>
       </c>
       <c r="B26" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
@@ -978,10 +978,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B27" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B28" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>3</v>
@@ -1000,10 +1000,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>3</v>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>59</v>
+        <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>3</v>
@@ -1022,7 +1022,7 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>61</v>
+        <v>6</v>
       </c>
       <c r="B31" t="s">
         <v>62</v>
@@ -1033,10 +1033,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="B32" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>3</v>
@@ -1044,7 +1044,7 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>64</v>
+        <v>6</v>
       </c>
       <c r="B33" t="s">
         <v>65</v>
@@ -1055,7 +1055,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B34" t="s">
         <v>66</v>
@@ -1066,10 +1066,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="B35" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>3</v>
@@ -1077,10 +1077,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>5</v>
+        <v>69</v>
       </c>
       <c r="B36" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>3</v>
@@ -1091,7 +1091,7 @@
         <v>4</v>
       </c>
       <c r="B37" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>3</v>
@@ -1099,10 +1099,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B38" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>3</v>
@@ -1110,10 +1110,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B39" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>3</v>
@@ -1121,10 +1121,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B40" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>3</v>
@@ -1132,10 +1132,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>74</v>
+        <v>5</v>
       </c>
       <c r="B41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>3</v>
@@ -1146,7 +1146,7 @@
         <v>74</v>
       </c>
       <c r="B42" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>3</v>
@@ -1154,10 +1154,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>74</v>
+        <v>13</v>
       </c>
       <c r="B43" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>3</v>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="B44" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>3</v>
@@ -1176,10 +1176,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="B45" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>3</v>
@@ -1187,10 +1187,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B46" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>3</v>
@@ -1198,10 +1198,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B47" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>3</v>
@@ -1209,10 +1209,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B48" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>3</v>
@@ -1220,25 +1220,18 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B49" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>87</v>
-      </c>
-      <c r="B50" t="s">
-        <v>88</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A50"/>
+      <c r="B50"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51"/>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Dados e Relatórios\Envio de e-mail retorno GO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45C53E74-8A2C-4269-803E-4529E52EE45C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{538C4DCD-9AF1-4E26-9550-ED65FAF583C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29010" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envio Robô" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="160">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -307,6 +307,216 @@
   </si>
   <si>
     <t>Retorno de GO referência-12512149400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12888162500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>renato.lopes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12929146700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>erica.cassandre@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12926024600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>luiz.junior@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12915607000000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>jaciely.dias@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12603181800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>sonia.bortoleto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12929767400000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>gisele.mazzucco@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-4238496620 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>saulo.santiago@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12916951600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>monica.prates@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12931543900000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>fernando.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12908379000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>bruna.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12924648300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>fernanda.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12930233600000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>cristiane.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12738856000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12883737000000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12923451600000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12924291600000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12927118200000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12927178500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12928187800000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12930680700000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12930705700000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12930755300000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12930858000000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12930918100000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12930944700000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12931276800000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12931487300000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12931495200000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>betina.carrasco@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12634112200000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>carla.nascimento@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12870921600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>filipe.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12889897200000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>marcio.kaminski@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-7204683960 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>cristiane.lozano@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12522729800000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>rogerio.souza@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12552518100000 Nota 167 - Retorno Cobrança op53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12763415500000 Nota 167 - Retorno Cobrança op53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12764703700000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>rosemeire.faria@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12910335600000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12910682200000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12913959900000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12921466000000 Nota 167 - Retorno Cobrança op53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12922512100000 Nota 167 - Retorno Cobrança op53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12924895200000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12928773600000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>daniella.andrade@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12931027000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>graziella.pignataro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12925092300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-63392895687 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>stefani.saracho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12747650600000 Nota 167 - Retorno Cobrança op53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-42295337000113 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -356,14 +566,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -682,12 +889,12 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:C124"/>
+  <dimension ref="A1:C99"/>
   <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="55.5703125" style="2" customWidth="1"/>
     <col min="2" max="2" width="101.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="255.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="143.28515625" style="2" customWidth="1"/>
     <col min="4" max="6" width="9.42578125" style="2"/>
     <col min="7" max="7" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="8" max="16384" width="9.42578125" style="2"/>
@@ -739,10 +946,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>90</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -750,10 +957,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -761,10 +968,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -772,10 +979,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -783,10 +990,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>94</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -794,10 +1001,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -805,10 +1012,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -816,10 +1023,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -827,10 +1034,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -838,10 +1045,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -849,10 +1056,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -860,10 +1067,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -871,10 +1078,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -882,10 +1089,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -893,10 +1100,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="B19" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -904,10 +1111,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -915,10 +1122,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -926,10 +1133,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>44</v>
+        <v>99</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -937,10 +1144,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>49</v>
+        <v>101</v>
       </c>
       <c r="B23" t="s">
-        <v>50</v>
+        <v>102</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -948,10 +1155,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
@@ -959,10 +1166,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>52</v>
+        <v>7</v>
       </c>
       <c r="B25" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -970,10 +1177,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="B26" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
@@ -981,10 +1188,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="B27" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -992,10 +1199,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>9</v>
+        <v>103</v>
       </c>
       <c r="B28" t="s">
-        <v>58</v>
+        <v>104</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>3</v>
@@ -1003,10 +1210,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="B29" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>3</v>
@@ -1014,10 +1221,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="B30" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>3</v>
@@ -1025,10 +1232,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>3</v>
@@ -1036,10 +1243,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>3</v>
@@ -1047,10 +1254,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>5</v>
+        <v>105</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
+        <v>106</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>3</v>
@@ -1058,10 +1265,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="B34" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>3</v>
@@ -1069,10 +1276,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>5</v>
+        <v>107</v>
       </c>
       <c r="B35" t="s">
-        <v>65</v>
+        <v>108</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>3</v>
@@ -1080,10 +1287,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>5</v>
+        <v>54</v>
       </c>
       <c r="B36" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>3</v>
@@ -1091,10 +1298,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>5</v>
+        <v>109</v>
       </c>
       <c r="B37" t="s">
-        <v>67</v>
+        <v>110</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>3</v>
@@ -1102,10 +1309,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="B38" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>3</v>
@@ -1113,10 +1320,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>3</v>
@@ -1124,10 +1331,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="B40" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>3</v>
@@ -1135,10 +1342,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>73</v>
+        <v>5</v>
       </c>
       <c r="B41" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>3</v>
@@ -1146,10 +1353,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="B42" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>3</v>
@@ -1157,10 +1364,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B43" t="s">
-        <v>77</v>
+        <v>115</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>3</v>
@@ -1168,10 +1375,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B44" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>3</v>
@@ -1179,10 +1386,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B45" t="s">
-        <v>79</v>
+        <v>116</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>3</v>
@@ -1190,10 +1397,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B46" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>3</v>
@@ -1201,10 +1408,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B47" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>3</v>
@@ -1212,10 +1419,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>82</v>
+        <v>5</v>
       </c>
       <c r="B48" t="s">
-        <v>83</v>
+        <v>119</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>3</v>
@@ -1223,10 +1430,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>84</v>
+        <v>5</v>
       </c>
       <c r="B49" t="s">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>3</v>
@@ -1234,10 +1441,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>86</v>
+        <v>5</v>
       </c>
       <c r="B50" t="s">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>3</v>
@@ -1245,307 +1452,542 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>5</v>
+      </c>
+      <c r="B51" t="s">
+        <v>62</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>5</v>
+      </c>
+      <c r="B52" t="s">
+        <v>63</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53" t="s">
+        <v>64</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54" t="s">
+        <v>65</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>5</v>
+      </c>
+      <c r="B55" t="s">
+        <v>66</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56" t="s">
+        <v>67</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>5</v>
+      </c>
+      <c r="B57" t="s">
+        <v>68</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>5</v>
+      </c>
+      <c r="B58" t="s">
+        <v>121</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>5</v>
+      </c>
+      <c r="B59" t="s">
+        <v>122</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>5</v>
+      </c>
+      <c r="B60" t="s">
+        <v>123</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>5</v>
+      </c>
+      <c r="B61" t="s">
+        <v>124</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>5</v>
+      </c>
+      <c r="B62" t="s">
+        <v>125</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>5</v>
+      </c>
+      <c r="B63" t="s">
+        <v>126</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>5</v>
+      </c>
+      <c r="B64" t="s">
+        <v>127</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>5</v>
+      </c>
+      <c r="B65" t="s">
+        <v>128</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>5</v>
+      </c>
+      <c r="B66" t="s">
+        <v>129</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>130</v>
+      </c>
+      <c r="B67" t="s">
+        <v>131</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>69</v>
+      </c>
+      <c r="B68" t="s">
+        <v>70</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>132</v>
+      </c>
+      <c r="B69" t="s">
+        <v>133</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>71</v>
+      </c>
+      <c r="B70" t="s">
+        <v>72</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>73</v>
+      </c>
+      <c r="B71" t="s">
+        <v>74</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>75</v>
+      </c>
+      <c r="B72" t="s">
+        <v>76</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>134</v>
+      </c>
+      <c r="B73" t="s">
+        <v>135</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>136</v>
+      </c>
+      <c r="B74" t="s">
+        <v>137</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>138</v>
+      </c>
+      <c r="B75" t="s">
+        <v>139</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B99" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52"/>
-      <c r="B52"/>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53"/>
-      <c r="B53"/>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54"/>
-      <c r="B54"/>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55"/>
-      <c r="B55"/>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56"/>
-      <c r="B56"/>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57"/>
-      <c r="B57"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58"/>
-      <c r="B58"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59"/>
-      <c r="B59"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60"/>
-      <c r="B60"/>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61"/>
-      <c r="B61"/>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62"/>
-      <c r="B62"/>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63"/>
-      <c r="B63"/>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64"/>
-      <c r="B64"/>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65"/>
-      <c r="B65"/>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66"/>
-      <c r="B66"/>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67"/>
-      <c r="B67"/>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68"/>
-      <c r="B68"/>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69"/>
-      <c r="B69"/>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70"/>
-      <c r="B70"/>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71"/>
-      <c r="B71"/>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72"/>
-      <c r="B72"/>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73"/>
-      <c r="B73"/>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74"/>
-      <c r="B74"/>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75"/>
-      <c r="B75"/>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76"/>
-      <c r="B76"/>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77"/>
-      <c r="B77"/>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78"/>
-      <c r="B78"/>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79"/>
-      <c r="B79"/>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80"/>
-      <c r="B80"/>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81"/>
-      <c r="B81"/>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82"/>
-      <c r="B82"/>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83"/>
-      <c r="B83"/>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84"/>
-      <c r="B84"/>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85"/>
-      <c r="B85"/>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86"/>
-      <c r="B86"/>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87"/>
-      <c r="B87"/>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88"/>
-      <c r="B88"/>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89"/>
-      <c r="B89"/>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90"/>
-      <c r="B90"/>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91"/>
-      <c r="B91"/>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92"/>
-      <c r="B92"/>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93"/>
-      <c r="B93"/>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94"/>
-      <c r="B94"/>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95"/>
-      <c r="B95"/>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96"/>
-      <c r="B96"/>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97"/>
-      <c r="B97"/>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98"/>
-      <c r="B98"/>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99"/>
-      <c r="B99"/>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100"/>
-      <c r="B100"/>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101"/>
-      <c r="B101"/>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102"/>
-      <c r="B102"/>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103"/>
-      <c r="B103"/>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104"/>
-      <c r="B104"/>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105"/>
-      <c r="B105"/>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106"/>
-      <c r="B106"/>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107"/>
-      <c r="B107"/>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108"/>
-      <c r="B108"/>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109"/>
-      <c r="B109"/>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110"/>
-      <c r="B110"/>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111"/>
-      <c r="B111"/>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112"/>
-      <c r="B112"/>
-    </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A113"/>
-      <c r="B113"/>
-    </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A114"/>
-      <c r="B114"/>
-    </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A115"/>
-      <c r="B115"/>
-    </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A116"/>
-      <c r="B116"/>
-    </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A117"/>
-      <c r="B117"/>
-    </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A118"/>
-      <c r="B118"/>
-    </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A119"/>
-      <c r="B119"/>
-    </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A120"/>
-      <c r="B120"/>
-    </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A121"/>
-      <c r="B121"/>
-    </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A122"/>
-      <c r="B122"/>
-    </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A123"/>
-      <c r="B123"/>
-    </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A124"/>
-      <c r="B124"/>
-      <c r="C124" s="3"/>
+      <c r="C99" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FD3B9D6-168C-4F93-9F85-C6CE5CCC6150}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47298F5-5D77-493A-B7DD-70ECE0490706}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="834" uniqueCount="508">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -51,190 +51,1570 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>adriano.guerra@allianz.com.br</t>
-  </si>
-  <si>
-    <t>ana.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>claudia.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
     <t>fernando.martins1@allianz.com.br</t>
   </si>
   <si>
-    <t>mary.leme@allianz.com.br</t>
-  </si>
-  <si>
-    <t>lucas.monteiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>karla.cunha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>fernanda.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>marcio.kaminski@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-7204683960 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>rogerio.souza@allianz.com.br</t>
   </si>
   <si>
-    <t>tadeu.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12894151500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>bruno.ribas@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12929170700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12908927400000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12930333600000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>juliano.guimaraes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12881158100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>matheus.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12926978900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>rosthiane.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12599474100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12911417300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>adriana.silveira1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12777673500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12812969300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12927520700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>william.rosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12855114600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>mayara.sampaio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12778798500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>talita.meneses@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12616839100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>aline.carpes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12927240200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>danilo.ruas@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12928103500000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12933096300000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12748432500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>rodrigo.amorim@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12766935500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>leticia.bezerra@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12926276900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12930512300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12815586000000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12895187800000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>ana.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12929709700000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
     <t>laerte.silva@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12613250600000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12777933800000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
     <t>rosana.pessoa@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12920675400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>janaina.cazelato@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12833875800000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12848725300000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
     <t>nelma.xavier@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12875355000000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>carlos.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11501238700000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12527663500000 Nota 242 - Retorno Cobrança</t>
+    <t>daniel.lourenco@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12892674600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>kaue.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12925570900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>daniela.leal@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12654025500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>vanessa.campos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12921427300000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>ana.sales@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12912446600000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12930846000000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>gisele.cardoso1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-72189707000107 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>bernardo.barbosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-9190581679 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>barbara.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12932409600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>andre.gouvea@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12930986800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>luciana.belisario@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12934547300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>eduardo.marques@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-27870501824 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>claudia.pires@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12902436300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>saulo.santiago@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-51196961000154 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>nilcea.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12846040400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12849663500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>flavio.funke@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12917402200000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>karen.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12936451000000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>marcio.ferreira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12931334500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>raphael.callado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12935505500000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>gabriela.logrado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12720161500035 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12927510600000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12930708000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12930708000000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12931165100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12934639900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12934832400000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12935049600000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12935403900000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12935476300000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12935479800000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12935551800000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12935728500000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12935763300000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12935771300000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12935794400000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>rosemeire.faria@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12581832500000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12588910400000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>carolina.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12626074500000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>ivone.jesus@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12659962000000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12763804500000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12788668700000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12823579400000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12875872500000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12923350700000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12927130700000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12932572000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12920166900000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>naiara.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12927514800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>atendimento@metacorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125918499 - JULIA FIGUEIRA MARTINS</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 10 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>almar@segurosalmar.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125965937 - JOAO NOE MADALOSSO</t>
+  </si>
+  <si>
+    <t>suporte.vvd@vwfs.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126098641 - RINALDO GOMES DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>ro.seguros@yahoo.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126084541 - RODOLPHO DE PAIVA FELIPPE</t>
+  </si>
+  <si>
+    <t>aricorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126403872 - ANA LUCIA ALMEIDA PIRES</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 9 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>renovacaoseguros@honda.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126391152 - PERCIVAL BARBOSA DE ARAUJO</t>
+  </si>
+  <si>
+    <t>oestefozseguros@oestefoz.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126412471 - TELMA TERESINHA FERREIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126416187 - ANTONIO EDEGLEIR FARIAS DA CRUZ</t>
+  </si>
+  <si>
+    <t>paquela.seguros@terra.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126715576 - ALESSANDRA GUASTI XAVIER</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 8 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126751425 - JOYCE HOLANDA PINHEIRO</t>
+  </si>
+  <si>
+    <t>backofficecorretora@segurostoyota.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127027395 - TERESA LOSADA VALLE</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127018083 - WALDECY CAMELO</t>
+  </si>
+  <si>
+    <t>3c@seguros3c.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127336128 - SIMONE FRANCO LOBATO</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 6 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127376918 - MARXSUEL ARAUJO DA SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127636746 - DANIEL PACHECO CURCIO</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127696629 - LAELL DE SIQUEIRA LIRA</t>
+  </si>
+  <si>
+    <t>vladimircorretor@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127895920 - MARCIA APARECIDA DE OLIVEIRA GONCALVES</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>gerenciador@ei-seguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128005519 - LUCIANA DALLA ROSA</t>
+  </si>
+  <si>
+    <t>marciosantana@aecsseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128274490 - IVENIO MOREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 3 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>contato@hlseguroscorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128344086 - KAMILLA RAQUEL SILVA</t>
+  </si>
+  <si>
+    <t>parvicorretorama@parvicorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128419156 - JOSE MARCELO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>leonicetr@uol.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128859588 - MARCO ANTONIO MOLINA BECHIR</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 2 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>solssia@solssiaseguro.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128388249 - JOSIANE CRISTINA FRANCHON KODAMA</t>
+  </si>
+  <si>
+    <t>contato@diliseg.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126605921 - MANOEL MESSIAS CLEMENTINO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>diretoria@cedroseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126683956 - MARIANA CAROLINY FERREIRA</t>
+  </si>
+  <si>
+    <t>lamadreseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128429965 - LUIZ ANTONIO RUSCHEL</t>
+  </si>
+  <si>
+    <t>abrigo@abrigo.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128836860 - SIMONE MARIE RONDON</t>
+  </si>
+  <si>
+    <t>bellia@bellia.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126106818 - CRISTIANE CARLA RIBEIRO</t>
+  </si>
+  <si>
+    <t>renatahutter.seguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126084610 - JAQUELINE VORIQUE NICOLAY</t>
+  </si>
+  <si>
+    <t>julian@ccsegurospelotas.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126105276 - DIEGO MANUEL LANDACHE SOSA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126522668 - CAMILA CARLA ROCHA</t>
+  </si>
+  <si>
+    <t>diretoria@dodeles.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127042933 - ANA VERONICA SILVA FERREIRA MACHADO</t>
+  </si>
+  <si>
+    <t>alessandro@aspadmseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127037175 - MAGNO ALVES BATISTA JUNIOR</t>
+  </si>
+  <si>
+    <t>gloria.vitoriano@terra.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127022416 - CAMILLA AQUINO VITORIANO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127007367 - EVELYN NERY DE SANTANA MARCULINO</t>
+  </si>
+  <si>
+    <t>operacional@durangocorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127332011 - DANIELE CRISTINA PIMENTA DE PAOLI VIANA</t>
+  </si>
+  <si>
+    <t>craveiro.corretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127331976 - MARIA VICTORIA CRAVEIRO DUTRA DA SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127631951 - MARLY CORREA LARA DE ANDRADE</t>
+  </si>
+  <si>
+    <t>mdseguros@mdseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127957733 - PAULO ROBERTO MOTA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128402673 - ROBERTA MARIA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>contato@unifisaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127288504 - ANA CAROLINA MATOS AUGUSTO</t>
+  </si>
+  <si>
+    <t>polisegseguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126670406 - ANSELMA DE OLIVEIRA NUNES BANDEIRA DE MELLO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126705042 - YVIS ESTEFANIA YOSHIMURA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127027826 - ROBERTT BARBOSA ALVES</t>
+  </si>
+  <si>
+    <t>tostesenunes@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127041016 - PRISCILA MOURA CARRASCO CARVALHO</t>
+  </si>
+  <si>
+    <t>enseadaseg@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127328662 - GISELE CARVALHO CAVALCANTE REBOLI</t>
+  </si>
+  <si>
+    <t>backofficeseguros@vwfs.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127615147 - JOAO BATISTA DA SILVA</t>
+  </si>
+  <si>
+    <t>oriento@orientoseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127909159 - GABRIEL DEL CASTAGNE</t>
+  </si>
+  <si>
+    <t>totalcorretora.jaru@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127988891 - MISAEL DE LUCA COSTA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127984021 - ALESSANDRA DA SILVA D ALMEIDA DOMINGUES</t>
+  </si>
+  <si>
+    <t>arthur@apisseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128361371 - ROBERTA MONTENEGRO MORAES</t>
+  </si>
+  <si>
+    <t>emissao@seefeldseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128779861 - ANDRE PINHEIRO MACHADO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128886372 - IVONETE QUINTANA COSTA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126056500 - GRLIS SECURITIZADORA S/A</t>
+  </si>
+  <si>
+    <t>trialseg@bx3seguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126033382 - KAYOBRUCE SORY MEDEIROS DE MACEDO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126315681 - NEIDE MARIA SILVA CERQUEIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126371524 - WELTON AREDES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126383139 - FERNANDO LUIS MARQUES</t>
+  </si>
+  <si>
+    <t>stautseg@stautseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126376605 - SHIRLEY PIRES DE GODOI BORGHI</t>
+  </si>
+  <si>
+    <t>convictacorretora@convictacorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126634979 - ODETTE SILVA BRAGANCA</t>
+  </si>
+  <si>
+    <t>hodieseg@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126692691 - MARIO LUIS DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>maiseguros@maiseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126688808 - ANA LUCIA TAVARES DA SILVA</t>
+  </si>
+  <si>
+    <t>backoffice.corretora@yamaha-motor.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126707646 - MONIQUE IARA ARAUJO DE CAMPOS</t>
+  </si>
+  <si>
+    <t>potiguarcorretora@redencao.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126973605 - KARINA PATRICIA VIEIRA DA CUNHA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126974336 - GILMARA SILVA DOS SANTOS ROBERTO</t>
+  </si>
+  <si>
+    <t>jmvcorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126974457 - GUILHERME VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>diana@diamanteseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126954205 - CAROLINA DE MELO FREIRE GOUVEIA AVILA</t>
+  </si>
+  <si>
+    <t>domazi@grupodomani.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126979839 - OSVALDO RAMON NUNES LEMES</t>
+  </si>
+  <si>
+    <t>corretora@credisis.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126979755 - P S G PEREIRA LTDA ME</t>
+  </si>
+  <si>
+    <t>leonardo@prataenavega.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126979617 - JOSE PAU FONTELLES</t>
+  </si>
+  <si>
+    <t>rosana@wrseguros.net.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126980933 - EDSON MARCO</t>
+  </si>
+  <si>
+    <t>contato@hmdias.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126983004 - CLARISSA ESPINHARA WANDERLEY FERRARI</t>
+  </si>
+  <si>
+    <t>2f@2fseguros.net.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126982782 - AMERICAS COPACABANA HOTEL LTDA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126985448 - LEONARDO FERREIRA BRAGA</t>
+  </si>
+  <si>
+    <t>seguros@piccolicorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127007560 - ANDRE LUIZ DA SILVEIRA LOPES</t>
+  </si>
+  <si>
+    <t>miraldiseguros@uol.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127007470 - CLEIDE GOMES DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>pessoaseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126974601 - CLAUDIO ALEXANDRE SOUZA MADRUGA BARROS</t>
+  </si>
+  <si>
+    <t>diviseg@divinopolisseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126989865 - HANDERSON XAVIER DOS SANTOS</t>
+  </si>
+  <si>
+    <t>contato.cgseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126989425 - NORMANDO JOSE PIRES</t>
+  </si>
+  <si>
+    <t>protecta@protectaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126987830 - RAQUEL DATI MACEDO BERSELLI</t>
+  </si>
+  <si>
+    <t>emissao@tbmcorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126987775 - GUSTAVO LEMOS CAMPOS SOUSA</t>
+  </si>
+  <si>
+    <t>camposkarla2003@yahoo.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127009880 - ROSANE DOS REIS VARGAS</t>
+  </si>
+  <si>
+    <t>supercorretora@bol.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127011196 - JEANE FLAVIA OLIVEIRA BARROS DE INTURIAS</t>
+  </si>
+  <si>
+    <t>renata.santos.seguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127013098 - KETURE SALLES DE MELO</t>
+  </si>
+  <si>
+    <t>ursuscorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127013018 - NEW GENERATION TRANSPORTE LTDA ME</t>
+  </si>
+  <si>
+    <t>nobreseguro@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127012988 - MARIA JOSE DOS SANTOS</t>
+  </si>
+  <si>
+    <t>contato@gerarcorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127012541 - EDILENE DE CALDAS RHENIUS</t>
+  </si>
+  <si>
+    <t>pendencias@costabastos.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127013840 - CARLOS RENATO GARCIA DA COSTA</t>
+  </si>
+  <si>
+    <t>jamil@jamilseguros.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127013566 - SONIA CRISTINA DE CASTRO CUYABANO DOS REIS</t>
+  </si>
+  <si>
+    <t>ronildagrocha@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127013334 - JOSIANE DE FATIMA FERREIRA</t>
+  </si>
+  <si>
+    <t>tania@valentimseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127015048 - LEONARDO NOVAES DE PAIVA</t>
+  </si>
+  <si>
+    <t>claudio@numeseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127015039 - RONAN DE ABREU GUIMARAES</t>
+  </si>
+  <si>
+    <t>viperppr@terra.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127014983 - ALEKISANDRA BATISTA</t>
+  </si>
+  <si>
+    <t>atendimento@sextanteseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127017913 - ELIAS FERREIRA BATISTA</t>
+  </si>
+  <si>
+    <t>niceseguros@niceseguros.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127017774 - MARIO VANI JOAQUIM</t>
+  </si>
+  <si>
+    <t>pinha@conquistaseguros.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127017674 - GINIVALDO MIGUEL DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>topbras@topbras.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127017649 - NANCY AMARAL RIBEIRO DASA</t>
+  </si>
+  <si>
+    <t>magdiel@mantiqueiraseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127019463 - JOSE FRANCISCO CLARO</t>
+  </si>
+  <si>
+    <t>associadosseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127019361 - SUELI MAXIMINO DE ARRUDA</t>
+  </si>
+  <si>
+    <t>nrlimaseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127019136 - MARCIEL JUNIOR FARIA</t>
+  </si>
+  <si>
+    <t>lccseguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127018962 - VALQUIRIA SILVA LIMA</t>
+  </si>
+  <si>
+    <t>hilario.neto1@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126965172 - HILARIO DA SILVA NEIVA NETO</t>
+  </si>
+  <si>
+    <t>terraroxaseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127018950 - ROSELI DE AZEVEDO</t>
+  </si>
+  <si>
+    <t>priscila@rolimseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127010048 - ART E DESIGN CONFECCOES E COMERCIO LTDA ME</t>
+  </si>
+  <si>
+    <t>forbeci@forbeciseguros.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127009929 - DANIEL ELIAS PIOLI</t>
+  </si>
+  <si>
+    <t>moises@madalozzo.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127023318 - EDMAR JOAQUIM DA SILVA</t>
+  </si>
+  <si>
+    <t>pendencia@seguralta.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127008795 - FERNANDA GONCALVES</t>
+  </si>
+  <si>
+    <t>newtonseguros1986@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127008739 - ANA PATRICIA GARBIN LISSE</t>
+  </si>
+  <si>
+    <t>lpblcorretoradeseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127008352 - HELOISA DA MATA BOREL</t>
+  </si>
+  <si>
+    <t>isa.bertholazo@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127007944 - LEONICE PADILHA BERTHOLAZO</t>
+  </si>
+  <si>
+    <t>junior@canolaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127026016 - MARCELO PINAFI DE SOUZA</t>
+  </si>
+  <si>
+    <t>lauro@segurosarco.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127025776 - VALDELICE ALMEIDA DE SOUZA</t>
+  </si>
+  <si>
+    <t>rodrigo@tubaraoseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127025710 - MJ SOLUCOES EM SERVICOS LTDA ME</t>
+  </si>
+  <si>
+    <t>emissao@brasilconsult.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127025535 - TATIANA PEREIRA DE SOUZA AQUINO</t>
+  </si>
+  <si>
+    <t>fontel@fontelseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127005116 - JULIANO VALESE</t>
+  </si>
+  <si>
+    <t>bianca@seguroslugano.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127030006 - LUIZA CAROLINA MARIA DORLEANS DE BRAGANCA</t>
+  </si>
+  <si>
+    <t>bruna@ozonioseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127004225 - FABIANO TEIXEIRA SERAFIN</t>
+  </si>
+  <si>
+    <t>gerencia@sidseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127003785 - MARA RUBIA VITI</t>
+  </si>
+  <si>
+    <t>cincoseguros@cincoseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126990531 - ROSEBEL CUNHA NALESSO</t>
+  </si>
+  <si>
+    <t>corretoramclartymaia@mclartymaia.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126983814 - MARCIA MARCELA SILVA MARTINS</t>
+  </si>
+  <si>
+    <t>luizdall@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127009416 - PAULA CAROLINA GHELLER</t>
+  </si>
+  <si>
+    <t>realpluscorretoradeseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127160549 - LEONCIO DE SALIGNAC E SOUZA NETO</t>
+  </si>
+  <si>
+    <t>airton.durante@decaprioseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127193553 - AIRTON DURANTE JUNIOR</t>
+  </si>
+  <si>
+    <t>geopcelula1@brbseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127197436 - ROGERIO BAHIA DAS NEVES</t>
+  </si>
+  <si>
+    <t>joaovidal@joaovidalseguros.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127281132 - FABRICIO SILVA CARVALHO E CARVALHO</t>
+  </si>
+  <si>
+    <t>migueloti2@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127282164 - CAMILA SANT ANA DOS SANTOS DAFLON</t>
+  </si>
+  <si>
+    <t>rafael@novaeracorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127283026 - THAIS ALARCON CAVALCANTI DE ALBUQUERQUE PASSO</t>
+  </si>
+  <si>
+    <t>abc@abccorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127323897 - PATRICK SCIALOM FRANCA</t>
+  </si>
+  <si>
+    <t>kassia@kmcor.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127310412 - LEILA OLIVEIRA CARDOSO</t>
+  </si>
+  <si>
+    <t>allianz1@allianz1.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127329383 - WILSON APARECIDO SIMPLICIO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127328022 - ROSEMBERG ROCHA DE CARVALHO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127336108 - MONICA DE SOUZA LENZI BARALDI</t>
+  </si>
+  <si>
+    <t>resseguros@resseguroscorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127325147 - ALEX MASSAYUKI YONEKUBO</t>
+  </si>
+  <si>
+    <t>intercrop@grupointermedium.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127337322 - TATIANE CRISTINA MESQUITA CASSU BOGIK</t>
+  </si>
+  <si>
+    <t>automovel@grupotgl.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127338597 - THIAGO TORRES DIAS</t>
+  </si>
+  <si>
+    <t>seguroscapinter@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127338288 - SIMONE CRISTINA ROBETE</t>
+  </si>
+  <si>
+    <t>costamarseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127337894 - DIEGO SIMOES SANCHES</t>
+  </si>
+  <si>
+    <t>cnlo.seg@uol.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127337754 - NATALIA MARIA AIRES FRANCA</t>
+  </si>
+  <si>
+    <t>luiz.otavio.cazevedo@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127344584 - DORACI AZEVEDO CARDOSO</t>
+  </si>
+  <si>
+    <t>bruno@bfsolucoescorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127345598 - PAULO SERGIO DE BARROS JUNIOR</t>
+  </si>
+  <si>
+    <t>mzadmcorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127338080 - ALEXANDRE GROBERIO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>paulistarhs80@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127337769 - RODRIGO HENRIQUE DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127336535 - EDNA DE MOURA</t>
+  </si>
+  <si>
+    <t>adm@operacionalseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127350035 - SABRINA PEREIRA VAZ FERREIRA</t>
+  </si>
+  <si>
+    <t>emaiscorretora@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127334459 - RUI BRAGA BARROSO</t>
+  </si>
+  <si>
+    <t>sarandi@sarandiseguros.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127309429 - MARIA HELENA TURRA</t>
+  </si>
+  <si>
+    <t>ciraganseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127308581 - ANTONIO MARCOS PEREIRA DE ALMEIDA JUNIOR</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127350350 - BRUNO DOS SANTOS COSTA</t>
+  </si>
+  <si>
+    <t>cacaudeouro.corretora@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127351243 - LAMARE CARVALHO DE ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>atendimento@neivabraga.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127351293 - IRAMAIA CARVALHO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>andre.vassal@novabarraseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127387384 - VALERIA DE SOUZA SALGADO DE AZEVEDO</t>
+  </si>
+  <si>
+    <t>antonio.tenorio@h2tseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127443850 - MATHEUS GARDIN DE SOUZA</t>
+  </si>
+  <si>
+    <t>ldwseguros@uol.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127457999 - ROBERTO OEY</t>
+  </si>
+  <si>
+    <t>machado.neuza@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127460953 - ROGERIO ROTHE</t>
+  </si>
+  <si>
+    <t>boaviagemcorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127470099 - BARTOLOMEU VIEIRA DE MELO</t>
+  </si>
+  <si>
+    <t>ferreira@dacarseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127473220 - CONEXAO EVENTOS E PRODUCOES ARTISTICAS LTDA M</t>
+  </si>
+  <si>
+    <t>juliojubell@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127477627 - SUELEN GHEDINI MARTINELLI</t>
+  </si>
+  <si>
+    <t>rede@redecorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127486326 - DANYELLE DOS ANJOS CARDOSO</t>
+  </si>
+  <si>
+    <t>galves@mmseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127609990 - VALERIA MARIA NEVES FERREIRA</t>
+  </si>
+  <si>
+    <t>contato@segurosseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127631716 - LUCIANO ALMEIDA PEREIRA</t>
+  </si>
+  <si>
+    <t>astracorseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127641339 - MARINA VEIGA CAMPOLINA MACHADO</t>
+  </si>
+  <si>
+    <t>maxsegur@maxsegur.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127645851 - GEISY PATRICIA VIEIRA GOMES</t>
+  </si>
+  <si>
+    <t>protecta@potectaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127641932 - ELZENI PINHEIRO MORENO</t>
+  </si>
+  <si>
+    <t>comercial@magoseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127641146 - SONIA REGINA DA SILVA</t>
+  </si>
+  <si>
+    <t>geancarlo.almeida@atuarsolucoes.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127646467 - EDINO JOSE DA SILVA</t>
+  </si>
+  <si>
+    <t>otavio.caixeta@caixetaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127646666 - JOAO BATISTA JARDIM</t>
+  </si>
+  <si>
+    <t>seguros@avanseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127647489 - TANIA REGINA PEREIRA PINTO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127604612 - DALVA REGINA AMARAL TEIXEIRA</t>
+  </si>
+  <si>
+    <t>supervisor1.corretora@grupoleauto.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127608036 - NECI ORLANDO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127653338 - TAINAH OLIVEIRA JAMBEIRO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127656322 - JOAO VICTOR FERREIRA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>arbdias@ordernet.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127658091 - MARLENE CAETANO COSTA</t>
+  </si>
+  <si>
+    <t>sbbseguros@sbbseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127658062 - MICHELLE RABISCHOFFSKY</t>
+  </si>
+  <si>
+    <t>vanderson.matos@cocoonseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127658018 - MARCOS JOSE CANDIDO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127657996 - FRANCISCO DE ASSIS PEREIRA HOLANDA JUNIOR</t>
+  </si>
+  <si>
+    <t>joaquim@britopereiraseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127657986 - MARIO LUCIO ALVES PEREIRA</t>
+  </si>
+  <si>
+    <t>robson@rmartinsseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127657957 - CASEIMOVEIS CASEMIRO ROSA ADMINISTRADORA DE I</t>
+  </si>
+  <si>
+    <t>denver@denverseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127657887 - CLELIA VILAR DOS SANTOS DE SOUZA</t>
+  </si>
+  <si>
+    <t>regis.ignatti@terra.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127657874 - JULIANA AUGUSTA DA SILVA TOLEDO</t>
+  </si>
+  <si>
+    <t>emissao@moacirseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127657822 - BENTO CARVALHO DA SILVA</t>
+  </si>
+  <si>
+    <t>corretora.20093@sicoob.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127657780 - LUANA ENGELER FELIPPI PAVAN</t>
+  </si>
+  <si>
+    <t>mauricio@annisioseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127655705 - VANIA REGINA SEIBERT LAZARETTI</t>
+  </si>
+  <si>
+    <t>dacorretora.adm@gamil.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127655639 - FERREIRA FERREIRA PARTICIPACOES SOCIETARIAS L</t>
+  </si>
+  <si>
+    <t>contato@rtcorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127655506 - EVALDO SERGIO FRANCO DE ARRUDA</t>
+  </si>
+  <si>
+    <t>seguros.rodrigo@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127655513 - JOAO VICTOR DA SILVA CORDEIRO</t>
+  </si>
+  <si>
+    <t>contato@azbertier.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127655504 - RENATA ELAINE MESEL KAUFMAN</t>
+  </si>
+  <si>
+    <t>auto@cwseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127655374 - ELIZABETH PIFFER MACHADO</t>
+  </si>
+  <si>
+    <t>caragua.seg@uol.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127658655 - L M ENGENHARIA LTDA ME</t>
+  </si>
+  <si>
+    <t>newsegbrasil.corretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127658648 - RITA DE CASSIA PAULINO MENDES</t>
+  </si>
+  <si>
+    <t>nemoseguros.reis@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127658617 - OSCAR MORAES</t>
+  </si>
+  <si>
+    <t>silvana@corretoraharpya.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127658552 - ALCIDIO RODRIGUES</t>
+  </si>
+  <si>
+    <t>fred@quintellaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127898696 - MARIA DO SOCORRO RODRIGUES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>aoseguros@aoseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127912076 - ELISA BUSCACIO BONATO</t>
+  </si>
+  <si>
+    <t>adriana.faria@jorlan.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128145728 - NILZA AMORIM PEREIRA FROIS</t>
+  </si>
+  <si>
+    <t>seguros@assuntacorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128235742 - LUIZ HENRIQUE ARCHILHA</t>
+  </si>
+  <si>
+    <t>carrerocorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128813663 - JORGE ASSAMU MORI</t>
+  </si>
+  <si>
+    <t>aluguel@palavraseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128836603 - ANDRE LUIZ LINS GONCALEZ</t>
+  </si>
+  <si>
+    <t>raul@ruralmaxseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128834079 - ADOLFO FARIAS DOS SANTOS</t>
+  </si>
+  <si>
+    <t>mabemseguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125981444 - ZILDA RODRIGUES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>asuzanocorretora@hotmail.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126049574 - ALINE MORELLI WIRTHMANN</t>
+  </si>
+  <si>
+    <t>contato@waseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126033194 - JEFFERSON TIAGO DA COSTA</t>
+  </si>
+  <si>
+    <t>luizalbertodionysio56@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126001156 - LUCIANO GONCALVES DA ROCHA</t>
+  </si>
+  <si>
+    <t>chsseguros@outlook.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126269448 - DANIELI DE CASTRO BISSOLI</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126350938 - GIULLBER VALENTIM DA SILVA</t>
+  </si>
+  <si>
+    <t>elaine.teixeira@polivias.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126644430 - ELAINE TEIXEIRA</t>
+  </si>
+  <si>
+    <t>fante@fanteseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127012898 - JANETE PERES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127335192 - MARCELO MARIANO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127338296 - LUCIANA FELIX GONCALVES PINTO</t>
+  </si>
+  <si>
+    <t>pendencias@rbmseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127315947 - JOSEANE PARELLADA BRANDT</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127883748 - MARCIA APARECIDA SILVA ERHARDT</t>
+  </si>
+  <si>
+    <t>juliana@maisgarraseguros.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127962814 - MARIA CAROLINA BUCAR BAHIA</t>
+  </si>
+  <si>
+    <t>emissao@vrseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127961977 - R W FERRAGENS VITORIA LTDA ME</t>
+  </si>
+  <si>
+    <t>carla.martins@romap.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128292803 - NIRZETE FERNANDES DE REZENDE</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128326041 - IZABELA RODRIGUES DA SILVA FREIRE</t>
+  </si>
+  <si>
+    <t>lidercorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128308268 - MARIA GOMES VIEIRA SANTOS</t>
+  </si>
+  <si>
+    <t>contato@luganocorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128296873 - ROSEMARY APARECIDA ALBERTO GIGOR</t>
+  </si>
+  <si>
+    <t>diretoria@lapisbellus.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126350664 - DOUGLAS SOLEDADE DA SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126674196 - ANTONIO CARLOS DE FONTES</t>
+  </si>
+  <si>
+    <t>sudeste@sudesteseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126704888 - TANISE RODRIGUES DA SILVA FONTES</t>
+  </si>
+  <si>
+    <t>gilsoncaet@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126884194 - GILSON CAETANO DA SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126990070 - JAIRO IZIDIO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127315618 - TIELE DENISE NOGUEIRA</t>
+  </si>
+  <si>
+    <t>cvf.corretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127323098 - CARLA DE FREITAS QUADROS COSTA</t>
+  </si>
+  <si>
+    <t>segurosat@segurosat.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127292567 - ANDRE MARQUES AVELAR PEREIRA</t>
+  </si>
+  <si>
+    <t>madalozzo@madalozzocorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127583322 - ISABELA SALUM LIBOS</t>
+  </si>
+  <si>
+    <t>tavseg@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128359972 - FRANCISCO LAVRA DA SILVA PINTO</t>
+  </si>
+  <si>
+    <t>contato@radaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128372814 - VALDETE VIEIRA DA SILVA TINELI</t>
   </si>
 </sst>
 </file>
@@ -607,7 +1987,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:C34"/>
+  <dimension ref="A1:C278"/>
   <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="55.5703125" style="2" customWidth="1"/>
@@ -631,10 +2011,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -642,10 +2022,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -653,10 +2033,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -664,10 +2044,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -675,10 +2055,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -686,10 +2066,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -697,10 +2077,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -708,10 +2088,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -719,10 +2099,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -730,10 +2110,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -741,10 +2121,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -752,10 +2132,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -763,10 +2143,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -774,10 +2154,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -785,10 +2165,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -796,10 +2176,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -807,10 +2187,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -818,10 +2198,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>9</v>
+        <v>41</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -829,10 +2209,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -840,10 +2220,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>47</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -851,7 +2231,7 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>48</v>
@@ -862,10 +2242,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -873,10 +2253,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
@@ -884,10 +2264,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>14</v>
+        <v>47</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -895,7 +2275,7 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>52</v>
@@ -906,10 +2286,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -917,10 +2297,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>3</v>
@@ -928,10 +2308,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>3</v>
@@ -939,10 +2319,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>3</v>
@@ -950,10 +2330,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>3</v>
@@ -961,10 +2341,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>3</v>
@@ -972,10 +2352,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>3</v>
@@ -983,13 +2363,2697 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="C152" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="C153" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="C154" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="C155" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C156" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="C159" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="C160" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="C161" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="C162" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="C163" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="C164" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="C165" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="C166" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="C167" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C168" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="C169" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="C170" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="C171" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="C175" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="C177" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C178" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="C179" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="C180" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C181" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A184" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="C184" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A185" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="C185" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A186" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="C186" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A187" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="C187" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A188" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="C188" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A189" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="C189" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A190" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="C190" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A191" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="C191" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A192" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="C192" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A193" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="C193" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A194" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="C194" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A195" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="C195" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A196" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="C196" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A197" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="C197" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A198" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="C198" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A199" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="C199" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A200" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A201" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A202" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="C202" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A203" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C203" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A204" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="C204" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A205" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A206" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A207" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A208" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="C208" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A209" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="C209" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A210" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B210" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="C210" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A211" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B211" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="C211" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A212" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B212" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="C212" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A213" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B213" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A214" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B214" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A215" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A216" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B216" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A217" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B217" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="C217" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A218" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B218" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="C218" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A219" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B219" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="C219" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A220" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B220" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C220" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A221" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B221" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="C221" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A222" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B222" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="C222" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A223" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B223" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C223" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A224" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B224" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="C224" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="225" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A225" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B225" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="C225" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="226" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A226" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B226" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="C226" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="227" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A227" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B227" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C227" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="228" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A228" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B228" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C228" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="229" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A229" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B229" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="230" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A230" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B230" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C230" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="231" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A231" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="B231" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="C231" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="232" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A232" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="B232" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="C232" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="233" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A233" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B233" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C233" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="234" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A234" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B234" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="C234" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="235" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A235" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B235" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="C235" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A236" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B236" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="C236" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A237" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A238" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="B238" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="C238" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="239" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A239" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="B239" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="240" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A240" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="B240" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="C240" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A241" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B241" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A242" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B242" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A243" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B243" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="C243" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A244" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B244" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A245" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B245" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="C245" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A246" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B246" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="C246" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A247" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B247" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C247" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A248" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A249" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B249" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A250" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B250" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A251" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B251" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A252" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B252" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="C252" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A253" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B253" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A254" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="B254" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="C254" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A255" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B255" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A256" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B256" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A257" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B257" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A258" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B258" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A259" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B259" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A260" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A261" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="B261" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A262" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B262" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A263" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B263" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A264" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="B264" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A265" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A266" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="B266" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A267" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="B267" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A268" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B268" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A269" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B269" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A270" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B270" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A271" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B271" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="C271" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A272" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B272" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C272" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A273" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B273" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="C273" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A274" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B274" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="C274" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="275" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A275" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B275" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="C275" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="276" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A276" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B276" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="C276" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="277" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A277" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="C277" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="278" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A278" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B278" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C278" s="2" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C0B478-1417-4656-ABC0-BB8A866AE66D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F09F80E-0CBA-4672-8476-74A0EA0EAE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="120">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -49,18 +49,6 @@
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12912446600000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>rosemeire.faria@allianz.com.br</t>
-  </si>
-  <si>
-    <t>carolina.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>ivone.jesus@allianz.com.br</t>
   </si>
   <si>
     <t>Prezado(a), 
@@ -96,9 +84,6 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>backofficecorretora@segurostoyota.com.br</t>
-  </si>
-  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 6 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -144,244 +129,328 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>backofficeseguros@vwfs.com</t>
-  </si>
-  <si>
-    <t>contato@waseguros.com.br</t>
-  </si>
-  <si>
-    <t>diretoria@lapisbellus.com.br</t>
-  </si>
-  <si>
-    <t>dimas.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12933668400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
     <t>marilia.martins@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12752788700000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>sonia.nascimento@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12934323000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>patricia.farias@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12936150400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>bruno.castro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12836163700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>afonso.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11249095670 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>mayara.sampaio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12936737300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>vitor.mattos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12569998300000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>gustavo.correa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12687282800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12763825600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>monica.prates@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12934481900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-33907067000163 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daisy.marangoni@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12856495500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>nicole.demori@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12901980000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12809898300000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
     <t>weldja.bozi@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12824965200000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12880356200000 Nota 167 - Retorno Cobrança op53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12881857900000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
     <t>karina.vieira@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12448112600000 Nota 167 - Retorno Cobrança op53</t>
-  </si>
-  <si>
-    <t>ana.carneiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-61574273000134 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>stefani.saracho@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12223851200000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>carlos.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12017098700000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>atendimento@viaseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126045964 - RAIMUNDO PINHEIRO FILHO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126082035 - MARCIA MENDES VIRGINIO</t>
-  </si>
-  <si>
-    <t>contate@gebramseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126405794 - ENIDE MARIA RIBEIRO ALVES</t>
-  </si>
-  <si>
-    <t>simplusseguros@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126427057 - CARLOS ALEXANDRE SALIM MAGALHAES</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126431014 - LUCIANA MARLENE DA SILVA</t>
-  </si>
-  <si>
-    <t>rogersmartins@hotmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126617954 - ELIANE FEDERZONI</t>
-  </si>
-  <si>
-    <t>makey@makey.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126751134 - MAURO MARSOLA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126756822 - JONNYS DE MOURA</t>
-  </si>
-  <si>
-    <t>atendimento@bigbrasilseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126675393 - VIVIANE APARECIDA DOS SANTOS</t>
-  </si>
-  <si>
-    <t>l3corretoraseguros@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127264181 - DANILO VINICIUS DE OLIVEIRA COSTA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127377645 - ILIDIO DE JESUS COELHO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127367989 - FELIPE CAMILO CARDOSO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>petra@petraseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127345819 - CIDADE DA MODA FASHION LOCACOES DE BOX LTDA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127390967 - RITA DE CASSIA CORREA PESSOA</t>
-  </si>
-  <si>
-    <t>klimaseguros@klimaseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127659911 - JONAS DE MATTOS</t>
-  </si>
-  <si>
-    <t>aliancadowsley@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127714653 - JOSE MARTINS DA SILVA JUNIOR</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127718928 - WESLEI BATISTA ALMEIDA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127945266 - MARLENE NUNES GOMES RICATTO</t>
-  </si>
-  <si>
-    <t>operacional@seguroo.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128045838 - ROSANA THOME</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127968570 - THIANA DA SILVA CERQUEIRA</t>
-  </si>
-  <si>
-    <t>contato@cellenceseguros.net.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126202132 - PAULO RONALDO RAMOS DE MACEDO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128051737 - WELLINGTON JOSE DA SILVA</t>
-  </si>
-  <si>
-    <t>unitas@unitasnet.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128457500 - JENIEL RODRIGUES DE OLIVEIRA</t>
-  </si>
-  <si>
     <t>ativa@ativaseguros.net</t>
   </si>
   <si>
-    <t>Captura de parcela rejeitada - Apólice 128908206 - TATIANA FERREIRA ANGST</t>
+    <t>stephanye.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12908531600000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>silvia.taschetti@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12757346200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12776710100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>crislaine.trindade@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12938508900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>daniel.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12934543900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>jose.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12278257700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>vanessa.campos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12927514700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>vanessa.penatti@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12502038100000 Nota 595 - ERRO PDF retoeno</t>
+  </si>
+  <si>
+    <t>priscila.santana@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12893003600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12898834600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12935047600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>elisangela.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12621632500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>daniela.gui@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12937691900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>barbara.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12932633900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>adonias.brito@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-88818379900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>fabio.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12934229900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>raphael.callado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11237572500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>danilo.ruas@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12938272100000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12938296500000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>gabriela.logrado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12871520100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12932011600000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12933552300000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12934207700000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12935174900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12935713700000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>jacqueline.mendes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12924830900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>bruna.carneiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12882037400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>rafael.leite@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12928659600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>eduardo.santos1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12497647200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12733931900000 Nota 167 - Retorno Cobrança op53</t>
+  </si>
+  <si>
+    <t>cristiane.lozano@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12927371800000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>graziella.pignataro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12900796100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12915447600000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12223851200000 Nota 167 - Retorno Cobrança op53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12302937300000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12448063500000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12762122900000 Nota 167 - Retorno Cobrança op53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12792564300000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>ana.brito@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12902400000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 125965369 - GABRIEL SILVA CAMPOS</t>
+  </si>
+  <si>
+    <t>jlcs@jlcs.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126080107 - SONIA MARA ZIMMER CORREA</t>
+  </si>
+  <si>
+    <t>segsulbrasil@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126117501 - VALERIA DE OLIVEIRA COSTA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126058903 - ELIANE MACEDO RODRIGUES SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126413093 - CARLA ANGELICA PICCININI CANOVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126433552 - ESROM FELIX DE ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>fernando@assimseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126407572 - RONALDO NASSER ALVES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126440682 - RENATA FERNANDES PINHEIRO DOMINGUES</t>
+  </si>
+  <si>
+    <t>adm@marconcinseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126412503 - AMANDA ALINE MACIEL GOMES</t>
+  </si>
+  <si>
+    <t>adm@pattini.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126661929 - BRUNA ALVARES</t>
+  </si>
+  <si>
+    <t>camilo@riosegon.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126685311 - ROMILDO BATISTA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>protencorseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127025095 - MARILENE FERREIRA GOMES MARTINS</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>andrea@thompsonseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127318325 - KATIA REGINA RODRIGUES DA SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127405275 - VIVIAN FELIPPE FERRAZ</t>
+  </si>
+  <si>
+    <t>contatoenaseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127707310 - ISABELLA MARIA PEREIRA DE AVILA</t>
+  </si>
+  <si>
+    <t>rede@redecorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127698670 - RODRIGO DA MOTA</t>
+  </si>
+  <si>
+    <t>milton@remaviseguros.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128011609 - PAULO CESAR DA SILVA FREITAS</t>
+  </si>
+  <si>
+    <t>diamantinaseguros@diamantinaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128036321 - FELIPE AUGUSTO GUEDES DUPIM</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128070630 - CLEOMAR COSMI DE FREITAS</t>
+  </si>
+  <si>
+    <t>seguros@batalhacorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128070380 - MOACYR FALCAO</t>
+  </si>
+  <si>
+    <t>financeiro@brasal.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128453948 - DANYELLE DE SIQUEIRA CAMPOS GIL LEMOS BARRETO</t>
+  </si>
+  <si>
+    <t>claudinei.seguros@yahoo.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128452587 - VINICIUS DAVI DE SOU</t>
+  </si>
+  <si>
+    <t>daterraseguros@terra.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128895294 - ALEXANDRE GONCALVES</t>
   </si>
 </sst>
 </file>
@@ -431,14 +500,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -757,7 +823,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:C48"/>
+  <dimension ref="A1:C63"/>
   <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="55.5703125" style="2" customWidth="1"/>
@@ -781,10 +847,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -792,10 +858,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -803,10 +869,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -814,10 +880,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -825,10 +891,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -836,10 +902,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -847,10 +913,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -858,10 +924,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -869,10 +935,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -880,10 +946,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -891,10 +957,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -902,10 +968,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -913,10 +979,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -924,10 +990,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -935,10 +1001,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>7</v>
+        <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -946,10 +1012,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -957,10 +1023,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -968,10 +1034,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>5</v>
+        <v>49</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -979,10 +1045,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>6</v>
+        <v>49</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>4</v>
+        <v>51</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -990,10 +1056,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>53</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>54</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -1001,10 +1067,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -1012,10 +1078,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -1023,277 +1089,442 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B24" s="2" t="s">
+      <c r="B27" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
+      <c r="C27" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B28" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C28" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="C26" s="2" t="s">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>64</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C27" s="2" t="s">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C55" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>66</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="C28" s="2" t="s">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C56" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>69</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C30" s="2" t="s">
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C61" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>71</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C31" s="2" t="s">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C63" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>74</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>76</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>21</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>9</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>80</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>19</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>83</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>85</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>11</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>13</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>89</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>11</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>92</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>11</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>95</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>97</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Envio de e-mail retorno GO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Dados e Relatórios\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{117960AF-1F34-4B08-9C20-84B057E42734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D15F8E18-E08A-4D42-8554-8919D477F933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29010" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envio Robô" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="74">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -51,163 +51,214 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>cristiane.lozano@allianz.com.br</t>
-  </si>
-  <si>
     <t>graziella.pignataro@allianz.com.br</t>
   </si>
   <si>
-    <t>ana.brito@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12902400000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>monica.betoni@allianz.com.br</t>
-  </si>
-  <si>
-    <t>douglas.morais@allianz.com.br</t>
-  </si>
-  <si>
-    <t>priscila.rubio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>gustavo.correa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>dimas.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>rogerio.souza@allianz.com.br</t>
-  </si>
-  <si>
-    <t>ana.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
     <t>janaina.cazelato@allianz.com.br</t>
   </si>
   <si>
-    <t>micael.siqueira@allianz.com.br</t>
-  </si>
-  <si>
     <t>carlos.neves@allianz.com.br</t>
   </si>
   <si>
-    <t>fernando.duque@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12935111100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>jose.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12801773200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>vanessa.campos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12927080400000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>priscila.santana@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12878130500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12942325800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12667582800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>angela.carmo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12807824800000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
     <t>mayara.sampaio@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13471232000331 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>rodrigo.kuguyama@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12763415500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>talita.meneses@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12811205200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12874888100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12879438100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>leticia.pitkowski@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12933132700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12933233900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12933299600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12919655800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>thays.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12904439300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>lais.xavier@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12919127800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>marcio.kaminski@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12940779500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12784066300000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12923587700000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12932376500000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12936509900000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-5631253909 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12898701400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12480221500011 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12429751500000 Nota 242 - Retorno Cobrança</t>
+    <t>aline.nogueira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12739374300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rosangela.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12920811700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>jessika.pazin@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-44916906934 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>claudia.malaggi@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12942169900001 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>flavio.cesar@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12940984500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>gleison.ferreira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12947279900000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>renata.matheus@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12842181800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12531740200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>renata.magalhaes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12946271900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>flavio.funke@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12860508400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>viviane.corbari@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12713104400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>bruna.teixeira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12938975900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>flavia.costa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12945785700000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>fernando.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12945976200000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>nathalie.carmo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12944574900000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>dayane.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12919160900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>gabriela.logrado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12937582500000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12939314200000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12940155000000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12944045700000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12944161200000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12944257200000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12944342500000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12944520300000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12944527800000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12945088300000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12945115400000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12945338800000 Nota 595 - ERRO PDF RETORNO' RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12945388500000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12945448900000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12945839200000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>daniela.carvalho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-88818555700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>leticia.bezerra@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12630811400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12943143500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>filipe.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12153705700000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12153719700000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>weldja.bozi@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12589323900000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>rosemeire.faria@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12630811400000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12849051600000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-68570325053 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>mauricio.santo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12447957300000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11402906800000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11564280000000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12279962800000 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -580,7 +631,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:C29"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="55.5703125" style="2" customWidth="1"/>
@@ -604,10 +655,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -615,10 +666,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -626,10 +677,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -637,10 +688,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -648,10 +699,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -659,10 +710,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -670,10 +721,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -681,10 +732,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -692,10 +743,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -703,10 +754,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -714,10 +765,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -725,10 +776,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>37</v>
+        <v>30</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -736,10 +787,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -747,10 +798,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -758,10 +809,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -769,10 +820,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -780,10 +831,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -791,10 +842,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -802,10 +853,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -813,10 +864,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -824,10 +875,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -835,10 +886,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>4</v>
+        <v>39</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -846,10 +897,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
@@ -857,10 +908,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -868,10 +919,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
@@ -879,10 +930,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -890,10 +941,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>3</v>
@@ -901,12 +952,188 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="2" t="s">
+      <c r="B43" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>3</v>
       </c>
     </row>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26731"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50159704-9B62-4339-82A7-078DED071D8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF89D5DE-AA5F-4D4D-AA9F-928A27E49EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28545" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envio Robô" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="44">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -51,172 +51,124 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>flavia.costa@allianz.com.br</t>
-  </si>
-  <si>
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
     <t>daniel.lourenco@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12526792100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>tadeu.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12797111300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>kaue.silva@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12952315500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>juliano.guimaraes@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12945971900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>danillo.boem@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-45817117000109 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>vanessa.campos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-411636219 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>bruno.castro@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12929381300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>elisangela.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12695744200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>lidiane.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12893563800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>juliana.diniz@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12942166800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>wagner.simon@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12953018200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
     <t>vitor.mattos@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12569998300000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12958512700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12956330600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>jonatas.lauretto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12929869000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>pedro.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12957197300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>rafael.leite@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12949506700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>thays.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12955204600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>diego.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12954772100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>karinne.furtado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12958161600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12958161700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
     <t>ana.rodrigues@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12563636300000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>karla.cunha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12920180100000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>anderson.menezes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-2000831300000 Nota 742 - Prêmio</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-10455487800000 Nota 742 - Prêmio</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-10985391600000 Nota 742 - Prêmio</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11236143500000 Nota 742 - Prêmio</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11412163500000 Nota 742 - Prêmio</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12271684500000 Nota 742 - Prêmio</t>
-  </si>
-  <si>
-    <t>janaina.cazelato@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12934517100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>adriana.abreu@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12840224000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>Retorno de GO referência-12526792100000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12960219800000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12962567000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>kaue.medeiros@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12704722700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12953325700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>caroline.wojciechowski@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12959912000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>janaina.moura@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12961712000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12961932400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>renata.magalhaes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12941992700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>priscila.rubio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12706117700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12569789700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>jheniffer.emiliano@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12586496000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>dayane.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12960172700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>raphael.callado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12935995000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12947612800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>lucas.monteiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12954395800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>jocineia.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12959693400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>wagner.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12950372800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12535819900000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>aline.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12866009000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12866053400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
   </si>
 </sst>
 </file>
@@ -616,10 +568,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -627,10 +579,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -638,10 +590,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -649,10 +601,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -660,10 +612,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -671,10 +623,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -682,10 +634,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -693,7 +645,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
         <v>21</v>
@@ -726,10 +678,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B12" t="s">
         <v>26</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -737,10 +689,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
         <v>28</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -748,7 +700,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
@@ -759,10 +711,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -770,7 +722,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="B16" t="s">
         <v>33</v>
@@ -814,10 +766,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B20" t="s">
         <v>40</v>
-      </c>
-      <c r="B20" t="s">
-        <v>41</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -825,10 +777,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" t="s">
         <v>42</v>
-      </c>
-      <c r="B21" t="s">
-        <v>43</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -836,124 +788,54 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>45</v>
-      </c>
-      <c r="B23" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A23"/>
+      <c r="B23"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A24"/>
+      <c r="B24"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A25"/>
+      <c r="B25"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>49</v>
-      </c>
-      <c r="B26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A26"/>
+      <c r="B26"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>49</v>
-      </c>
-      <c r="B27" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A27"/>
+      <c r="B27"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>49</v>
-      </c>
-      <c r="B28" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A28"/>
+      <c r="B28"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>49</v>
-      </c>
-      <c r="B29" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A29"/>
+      <c r="B29"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>49</v>
-      </c>
-      <c r="B30" t="s">
-        <v>55</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A30"/>
+      <c r="B30"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>56</v>
-      </c>
-      <c r="B31" t="s">
-        <v>57</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A31"/>
+      <c r="B31"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>58</v>
-      </c>
-      <c r="B32" t="s">
-        <v>59</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A32"/>
+      <c r="B32"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33"/>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF89D5DE-AA5F-4D4D-AA9F-928A27E49EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0CC7536-E119-4CA7-A606-6AE585BD0316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28545" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28875" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envio Robô" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="67">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -54,121 +54,190 @@
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
-    <t>daniel.lourenco@allianz.com.br</t>
-  </si>
-  <si>
-    <t>kaue.silva@allianz.com.br</t>
-  </si>
-  <si>
     <t>juliano.guimaraes@allianz.com.br</t>
   </si>
   <si>
-    <t>bruno.castro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>vitor.mattos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>ana.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12526792100000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12960219800000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12962567000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>kaue.medeiros@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12704722700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12953325700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>caroline.wojciechowski@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12959912000000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>janaina.moura@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12961712000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12961932400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>renata.magalhaes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12941992700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>priscila.rubio@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12706117700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12569789700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>jheniffer.emiliano@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12586496000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
     <t>dayane.oliveira@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12960172700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>raphael.callado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12935995000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12947612800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>lucas.monteiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12954395800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>jocineia.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12959693400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>wagner.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12950372800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12535819900000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>aline.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12866009000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12866053400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>ana.brito@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12871786700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>adriana.coelho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12861424000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>irene.rosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12962742200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>erica.cassandre@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12886745100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12951564800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>tatiany.macedo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12961277900000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>priscila.sousa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12961661600000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>juliana.diniz@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12954183300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>renata.matheus@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12960646400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>gisele.cardoso1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-8188848000106 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-88818399800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>monica.betoni@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12961704300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-10248580000194 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rodrigo.kuguyama@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12791946400000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>talita.meneses@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12921221900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rosilene.nogueira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12961409400000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>ana.cunha@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12779301000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>diogo.junior@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12730315600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-88818634100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>marcus.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12955541500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>fernanda.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12961881300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12960974000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>geiza.vinand@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12936696600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>pedro.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12957197300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>jacqueline.mendes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12962530400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>aparecida.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-8355189655 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>thays.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12674811400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>eduardo.santos1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12948003300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>laila.steil@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12961336500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>adriana.abreu@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12840224000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>jose.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12326670800000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>carlos.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12121449200000 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -568,10 +637,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -579,10 +648,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -590,7 +659,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -612,7 +681,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
@@ -645,10 +714,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -656,10 +725,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -667,10 +736,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -678,10 +747,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -689,10 +758,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -700,7 +769,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
@@ -722,10 +791,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -733,10 +802,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -744,10 +813,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -755,10 +824,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -766,10 +835,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -777,10 +846,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -788,62 +857,146 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23"/>
-      <c r="B23"/>
+      <c r="A23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24"/>
-      <c r="B24"/>
+      <c r="A24" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25"/>
-      <c r="B25"/>
+      <c r="A25" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26"/>
-      <c r="B26"/>
+      <c r="A26" t="s">
+        <v>51</v>
+      </c>
+      <c r="B26" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27"/>
-      <c r="B27"/>
+      <c r="A27" t="s">
+        <v>53</v>
+      </c>
+      <c r="B27" t="s">
+        <v>54</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28"/>
-      <c r="B28"/>
+      <c r="A28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" t="s">
+        <v>56</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29"/>
-      <c r="B29"/>
+      <c r="A29" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30"/>
-      <c r="B30"/>
+      <c r="A30" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31"/>
-      <c r="B31"/>
+      <c r="A31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32"/>
-      <c r="B32"/>
+      <c r="A32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33"/>
-      <c r="B33"/>
+      <c r="A33" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" t="s">
+        <v>66</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34"/>
-      <c r="B34"/>
+      <c r="A34" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35"/>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0CC7536-E119-4CA7-A606-6AE585BD0316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4916C1DC-5675-483A-8643-617F6FACD9D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28875" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envio Robô" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="36">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -51,193 +51,100 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>gabriela.logrado@allianz.com.br</t>
-  </si>
-  <si>
     <t>juliano.guimaraes@allianz.com.br</t>
   </si>
   <si>
     <t>priscila.rubio@allianz.com.br</t>
   </si>
   <si>
-    <t>dayane.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>ana.brito@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12871786700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>adriana.coelho@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12861424000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>irene.rosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12962742200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>erica.cassandre@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12886745100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12951564800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>tatiany.macedo@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12961277900000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>priscila.sousa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12961661600000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>juliana.diniz@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12954183300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>renata.matheus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12960646400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
     <t>gisele.cardoso1@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-8188848000106 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-88818399800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>monica.betoni@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12961704300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-10248580000194 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>rodrigo.kuguyama@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12791946400000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>talita.meneses@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12921221900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>rosilene.nogueira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12961409400000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>ana.cunha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12779301000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>diogo.junior@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12730315600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-88818634100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>marcus.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12955541500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>fernanda.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12961881300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12960974000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>geiza.vinand@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12936696600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>pedro.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12957197300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>jacqueline.mendes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12962530400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>aparecida.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-8355189655 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>thays.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12674811400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>eduardo.santos1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12948003300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>laila.steil@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12961336500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>adriana.abreu@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12840224000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>jose.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12326670800000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>carlos.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12121449200000 Nota 242 - Retorno Cobrança</t>
+    <t>tadeu.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12967808700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>renato.lopes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12956600700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>valdirene.barbosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12735673400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12961609100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>luiz.junior@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-52113594000140 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>daniel.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12859434300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-56797583000188 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>gisele.mazzucco@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12959757700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12955324000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>viviane.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12505382500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12946715700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>flavio.funke@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12739835000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>douglas.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12955710800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>laiane.martins@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12934924200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>luiz.sanchetta@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12682469400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>carla.catalani@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12947054100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
   </si>
 </sst>
 </file>
@@ -670,10 +577,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -681,7 +588,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
         <v>16</v>
@@ -703,10 +610,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
         <v>19</v>
-      </c>
-      <c r="B8" t="s">
-        <v>20</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -714,10 +621,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" t="s">
         <v>21</v>
-      </c>
-      <c r="B9" t="s">
-        <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -725,10 +632,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -736,10 +643,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -747,10 +654,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" t="s">
         <v>25</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -758,10 +665,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -769,10 +676,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -780,10 +687,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>30</v>
+      </c>
+      <c r="B15" t="s">
         <v>31</v>
-      </c>
-      <c r="B15" t="s">
-        <v>32</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -791,10 +698,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" t="s">
         <v>33</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -802,201 +709,82 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" t="s">
         <v>35</v>
       </c>
-      <c r="B17" t="s">
-        <v>36</v>
-      </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A18"/>
+      <c r="B18"/>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A19"/>
+      <c r="B19"/>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" t="s">
-        <v>41</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A20"/>
+      <c r="B20"/>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A21"/>
+      <c r="B21"/>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A22"/>
+      <c r="B22"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A23"/>
+      <c r="B23"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" t="s">
-        <v>48</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A24"/>
+      <c r="B24"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>49</v>
-      </c>
-      <c r="B25" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A25"/>
+      <c r="B25"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>51</v>
-      </c>
-      <c r="B26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A26"/>
+      <c r="B26"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A27"/>
+      <c r="B27"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>55</v>
-      </c>
-      <c r="B28" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A28"/>
+      <c r="B28"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>57</v>
-      </c>
-      <c r="B29" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A29"/>
+      <c r="B29"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>59</v>
-      </c>
-      <c r="B30" t="s">
-        <v>60</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A30"/>
+      <c r="B30"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31" t="s">
-        <v>62</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A31"/>
+      <c r="B31"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>63</v>
-      </c>
-      <c r="B32" t="s">
-        <v>64</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A32"/>
+      <c r="B32"/>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>65</v>
-      </c>
-      <c r="B33" t="s">
-        <v>66</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A33"/>
+      <c r="B33"/>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>65</v>
-      </c>
-      <c r="B34" t="s">
-        <v>64</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A34"/>
+      <c r="B34"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35"/>
@@ -1439,31 +1227,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAzNTMxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MzAvMTIvMjAyMCAxMTo0NTo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAzMC8xMi8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41A8E509-6991-4B84-B1B5-13851E156C6A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DBFCB3-53E5-4527-B13D-DC7A854D4B55}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41A8E509-6991-4B84-B1B5-13851E156C6A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4916C1DC-5675-483A-8643-617F6FACD9D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A90B972-94FD-4171-A0F4-AC58673BD294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28980" windowHeight="14460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envio Robô" sheetId="2" r:id="rId1"/>
@@ -30,6 +30,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="68">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -51,107 +53,205 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>juliano.guimaraes@allianz.com.br</t>
-  </si>
-  <si>
     <t>priscila.rubio@allianz.com.br</t>
   </si>
   <si>
-    <t>tatiany.macedo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>gisele.cardoso1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>tadeu.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12967808700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>renato.lopes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12956600700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>valdirene.barbosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12735673400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12961609100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>luiz.junior@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-52113594000140 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daniel.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12859434300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-56797583000188 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>gisele.mazzucco@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12959757700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12955324000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>viviane.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12505382500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12946715700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>flavio.funke@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12739835000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>douglas.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12955710800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>laiane.martins@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12934924200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>luiz.sanchetta@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12682469400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>carla.catalani@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12947054100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>eliana.pedroso@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12557957400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>diego.vasconcelos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12941003600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>caroline.falcao@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12966387900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>fernando.martins1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12716572500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>priscila.santana@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12898834600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12966016600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>monica.betoni@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12963690400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>angela.carmo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12828515500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>luciana.belisario@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12965887800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>talita.meneses@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12938446300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12947268400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12947402500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>leandro.santos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12952663100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>saulo.santiago@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-40155388000114 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>armando.filho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12650420000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>vitor.mattos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12683799900000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12921336700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>ana.cunha@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12779301000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>lucas.godinho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12959250700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>nathalie.carmo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12963552000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>fernanda.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12961357100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>gabriela.logrado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12965375500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12965938200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12966008100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12966087000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12966310500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12966377100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12966416200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>enriete.saucedo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-10189820000127 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>eduardo.santos1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-80712754091 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rosana.pessoa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12954815100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12963483300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>janaina.cazelato@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12941922100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>naiara.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12841033500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>segurosconclusiva@gmail.com</t>
+  </si>
+  <si>
+    <t>dalmo@dalmoseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126313453 - AUREA ANTONIA COSTA BRILHANTE</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126627209 - GISLEINE VIEIRA DE OLIVEIRA BOSQUIM</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 10 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pag</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 9 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao paga</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -167,8 +267,120 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -181,8 +393,176 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -190,11 +570,103 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -202,6 +674,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -544,10 +1019,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -555,10 +1030,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -566,10 +1041,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -577,10 +1052,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -588,10 +1063,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -599,10 +1074,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -610,10 +1085,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -621,10 +1096,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -632,10 +1107,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -643,10 +1118,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
         <v>23</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -654,10 +1129,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -665,10 +1140,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -676,10 +1151,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -687,10 +1162,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -698,10 +1173,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -709,94 +1184,234 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" t="s">
+        <v>33</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>30</v>
+      </c>
+      <c r="B18" t="s">
         <v>34</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C18" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18"/>
-      <c r="B18"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19"/>
-      <c r="B19"/>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20"/>
-      <c r="B20"/>
+      <c r="A20" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21"/>
-      <c r="B21"/>
+      <c r="A21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B21" t="s">
+        <v>40</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22"/>
-      <c r="B22"/>
+      <c r="A22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23"/>
-      <c r="B23"/>
+      <c r="A23" t="s">
+        <v>43</v>
+      </c>
+      <c r="B23" t="s">
+        <v>44</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24"/>
-      <c r="B24"/>
+      <c r="A24" t="s">
+        <v>43</v>
+      </c>
+      <c r="B24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25"/>
-      <c r="B25"/>
+      <c r="A25" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26"/>
-      <c r="B26"/>
+      <c r="A26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27"/>
-      <c r="B27"/>
+      <c r="A27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" t="s">
+        <v>48</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28"/>
-      <c r="B28"/>
+      <c r="A28" t="s">
+        <v>43</v>
+      </c>
+      <c r="B28" t="s">
+        <v>49</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29"/>
-      <c r="B29"/>
+      <c r="A29" t="s">
+        <v>43</v>
+      </c>
+      <c r="B29" t="s">
+        <v>50</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30"/>
-      <c r="B30"/>
+      <c r="A30" t="s">
+        <v>51</v>
+      </c>
+      <c r="B30" t="s">
+        <v>52</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31"/>
-      <c r="B31"/>
+      <c r="A31" t="s">
+        <v>53</v>
+      </c>
+      <c r="B31" t="s">
+        <v>54</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32"/>
-      <c r="B32"/>
+      <c r="A32" t="s">
+        <v>55</v>
+      </c>
+      <c r="B32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33"/>
-      <c r="B33"/>
+      <c r="A33" t="s">
+        <v>55</v>
+      </c>
+      <c r="B33" t="s">
+        <v>57</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34"/>
-      <c r="B34"/>
+      <c r="A34" t="s">
+        <v>58</v>
+      </c>
+      <c r="B34" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35"/>
-      <c r="B35"/>
+      <c r="A35" t="s">
+        <v>60</v>
+      </c>
+      <c r="B35" t="s">
+        <v>61</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36"/>
-      <c r="B36"/>
+      <c r="A36" t="s">
+        <v>62</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37"/>
-      <c r="B37"/>
+      <c r="A37" t="s">
+        <v>63</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38"/>
@@ -1227,31 +1842,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAzNTMxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MzAvMTIvMjAyMCAxMTo0NTo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAzMC8xMi8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAzNTMxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MzAvMTIvMjAyMCAxMTo0NTo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAzMC8xMi8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DBFCB3-53E5-4527-B13D-DC7A854D4B55}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41A8E509-6991-4B84-B1B5-13851E156C6A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DBFCB3-53E5-4527-B13D-DC7A854D4B55}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A90B972-94FD-4171-A0F4-AC58673BD294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43DD5149-28BB-4D50-93B6-3E616D6496BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28980" windowHeight="14460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envio Robô" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="57">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -53,205 +53,170 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>priscila.rubio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>eliana.pedroso@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12557957400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>diego.vasconcelos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12941003600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>caroline.falcao@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12966387900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>fernando.martins1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12716572500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>priscila.santana@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12898834600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12966016600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>monica.betoni@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12963690400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>angela.carmo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12828515500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>luciana.belisario@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12965887800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>talita.meneses@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12938446300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12947268400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12947402500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>leandro.santos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12952663100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>saulo.santiago@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-40155388000114 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>armando.filho@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12650420000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>vitor.mattos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12683799900000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12921336700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>ana.cunha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12779301000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>lucas.godinho@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12959250700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>nathalie.carmo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12963552000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>fernanda.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12961357100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12965375500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12965938200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12966008100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12966087000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12966310500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12966377100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12966416200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
     <t>enriete.saucedo@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-10189820000127 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>eduardo.santos1@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-80712754091 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>rosana.pessoa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12954815100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12963483300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>janaina.cazelato@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12941922100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>naiara.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12841033500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>segurosconclusiva@gmail.com</t>
-  </si>
-  <si>
-    <t>dalmo@dalmoseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126313453 - AUREA ANTONIA COSTA BRILHANTE</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126627209 - GISLEINE VIEIRA DE OLIVEIRA BOSQUIM</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 10 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pag</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 9 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao paga</t>
+    <t>rubiane.bendlin@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12885588600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>jaciely.dias@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12939095600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>raquel.sech@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12947118700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12961377000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12796194400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>renata.matheus@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12557973300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>renata.magalhaes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12941992700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>isabel.cit@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12967553900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>laiane.martins@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12934924200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>flavia.costa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12968357500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12968387300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>luiz.sanchetta@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12967916400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12694728700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12964921900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12965071100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12965130900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12965216100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12965259000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12965398900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12966301600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12966451000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12967114500000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12967264900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12968316600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12968727600000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12968773800000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12969027300000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12969453200000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12969877200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12970122300000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12970162000000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>wagner.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-35364895831 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>filipe.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12153705700000 Nota 595 - ERRO PDF retrono</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12153719700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12824886100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12844601500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>carlos.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12246736700000 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -267,120 +232,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -393,273 +246,13 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.39997558519241921"/>
-        <bgColor indexed="65"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thick">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1019,10 +612,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -1030,10 +623,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -1041,10 +634,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -1052,10 +645,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -1063,10 +656,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -1074,10 +667,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -1085,10 +678,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -1096,10 +689,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -1107,10 +700,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -1118,10 +711,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -1129,10 +722,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -1140,10 +733,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -1151,10 +744,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -1162,10 +755,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>28</v>
+        <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -1173,7 +766,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="B16" t="s">
         <v>31</v>
@@ -1184,10 +777,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" t="s">
         <v>32</v>
-      </c>
-      <c r="B17" t="s">
-        <v>33</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -1195,10 +788,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -1206,10 +799,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -1217,10 +810,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -1228,10 +821,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -1239,10 +832,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -1250,10 +843,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -1261,10 +854,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
@@ -1272,10 +865,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -1283,10 +876,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B26" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
@@ -1294,10 +887,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -1305,10 +898,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>5</v>
+      </c>
+      <c r="B28" t="s">
         <v>43</v>
-      </c>
-      <c r="B28" t="s">
-        <v>49</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>3</v>
@@ -1316,10 +909,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B29" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>3</v>
@@ -1327,10 +920,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>51</v>
+        <v>5</v>
       </c>
       <c r="B30" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>3</v>
@@ -1338,10 +931,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
       <c r="B31" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>3</v>
@@ -1349,10 +942,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="B32" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>3</v>
@@ -1360,10 +953,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>3</v>
@@ -1371,10 +964,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="B34" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>3</v>
@@ -1382,10 +975,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B35" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>3</v>
@@ -1393,29 +986,36 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>62</v>
+        <v>7</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>66</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>63</v>
+        <v>6</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>67</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38"/>
-      <c r="B38"/>
+      <c r="A38" t="s">
+        <v>55</v>
+      </c>
+      <c r="B38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39"/>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A18C04F-5231-4AA6-A4CA-C34C4784A7E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A6886B-0C1B-4158-A252-2CA7A9BDB793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28965" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envio Robô" sheetId="2" r:id="rId1"/>
@@ -53,9 +53,6 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>priscila.santana@allianz.com.br</t>
-  </si>
-  <si>
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
@@ -65,166 +62,169 @@
     <t>adriano.guerra@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12971296100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>diego.vasconcelos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12972187000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>lucineide.medeiros@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-88528014720 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>kaue.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-36385637824 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>eduardo.olicshevis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12972496100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>daniela.leal@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12669990000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12971845600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>afonso.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12966127600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>janaina.moura@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12971825200000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
     <t>rodrigo.kuguyama@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12843725200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12969315900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>viviane.corbari@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12969638400000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>vitor.mattos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12963489600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>andreia.cardias@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-47219920091 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>rosilene.nogueira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12904910000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
     <t>fernanda.oliveira@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12972105100000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12962263400000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12968728000000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12969014500000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12969017300000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12969598000000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12969997700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12970125000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>geiza.vinand@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12818683600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>jacqueline.mendes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12971306900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12971320300000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>bruna.carneiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12552799700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>rafael.leite@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12968973900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
     <t>daisy.marangoni@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-15709400000148 Nota 127 - Retorno de solicitação Produto Automóvel</t>
-  </si>
-  <si>
     <t>carla.catalani@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12948015600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>thaiana.felipe@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12922301000000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>naiara.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12929359400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12730405600000 Nota 242 - Retorno Cobrança</t>
+    <t>Retorno de GO referência-12946541200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>valdirene.barbosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12971003900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>erica.cassandre@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12942600900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>juliano.guimaraes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12833791300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12907620500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>claudia.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12969291000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>kaue.medeiros@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12964806400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>cleyciane.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12971105100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12971580400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12972129600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>gisele.cardoso1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-52910023000137 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>viviane.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12505382500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>claudia.gomes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12954469900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12974097100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>fernanda.carneiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12963894600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>endyane.marques@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12770014200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>andrea.duarte@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12966053300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>gustavo.arruda@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12953820600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12973426800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12974842000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12964489500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12965785100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12969170400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12973345100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>carla.nascimento@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12965782200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12790623500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>thays.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12973663700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-70883548968 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>laerte.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12857976400000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12535202000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12947054100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>karina.vieira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12485914800000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-10246495900000 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -627,10 +627,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -638,10 +638,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -649,10 +649,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -660,10 +660,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -671,10 +671,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -682,10 +682,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -693,10 +693,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -704,10 +704,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -715,10 +715,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -729,7 +729,7 @@
         <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -737,10 +737,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -748,10 +748,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -759,10 +759,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -770,10 +770,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -792,10 +792,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -803,10 +803,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -814,10 +814,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -825,10 +825,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -836,10 +836,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -847,10 +847,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -858,10 +858,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B23" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
@@ -880,10 +880,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="B25" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -891,10 +891,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B26" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
@@ -902,10 +902,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -913,10 +913,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B28" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>3</v>
@@ -924,10 +924,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>3</v>
@@ -935,10 +935,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B30" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>3</v>
@@ -946,10 +946,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="B31" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>3</v>
@@ -957,7 +957,7 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>57</v>
+        <v>11</v>
       </c>
       <c r="B32" t="s">
         <v>58</v>
@@ -979,7 +979,7 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B34" t="s">
         <v>61</v>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68A6886B-0C1B-4158-A252-2CA7A9BDB793}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E42F5A-A4CC-4F72-85D6-C7CD9876F412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28965" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envio Robô" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="64">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -56,175 +56,181 @@
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
-    <t>carlos.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>adriano.guerra@allianz.com.br</t>
-  </si>
-  <si>
-    <t>rodrigo.kuguyama@allianz.com.br</t>
-  </si>
-  <si>
-    <t>fernanda.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>rafael.leite@allianz.com.br</t>
-  </si>
-  <si>
-    <t>daisy.marangoni@allianz.com.br</t>
-  </si>
-  <si>
-    <t>carla.catalani@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12946541200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>valdirene.barbosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12971003900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>erica.cassandre@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12942600900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>juliano.guimaraes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12833791300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12907620500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>claudia.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12969291000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>kaue.medeiros@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12964806400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>cleyciane.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12971105100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12971580400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12972129600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>gisele.cardoso1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-52910023000137 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>viviane.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12505382500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>claudia.gomes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12954469900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12974097100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>fernanda.carneiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12963894600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>endyane.marques@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12770014200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>andrea.duarte@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12966053300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>gustavo.arruda@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12953820600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12973426800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12974842000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12964489500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12965785100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12969170400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12973345100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>carla.nascimento@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12965782200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12790623500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>thays.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12973663700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-70883548968 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>laerte.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12857976400000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12535202000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12947054100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>karina.vieira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12485914800000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-10246495900000 Nota 242 - Retorno Cobrança</t>
+    <t>tadeu.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12969686600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>danielle.nascimento@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12683484300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>fernando.duque@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12940757200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>raquel.sech@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12704338400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>fausto.reis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12955863800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>william.bichet@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12965055400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>lucas.almeida@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12958578700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>priscila.rubio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-7657649000129 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>talita.meneses@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12876115400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>isabel.cit@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12943586700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>vitor.mattos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12973012100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>andreia.cardias@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-47219920091 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rosilene.nogueira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-88818787400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>pamela.burige@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12975390700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11376374600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12968229300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12972347300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12974014800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12974042000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12974956500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12975695300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12975788400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12975962300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12975977600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12976073200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12976274000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12976274200000 Nota 595 - ERRO PDF Retorno retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12976281200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>geiza.vinand@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12973341800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>patricia.soares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12882609500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>andrea.farias1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12967528900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>marli.rocha@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12522629900000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>ivone.jesus@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12782527100000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>weldja.bozi@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12831419500000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12882709300000 Nota 167 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>juliana.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-38053722000187 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>ana.carneiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-61574273000134 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -603,7 +609,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:C170"/>
+  <dimension ref="A1:C138"/>
   <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="55.5703125" style="2" customWidth="1"/>
@@ -627,10 +633,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
         <v>6</v>
-      </c>
-      <c r="B2" t="s">
-        <v>12</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -638,10 +644,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -649,10 +655,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
+        <v>9</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -660,10 +666,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B5" t="s">
-        <v>18</v>
+        <v>11</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -671,10 +677,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -682,10 +688,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -693,10 +699,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -704,10 +710,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -715,10 +721,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -726,10 +732,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
         <v>24</v>
-      </c>
-      <c r="B11" t="s">
-        <v>27</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -737,10 +743,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -748,10 +754,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -759,10 +765,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -770,10 +776,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -781,10 +787,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -792,10 +798,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -803,10 +809,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>39</v>
+        <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -814,288 +820,300 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C24" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>8</v>
-      </c>
-      <c r="B20" t="s">
+      <c r="C25" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" t="s">
+      <c r="C26" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="C27" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B28" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="C28" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B29" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" t="s">
+      <c r="C29" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C24" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="B30" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C25" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="C30" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B31" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" t="s">
+      <c r="C31" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="B32" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C32" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>10</v>
-      </c>
-      <c r="B29" t="s">
+      <c r="B33" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="C29" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+      <c r="C33" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B34" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="C30" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>11</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="C34" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>11</v>
-      </c>
-      <c r="B32" t="s">
+      <c r="B35" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
+      <c r="C35" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B33" t="s">
+      <c r="C36" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C33" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>5</v>
-      </c>
-      <c r="B34" t="s">
+      <c r="B37" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35"/>
-      <c r="B35"/>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36"/>
-      <c r="B36" s="4"/>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37"/>
+      <c r="C37" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38"/>
-      <c r="B38"/>
+      <c r="A38" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39"/>
-      <c r="B39"/>
+      <c r="C39" s="3"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40"/>
-      <c r="B40"/>
+      <c r="C40" s="3"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41"/>
-      <c r="B41"/>
+      <c r="C41" s="3"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42"/>
-      <c r="B42"/>
+      <c r="C42" s="3"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43"/>
-      <c r="B43"/>
+      <c r="C43" s="3"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44"/>
-      <c r="B44"/>
+      <c r="C44" s="3"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45"/>
-      <c r="B45"/>
+      <c r="C45" s="3"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46"/>
-      <c r="B46"/>
+      <c r="C46" s="3"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47"/>
-      <c r="B47"/>
+      <c r="C47" s="3"/>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48"/>
-      <c r="B48"/>
       <c r="C48" s="3"/>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49"/>
-      <c r="B49"/>
+    <row r="49" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C49" s="3"/>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50"/>
-      <c r="B50"/>
+    <row r="50" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C50" s="3"/>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51"/>
-      <c r="B51"/>
+    <row r="51" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C51" s="3"/>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C52" s="3"/>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C53" s="3"/>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C54" s="3"/>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C55" s="3"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C56" s="3"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C57" s="3"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C58" s="3"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C59" s="3"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C60" s="3"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C61" s="3"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C62" s="3"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C63" s="3"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C64" s="3"/>
     </row>
     <row r="65" spans="3:3" x14ac:dyDescent="0.25">
@@ -1319,102 +1337,6 @@
     </row>
     <row r="138" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C138" s="3"/>
-    </row>
-    <row r="139" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C139" s="3"/>
-    </row>
-    <row r="140" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C140" s="3"/>
-    </row>
-    <row r="141" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C141" s="3"/>
-    </row>
-    <row r="142" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C142" s="3"/>
-    </row>
-    <row r="143" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C143" s="3"/>
-    </row>
-    <row r="144" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C144" s="3"/>
-    </row>
-    <row r="145" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C145" s="3"/>
-    </row>
-    <row r="146" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C146" s="3"/>
-    </row>
-    <row r="147" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C147" s="3"/>
-    </row>
-    <row r="148" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C148" s="3"/>
-    </row>
-    <row r="149" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C149" s="3"/>
-    </row>
-    <row r="150" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C150" s="3"/>
-    </row>
-    <row r="151" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C151" s="3"/>
-    </row>
-    <row r="152" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C152" s="3"/>
-    </row>
-    <row r="153" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C153" s="3"/>
-    </row>
-    <row r="154" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C154" s="3"/>
-    </row>
-    <row r="155" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C155" s="3"/>
-    </row>
-    <row r="156" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C156" s="3"/>
-    </row>
-    <row r="157" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C157" s="3"/>
-    </row>
-    <row r="158" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C158" s="3"/>
-    </row>
-    <row r="159" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C159" s="3"/>
-    </row>
-    <row r="160" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C160" s="3"/>
-    </row>
-    <row r="161" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C161" s="3"/>
-    </row>
-    <row r="162" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C162" s="3"/>
-    </row>
-    <row r="163" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C163" s="3"/>
-    </row>
-    <row r="164" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C164" s="3"/>
-    </row>
-    <row r="165" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C165" s="3"/>
-    </row>
-    <row r="166" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C166" s="3"/>
-    </row>
-    <row r="167" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C167" s="3"/>
-    </row>
-    <row r="168" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C168" s="3"/>
-    </row>
-    <row r="169" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C169" s="3"/>
-    </row>
-    <row r="170" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C170" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Envio de e-mail retorno GO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83E42F5A-A4CC-4F72-85D6-C7CD9876F412}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6B7158-E2D9-4865-A8BC-E4DA5E77857B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="204">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -59,178 +59,652 @@
     <t>tadeu.silva@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12969686600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>danielle.nascimento@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12683484300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>fernando.duque@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12940757200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>raquel.sech@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12704338400000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>fausto.reis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12955863800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>william.bichet@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12965055400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
     <t>lucas.almeida@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12958578700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>priscila.rubio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-7657649000129 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>talita.meneses@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12876115400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>isabel.cit@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12943586700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>vitor.mattos@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12973012100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>andreia.cardias@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-47219920091 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>rosilene.nogueira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-88818787400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>pamela.burige@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12975390700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11376374600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12968229300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12972347300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12974014800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12974042000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12974956500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12975695300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12975788400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12975962300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12975977600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12976073200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12976274000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12976274200000 Nota 595 - ERRO PDF Retorno retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12976281200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>geiza.vinand@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12973341800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>patricia.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12882609500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>andrea.farias1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12967528900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>marli.rocha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12522629900000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
     <t>ivone.jesus@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12782527100000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>weldja.bozi@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12831419500000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12882709300000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
     <t>juliana.silva@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-38053722000187 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>ana.carneiro@allianz.com.br</t>
   </si>
   <si>
     <t>Retorno de GO referência-61574273000134 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12586974000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>lilian.sudati@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12650838100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>renato.lopes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12965737800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>caroline.falcao@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-9385813000111 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>erica.cassandre@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12972621100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>claudia.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12438310900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12914148600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12657647800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>priscila.sousa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12974928600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>wagner.simon@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-75203000147 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>viviane.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12505382500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>eduardo.marques@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12968506500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12964849500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>andreia.brixner@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12966004000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12683799900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rodrigo.deus@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12970983200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>rosana.teixeira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12968880300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>daniele.beck@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12699647500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12845224700000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12934531200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12934557200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12974931500000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12977118100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12977351900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12977470400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12977576600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12978071700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12978170100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>enriete.saucedo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12946336000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12760826600000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12825472200000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>ana.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12963651400000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>lucidene.santana@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12965055400000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>claudenice.barbosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12977470400000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>anderson.menezes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12788428800000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12846347000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12902410200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12934794100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>alessandra.guedes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-1689588000103 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>carlos.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11442837500000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>elaine.coelho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12812131600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>renovacaoseguros@honda.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126315681 - NEIDE MARIA SILVA CERQUEIRA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 10 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>suporte.vvd@vwfs.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126371524 - WELTON AREDES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126383139 - FERNANDO LUIS MARQUES</t>
+  </si>
+  <si>
+    <t>hodieseg@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126692691 - MARIO LUIS DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 9 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>maiseguros@maiseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126688808 - ANA LUCIA TAVARES DA SILVA</t>
+  </si>
+  <si>
+    <t>backoffice.corretora@yamaha-motor.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126707646 - MONIQUE IARA ARAUJO DE CAMPOS</t>
+  </si>
+  <si>
+    <t>backofficecorretora@segurostoyota.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126985448 - LEONARDO FERREIRA BRAGA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 8 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>luizdall@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127009416 - PAULA CAROLINA GHELLER</t>
+  </si>
+  <si>
+    <t>kassia@kmcor.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127310412 - LEILA OLIVEIRA CARDOSO</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127336535 - EDNA DE MOURA</t>
+  </si>
+  <si>
+    <t>ciraganseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127308581 - ANTONIO MARCOS PEREIRA DE ALMEIDA JUNIOR</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127350350 - BRUNO DOS SANTOS COSTA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127604612 - DALVA REGINA AMARAL TEIXEIRA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 6 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127656322 - JOAO VICTOR FERREIRA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>fred@quintellaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127898696 - MARIA DO SOCORRO RODRIGUES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>aoseguros@aoseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127912076 - ELISA BUSCACIO BONATO</t>
+  </si>
+  <si>
+    <t>reinaldo.alves@carmais.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127858684 - JEFFERSON MARINHO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>ciasdaconseg@wiz.co</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127969280 - IRAN CARLOS BORGES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127996621 - JEAN CARLO ANTUNES DE SOUZA</t>
+  </si>
+  <si>
+    <t>adriana.faria@jorlan.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128145728 - NILZA AMORIM PEREIRA FROIS</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>cristina@assuntacorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128235742 - LUIZ HENRIQUE ARCHILHA</t>
+  </si>
+  <si>
+    <t>mauriciocuriseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128669609 - MARIA AMELIA DE AZAMBUJA MACEDO ROSA E SILVA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 3 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>wfgseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128794884 - ANA MARIA PALADINO</t>
+  </si>
+  <si>
+    <t>carrerocorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128813663 - JORGE ASSAMU MORI</t>
+  </si>
+  <si>
+    <t>fernandobueno@aspiral.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128843918 - CARLA GARRAFOLI</t>
+  </si>
+  <si>
+    <t>totalcorretora.jaru@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127988891 - MISAEL DE LUCA COSTA</t>
+  </si>
+  <si>
+    <t>aluguel@palavraseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128836603 - ANDRE LUIZ LINS GONCALEZ</t>
+  </si>
+  <si>
+    <t>raul@ruralmaxseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128834079 - ADOLFO FARIAS DOS SANTOS</t>
+  </si>
+  <si>
+    <t>andre.oliveira@braseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128760161 - DAVID BELO FONSECA</t>
+  </si>
+  <si>
+    <t>pendencia@seguralta.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128935266 - JOSE CLOVIS DA SILVA BARBOSA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 2 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>olbencor@terra.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129299305 - JUAN JENETON JORGE</t>
+  </si>
+  <si>
+    <t>chsseguros@outlook.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126269448 - DANIELI DE CASTRO BISSOLI</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126350938 - GIULLBER VALENTIM DA SILVA</t>
+  </si>
+  <si>
+    <t>talita@serranacorretora.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127260576 - PRICILA LOPES DOS SANTOS DOTTO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127338296 - LUCIANA FELIX GONCALVES PINTO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127343374 - JOSEILDO DOMINGOS DOS SANTOS</t>
+  </si>
+  <si>
+    <t>contato@bragseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127348557 - MARINA EDNA CAMPOS</t>
+  </si>
+  <si>
+    <t>pendencias@rbmseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127315947 - JOSEANE PARELLADA BRANDT</t>
+  </si>
+  <si>
+    <t>contato@vnseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127349346 - WALDEMAR NAZARENO AIRES CARDOSO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127883748 - MARCIA APARECIDA SILVA ERHARDT</t>
+  </si>
+  <si>
+    <t>juliana@maisgarraseguros.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127962814 - MARIA CAROLINA BUCAR BAHIA</t>
+  </si>
+  <si>
+    <t>vapt.seguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127957385 - DELANIA FRANCISCA DA ROCHA</t>
+  </si>
+  <si>
+    <t>sustentare@sustentareseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127981069 - MARCIANA MACHADO MENEGAZ</t>
+  </si>
+  <si>
+    <t>pina@brunosilvaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127981047 - HENRIQUE MIRANDA DO CARMO</t>
+  </si>
+  <si>
+    <t>contato@cardosoribeiroseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127981042 - MARIA ANA DE JESUS MACEDO SANTOS</t>
+  </si>
+  <si>
+    <t>gustavo@gcan.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127980962 - MARIA DO SOCORRO CARLOS</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128310469 - NERIO DA SILVA CONSOLI</t>
+  </si>
+  <si>
+    <t>3c@seguros3c.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128326041 - IZABELA RODRIGUES DA SILVA FREIRE</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128372092 - RENATO BRAGANCA FERNANDES</t>
+  </si>
+  <si>
+    <t>lidercorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128308268 - MARIA GOMES VIEIRA SANTOS</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128381505 - ARTUR OLIVEIRA PIRES</t>
+  </si>
+  <si>
+    <t>joana@balsano.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127638499 - ANTONIO VITOR TUCHINSKI</t>
+  </si>
+  <si>
+    <t>diretoria@lapisbellus.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126350664 - DOUGLAS SOLEDADE DA SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126674196 - ANTONIO CARLOS DE FONTES</t>
+  </si>
+  <si>
+    <t>sudeste@sudesteseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126704888 - TANISE RODRIGUES DA SILVA FONTES</t>
+  </si>
+  <si>
+    <t>gilsoncaet@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126884194 - GILSON CAETANO DA SILVA</t>
+  </si>
+  <si>
+    <t>marcozzicorretora@yahoo.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126962161 - JOSE TELMO MONTEIRO DE ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>seg.cac@terra.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126969832 - JEAN ONESIMO FERREIRA DA COSTA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126990070 - JAIRO IZIDIO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>juliobairros@terra.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126995774 - LUIZ AFONSO E SILVA MACHADO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127315618 - TIELE DENISE NOGUEIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127316956 - VITORIA ALVES ROQUE DA SILVA</t>
+  </si>
+  <si>
+    <t>cvf.corretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127323098 - CARLA DE FREITAS QUADROS COSTA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127307913 - SOLANGE SOUZA ARAUJO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127332577 - HAMILTON MOREIRA BARROS JUNIOR</t>
+  </si>
+  <si>
+    <t>madalozzo@madalozzocorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127954387 - FERNANDA FANTINELLI RIBEIRO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128367317 - LIDIANE TORMENA CAVALCANTE</t>
+  </si>
+  <si>
+    <t>emissao@segurosarinos.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128349358 - SERGIO ARMANDO MARTINHO FERREIRA</t>
+  </si>
+  <si>
+    <t>trevigo@trevigo.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129212989 - MARIA NEUSA RUSSI</t>
+  </si>
+  <si>
+    <t>ana.cezaro@terra.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129247740 - RENE PAULO ROSSI</t>
   </si>
 </sst>
 </file>
@@ -609,7 +1083,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:C138"/>
+  <dimension ref="A1:C183"/>
   <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="55.5703125" style="2" customWidth="1"/>
@@ -636,7 +1110,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -644,10 +1118,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -655,10 +1129,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -666,10 +1140,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -677,10 +1151,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -688,10 +1162,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -699,10 +1173,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -710,10 +1184,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -721,10 +1195,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -732,10 +1206,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -743,10 +1217,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -754,10 +1228,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -765,10 +1239,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -776,10 +1250,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -787,10 +1261,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -798,10 +1272,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -809,10 +1283,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -820,10 +1294,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -834,7 +1308,7 @@
         <v>4</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -845,7 +1319,7 @@
         <v>4</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -856,7 +1330,7 @@
         <v>4</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -867,7 +1341,7 @@
         <v>4</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -878,7 +1352,7 @@
         <v>4</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
@@ -889,7 +1363,7 @@
         <v>4</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -900,7 +1374,7 @@
         <v>4</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
@@ -911,7 +1385,7 @@
         <v>4</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -922,7 +1396,7 @@
         <v>4</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>3</v>
@@ -933,7 +1407,7 @@
         <v>4</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>3</v>
@@ -941,10 +1415,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>3</v>
@@ -952,10 +1426,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>49</v>
+        <v>9</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>3</v>
@@ -963,10 +1437,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>51</v>
+        <v>9</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>3</v>
@@ -974,10 +1448,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>3</v>
@@ -985,10 +1459,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>3</v>
@@ -996,10 +1470,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>3</v>
@@ -1007,10 +1481,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>3</v>
@@ -1018,10 +1492,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>3</v>
@@ -1029,314 +1503,1609 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C39" s="3"/>
+      <c r="A39" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C40" s="3"/>
+      <c r="A40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C41" s="3"/>
+      <c r="A41" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C42" s="3"/>
+      <c r="A42" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C43" s="3"/>
+      <c r="A43" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C44" s="3"/>
+      <c r="A44" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C45" s="3"/>
+      <c r="A45" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C46" s="3"/>
+      <c r="A46" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C47" s="3"/>
+      <c r="A47" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>83</v>
+      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C48" s="3"/>
-    </row>
-    <row r="49" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C49" s="3"/>
-    </row>
-    <row r="50" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C50" s="3"/>
-    </row>
-    <row r="51" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C51" s="3"/>
-    </row>
-    <row r="52" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C52" s="3"/>
-    </row>
-    <row r="53" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C53" s="3"/>
-    </row>
-    <row r="54" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C54" s="3"/>
-    </row>
-    <row r="55" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C55" s="3"/>
-    </row>
-    <row r="56" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C56" s="3"/>
-    </row>
-    <row r="57" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C57" s="3"/>
-    </row>
-    <row r="58" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C58" s="3"/>
-    </row>
-    <row r="59" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C59" s="3"/>
-    </row>
-    <row r="60" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C60" s="3"/>
-    </row>
-    <row r="61" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C61" s="3"/>
-    </row>
-    <row r="62" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C62" s="3"/>
-    </row>
-    <row r="63" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C63" s="3"/>
-    </row>
-    <row r="64" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C64" s="3"/>
-    </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C65" s="3"/>
-    </row>
-    <row r="66" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C66" s="3"/>
-    </row>
-    <row r="67" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C67" s="3"/>
-    </row>
-    <row r="68" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C68" s="3"/>
-    </row>
-    <row r="69" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C69" s="3"/>
-    </row>
-    <row r="70" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C70" s="3"/>
-    </row>
-    <row r="71" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C71" s="3"/>
-    </row>
-    <row r="72" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C72" s="3"/>
-    </row>
-    <row r="73" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C73" s="3"/>
-    </row>
-    <row r="74" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C74" s="3"/>
-    </row>
-    <row r="75" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C75" s="3"/>
-    </row>
-    <row r="76" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C76" s="3"/>
-    </row>
-    <row r="77" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C77" s="3"/>
-    </row>
-    <row r="78" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C78" s="3"/>
-    </row>
-    <row r="79" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C79" s="3"/>
-    </row>
-    <row r="80" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C80" s="3"/>
-    </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C81" s="3"/>
-    </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C82" s="3"/>
-    </row>
-    <row r="83" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C83" s="3"/>
-    </row>
-    <row r="84" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C84" s="3"/>
-    </row>
-    <row r="85" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C85" s="3"/>
-    </row>
-    <row r="86" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C86" s="3"/>
-    </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C87" s="3"/>
-    </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C88" s="3"/>
-    </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C89" s="3"/>
-    </row>
-    <row r="90" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C90" s="3"/>
-    </row>
-    <row r="91" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C91" s="3"/>
-    </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C92" s="3"/>
-    </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C93" s="3"/>
-    </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C94" s="3"/>
-    </row>
-    <row r="95" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C95" s="3"/>
-    </row>
-    <row r="96" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C96" s="3"/>
-    </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C97" s="3"/>
-    </row>
-    <row r="98" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C98" s="3"/>
-    </row>
-    <row r="99" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C99" s="3"/>
-    </row>
-    <row r="100" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C100" s="3"/>
-    </row>
-    <row r="101" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C101" s="3"/>
-    </row>
-    <row r="102" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C102" s="3"/>
-    </row>
-    <row r="103" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C103" s="3"/>
-    </row>
-    <row r="104" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C104" s="3"/>
-    </row>
-    <row r="105" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C105" s="3"/>
-    </row>
-    <row r="106" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C106" s="3"/>
-    </row>
-    <row r="107" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C107" s="3"/>
-    </row>
-    <row r="108" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C108" s="3"/>
-    </row>
-    <row r="109" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C109" s="3"/>
-    </row>
-    <row r="110" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C110" s="3"/>
-    </row>
-    <row r="111" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C111" s="3"/>
-    </row>
-    <row r="112" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C112" s="3"/>
-    </row>
-    <row r="113" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C113" s="3"/>
-    </row>
-    <row r="114" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C114" s="3"/>
-    </row>
-    <row r="115" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C115" s="3"/>
-    </row>
-    <row r="116" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C116" s="3"/>
-    </row>
-    <row r="117" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C117" s="3"/>
-    </row>
-    <row r="118" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C118" s="3"/>
-    </row>
-    <row r="119" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C119" s="3"/>
-    </row>
-    <row r="120" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C120" s="3"/>
-    </row>
-    <row r="121" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C121" s="3"/>
-    </row>
-    <row r="122" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C122" s="3"/>
-    </row>
-    <row r="123" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C123" s="3"/>
-    </row>
-    <row r="124" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C124" s="3"/>
-    </row>
-    <row r="125" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C125" s="3"/>
-    </row>
-    <row r="126" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C126" s="3"/>
-    </row>
-    <row r="127" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C127" s="3"/>
-    </row>
-    <row r="128" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C128" s="3"/>
-    </row>
-    <row r="129" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C129" s="3"/>
-    </row>
-    <row r="130" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C130" s="3"/>
-    </row>
-    <row r="131" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C131" s="3"/>
-    </row>
-    <row r="132" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C132" s="3"/>
-    </row>
-    <row r="133" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C133" s="3"/>
-    </row>
-    <row r="134" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C134" s="3"/>
-    </row>
-    <row r="135" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C135" s="3"/>
-    </row>
-    <row r="136" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C136" s="3"/>
-    </row>
-    <row r="137" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C137" s="3"/>
-    </row>
-    <row r="138" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C138" s="3"/>
+      <c r="A48" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A123" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C123" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A124" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C124" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A125" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C125" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A126" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C126" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A127" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C127" s="3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A128" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C128" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A129" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C129" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A130" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C130" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A131" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C131" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A132" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C132" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A133" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C133" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A134" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C134" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A135" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C135" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A136" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C136" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A137" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C137" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A138" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C138" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A139" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C139" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A140" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C140" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A141" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C141" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A142" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C142" s="3" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A143" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C143" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A144" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C144" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A145" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C145" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A146" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C146" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A147" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C147" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A148" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C148" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A149" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C149" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A150" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A151" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C151" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A152" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C152" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A153" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C153" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A154" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C154" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A155" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C155" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A156" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C156" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A157" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C157" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A158" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C158" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A159" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C159" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A160" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C160" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A161" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C161" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A162" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C162" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A163" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C163" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A164" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C164" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A165" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C165" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A166" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C166" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A167" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C167" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A168" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C168" s="3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A169" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C169" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A170" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C170" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A171" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C171" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A172" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C172" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A173" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C173" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A174" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C174" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A175" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A176" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C176" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A177" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C177" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A178" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C178" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A179" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C179" s="3" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A180" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C180" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A181" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C181" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A182" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C182" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A183" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C183" s="3" t="s">
+        <v>137</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7F9F507-1BE8-473E-B0CD-E90E97156F8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06EC7B3C-AAFB-4A90-8C3B-F4F95FBC48BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28935" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envio Robô" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="215">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -53,7 +53,406 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
+    <t>diogo.junior@allianz.com.br</t>
+  </si>
+  <si>
+    <t>thomaz.jesus@allianz.com.br</t>
+  </si>
+  <si>
+    <t>matheus.gomes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12975234400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>rosangela.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12910774200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>juliano.guimaraes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12977511000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>juliana.almeida@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12982117300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>cleyciane.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12977253900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>gisele.cardoso1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12976013800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>afonso.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12972031200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>alan.peter@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12972432400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12982197500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>armando.filho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-70006407749 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12703749300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rosana.teixeira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12968069200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12968880300000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>fernanda.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12982775800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>gabriela.logrado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12975902600000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12975903800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>cristiane.konrad@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12980433800000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>luiz.junior1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12980744500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>rodrigo.amorim@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12979923100000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>wagner.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12692297800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>leinny.amorim@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12978394900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>eduardo.santos1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12904848600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>laila.steil@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12979620200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>lucidene.santana@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12975939900000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12223851200000 Nota 167 - Retorno Cobrança op53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12302937300000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12448063500000 Nota 167 - Retorno Cobrança op53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12762122900000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12792564300000 Nota 167 - Retorno Cobrança op53</t>
+  </si>
+  <si>
+    <t>renata.scarpino@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12951535500000 Nota 418 - Vida - Faturamento - Proposta/DPS</t>
+  </si>
+  <si>
+    <t>ana.morais@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-29473523866 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>cristiane.lozano@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12676327600000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>ana.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12973943500000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12974393100000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>tamaniniseg@onda.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126722460 - JONAS BELCHIOR TAMANINI</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 9 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>suporte.vvd@vwfs.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126768937 - ANA KARINE LEITE AGUIAR AMORIM</t>
+  </si>
+  <si>
+    <t>backofficecorretora@segurostoyota.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126779904 - CAMILA ROCHA LOUZEIRO</t>
+  </si>
+  <si>
+    <t>financeiro@brasal.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126752758 - MARILDA DAS CHAGAS GOMES</t>
+  </si>
+  <si>
     <t>renovacaoseguros@honda.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126799458 - JOAO PAULO PEREIRA GALENO</t>
+  </si>
+  <si>
+    <t>segurarty@segurarty.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126745307 - JIDIANE CACHIONE ROSSI ROCHA</t>
+  </si>
+  <si>
+    <t>heliomontanari@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127094896 - LUISA CAVALCANTI DE FARIAS</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 8 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127116093 - PAULO HENRIQUE FERREIRA CERQUEIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127118606 - GENILDO ERMINIO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>beloporto@beloporto.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127104389 - FABIOLA LIONCIO GERMANO</t>
+  </si>
+  <si>
+    <t>nogueirasegurosss@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127097075 - JEAN RANGELL BATISTA ROCHA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127660773 - THAMIRES DA SILVA OLIVEIRA MORAIS</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 6 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>pendencias@rbmseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127717084 - MARIO LUIZ MOTA DA SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127747911 - IVO DA ROSA SOARES</t>
+  </si>
+  <si>
+    <t>atendimento@antoniollicorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127717903 - ELAINE DE SOUZA MORAIS</t>
+  </si>
+  <si>
+    <t>faleconosco@mapma.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128007433 - EDILENE PACHECO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>senhaseguros@senhaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128044058 - JANICE MARIA LEITE</t>
+  </si>
+  <si>
+    <t>diretoria@lapisbellus.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128108260 - LUCIMAR ALVES SILVA DO VALLE</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127979787 - MAURO TRINDADE DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128110541 - SANDRA RUBIA WOLTER</t>
+  </si>
+  <si>
+    <t>contato@valdirenecorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127966316 - ROBERTO CARLOS LOMBA FILHO</t>
+  </si>
+  <si>
+    <t>grandevitoria@gvcorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128058832 - TATYANA PRATTI BRAGATTO DE SOUZA</t>
+  </si>
+  <si>
+    <t>lissa@americaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128118179 - ANA PAULA BELLINTANI DELAI</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128121831 - AMARO MARCULINO SILVA</t>
+  </si>
+  <si>
+    <t>investseg.tm@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128447295 - ROSANI TRATSCH</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>aoseguros@aoseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128942820 - CHRISTINE CANDIAN CABRAL DISCACCIATI</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 3 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>adm@buildingseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128975233 - FLAVIO SORANSO</t>
+  </si>
+  <si>
+    <t>fielcs@fielcs.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128990827 - PAULO MIGUEL DOS SANTOS</t>
+  </si>
+  <si>
+    <t>briciaseguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129291514 - CLEIA DA SILVA NASCIMENTO</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 2 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>seguros@grupovia1.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126413655 - NATHALIA DE ARAUJO VASCONCELLOS</t>
   </si>
   <si>
     <t>Prezado(a), 
@@ -65,16 +464,58 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 9 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>backofficecorretora@segurostoyota.com.br</t>
+    <t>Captura de parcela rejeitada - Apólice 126396136 - FELIPE ZACHARIAS LUTTERBACH</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126443695 - FELIPE BARBOSA DO REGO BARROS</t>
+  </si>
+  <si>
+    <t>pendencia@vilavelha.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126438159 - MARINALVA RAMIRO DE OLIVEIRA COSTA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126434390 - LUCIANA BUAES SCHEPKE CAIAFA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126740496 - NEILTON BARRETO SOCORRO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126684300 - ESTHER WAIHRICH QUEIROZ DE MENEZES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126975680 - ANDREA BARBOZA ARAUJO DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127061446 - ADRIANA ALVES DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>banseg@bansegseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127077654 - FERNANDA DE MASCENA ALVES SOUZA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127079691 - DELMA CREMONEZI LOMBARDI</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127093901 - ALBERIO ANTONIO DE LIMA</t>
+  </si>
+  <si>
+    <t>elittecorretora@elittecorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127071948 - KENIA WALERIA DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>atlantic.admseg@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127037871 - DIRLENE MARIA MOREIRA SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127306633 - LUCAS BUENO HORT</t>
   </si>
   <si>
     <t>Prezado(a), 
@@ -86,352 +527,217 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 6 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 3 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 2 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>diogo.junior@allianz.com.br</t>
-  </si>
-  <si>
-    <t>thomaz.jesus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>matheus.gomes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12975234400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>rosangela.silva1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12910774200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>juliano.guimaraes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12977511000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>juliana.almeida@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12982117300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>cleyciane.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12977253900000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>gisele.cardoso1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12976013800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>afonso.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12972031200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>alan.peter@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12972432400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12982197500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>armando.filho@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-70006407749 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12703749300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>rosana.teixeira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12968069200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12968880300000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>fernanda.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12982775800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>gabriela.logrado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12975902600000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12975903800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>cristiane.konrad@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12980433800000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>luiz.junior1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12980744500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>rodrigo.amorim@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12979923100000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>wagner.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12692297800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>leinny.amorim@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12978394900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>eduardo.santos1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12904848600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>laila.steil@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12979620200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>lucidene.santana@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12975939900000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12223851200000 Nota 167 - Retorno Cobrança op53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12302937300000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12448063500000 Nota 167 - Retorno Cobrança op53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12762122900000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12792564300000 Nota 167 - Retorno Cobrança op53</t>
-  </si>
-  <si>
-    <t>renata.scarpino@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12951535500000 Nota 418 - Vida - Faturamento - Proposta/DPS</t>
-  </si>
-  <si>
-    <t>ana.morais@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-29473523866 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>contate@gebramseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126405794 - ENIDE MARIA RIBEIRO ALVES</t>
-  </si>
-  <si>
-    <t>simplusseguros@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126427057 - CARLOS ALEXANDRE SALIM MAGALHAES</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126431014 - LUCIANA MARLENE DA SILVA</t>
-  </si>
-  <si>
-    <t>rogersmartins@hotmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126617954 - ELIANE FEDERZONI</t>
-  </si>
-  <si>
-    <t>makey@makey.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126751134 - DANIEL DINIZ MARSOLA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126756822 - JONNYS DE MOURA</t>
-  </si>
-  <si>
-    <t>jaqueline@horahseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126723448 - VANESSA FERREIRA LOURENCO ORDONHES</t>
-  </si>
-  <si>
-    <t>bramerseguros@terra.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126723185 - TEREZINHA MENDONCA SALOMAO</t>
-  </si>
-  <si>
-    <t>l3corretoraseguros@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127264181 - DANILO VINICIUS DE OLIVEIRA COSTA</t>
-  </si>
-  <si>
-    <t>diretoria@lapisbellus.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127377645 - ILIDIO DE JESUS COELHO</t>
-  </si>
-  <si>
-    <t>suporte.vvd@vwfs.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127367989 - FELIPE CAMILO CARDOSO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>backofficeseguros@vwfs.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127390967 - RITA DE CASSIA CORREA PESSOA</t>
-  </si>
-  <si>
-    <t>klimaseguros@klimaseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127659911 - JONAS DE MATTOS</t>
-  </si>
-  <si>
-    <t>aliancadowsley@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127714653 - JOSE MARTINS DA SILVA JUNIOR</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127718928 - WESLEI BATISTA ALMEIDA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127945266 - MARLENE NUNES GOMES RICATTO</t>
-  </si>
-  <si>
-    <t>operacional@seguroo.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128045838 - ROSANA THOME</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127968570 - THIANA DA SILVA CERQUEIRA</t>
-  </si>
-  <si>
-    <t>contato@cellenceseguros.net.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126202132 - PAULO RONALDO RAMOS DE MACEDO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128051737 - WELLINGTON JOSE DA SILVA</t>
-  </si>
-  <si>
-    <t>bianca.rezende@officebseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128438248 - ZURLINDE CABRAL LOURO JUNIOR</t>
-  </si>
-  <si>
-    <t>jethaseguros@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128445075 - SARA ELZA CALDAS DE SANTANA</t>
-  </si>
-  <si>
-    <t>unitas@unitasnet.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128457500 - JENIEL RODRIGUES DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>corretora@pessego.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128919037 - HAMILTON IMACULADO CONCEICAO SILVA</t>
+    <t>tacon.seguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127366145 - CLAUDIO ALVAREZ SIMOES</t>
+  </si>
+  <si>
+    <t>diamantinaseguros@diamantinaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127408313 - LUCIVAN ALVES OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127412715 - LEANDRO DOS SANTOS SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127417364 - LUANA DOS SANTOS AZEVEDO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127609885 - HELENO JOAO DA COSTA</t>
+  </si>
+  <si>
+    <t>daniel@fernandocorretora.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127711479 - MARIO SERGIO SPOLADORE FILHO</t>
+  </si>
+  <si>
+    <t>agnseguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128065636 - CAMILA ESTEVES ALVES PEREIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128403376 - ALINE FATIMA DE SOUZA</t>
+  </si>
+  <si>
+    <t>ricardovianna@rrbrokrs.net.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128415504 - MARCIA MULLER GARCEZ</t>
+  </si>
+  <si>
+    <t>pendencia@seguralta.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128404056 - FERNANDA GRAEFF ZANOTELLI</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128434785 - MARGARIDA WESZ VOGADO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128407810 - EVAN JOSE ARGOLO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>adm.corretora@revemar.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128912631 - TONNY JAMERSON MIRALHA SEABRA</t>
+  </si>
+  <si>
+    <t>orcaseguros1@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128912522 - MARIA LUIZA MACHADO</t>
+  </si>
+  <si>
+    <t>atendimento@segurosdobrasil.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128940095 - DANIEL EUGENIO KUCK</t>
+  </si>
+  <si>
+    <t>portilho@portilho.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128847956 - LUCELIA MARIA MELO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>tasegurocorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129382797 - GILMAR LIMA</t>
+  </si>
+  <si>
+    <t>daniel.c@aruakseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129416339 - ISAQUE MARQUES DA SILVA</t>
   </si>
   <si>
     <t>ativa@ativaseguros.net</t>
   </si>
   <si>
-    <t>Captura de parcela rejeitada - Apólice 128908206 - TATIANA FERREIRA ANGST</t>
-  </si>
-  <si>
-    <t>ajs_corretordeseguros@hotmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126721349 - MANOEL MESSIAS PINHEIRO DA SILVA</t>
+    <t>Captura de parcela rejeitada - Apólice 126413093 - CARLA ANGELICA PICCININI CANOVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126433552 - ESROM FELIX DE ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126440682 - RENATA FERNANDES PINHEIRO DOMINGUES</t>
+  </si>
+  <si>
+    <t>adm@marconcinseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126412503 - AMANDA ALINE MACIEL GOMES</t>
+  </si>
+  <si>
+    <t>adm@pattini.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126661929 - BRUNA ALVARES</t>
+  </si>
+  <si>
+    <t>camilo@riosegon.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126685311 - ROMILDO BATISTA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>protencorseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127025095 - MARILENE FERREIRA GOMES MARTINS</t>
+  </si>
+  <si>
+    <t>andrea@thompsonseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127318325 - KATIA REGINA RODRIGUES DA SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127385270 - CHIRLEI DOURADO ALVES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127405275 - VIVIAN FELIPPE FERRAZ</t>
+  </si>
+  <si>
+    <t>rede@redecorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127698670 - RODRIGO DA MOTA</t>
+  </si>
+  <si>
+    <t>milton@remaviseguros.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128011609 - LUIZ HENRIQUE DA SILVA FREITAS</t>
+  </si>
+  <si>
+    <t>proverseguros@proverseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128038978 - DEMETRIO OLIVEIRA DE SOUZA</t>
+  </si>
+  <si>
+    <t>sistema.oliver.diretor@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126183357 - BRUNA CARLA POLTRONIERI PAULON AUGUSTO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128036321 - FELIPE AUGUSTO GUEDES DUPIM</t>
+  </si>
+  <si>
+    <t>elizabeth@patriciaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128034628 - SARITA BASILIO BRIGHENTI</t>
+  </si>
+  <si>
+    <t>adriana.faria@jorlan.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128063025 - MARCELO RENATO MAGALHAES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128070630 - CLEOMAR COSMI DE FREITAS</t>
+  </si>
+  <si>
+    <t>seguros@batalhacorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128070380 - MOACYR FALCAO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128453948 - DANYELLE DE SIQUEIRA CAMPOS GIL LEMOS BARRETO</t>
+  </si>
+  <si>
+    <t>marcelo@perroneseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128452761 - CELSO SOUZA ISBERNER</t>
+  </si>
+  <si>
+    <t>claudinei.seguros@yahoo.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128452587 - VINICIUS DAVI DE SOU</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128478444 - JOSE DO ROSARIO OLIVEIRA</t>
+  </si>
+  <si>
+    <t>parviseguros-am@parviseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129263154 - JOSE MARIA BARBOSA EVANGELISTA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129380424 - JOAO VICTOR MOREIRA DE SOUZA</t>
   </si>
 </sst>
 </file>
@@ -834,10 +1140,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -845,10 +1151,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -856,10 +1162,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -867,10 +1173,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -878,10 +1184,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -889,10 +1195,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -900,10 +1206,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -911,10 +1217,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -922,10 +1228,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -933,10 +1239,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -944,10 +1250,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -955,10 +1261,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -966,10 +1272,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -977,10 +1283,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -988,10 +1294,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -999,10 +1305,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -1010,10 +1316,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -1021,10 +1327,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -1032,10 +1338,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -1043,10 +1349,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -1054,10 +1360,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -1065,10 +1371,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -1076,10 +1382,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
@@ -1087,10 +1393,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -1098,10 +1404,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
@@ -1109,10 +1415,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>15</v>
+        <v>59</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -1120,10 +1426,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>3</v>
@@ -1131,10 +1437,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>3</v>
@@ -1142,10 +1448,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>3</v>
@@ -1153,10 +1459,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>3</v>
@@ -1164,10 +1470,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>67</v>
+        <v>5</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>3</v>
@@ -1175,498 +1481,1010 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>69</v>
+        <v>5</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>70</v>
+        <v>54</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>73</v>
+        <v>58</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>6</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>6</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>6</v>
+        <v>66</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>6</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>6</v>
+        <v>66</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>8</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>8</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>8</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>8</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>9</v>
+        <v>79</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>9</v>
+        <v>87</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>4</v>
+        <v>91</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>10</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>4</v>
+        <v>96</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>11</v>
+        <v>95</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>105</v>
+        <v>69</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>11</v>
+        <v>95</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>107</v>
+        <v>69</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>11</v>
+        <v>95</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>12</v>
+        <v>95</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>12</v>
+        <v>95</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>106</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B61" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="C61" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C59" s="3"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C60" s="3"/>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C61" s="3"/>
-    </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C62" s="3"/>
-    </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C63" s="3"/>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C64" s="3"/>
-    </row>
-    <row r="65" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C65" s="3"/>
-    </row>
-    <row r="66" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C66" s="3"/>
-    </row>
-    <row r="67" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C67" s="3"/>
-    </row>
-    <row r="68" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C68" s="3"/>
-    </row>
-    <row r="69" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C69" s="3"/>
-    </row>
-    <row r="70" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C70" s="3"/>
-    </row>
-    <row r="71" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C71" s="3"/>
-    </row>
-    <row r="72" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C72" s="3"/>
-    </row>
-    <row r="73" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C73" s="3"/>
-    </row>
-    <row r="74" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C74" s="3"/>
-    </row>
-    <row r="75" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C75" s="3"/>
-    </row>
-    <row r="76" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C76" s="3"/>
-    </row>
-    <row r="77" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C77" s="3"/>
-    </row>
-    <row r="78" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C78" s="3"/>
-    </row>
-    <row r="79" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C79" s="3"/>
-    </row>
-    <row r="80" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C80" s="3"/>
-    </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C81" s="3"/>
-    </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C82" s="3"/>
-    </row>
-    <row r="83" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C83" s="3"/>
-    </row>
-    <row r="84" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C84" s="3"/>
-    </row>
-    <row r="85" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C85" s="3"/>
-    </row>
-    <row r="86" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C86" s="3"/>
-    </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C87" s="3"/>
-    </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C88" s="3"/>
-    </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C89" s="3"/>
-    </row>
-    <row r="90" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C90" s="3"/>
-    </row>
-    <row r="91" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C91" s="3"/>
-    </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C92" s="3"/>
-    </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C93" s="3"/>
-    </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C94" s="3"/>
-    </row>
-    <row r="95" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C95" s="3"/>
-    </row>
-    <row r="96" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C96" s="3"/>
-    </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C97" s="3"/>
-    </row>
-    <row r="98" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C98" s="3"/>
-    </row>
-    <row r="99" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C99" s="3"/>
-    </row>
-    <row r="100" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C100" s="3"/>
-    </row>
-    <row r="101" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C101" s="3"/>
-    </row>
-    <row r="102" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C102" s="3"/>
-    </row>
-    <row r="103" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C103" s="3"/>
-    </row>
-    <row r="104" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C104" s="3"/>
-    </row>
-    <row r="105" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C105" s="3"/>
-    </row>
-    <row r="106" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C106" s="3"/>
-    </row>
-    <row r="107" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C107" s="3"/>
-    </row>
-    <row r="108" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C108" s="3"/>
-    </row>
-    <row r="109" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C109" s="3"/>
-    </row>
-    <row r="110" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C110" s="3"/>
-    </row>
-    <row r="111" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C111" s="3"/>
-    </row>
-    <row r="112" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C112" s="3"/>
-    </row>
-    <row r="113" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C113" s="3"/>
-    </row>
-    <row r="114" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C114" s="3"/>
-    </row>
-    <row r="115" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C115" s="3"/>
-    </row>
-    <row r="116" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C116" s="3"/>
-    </row>
-    <row r="117" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C117" s="3"/>
-    </row>
-    <row r="118" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C118" s="3"/>
-    </row>
-    <row r="119" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C119" s="3"/>
-    </row>
-    <row r="120" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C120" s="3"/>
-    </row>
-    <row r="121" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C121" s="3"/>
-    </row>
-    <row r="122" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C122" s="3"/>
-    </row>
-    <row r="123" spans="3:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C63" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C68" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C72" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C74" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C75" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C76" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C77" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="210" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C123" s="3"/>
     </row>
-    <row r="124" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C124" s="3"/>
     </row>
-    <row r="125" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C125" s="3"/>
     </row>
-    <row r="126" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C126" s="3"/>
     </row>
-    <row r="127" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C127" s="3"/>
     </row>
-    <row r="128" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C128" s="3"/>
     </row>
     <row r="129" spans="3:3" x14ac:dyDescent="0.25">

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\Brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Envio de e-mail retorno GO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51F1987D-78D1-4755-A58E-F5D7A6163472}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C96EE787-DBA8-44ED-BC73-727A4A0F4A01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28800" windowHeight="14385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envio Robô" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="117">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -381,6 +381,15 @@
   </si>
   <si>
     <t>Retorno de GO referência-12883751700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12969771800000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>karina.vieira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11421879500000 Nota 742 - Prêmio</t>
   </si>
 </sst>
 </file>
@@ -1322,10 +1331,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>96</v>
+        <v>9</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>3</v>
@@ -1333,10 +1342,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>3</v>
@@ -1344,10 +1353,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>3</v>
@@ -1355,10 +1364,10 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>3</v>
@@ -1366,10 +1375,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>3</v>
@@ -1377,10 +1386,10 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>3</v>
@@ -1388,10 +1397,10 @@
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>3</v>
@@ -1399,10 +1408,10 @@
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>3</v>
@@ -1410,20 +1419,36 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="B59" s="2" t="s">
+      <c r="B61" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C59" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C60" s="3"/>
-    </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C61" s="3"/>
+      <c r="C61" s="2" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C62" s="3"/>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C82411-534E-4C57-A0F6-CA52660B034E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{862AF5B0-B7F2-445C-B26D-B57538FB361C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="114">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -59,100 +59,16 @@
     <t>Retorno de GO referência-12907201700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
   </si>
   <si>
-    <t>adriano.guerra@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12760840200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>dinah.castro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12989423600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>kaue.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12856251900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>matheus.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12995729700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>gleison.ferreira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12986292000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
     <t>angela.carmo@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12807824800000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>douglas.morais@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13200526653 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>clarissa.cavalli@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12751284300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>vitor.mattos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12569998300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>fernando.lima@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12992461800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>cristiane.silva1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12992055500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>lucidene.santana@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12975142900000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>cristiane.lozano@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12984126400000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
     <t>nelma.xavier@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12992117400000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>gabriela.galvao@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12586974000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>backofficecorretora@segurostoyota.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126534206 - ETIENE ALVES DA ROCHA GUSMAO</t>
   </si>
   <si>
     <t>Prezado(a), 
@@ -164,9 +80,6 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>Captura de parcela rejeitada - Apólice 126866523 - CRISTINA BRONZATO BUENO</t>
-  </si>
-  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 9 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -176,9 +89,6 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>Captura de parcela rejeitada - Apólice 127176963 - HUELIGTON PEREIRA DE MELO</t>
-  </si>
-  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 8 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -188,18 +98,6 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>rogerio@bw4seguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127173235 - DAYANE DA SILVA RODRIGUES DAMACENO</t>
-  </si>
-  <si>
-    <t>jeferson.beltran@beltrancorretora.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127276115 - SUELEN STEIL GEMERASCA</t>
-  </si>
-  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -212,25 +110,7 @@
     <t>pendencias@rbmseguros.com.br</t>
   </si>
   <si>
-    <t>Captura de parcela rejeitada - Apólice 127480986 - VALMIR BARZAN</t>
-  </si>
-  <si>
-    <t>dalviseguros@hotmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127493243 - NIVEA CRISTINA SENA COSTA</t>
-  </si>
-  <si>
     <t>suporte.vvd@vwfs.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127499979 - ALBERTO GONCALVES BRASIL FILHO</t>
-  </si>
-  <si>
-    <t>tecnico1@centrosulseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127797733 - LEODECIO BRAZ DA SILVA SEGUNDO</t>
   </si>
   <si>
     <t>Prezado(a), 
@@ -245,9 +125,6 @@
     <t>reinaldo.alves@carmais.com.br</t>
   </si>
   <si>
-    <t>Captura de parcela rejeitada - Apólice 128093132 - JOSE HAMISTERDAN DE LEMOS FELIX</t>
-  </si>
-  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -257,27 +134,6 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>daitxseguros@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128199787 - ANA LUCIA DUTRA RODRIGUES</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128199600 - ANA LUCIA DUTRA RODRIGUES</t>
-  </si>
-  <si>
-    <t>suzi@v12corretora.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128202610 - JULIO CESAR FERREIRA</t>
-  </si>
-  <si>
-    <t>agseguros@terra.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128552375 - WAGNER JOSE CORAZZARI FILHO</t>
-  </si>
-  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -287,12 +143,6 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>gripp@grippseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128952973 - JAYME EDUARDO JUNQUEIRA VENTURATO</t>
-  </si>
-  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 3 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -302,15 +152,6 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>divisaseguros@terra.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129069417 - NILSON SERGIO TRAVALINI</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129386173 - MERICIA FONSECA DE CARVALHO</t>
-  </si>
-  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 2 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -318,6 +159,282 @@
 Att.
 Departamento de Cobrança
 "Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>roberto.medeiros@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-66497686000186 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rosiane.honorato@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12989346700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>renato.lopes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12996223500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>erica.cassandre@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12987692400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rosthiane.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12995801400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>gisele.mazzucco@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12744359500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>juliana.diniz@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-15037035848 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-9117263654 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12807824800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>marcelo.mesquita@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-20090981001607 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12819711600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>renato.faillace@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12995690200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>raullison.castro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12996753300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>marco.vita@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12896898500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>adautina.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12963115700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12996717400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>leticia.bezerra@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12994299900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>daisy.marangoni@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-41623479000108 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-42746698900 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>enriete.saucedo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-75661264000195 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>ariane.bottini@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-14592156000113 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>claudinete.machado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12970212300000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12976661000000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>jaqueline.nicacio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-61620394391 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>carlos.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11975999200000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12237076100000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12394986600000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12691414500000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>contatoseguros.adm@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126536280 - TREVISAN COMERCIO DE ALIMENTOS LTDA ME</t>
+  </si>
+  <si>
+    <t>luizalbertodionysio56@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126538894 - ADRIANO FREIRE DIONYSIO</t>
+  </si>
+  <si>
+    <t>inaldo@ialcorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126877683 - WANDERSON STEWART PARREIRA MIRANDA</t>
+  </si>
+  <si>
+    <t>renovacaoseguros@honda.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126883392 - KELLY ANTUNES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126861536 - MARIA DAS GRACAS ZENI DE SOUZA</t>
+  </si>
+  <si>
+    <t>katia@cerbinocorretoradeseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127176243 - ROBERTO FAUSTO DE MENEZES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127163191 - MIRELLA ALBUQUERQUE SOUSA</t>
+  </si>
+  <si>
+    <t>protecta@protectaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127161511 - RAYZA OLIVEIRA ECHEVERRIA</t>
+  </si>
+  <si>
+    <t>orlandososeguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127186293 - ODILON VIAL SOBRINHO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127201032 - GILMAR GUEDES MORAIS JUNIOR</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127158524 - MIRIAM YAMAZAKI PEZZOTTA</t>
+  </si>
+  <si>
+    <t>qualities.seguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127500888 - DANIEL DE ANDRADE FERNANDES</t>
+  </si>
+  <si>
+    <t>allianz@redelojacorr.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127824531 - RODRIGO LEANDRO COSTA</t>
+  </si>
+  <si>
+    <t>contate@gebramseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127811818 - RODRIGO MUKAI DE ANDRADE ROSA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128209675 - MARCOS ANTONIO GUEDES DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128209743 - LUANA DOS SANTOS SILVA NOGUEIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128210020 - DARIO GOMES DE CASTRO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128518354 - LUCIA REGINA DA SILVEIRA SANTOS</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128559200 - ERIKA BARBOSA TEIXEIRA DE SOUSA</t>
+  </si>
+  <si>
+    <t>barralife.contato@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126548932 - CASSIA MAYARA CASTRO CARVALHO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128618656 - ROBERTA MARIA ARAUJO GADELHA</t>
+  </si>
+  <si>
+    <t>maria_gomes@ajg.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128628210 - SILVIA QUINTAO NADALINI</t>
+  </si>
+  <si>
+    <t>info@plataformaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129006215 - ALMIR DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>pendencia@seguralta.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129093203 - JOSE SOBREIRO</t>
+  </si>
+  <si>
+    <t>backoffice.corretora@yamaha-motor.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129102405 - CICERO DA SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129068349 - CARILE FERRO MENEGHELI</t>
+  </si>
+  <si>
+    <t>backofficeseguros@vwfs.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129479452 - ANTONIA ANELIZIA DE CASTRO MAIA CHAVES</t>
+  </si>
+  <si>
+    <t>atendimentoemissao@brcorretorafoz.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129507749 - RAPHAEL DE PAULA BARTHOLO</t>
   </si>
 </sst>
 </file>
@@ -699,8 +816,8 @@
   <dimension ref="A1:C183"/>
   <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="55.5703125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="101.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="95.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="179.85546875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="6" width="9.42578125" style="2"/>
     <col min="7" max="7" width="9.5703125" style="2" bestFit="1" customWidth="1"/>
@@ -731,10 +848,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -742,10 +859,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -753,10 +870,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -764,10 +881,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="B6" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -775,10 +892,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -786,10 +903,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -797,10 +914,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -808,10 +925,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -819,10 +936,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -830,10 +947,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -841,10 +958,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -852,10 +969,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -863,10 +980,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -874,10 +991,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>46</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -885,10 +1002,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -896,262 +1013,454 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>38</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>40</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>47</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>59</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>59</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>59</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>59</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>70</v>
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>70</v>
+        <v>11</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>74</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35"/>
+      <c r="A35" t="s">
+        <v>75</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36"/>
+      <c r="A36" t="s">
+        <v>78</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37"/>
+      <c r="A37" t="s">
+        <v>9</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38"/>
+      <c r="A38" t="s">
+        <v>81</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39"/>
+      <c r="A39" t="s">
+        <v>83</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40"/>
+      <c r="A40" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41"/>
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42"/>
+      <c r="A42" t="s">
+        <v>87</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43"/>
+      <c r="A43" t="s">
+        <v>89</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44"/>
+      <c r="A44" t="s">
+        <v>91</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45"/>
+      <c r="A45" t="s">
+        <v>17</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46"/>
+      <c r="A46" t="s">
+        <v>75</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47"/>
+      <c r="A47" t="s">
+        <v>17</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48"/>
+      <c r="A48" t="s">
+        <v>14</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49"/>
+      <c r="A49" t="s">
+        <v>75</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50"/>
+      <c r="A50" t="s">
+        <v>98</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51"/>
+      <c r="A51" t="s">
+        <v>75</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52"/>
+      <c r="A52" t="s">
+        <v>101</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53"/>
+      <c r="A53" t="s">
+        <v>103</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54"/>
+      <c r="A54" t="s">
+        <v>105</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55"/>
+      <c r="A55" t="s">
+        <v>107</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56"/>
+      <c r="A56" t="s">
+        <v>75</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57"/>
+      <c r="A57" t="s">
+        <v>110</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58"/>
+      <c r="A58" t="s">
+        <v>112</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C62" s="3"/>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{198DFE90-1240-48F8-A050-5B71B83C4C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EEDFD76-B9E7-4A4A-BAA7-8C41CC7F0948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28800" windowHeight="14655" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="222">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -53,406 +53,712 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>nelma.xavier@allianz.com.br</t>
-  </si>
-  <si>
-    <t>renato.lopes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>juliana.diniz@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-20090981001607 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>daniel.lourenco@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12526792100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>crislaine.trindade@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12687343100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>tadeu.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12797111300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12949760600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
     <t>kaue.silva@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12952315500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>william.bonifacio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12956477700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>rubiane.bendlin@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12885588600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>claudia.magalhaes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12929257000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>juliano.guimaraes@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12945971900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12993190200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>marcia.castelo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12996496600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>danillo.boem@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-45817117000109 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daniel.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12782917100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12991008300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>jose.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12999726500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>vanessa.campos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-411636219 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>kaue.medeiros@allianz.com.br</t>
   </si>
   <si>
     <t>Retorno de GO referência-12704722700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
   </si>
   <si>
-    <t>fernando.martins1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-10541607900000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
     <t>bruno.castro@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12929381300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>priscila.sousa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12998124700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13000811900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>tatiana.monis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12960701200000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>elisangela.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12695744200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>lidiane.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12893563800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12942166800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>renata.matheus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12957675600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12959757000000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12998243300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>wagner.simon@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12953018200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>claudia.gomes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12956155400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>herbert.goncalves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12956453500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>luciana.belisario@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12959810000000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>andriele.pala@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12960315600000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>claudia.pires@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12932996700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>vitor.mattos@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12569998300000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>ana.guanais@allianz.com.br</t>
-  </si>
-  <si>
-    <t>rodrigo.deus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-6761214467 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>leonardo.castro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13000013800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>flavia.costa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12958512700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>pamela.burige@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12961618800000 Nota 595 - ERRO PDF retono</t>
-  </si>
-  <si>
-    <t>gilberto.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12908537100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>luiz.sanchetta@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12960421000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>fernanda.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12988730700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>rafael.junior@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12999481000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12947153600000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12956330600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12959256000000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12960896500000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12997468800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12998649300000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>jonatas.lauretto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12929869000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>carla.nascimento@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12944226400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>pedro.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12957197300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>rodrigo.amorim@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13001403300000 Nota 595 - ERRO PDF retorna</t>
-  </si>
-  <si>
     <t>wagner.silva@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12795788100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>rafael.leite@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12949506700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>thays.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12955204600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12955416200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>diego.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12954772100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>karinne.furtado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12958161600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12958161700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>fernando.sousa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12947335300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>leinny.amorim@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12954887200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
     <t>ana.rodrigues@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12563636300000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>karla.cunha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12860383200000 Nota 167 - Retorno Cobrança op53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12920180100000 Nota 167 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>anderson.menezes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-2000831300000 Nota 742 - Prêmio</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-10455487800000 Nota 742 - Prêmio</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-10985391600000 Nota 742 - Prêmio</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11236143500000 Nota 742 - Prêmio</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11412163500000 Nota 742 - Prêmio</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12271684500000 Nota 742 - Prêmio</t>
-  </si>
-  <si>
-    <t>janaina.cazelato@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12934517100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12944270500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>johnny.lopes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12607131600000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>adriana.abreu@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12840224000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+    <t>Retorno de GO referência-12526792100000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12960219800000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12962567000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12953325700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>caroline.wojciechowski@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12959912000000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>janaina.moura@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12961712000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12961932400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>renata.magalhaes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12941992700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>priscila.rubio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12706117700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12569789700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>jheniffer.emiliano@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12586496000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>dayane.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12960172700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>raphael.callado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12935995000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12947612800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>lucas.monteiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12954395800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>jocineia.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12959693400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12950372800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12535819900000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>aline.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12866009000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12866053400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>vivalli@vivalliseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126578956 - SHEILA CRISTINA DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 10 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>operacional@holdcorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126565393 - ANNA CLARA LUGATO DAEMON</t>
+  </si>
+  <si>
+    <t>dimas.corretor@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126601545 - ANTONIO DIMAS DARIO DE SA</t>
+  </si>
+  <si>
+    <t>backofficecorretora@segurostoyota.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126572296 - BRUNA LUCENA DE MELO DIAS</t>
+  </si>
+  <si>
+    <t>falecom@alexsimon.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126538162 - VANESSA SANTOS BITTAR</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127200392 - PATRICIA DE MORAES SILVA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 8 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>operacional@durangocorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127491198 - CAIO CRUZ MENEZES VITORIO</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>nilsonfilho@nillmorseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127524663 - JUSCELINO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127545522 - FILIPE MARCEL BRITO DE SOUZA</t>
+  </si>
+  <si>
+    <t>renovacaoseguros@honda.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127552928 - HORACIO BATISTA DOS SANTOS JUNIOR</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128252495 - LUDMILA VIANA SILVA E SILVA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>reinaldo.alves@carmais.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128255047 - NAGELA MARIA SILVA DA ROCHA DE ANDRADE</t>
+  </si>
+  <si>
+    <t>administrativo@wagonseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128263248 - GLAUCIA DE JORGE CARVALHO PESSANHA</t>
+  </si>
+  <si>
+    <t>pc-seguros@bol.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128652439 - SANDRA REGINA GUIMARAES DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>omarjunior@wertseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129112986 - DIEGO RAFAEL MONTEIRO DINIZ</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 3 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129148480 - DAYANE MENEZES DOS SANTOS ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126609315 - RENATA NASCIMENTO PANIAGOA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126569548 - WEVERTON APARECIDO VIANA</t>
+  </si>
+  <si>
+    <t>segurarty@segurarty.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126792067 - ANA TEREZA FLORES CARVALHO</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 9 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>cnlo.seg@uol.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126877020 - MARCOS AURELIO FERNANDES MARTINS</t>
+  </si>
+  <si>
+    <t>chasecorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126867748 - ALEXANDRE OLIMPIO CAVALCANTI</t>
+  </si>
+  <si>
+    <t>contato@ethicalbrasil.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126891849 - MARIA APARECIDA PINTO ANCORA DA LUZ</t>
+  </si>
+  <si>
+    <t>backoffice.corretora@yamaha-motor.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127227451 - RUAN ADEODATO ALENCAR</t>
+  </si>
+  <si>
+    <t>suporte.vvd@vwfs.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127181924 - DAVID LUCAS DE ALMEIDA SOUSA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127547191 - LEANDRO ALVES DA ROCHA DANTAS</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127847254 - SHIRLEY CAROLINA RODRIGUES WERNECK</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 6 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>emissao@rodobens.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128207062 - HELOISA GREGIANINI</t>
+  </si>
+  <si>
+    <t>giselle.rodrigues@vtnseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128135703 - ROBERTO NOGUEIRA ALVES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128245135 - GUSTAVO QUEMEL ALVES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128246208 - JOSE SILVEIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128712623 - THAYNAH MARIA SANTOS PAIVA</t>
+  </si>
+  <si>
+    <t>diamantinaseguros@diamantinaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128633372 - CARLOS HENRIQUE DE SENA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128922475 - ANTONIO VENANCIO DE VASCONCELOS</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128995139 - JONAS FILGUEIRAS DE MELO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129012469 - ALESSANDRA TOMAL</t>
+  </si>
+  <si>
+    <t>juliana@centroseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129144984 - ERIKA ANTONIA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>seguros@inredeseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129116738 - LUCIANA SASSAKI DE JESUS</t>
+  </si>
+  <si>
+    <t>laysa.camargos@grupolider.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129530810 - ALINE BROZEGUINI CUNHA TRAGINO</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 2 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>andre.oliveira@braseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126545989 - NATALICIA BRITO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>seguros@sartoricorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126569336 - JENNITON BALDRAIA DA ROCHA</t>
+  </si>
+  <si>
+    <t>atendimento@miraseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126579867 - LUCIANE MARIA RODRIGUES SEIXAS</t>
+  </si>
+  <si>
+    <t>elisa.stolz1@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126581136 - CLAUDETE INES BARZOTTO STOLZ</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126592387 - LIEUTIENE KELIA VIEIRA DOS PASSOS</t>
+  </si>
+  <si>
+    <t>bacellarseguros@bacellarseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126591116 - ANA PAULA FRANCA ARAUJO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126588520 - FABIO PINHEIRO DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>vbsegs@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126844850 - LUIS CLAUDIO MATOS DA MOTA</t>
+  </si>
+  <si>
+    <t>contato@unifisaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126883216 - ANA CAROLINA TOLEDO BAYER</t>
+  </si>
+  <si>
+    <t>aferbrasil@aferbrasil.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126864149 - CAMILA ALBUQUERQUE LINHARES ROMEIRO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127173239 - ADRIANA DE LOURDES PIRES COELHO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127212741 - JOSE DA SILVA MOTTA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127214571 - FLAVIO WAKED DE MORAES REGO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127216564 - SOLARCHIO PARTICIPACOES LTDA</t>
+  </si>
+  <si>
+    <t>info@plataformaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127216197 - BRUNO SOARES DA SILVA</t>
+  </si>
+  <si>
+    <t>renova@procede.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127784824 - RODOLFO POLCARO SAENZ</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128198489 - RAQUEL RODRIGUES DE PAIVA LEITE</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128222524 - GEILSON BARBOSA SILVEIRA</t>
+  </si>
+  <si>
+    <t>norteemissao@nortecorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128224312 - CELESTE PIMENTEL FAYAL</t>
+  </si>
+  <si>
+    <t>pendencias@jlcf.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128545549 - CRISTIANE JANOTTI CERQUEIRA LEITE</t>
+  </si>
+  <si>
+    <t>roberto@susanseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128558559 - EDUARDO ZANETTI BUECKMANN</t>
+  </si>
+  <si>
+    <t>canastraseguro@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128641769 - ANTONIO VANDERCI DURAN</t>
+  </si>
+  <si>
+    <t>backoffic.mds04@altio-op.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129077510 - PEDRO GONCALVES JUNIOR</t>
+  </si>
+  <si>
+    <t>seguros@iconecorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129391959 - MARCELO MARQUES DE MIRANDA</t>
+  </si>
+  <si>
+    <t>ademirseguros@ademirseguros.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126562237 - LEONARDO DIAS SANTOS</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126559112 - RAISSA MODESTO DA COSTA</t>
+  </si>
+  <si>
+    <t>kempdarochaneves@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126557388 - ANTONIO CARLOS ANTONIETI JUNIOR</t>
+  </si>
+  <si>
+    <t>nassan@triang.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126541119 - JAMISSON CESAR VASCONCELOS DA SILVEIRA</t>
+  </si>
+  <si>
+    <t>seguros@grupovia1.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126455225 - WILKA GABRIELA MANSUR DOS SANTOS SILVA</t>
+  </si>
+  <si>
+    <t>supervisor1.corretora@grupoleauto.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127113578 - PALOMA MENDES VIEIRA</t>
+  </si>
+  <si>
+    <t>contigo@contigoseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127817719 - NAAMA PEGADO FERREIRA</t>
+  </si>
+  <si>
+    <t>renata.guedes@adtsa.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127828136 - MARIA ROSALIA DA SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127843551 - PAULO VICTOR CAMPELO COSTA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127853956 - ROSIMERE FERREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>paulomachado@novainsurance.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128628183 - MARIA TEREZA BEDANTE DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>atendimento@janaubacorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128628105 - JOAO BATISTA SANTOS</t>
+  </si>
+  <si>
+    <t>contato@arcanjocorretoradeseguros.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128628099 - ELIZABETE DOS REIS CARRARO</t>
+  </si>
+  <si>
+    <t>operacional@resguardeseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128648856 - SONIA DO NASCIMENTO DA CUNHA</t>
+  </si>
+  <si>
+    <t>pendencia@seguralta.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128660884 - PHRSYSTEM CONSTRUTORA LTDA ME</t>
+  </si>
+  <si>
+    <t>comercial@mercanteseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128637804 - TIAGO GOMES PEIXOTO</t>
+  </si>
+  <si>
+    <t>chsseguros@outlook.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128670043 - VILMA ALVIM DE CARVALHO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128524958 - DULCIANE NUNES DINIZ</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128605697 - MARTA CALDEIRA DE OLIVEIRA KALK</t>
+  </si>
+  <si>
+    <t>lucinea@hoyt.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128673022 - ANA LUIZA DE SIQUEIRA SIGAUD</t>
+  </si>
+  <si>
+    <t>azecor@azecor.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129027092 - KERLI CRISTINA VIGLIOTTI SILVESTRE</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129124183 - ITALO CORDEIRO DE BARROS IZAIAS</t>
+  </si>
+  <si>
+    <t>investseg.tm@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126516629 - VANESSA BERTAIOLLI</t>
+  </si>
+  <si>
+    <t>explendoreseguros02@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126522903 - DIENE CRISTINA DA SILVEIRA PIRES</t>
+  </si>
+  <si>
+    <t>milanoseguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126545315 - SIMONE DAINEZI</t>
+  </si>
+  <si>
+    <t>landim@landimcorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127359207 - SILVIO FERREIRA GOMES JUNIOR</t>
+  </si>
+  <si>
+    <t>contato@confiraseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127390706 - NILSON ALVES DA SILVA</t>
+  </si>
+  <si>
+    <t>anderson@a2l2.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127459858 - FERNANDA DINIZ VASCONCELOS</t>
+  </si>
+  <si>
+    <t>expansiva@expansivaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127484882 - GABRIELI OLIVEIRA DE BASTOS</t>
+  </si>
+  <si>
+    <t>josemar@jmsegscorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128175006 - NATHALIE DE ANGELIS RODRIGUES</t>
+  </si>
+  <si>
+    <t>cofargo@cofargo.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128628062 - LAVTEC SERVICOS E PARTICIPACOES LTDA ME</t>
+  </si>
+  <si>
+    <t>edson@ngcorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128628016 - SUELY APARECIDA ORSI</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128534128 - SANDRA CAMARA DA CRUZ</t>
+  </si>
+  <si>
+    <t>w.bonadio@terra.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128628042 - FABIO HENRIQUE MOLINA RODRIGUES</t>
+  </si>
+  <si>
+    <t>sbcorretordeseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128551963 - FABIO ANDRE DOS SANTOS PITTA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129134301 - MARCELA MARIA DE MELO</t>
+  </si>
+  <si>
+    <t>backoffice.mds04@altio-op.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129055364 - MOACY BARBOSA DA SILVA JUNIOR</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129574712 - ADELINO JOSE FRANCISCO</t>
   </si>
 </sst>
 </file>
@@ -855,10 +1161,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -866,10 +1172,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -877,10 +1183,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -888,10 +1194,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -899,10 +1205,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -910,10 +1216,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -921,10 +1227,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -932,7 +1238,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
         <v>22</v>
@@ -954,10 +1260,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -965,7 +1271,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="B12" t="s">
         <v>27</v>
@@ -998,10 +1304,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -1009,7 +1315,7 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
@@ -1042,10 +1348,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>12</v>
+      </c>
+      <c r="B19" t="s">
         <v>39</v>
-      </c>
-      <c r="B19" t="s">
-        <v>40</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -1053,10 +1359,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -1064,10 +1370,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -1075,10 +1381,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>45</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -1086,46 +1392,46 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>46</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="C24" s="2" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="C25" s="2" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>6</v>
+        <v>51</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>52</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
@@ -1136,62 +1442,62 @@
         <v>54</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>55</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
@@ -1199,647 +1505,1007 @@
         <v>63</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>3</v>
+        <v>66</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="B34" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>3</v>
+        <v>66</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>3</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>3</v>
+        <v>76</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>3</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>76</v>
+        <v>51</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>3</v>
+        <v>82</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>3</v>
+        <v>82</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>85</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>82</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>3</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>3</v>
+        <v>95</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>3</v>
+        <v>66</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>3</v>
+        <v>66</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>3</v>
+        <v>66</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>3</v>
+        <v>66</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>3</v>
+        <v>73</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>3</v>
+        <v>73</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>101</v>
+        <v>51</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>3</v>
+        <v>76</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>3</v>
+        <v>76</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>105</v>
+        <v>51</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>3</v>
+        <v>76</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>3</v>
+        <v>76</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>3</v>
+        <v>76</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>3</v>
+        <v>114</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>119</v>
+        <v>63</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>121</v>
+        <v>63</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>3</v>
+        <v>46</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>3</v>
+        <v>82</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>3</v>
+        <v>82</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>3</v>
+        <v>82</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>124</v>
+        <v>51</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>131</v>
+        <v>63</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>4</v>
+        <v>137</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>3</v>
+        <v>95</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>136</v>
+        <v>51</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C78" s="3"/>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C79" s="3"/>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="C80" s="3"/>
-    </row>
-    <row r="81" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C81" s="3"/>
-    </row>
-    <row r="82" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C82" s="3"/>
-    </row>
-    <row r="83" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C83" s="3"/>
-    </row>
-    <row r="84" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C84" s="3"/>
-    </row>
-    <row r="85" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C85" s="3"/>
-    </row>
-    <row r="86" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C86" s="3"/>
-    </row>
-    <row r="87" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C87" s="3"/>
-    </row>
-    <row r="88" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C88" s="3"/>
-    </row>
-    <row r="89" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C89" s="3"/>
-    </row>
-    <row r="90" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C90" s="3"/>
-    </row>
-    <row r="91" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C91" s="3"/>
-    </row>
-    <row r="92" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C92" s="3"/>
-    </row>
-    <row r="93" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C93" s="3"/>
-    </row>
-    <row r="94" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C94" s="3"/>
-    </row>
-    <row r="95" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C95" s="3"/>
-    </row>
-    <row r="96" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C96" s="3"/>
-    </row>
-    <row r="97" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C97" s="3"/>
-    </row>
-    <row r="98" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C98" s="3"/>
-    </row>
-    <row r="99" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C99" s="3"/>
-    </row>
-    <row r="100" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C100" s="3"/>
-    </row>
-    <row r="101" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C101" s="3"/>
-    </row>
-    <row r="102" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C102" s="3"/>
-    </row>
-    <row r="103" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C103" s="3"/>
-    </row>
-    <row r="104" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C104" s="3"/>
-    </row>
-    <row r="105" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C105" s="3"/>
-    </row>
-    <row r="106" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C106" s="3"/>
-    </row>
-    <row r="107" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C107" s="3"/>
-    </row>
-    <row r="108" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C108" s="3"/>
-    </row>
-    <row r="109" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C109" s="3"/>
-    </row>
-    <row r="110" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C110" s="3"/>
-    </row>
-    <row r="111" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C111" s="3"/>
-    </row>
-    <row r="112" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C112" s="3"/>
-    </row>
-    <row r="113" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C113" s="3"/>
-    </row>
-    <row r="114" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C114" s="3"/>
-    </row>
-    <row r="115" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C115" s="3"/>
-    </row>
-    <row r="116" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C116" s="3"/>
-    </row>
-    <row r="117" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C117" s="3"/>
-    </row>
-    <row r="118" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C118" s="3"/>
-    </row>
-    <row r="119" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C119" s="3"/>
-    </row>
-    <row r="120" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C120" s="3"/>
-    </row>
-    <row r="121" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C121" s="3"/>
-    </row>
-    <row r="122" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C122" s="3"/>
-    </row>
-    <row r="123" spans="3:3" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C78" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C79" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C89" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C90" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C91" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C92" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C94" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C95" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C96" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C97" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C99" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C100" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C101" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C102" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C104" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A105" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C105" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A106" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C106" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A107" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C107" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A108" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C108" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A109" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C109" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A110" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C110" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A111" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C111" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A112" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="C112" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A113" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="C113" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A114" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="C114" s="3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A115" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="C115" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A116" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C116" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A117" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C117" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C118" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A119" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C119" s="3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A120" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C120" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A121" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C121" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" ht="195" x14ac:dyDescent="0.25">
+      <c r="A122" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C122" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C123" s="3"/>
     </row>
-    <row r="124" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C124" s="3"/>
     </row>
-    <row r="125" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C125" s="3"/>
     </row>
-    <row r="126" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C126" s="3"/>
     </row>
-    <row r="127" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C127" s="3"/>
     </row>
-    <row r="128" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C128" s="3"/>
     </row>
     <row r="129" spans="3:3" x14ac:dyDescent="0.25">
@@ -2019,31 +2685,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAzNTMxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MzAvMTIvMjAyMCAxMTo0NTo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAzMC8xMi8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAzNTMxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MzAvMTIvMjAyMCAxMTo0NTo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAzMC8xMi8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DBFCB3-53E5-4527-B13D-DC7A854D4B55}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41A8E509-6991-4B84-B1B5-13851E156C6A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DBFCB3-53E5-4527-B13D-DC7A854D4B55}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14B64BC1-65A0-41E5-BF38-8B817B0C3502}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59CCF831-863F-41C4-8381-34B4DF2E7E52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="73">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -56,129 +56,12 @@
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
-    <t>raphael.callado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 10 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>backofficecorretora@segurostoyota.com.br</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 8 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>renovacaoseguros@honda.com.br</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 9 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>suporte.vvd@vwfs.com</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 6 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
     <t>lucas.almeida@allianz.com.br</t>
   </si>
   <si>
-    <t>adalberto.souza@allianz.com.br</t>
-  </si>
-  <si>
-    <t>lilian.sudati@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11556759835 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>silvia.taschetti@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13002993900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daniela.leal@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12979414900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13006288700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>fernando.martins1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12998597300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>mary.leme@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13006878800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>daniela.gui@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13005893400000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>william.rosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-9138528000104 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>andriele.pala@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13004392200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
     <t>leonardo.dache@allianz.com.br</t>
   </si>
   <si>
@@ -197,241 +80,184 @@
     <t>Retorno de GO referência-13008701100000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
-    <t>monica.plassa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-14239211867 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13004933500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13002557600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13005744500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13006776100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>jonatas.lauretto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12821089200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13000473400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>fabiola.caixeta@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13007731200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>cassia.silveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-94001588072 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-99095548953 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>marli.rocha@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13002461200000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>renata.scarpino@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11289955100000 Nota 418 - Vida - Faturamento - Proposta/DPS</t>
-  </si>
-  <si>
-    <t>jose.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12648948200000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>carlos.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11353935000000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12405731400000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12629853000000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>marcos@yeseg.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126607004 - AVANI FELICIANO LOPES</t>
-  </si>
-  <si>
-    <t>backoffice.corretora@yamaha-motor.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126616518 - STELLA SIMAO GOMES</t>
-  </si>
-  <si>
-    <t>emissao@willistowerswatson.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126577628 - CINDY DE SOUZA SANTIAGO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126906119 - JULIO CESAR LISBOA GOMES</t>
-  </si>
-  <si>
-    <t>corretora@camedseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126880155 - TAMIRES CAMARA BRITO</t>
-  </si>
-  <si>
-    <t>corretora@marcoteixeira.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126925279 - ALEX RENATO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>paessanna.corretor@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126930140 - MARCIO DE CASTRO JUNIOR</t>
-  </si>
-  <si>
-    <t>nihonseguros@nihonseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126932496 - GRAZIELLY NADJA FERREIRA DE SOUZA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126932991 - MARCELA SILVA DA GUIA</t>
-  </si>
-  <si>
-    <t>agnseguros@hotmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126640291 - SAYMON SILVA GOMES DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127261325 - MARCELA MONTEIRO SOARES</t>
-  </si>
-  <si>
-    <t>carlos@gomescorretoradeseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127554650 - DARIO AZEVEDO DOS SANTOS FILHO</t>
-  </si>
-  <si>
-    <t>nilsonfilho@nillmorseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127565909 - SANDRA ARANTES FELIPE</t>
-  </si>
-  <si>
-    <t>cmrpontual@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127817691 - MARCO ANTONIO NEVES</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127898883 - NELSON MOREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>protecta@protectaseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127902481 - LOURDES MENOTI DE CARVALHO</t>
-  </si>
-  <si>
-    <t>controleseguros@saganet.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128135737 - DANIEL FURUCHO SAKAI</t>
-  </si>
-  <si>
-    <t>gerenciador@ei-seguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128258374 - EVA ROSALINA DA SILVA</t>
-  </si>
-  <si>
-    <t>manicaseg@manica.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128264636 - JACQUELINE BERVIAN</t>
-  </si>
-  <si>
-    <t>daniel@fernandocorretora.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128291647 - MARIO SERGIO SPOLADORE FILHO</t>
-  </si>
-  <si>
-    <t>maristela@coliseoseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128295211 - SERGIO OLIVEIRA MENDES</t>
-  </si>
-  <si>
-    <t>renova@procede.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128297046 - TAMARA DEITOS DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>pendencia@seguralta.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128244777 - FABRICIO OLIVEIRA SILVA</t>
-  </si>
-  <si>
-    <t>gabrielcorretoradeseguros@hotmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126601650 - SILVANO MARCELINO DA SILVA</t>
-  </si>
-  <si>
-    <t>lcr@lcrseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128628749 - WAGNER APARECIDO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>segurarty@segurarty.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128533153 - ISOLETE CATARINA TEIXEIRA</t>
-  </si>
-  <si>
-    <t>emissao@segurosarinos.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128678503 - LORENA TELLES MARTINS</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128608077 - VERA LUCIA QUINHONES GUIDOLIN</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128704577 - JOSE DE FRANCA SOUZA</t>
+    <t>adriana.silveira1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12727352500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13005607300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>fausto.reis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-30807470000122 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13006015900000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13007010100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>cleyciane.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-21968017801 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>juliana.diniz@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12888593200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13003981900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13009096100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>claudia.pires@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12742307600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>leandro.santos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13006424800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>nilcea.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13008660400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>vitor.mattos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12569998300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>jheniffer.emiliano@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13007095800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>ana.guanais@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12937068500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>renata.melo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13006792400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>adriano.campos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12966720500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>karen.moraes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13005211700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>fernanda.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13006685300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12999474500000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13002767800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>adautina.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13002818300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13003164200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13007533900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13007953800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13008386400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13008476900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13008545100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13008635100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13008834800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13008955500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>cristiane.konrad@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-5255008982 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-52046466000121 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>luiz.junior1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13008761500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13008798200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>rogerio.souza@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12804890100000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>ana.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12993653100000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>laerte.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12726942600000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>eloiza.felippe@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13006515500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
   </si>
 </sst>
 </file>
@@ -834,10 +660,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -845,10 +671,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -856,10 +682,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -867,10 +693,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -878,10 +704,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -889,10 +715,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -900,10 +726,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -911,10 +737,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -922,10 +748,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -933,10 +759,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -944,10 +770,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -955,10 +781,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -966,10 +792,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -977,10 +803,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B15" t="s">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -988,10 +814,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -999,10 +825,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -1010,10 +836,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="B18" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -1021,10 +847,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -1032,10 +858,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -1043,10 +869,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -1054,10 +880,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>52</v>
+        <v>12</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -1065,10 +891,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -1076,10 +902,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
@@ -1087,10 +913,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>56</v>
+        <v>4</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -1098,10 +924,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>58</v>
+        <v>4</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
@@ -1109,10 +935,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -1120,10 +946,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>3</v>
@@ -1131,10 +957,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>60</v>
+        <v>4</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>3</v>
@@ -1142,322 +968,210 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>66</v>
+        <v>4</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>71</v>
+        <v>4</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>73</v>
+        <v>4</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>75</v>
+        <v>4</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>85</v>
+        <v>67</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>86</v>
+        <v>68</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>87</v>
+        <v>69</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>10</v>
+        <v>71</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>90</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="A45"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>92</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A46"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>94</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A47"/>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>96</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>98</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>100</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>102</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>104</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>106</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>108</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>111</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>113</v>
-      </c>
-      <c r="B56" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>94</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>104</v>
-      </c>
-      <c r="B58" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>110</v>
-      </c>
+      <c r="A48"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50"/>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52"/>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53"/>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54"/>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A55"/>
+    </row>
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A56"/>
+    </row>
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A57"/>
+    </row>
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A58"/>
     </row>
     <row r="78" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C78" s="3"/>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{688AB991-12C1-4DB2-BCA2-837088A02396}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04008F4-5DD1-46FF-99A7-FF2B381C90B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="68">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -53,328 +53,196 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>fernanda.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>ana.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12629169200000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
     <t>carolina.lima@allianz.com.br</t>
   </si>
   <si>
-    <t>backofficecorretora@segurostoyota.com.br</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 10 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>renovacaoseguros@honda.com.br</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 9 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 8 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>pendencia@seguralta.com.br</t>
-  </si>
-  <si>
-    <t>atendimento@douraseg.com.br</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 3 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 2 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>suporte.vvd@vwfs.com</t>
-  </si>
-  <si>
-    <t>marcella.carraro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-88818973500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daniela.leal@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12891492900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daniela.gui@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13009850600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>carla.ventura@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12933578400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>gisele.cardoso1@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13012730600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>monica.betoni@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12868840100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>angela.carmo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12625798100000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12807824800000 Nota 7022 - Help Desk</t>
-  </si>
-  <si>
-    <t>daiane.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13012882700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>claudia.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12890920500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13010486600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>patricia.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12665054400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>luiz.junior1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13007301700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>daniela.carvalho@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13014885400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>diego.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12829892900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>karinne.furtado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13006362500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>nicole.demori@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12533234800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12581703000000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>rosemeire.faria@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12860619100000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126674196 - ANTONIO CARLOS DE FONTES</t>
-  </si>
-  <si>
-    <t>sudeste@sudesteseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126704888 - TANISE RODRIGUES DA SILVA FONTES</t>
-  </si>
-  <si>
-    <t>gilsoncaet@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126884194 - GILSON CAETANO DA SILVA</t>
-  </si>
-  <si>
-    <t>joseronaldo@ccseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126900575 - GUILHERME MOREIRA CONCILIO</t>
-  </si>
-  <si>
-    <t>marcozzicorretora@yahoo.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126962161 - JOSE TELMO MONTEIRO DE ALBUQUERQUE</t>
-  </si>
-  <si>
-    <t>seg.cac@terra.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126969832 - JEAN ONESIMO FERREIRA DA COSTA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126990070 - JAIRO IZIDIO DOS SANTOS</t>
-  </si>
-  <si>
-    <t>juliobairros@terra.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126995774 - LUIZ AFONSO E SILVA MACHADO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127315618 - TIELE DENISE NOGUEIRA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127316956 - VITORIA ALVES ROQUE DA SILVA</t>
-  </si>
-  <si>
-    <t>cvf.corretora@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127323098 - CARLA DE FREITAS QUADROS COSTA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127307913 - SOLANGE SOUZA ARAUJO</t>
-  </si>
-  <si>
-    <t>agillizeseguros@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127543623 - JERUZA CARNEIRO DE LIMA BATISTA</t>
-  </si>
-  <si>
-    <t>pendencia@profee.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128297367 - JAMILE VENTURA JANUARIO BRUM</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128367317 - LIDIANE TORMENA CAVALCANTE</t>
-  </si>
-  <si>
-    <t>emissao@segurosarinos.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128349358 - SERGIO ARMANDO MARTINHO FERREIRA</t>
-  </si>
-  <si>
-    <t>trevigo@trevigo.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129212989 - MARIA NEUSA RUSSI</t>
-  </si>
-  <si>
-    <t>ana.cezaro@terra.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129247740 - RENE PAULO ROSSI</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129267972 - NORBERTO CANDIDO FERREIRA</t>
-  </si>
-  <si>
-    <t>ricardovianna@rrbrokrs.net.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129270017 - IDALINA AVILA BRIOSO</t>
-  </si>
-  <si>
-    <t>tiago@redealves.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129279886 - HORDONATO NUNES GUIMARAES</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129274054 - LEANDRO ARROYO</t>
-  </si>
-  <si>
-    <t>leandro@cabreraseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129275746 - BEATRIZ SILVA PELICIARI</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129245053 - THIAGO HENRIQUE DO ESPIRITO SANTO</t>
-  </si>
-  <si>
-    <t>seguros@rbmseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129669897 - BRUNO RAMOS LAVORATO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129727476 - ELIANE ASSIS PEREIRA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129734896 - JOSE HUNALDO DOS SANTOS</t>
+    <t>rosangela.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12715831300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>andreia.sato@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12895650400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>luiz.inocente@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13016772600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>ana.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13014425900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>priscila.sousa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13011553900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>mary.leme@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13016738100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>juliana.assis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13016748200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12976013800000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>andriele.pala@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13014941100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>luciana.belisario@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13016737600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>leonardo.dache@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13016796000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>erineuza.monzillo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13016791900000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>leandro.susanj@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13016657300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>gilberto.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12990152900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>raphael.callado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13011608400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>gustavo.arruda@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12895606800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>gabriela.logrado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12966982800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13011766000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13013022800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13013708800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13013961800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13013990200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13014165400000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13014182700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13014364200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13014555600000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13014914900000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13014998800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13016789800000 Nota 595 - ERRO PDF PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13016792600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>marco.vita@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13016793300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13016809400000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>stephanye.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12698225900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>leinny.amorim@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13016801900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>marli.rocha@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12585134700000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13001335800000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>thomaz.jesus@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12448112600000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>carlos.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-10329800600000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11353935000000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11473330800000 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -774,10 +642,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -785,10 +653,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -796,10 +664,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -807,10 +675,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -818,10 +686,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -829,10 +697,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -840,10 +708,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -851,10 +719,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -862,10 +730,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -873,10 +741,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="B11" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -884,10 +752,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -895,10 +763,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -906,10 +774,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -917,10 +785,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>32</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -928,10 +796,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -939,10 +807,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -950,10 +818,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="B18" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -961,10 +829,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="B19" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -972,10 +840,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>7</v>
+        <v>37</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -983,10 +851,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -994,300 +862,244 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>60</v>
+        <v>37</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>71</v>
+        <v>52</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>72</v>
+        <v>53</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>74</v>
+        <v>55</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>10</v>
+        <v>59</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>80</v>
+        <v>61</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>81</v>
+        <v>62</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>82</v>
+        <v>63</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>83</v>
+        <v>64</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>88</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="A42"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>16</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="A43"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>91</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="A44"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>16</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="A45"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>94</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>18</v>
-      </c>
+      <c r="A46"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>10</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>18</v>
-      </c>
+      <c r="A47"/>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>10</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>18</v>
-      </c>
+      <c r="A48"/>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49"/>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E04008F4-5DD1-46FF-99A7-FF2B381C90B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8B271BE-06BD-4B96-986C-22C6C49FDCC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28980" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envio Robô" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="187">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -243,6 +243,417 @@
   </si>
   <si>
     <t>Retorno de GO referência-11473330800000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>hodieseg@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126692691 - MARIO LUIS DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 10 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>maiseguros@maiseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126688808 - ANA LUCIA TAVARES DA SILVA</t>
+  </si>
+  <si>
+    <t>backoffice.corretora@yamaha-motor.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126707646 - MONIQUE IARA ARAUJO DE CAMPOS</t>
+  </si>
+  <si>
+    <t>backofficecorretora@segurostoyota.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126985448 - LEONARDO FERREIRA BRAGA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 9 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>luizdall@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127009416 - PAULA CAROLINA GHELLER</t>
+  </si>
+  <si>
+    <t>kassia@kmcor.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127310412 - LEILA OLIVEIRA CARDOSO</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 8 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127336535 - EDNA DE MOURA</t>
+  </si>
+  <si>
+    <t>ciraganseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127308581 - ANTONIO MARCOS PEREIRA DE ALMEIDA JUNIOR</t>
+  </si>
+  <si>
+    <t>renovacaoseguros@honda.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127350350 - BRUNO DOS SANTOS COSTA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127604612 - DALVA REGINA AMARAL TEIXEIRA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127656322 - JOAO VICTOR FERREIRA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>fred@quintellaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127898696 - MARIA DO SOCORRO RODRIGUES DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 6 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>aoseguros@aoseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127912076 - ELISA BUSCACIO BONATO</t>
+  </si>
+  <si>
+    <t>reinaldo.alves@carmais.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127858684 - JEFFERSON MARINHO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127996621 - JEAN CARLO ANTUNES DE SOUZA</t>
+  </si>
+  <si>
+    <t>adriana.faria@jorlan.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128145728 - NILZA AMORIM PEREIRA FROIS</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>cristina@assuntacorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128235742 - LUIZ HENRIQUE ARCHILHA</t>
+  </si>
+  <si>
+    <t>mauriciocuriseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128669609 - MARIA AMELIA DE AZAMBUJA MACEDO ROSA E SILVA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>wfgseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128794884 - ANA MARIA PALADINO</t>
+  </si>
+  <si>
+    <t>carrerocorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128813663 - JORGE ASSAMU MORI</t>
+  </si>
+  <si>
+    <t>atendimento@jardiniseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128839991 - TATIANE LOPES GONCALVES</t>
+  </si>
+  <si>
+    <t>aluguel@palavraseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128836603 - ANDRE LUIZ LINS GONCALEZ</t>
+  </si>
+  <si>
+    <t>raul@ruralmaxseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128834079 - ADOLFO FARIAS DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128779876 - ANTONIO COSTA MOREIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128771640 - MARCOS PAULO RAMOS</t>
+  </si>
+  <si>
+    <t>andre.oliveira@braseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128760161 - DAVID BELO FONSECA</t>
+  </si>
+  <si>
+    <t>pendencia@seguralta.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128935266 - JOSE CLOVIS DA SILVA BARBOSA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 3 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>michel@brks.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128975656 - CINTHIA DE SOUZA PEDROZO</t>
+  </si>
+  <si>
+    <t>belemdopara@pentonal.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129175035 - ADEMYR ANTONIO FERREIRA FARTO JUNIOR</t>
+  </si>
+  <si>
+    <t>seguros@zeitunemazoni.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129270742 - ELISANGELA BORGES YOSHIDA</t>
+  </si>
+  <si>
+    <t>anapaula@dakasaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129286428 - PAOLA BATISTA DA SILVEIRA</t>
+  </si>
+  <si>
+    <t>allianz@redelojacorr.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129297581 - SCHIRLLEY PATRICIA LOUREIRO CALADO</t>
+  </si>
+  <si>
+    <t>olbencor@terra.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129299305 - JUAN JENETON JORGE</t>
+  </si>
+  <si>
+    <t>prestseguros@uol.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129337086 - VALERIA BARRETO GAZZINELLI MAIOLINI</t>
+  </si>
+  <si>
+    <t>lfseguro@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129263973 - LANA ANDRADE NAPOLEAO LIMA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129187683 - ANA PAULA NEIVERT SIMAO</t>
+  </si>
+  <si>
+    <t>agf.matra@matraseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129738441 - SONIA REGINA NOVI ISRAEL</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 2 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126529872 - SANDROS DA CUNHA</t>
+  </si>
+  <si>
+    <t>juliana.brocca@jumeso.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126637266 - LUIZ DE SOUZA FERREIRA</t>
+  </si>
+  <si>
+    <t>darnisio@terra.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126708990 - CARMO SILVA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>solssia@solssiaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126948847 - RENATA MARIA LEME FLEURY</t>
+  </si>
+  <si>
+    <t>talita@serranacorretora.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127260576 - PRICILA LOPES DOS SANTOS DOTTO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127310091 - MAURICIO RECH</t>
+  </si>
+  <si>
+    <t>kflseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127327942 - VIVIAN KELLY SANTIAGO RIBEIRO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127338296 - LUCIANA FELIX GONCALVES PINTO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127343374 - JOSEILDO DOMINGOS DOS SANTOS</t>
+  </si>
+  <si>
+    <t>andradecorretoraseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127345395 - RODRIGO RODRIGUES DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>contato@bragseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127348557 - MARINA EDNA CAMPOS</t>
+  </si>
+  <si>
+    <t>pendencias@rbmseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127315947 - JOSEANE PARELLADA BRANDT</t>
+  </si>
+  <si>
+    <t>contato@vnseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127349346 - MARIA RENE SALVATIERRA CABRERA CARDOSO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127883748 - MARCIA APARECIDA SILVA ERHARDT</t>
+  </si>
+  <si>
+    <t>juliana@maisgarraseguros.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127962814 - MARIA CAROLINA BUCAR BAHIA</t>
+  </si>
+  <si>
+    <t>suporte.vvd@vwfs.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127974403 - JEAN MAYCON DA SILVA RIBEIRO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127930697 - JOSIANE DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128310469 - NERIO DA SILVA CONSOLI</t>
+  </si>
+  <si>
+    <t>3c@seguros3c.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128326041 - IZABELA RODRIGUES DA SILVA FREIRE</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128372092 - RENATO BRAGANCA FERNANDES</t>
+  </si>
+  <si>
+    <t>lidercorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128308268 - MARIA GOMES VIEIRA SANTOS</t>
+  </si>
+  <si>
+    <t>joana@balsano.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127638499 - ANTONIO VITOR TUCHINSKI</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128323980 - SELMA NAZARE DE ALMEIDA DANTAS</t>
+  </si>
+  <si>
+    <t>salesman@salesman.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128823704 - ERISSON MACARIO DE FARIA</t>
+  </si>
+  <si>
+    <t>pendencia@energybroker.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128832535 - LUSTOZA SERVICOS E SOLUCOES EM TI LTDA EPP</t>
+  </si>
+  <si>
+    <t>scania.seguros@scania.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129307181 - SILVA E SIMIAO LTDA ME</t>
   </si>
 </sst>
 </file>
@@ -618,7 +1029,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C104"/>
   <sheetFormatPr defaultColWidth="9.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="35.7109375" style="2" bestFit="1" customWidth="1"/>
@@ -1081,59 +1492,697 @@
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42"/>
+      <c r="A42" t="s">
+        <v>68</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43"/>
+      <c r="A43" t="s">
+        <v>71</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44"/>
+      <c r="A44" t="s">
+        <v>73</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45"/>
+      <c r="A45" t="s">
+        <v>75</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46"/>
+      <c r="A46" t="s">
+        <v>78</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47"/>
+      <c r="A47" t="s">
+        <v>80</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50"/>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51"/>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52"/>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53"/>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54"/>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55"/>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56"/>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57"/>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58"/>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59"/>
-      <c r="B59" s="3"/>
+      <c r="A48" t="s">
+        <v>75</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>84</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>86</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>75</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>86</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>91</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>94</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>96</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>86</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>99</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>102</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>104</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -1147,31 +2196,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAzNTMxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MzAvMTIvMjAyMCAxMTo0NTo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAzMC8xMi8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAzNTMxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MzAvMTIvMjAyMCAxMTo0NTo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAzMC8xMi8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DBFCB3-53E5-4527-B13D-DC7A854D4B55}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41A8E509-6991-4B84-B1B5-13851E156C6A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DBFCB3-53E5-4527-B13D-DC7A854D4B55}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C885671D-0470-476E-9A4D-150251B52F3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3293DF60-A400-4F04-A960-F045EE759C1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28980" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="202">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -56,136 +56,649 @@
     <t>gisele.cardoso1@allianz.com.br</t>
   </si>
   <si>
-    <t>jheniffer.emiliano@allianz.com.br</t>
-  </si>
-  <si>
-    <t>daisy.marangoni@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12794198600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>marilia.martins@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13010654600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>thais.pessoto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12809030400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>mariana.dolence@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-91933056991 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>eugenio.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13018213100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>juliana.almeida@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13019742200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>vanessa.campos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13022779300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>yuri.santos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-77067037115 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daniela.gui@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13023406700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12995450200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>leandro.santos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13022652800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13023557800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>monica.prates@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13023397500000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>pamela.burige@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13001141700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>cassia.souza@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13023387300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>geiza.vinand@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12655373600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12655384700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>adalberto.souza@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12742578200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
     <t>patricia.soares@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13023457300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
     <t>jocineia.silva@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13004137800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>daniela.gois@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13023387500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>aline.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12948508600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>carlos.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-10684696200000 Nota 242 - Retorno Cobrança</t>
+    <t>daniel.lourenco@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13017028300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>tadeu.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13023600400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>silvia.taschetti@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13023690600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>diego.vasconcelos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12987861600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>caroline.falcao@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13023436200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>luiz.junior@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12797946000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>claudia.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13021883100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>flavio.cesar@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12883107700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>fausto.reis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13023536300000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>daniela.leal@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13024342600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>lucas.almeida@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13023605600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>priscila.sousa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13023046500000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13023747900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>tatiana.monis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13023602600000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12928828200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>monica.betoni@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13022237000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>angela.carmo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12807824800000 Nota 7022 - Help Desk</t>
+  </si>
+  <si>
+    <t>douglas.morais@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12925141000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>fernando.freitas@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13023374800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>mayara.sampaio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13023326900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>claudia.pires@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13002675100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>viviane.corbari@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13021608500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>bruno.rosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13023405400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>laiane.martins@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13020836800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>rosana.teixeira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12807027600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>raphael.callado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12851861200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12998947800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13022171700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>raullison.castro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12865880500000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>fernanda.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13016070600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13023426600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13023596800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>gabriela.logrado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12726546700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12952385500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13016321400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13018673000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13020887300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13023594200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>rodrigo.nascimento@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13022592000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12632428400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13023408800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>daniela.carvalho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13023482400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-88819060100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rafael.leite@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13023602800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>leinny.amorim@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13025477900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>laila.steil@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12789059400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>cassia.silveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12848645900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>danieli.ferreira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13008584900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>carla.catalani@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12717586500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>karina.vieira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12302937300000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>paola.emidio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12978051200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>composeg@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126768625 - DAIANA JAQUELINE HAGERS LAGRANHA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 10 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>operacional@holdcorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126776887 - MARIA BENVINDA DE ALMEIDA COSTA</t>
+  </si>
+  <si>
+    <t>jroberto@moradadosolseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126975698 - TATIANA BARBIERI BOMBARDA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 9 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>contato@verisseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127040934 - NEIDE PAES</t>
+  </si>
+  <si>
+    <t>top.seguros@yahoo.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127079581 - DIEGO EMMANUELL RIBEIRO REIS</t>
+  </si>
+  <si>
+    <t>faleconosco@mapma.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127340306 - ANA CLAUDIA BASTOS CARDOSO</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 8 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>seguros@grupovia1.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127422230 - ANA CAROLINA RODRIGUES VERAS CABRAL</t>
+  </si>
+  <si>
+    <t>renovacaoseguros@honda.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127723948 - LUZITANIA TEIXEIRA SANDES BARBOSA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127723934 - VANDERLAN DE MORAIS PINHEIRO</t>
+  </si>
+  <si>
+    <t>xvseguros@xvseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127727018 - ANTONIO RIBEIRO FERNANDES</t>
+  </si>
+  <si>
+    <t>fabio@milaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128089504 - MARIA ANTONIA DA SILVA CAMPGNOL</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 6 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>suporte.vvd@vwfs.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128086757 - VANIA SOVRANI RIBAS</t>
+  </si>
+  <si>
+    <t>gerenciador@ei-seguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128875432 - ESDRAS TOZETTI ALVES</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>contato@berce.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128931429 - LEONARDO RODRIGUES DA SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128964752 - JOSE AMANCIO JUNIOR</t>
+  </si>
+  <si>
+    <t>ouro@vidadeouro.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129154145 - LEONARDO DE SOUZA MERCEDO CAMANZI</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 3 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>atendimento@douraseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129838023 - WANESSA MARTINS DA SILVA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 2 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>gripp@grippseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129831426 - VERA PETROCINIO PIMENTA</t>
+  </si>
+  <si>
+    <t>backofficecorretora@segurostoyota.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126740496 - NEILTON BARRETO SOCORRO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126704909 - EZEQUIEL LUIZ VIEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126684300 - ESTHER WAIHRICH QUEIROZ DE MENEZES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126975680 - ANDREA BARBOZA ARAUJO DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127061446 - ADRIANA ALVES DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>banseg@bansegseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127077654 - FERNANDA DE MASCENA ALVES SOUZA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127079691 - DELMA CREMONEZI LOMBARDI</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127093901 - ALBERIO ANTONIO DE LIMA</t>
+  </si>
+  <si>
+    <t>elittecorretora@elittecorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127071948 - KENIA WALERIA DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>atlantic.admseg@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127037871 - DIRLENE MARIA MOREIRA SILVA</t>
+  </si>
+  <si>
+    <t>segurarty@segurarty.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127306633 - LUCAS BUENO HORT</t>
+  </si>
+  <si>
+    <t>kakopp@uol.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127374968 - PEDRO IGNACIO DA CUNHA</t>
+  </si>
+  <si>
+    <t>tacon.seguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127366145 - CLAUDIO ALVAREZ SIMOES</t>
+  </si>
+  <si>
+    <t>diamantinaseguros@diamantinaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127408313 - LUCIVAN ALVES OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127412715 - LEANDRO DOS SANTOS SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127417364 - LUANA DOS SANTOS AZEVEDO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127609885 - HELENO JOAO DA COSTA</t>
+  </si>
+  <si>
+    <t>corretorasultec@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127709268 - RENATA PAPA DE OLIVEIRA MARQUES DE CARVALHO D</t>
+  </si>
+  <si>
+    <t>daniel@fernandocorretora.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127711479 - MARIO SERGIO SPOLADORE FILHO</t>
+  </si>
+  <si>
+    <t>trf@trfseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127713783 - ANTONIO GOMES</t>
+  </si>
+  <si>
+    <t>agnseguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128065636 - CAMILA ESTEVES ALVES PEREIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128403376 - ALINE FATIMA DE SOUZA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>ricardovianna@rrbrokrs.net.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128415504 - MARCIA MULLER GARCEZ</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128416642 - DEUSA MARIA HENRIQUES DE FARIAS</t>
+  </si>
+  <si>
+    <t>falecom@alexsimon.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128474785 - WALDIRNEI ALVES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128479219 - COPYNORTE SERVICOS E COMERCIO LTDA EPP</t>
+  </si>
+  <si>
+    <t>carlos.seigo@personaseguros.net.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128494258 - GUSTAVO HENRIQUE BARO</t>
+  </si>
+  <si>
+    <t>pendencia@seguralta.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128404056 - FERNANDA GRAEFF ZANOTELLI</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128434785 - MARGARIDA WESZ VOGADO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128407810 - EVAN JOSE ARGOLO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>ljtcorretora@ljtcorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128489624 - ARMANDO LEOMORINO DA LUZ FILHO</t>
+  </si>
+  <si>
+    <t>orcaseguros1@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128912522 - MARIA LUIZA MACHADO</t>
+  </si>
+  <si>
+    <t>backoffice.corretora@yamaha-motor.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128935571 - FABIO BATISTA DE ABREU</t>
+  </si>
+  <si>
+    <t>atendimento@segurosdobrasil.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128940095 - DANIEL EUGENIO KUCK</t>
+  </si>
+  <si>
+    <t>portilho@portilho.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128847956 - LUCELIA MARIA MELO DOS SANTOS</t>
+  </si>
+  <si>
+    <t>tasegurocorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129382797 - GILMAR LIMA</t>
+  </si>
+  <si>
+    <t>leandro@vulkseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129394122 - DANIELE ELISE MUELLER</t>
+  </si>
+  <si>
+    <t>daniel.c@aruakseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129416339 - ISAQUE MARQUES DA SILVA</t>
+  </si>
+  <si>
+    <t>backoffice.mds04@altio-op.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129553358 - JOSE MARCOS DE JESUS</t>
   </si>
 </sst>
 </file>
@@ -585,10 +1098,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" t="s">
         <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -596,10 +1109,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
         <v>10</v>
-      </c>
-      <c r="B3" t="s">
-        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -607,10 +1120,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
         <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -618,10 +1131,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" t="s">
         <v>14</v>
-      </c>
-      <c r="B5" t="s">
-        <v>15</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -629,10 +1142,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
         <v>16</v>
-      </c>
-      <c r="B6" t="s">
-        <v>17</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -640,10 +1153,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" t="s">
         <v>18</v>
-      </c>
-      <c r="B7" t="s">
-        <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -651,10 +1164,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" t="s">
         <v>20</v>
-      </c>
-      <c r="B8" t="s">
-        <v>21</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -662,10 +1175,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" t="s">
         <v>22</v>
-      </c>
-      <c r="B9" t="s">
-        <v>23</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -673,7 +1186,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
         <v>24</v>
@@ -695,10 +1208,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -706,10 +1219,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -717,7 +1230,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
         <v>31</v>
@@ -739,10 +1252,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" t="s">
         <v>34</v>
-      </c>
-      <c r="B16" t="s">
-        <v>35</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -750,7 +1263,7 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
         <v>36</v>
@@ -805,10 +1318,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>7</v>
+        <v>46</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -816,10 +1329,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -827,255 +1340,957 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33"/>
-      <c r="B33" s="3"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36"/>
-      <c r="B36" s="3"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43"/>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44"/>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45"/>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46"/>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47"/>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50"/>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52"/>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53"/>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54"/>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55"/>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56"/>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57"/>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58"/>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59"/>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60"/>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61"/>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62"/>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A63"/>
-    </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A64"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70"/>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71"/>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73"/>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74"/>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75"/>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77"/>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78"/>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79"/>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80"/>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81"/>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82"/>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83"/>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84"/>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85"/>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86"/>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87"/>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88"/>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89"/>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90"/>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91"/>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92"/>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93"/>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94"/>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95"/>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96"/>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97"/>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98"/>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99"/>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100"/>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101"/>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102"/>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103"/>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104"/>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A105"/>
-    </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A106"/>
-    </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A107"/>
-    </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A108"/>
-    </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A109"/>
-    </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>65</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>65</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>65</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>65</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>65</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>72</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>5</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>5</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>76</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>79</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>81</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>83</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>85</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>87</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>89</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>91</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>93</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>95</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>98</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>100</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>103</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>105</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>107</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>110</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>112</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>112</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>116</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>118</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>121</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>123</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>126</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>112</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>129</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>132</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>135</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>137</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>137</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>137</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>107</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>112</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>143</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>112</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>112</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>147</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>149</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>151</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>153</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>155</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>157</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>112</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>112</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>112</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>162</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>164</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>166</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>168</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>137</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>172</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>137</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>175</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>137</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>178</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>180</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>180</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>137</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>184</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>186</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>188</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>190</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>192</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>194</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>196</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>198</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>200</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112"/>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E3B56D6-C462-4E26-966B-73D00EAF2364}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7151D478-AD1A-4684-A8AE-D6F97D228F46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28980" windowHeight="14760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envio Robô" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="198">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -51,9 +51,6 @@
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
-  </si>
-  <si>
-    <t>lucas.almeida@allianz.com.br</t>
   </si>
   <si>
     <t>gabriela.logrado@allianz.com.br</t>
@@ -137,12 +134,6 @@
     <t>backofficecorretora@segurostoyota.com.br</t>
   </si>
   <si>
-    <t>segurarty@segurarty.com.br</t>
-  </si>
-  <si>
-    <t>diamantinaseguros@diamantinaseguros.com.br</t>
-  </si>
-  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -152,256 +143,550 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>aline.nogueira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12637338200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>adriana.coelho@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12367461716 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13003341600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>edirilsa.bastos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13026428700000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12725168700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>gleison.ferreira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12911737600000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>mary.leme@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13017129100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>talita.meneses@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13007672000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>saulo.santiago@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13024786100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>marcio.ferreira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-7377015446 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>monica.prates@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13023461600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13022718200000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13022876700000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13022999100000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13023654700000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13026928700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13026977600000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>andrea.farias1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12839757800000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>enriete.saucedo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12840567000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13026283000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>ivone.jesus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12861913700000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12340783000000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>tamaniniseg@onda.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126722460 - JONAS BELCHIOR TAMANINI</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126768937 - ANA KARINE LEITE AGUIAR AMORIM</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126779904 - CAMILA ROCHA LOUZEIRO</t>
-  </si>
-  <si>
-    <t>financeiro@brasal.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126752758 - MARILDA DAS CHAGAS GOMES</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126799458 - JOAO PAULO PEREIRA GALENO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126745307 - JIDIANE CACHIONE ROSSI ROCHA</t>
-  </si>
-  <si>
-    <t>heliomontanari@hotmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127094896 - LUISA CAVALCANTI DE FARIAS</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127116093 - PAULO HENRIQUE FERREIRA CERQUEIRA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127118606 - GENILDO ERMINIO DOS SANTOS</t>
-  </si>
-  <si>
-    <t>beloporto@beloporto.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127104389 - FABIOLA LIONCIO GERMANO</t>
-  </si>
-  <si>
-    <t>nogueirasegurosss@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127097075 - JEAN RANGELL BATISTA ROCHA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127660773 - THAMIRES DA SILVA OLIVEIRA MORAIS</t>
-  </si>
-  <si>
     <t>pendencias@rbmseguros.com.br</t>
   </si>
   <si>
-    <t>Captura de parcela rejeitada - Apólice 127717084 - MARIO LUIZ MOTA DA SILVA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127747911 - IVO DA ROSA SOARES</t>
-  </si>
-  <si>
-    <t>atendimento@antoniollicorretora.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127717903 - ELAINE DE SOUZA MORAIS</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128007433 - EDILENE PACHECO DO NASCIMENTO</t>
-  </si>
-  <si>
     <t>diretoria@lapisbellus.com.br</t>
   </si>
   <si>
-    <t>Captura de parcela rejeitada - Apólice 128108260 - TAIANE DE MELO MACHADO CORREA PINHEIRO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127979787 - MAURO TRINDADE DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128110541 - SANDRA RUBIA WOLTER</t>
-  </si>
-  <si>
-    <t>contato@valdirenecorretora.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127966316 - ROBERTO CARLOS LOMBA FILHO</t>
-  </si>
-  <si>
-    <t>grandevitoria@gvcorretora.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128058832 - TATYANA PRATTI BRAGATTO DE SOUZA</t>
-  </si>
-  <si>
-    <t>lissa@americaseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128118179 - ANA PAULA BELLINTANI DELAI</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128121831 - AMARO MARCULINO SILVA</t>
-  </si>
-  <si>
-    <t>carol@ribasseg.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128500856 - MARLENE GADENS BOSCARDIN</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128950363 - ANDREA VIRGINIA LEMOS FERREIRA</t>
-  </si>
-  <si>
     <t>aoseguros@aoseguros.com.br</t>
   </si>
   <si>
-    <t>Captura de parcela rejeitada - Apólice 128942820 - CHRISTINE CANDIAN CABRAL DISCACCIATI</t>
-  </si>
-  <si>
-    <t>adm@buildingseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128975233 - FLAVIO SORANSO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128977235 - MEIRENICY APARECIDA GOMES</t>
-  </si>
-  <si>
-    <t>fielcs@fielcs.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128990827 - PAULO MIGUEL DOS SANTOS</t>
-  </si>
-  <si>
-    <t>briciaseguros@hotmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129291514 - CLEIA DA SILVA NASCIMENTO</t>
-  </si>
-  <si>
-    <t>melorios@hotmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129645153 - MELINA OCAMPO RIOS ALELUIA</t>
-  </si>
-  <si>
-    <t>geopcelula1@brbseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129792600 - ELAINE TEREZINHA OLIVEIRA SCHNEIDER</t>
+    <t>caroline.falcao@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13008295800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13027105800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13028032400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>erica.cassandre@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13028248700000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>alessandra.araujo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12638425500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>wagner.simon@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12630544800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>monica.betoni@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13026413700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>andre.gouvea@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13028461900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>mayara.sampaio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13030848700000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>claudia.pires@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12584062900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12738929500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12862071300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>eliane.outor@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13019176600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>leticia.pitkowski@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13021532300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>roberto.medeiros@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12500584200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>erica.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13025660700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13026280300000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13030245500000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>lais.xavier@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13028284700000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>fabiola.caixeta@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13027939400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13027963300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>eduardo.santos1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13018084500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>rosemeire.faria@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12691705800000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>lucidene.santana@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13018119200000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-10714136800000 Nota 418 - Vida - Faturamento - Proposta/DPS</t>
+  </si>
+  <si>
+    <t>carlos.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12527663500000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12691414500000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>miraggioseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126830875 - CARMEN LUCIA DUSO RIBEIRO MENDES</t>
+  </si>
+  <si>
+    <t>atendimento@projacseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127093243 - VANIA MOULIN BITTENCOURT</t>
+  </si>
+  <si>
+    <t>contato@luganocorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127100809 - GIOVANA FRANCO UCHOA ZANFELICE</t>
+  </si>
+  <si>
+    <t>jlcs@jlcs.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127404547 - MARCONI TARBES VIANNA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 8 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>lucas.araujo@premiumsegurospmw.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127455034 - MARIA LENIRCE DE SOUZA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127788201 - FELINDA FERNANDES FIGUEIREDO</t>
+  </si>
+  <si>
+    <t>duromarcorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127761486 - ROMILDA DE SOUZA FONSECA</t>
+  </si>
+  <si>
+    <t>ademirseguros@ademirseguros.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126562237 - LEONARDO DIAS SANTOS</t>
+  </si>
+  <si>
+    <t>pendencia@seguralta.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127791233 - JULIANA VILELA VIEIRA</t>
+  </si>
+  <si>
+    <t>maisbrasilcor@maisbrasilcor.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128126610 - BRENDA VANIA OLIVEIRA E SILVA</t>
+  </si>
+  <si>
+    <t>pendencia@profee.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128112902 - ANNA MARIA COIMBRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128122096 - JULIANA HUTHER ALBERNAZ CRESPO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128067960 - WELTON CARLOS PAIXAO SIQUEIRA</t>
+  </si>
+  <si>
+    <t>atendimento@douraseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128137762 - JOAO JOAQUIM FELIPE</t>
+  </si>
+  <si>
+    <t>backoffice.corretora@yamaha-motor.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128554625 - MARCOS TEODORO DE MORAES</t>
+  </si>
+  <si>
+    <t>ativa@ativaseguros.net</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128557404 - MONIZE SAMARA VISENTINI</t>
+  </si>
+  <si>
+    <t>reinaldo.alves@carmais.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128564078 - WELLINGTON MARCOS SOARES DA SILVA</t>
+  </si>
+  <si>
+    <t>gilberto.a.sousa@gasmultiseg.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128989005 - VIVIANE BELLO FERRAZ CASSAROTTI</t>
+  </si>
+  <si>
+    <t>sfera@sferaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128966178 - SERGIO LUIS ESVICERO</t>
+  </si>
+  <si>
+    <t>marlucecarmoseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128926849 - MARCOS ANTONIO DA PAIXAO</t>
+  </si>
+  <si>
+    <t>higino@higinoseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129445123 - FLAVIA SANTOS</t>
+  </si>
+  <si>
+    <t>costamarina@costamarina.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129449306 - ANDRESSA RODRIGUES</t>
+  </si>
+  <si>
+    <t>edgard@futurocorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129786337 - JULIO CESAR ARAUJO JUNIOR</t>
+  </si>
+  <si>
+    <t>bruna.santos@alperseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129898040 - JULIA CAROLINA TEIXEIRA MOTTA</t>
+  </si>
+  <si>
+    <t>barizon@barizoncorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129893305 - PAMELA MELCHORA GIMENEZ RIBEIRO</t>
+  </si>
+  <si>
+    <t>midcorretora@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126796992 - IRENE DE ARAUJO ME</t>
+  </si>
+  <si>
+    <t>edson@govec.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126815705 - ROSEMEIRE STABILE SCARIN</t>
+  </si>
+  <si>
+    <t>sbbseguros@sbbseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126817170 - VANDRIA DA SILVA CORREIA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126796782 - AGENOR OLIVEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>contato@corretorarsantos.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126795590 - DENER EDUARDO ALVES DE PAULA</t>
+  </si>
+  <si>
+    <t>seguros@grupovia1.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126769913 - NAIRLA MARIA SILVA COELHO DE BRITO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126754211 - ERICA SUSE LEMOS DE LIMA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127040218 - ADILSON LOPES BORGES</t>
+  </si>
+  <si>
+    <t>contato@berce.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127140144 - PENNY PESSOA DALMAR NOBEL HOLM</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127138158 - GRASIELLY JERONIMO DOS SANTOS MARIANO</t>
+  </si>
+  <si>
+    <t>maiseguros@maiseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127128849 - EBER LINO DE BARROS</t>
+  </si>
+  <si>
+    <t>seguros@guaracorretora.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127142594 - REILMA KARLA DA SILVA SOL</t>
+  </si>
+  <si>
+    <t>essenciale@suacorretoradeseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127434140 - JEANETE DOROCIL VOLLANI</t>
+  </si>
+  <si>
+    <t>disalseguros@grupodisal.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127433470 - ELISEU SOUSA DA SILVA</t>
+  </si>
+  <si>
+    <t>patcor@terra.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127432966 - AMAURI AVELINO DO NASCIMENTO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127441574 - LAURA BIGLIASSI</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127416978 - ANDRESSA GALVAO DE ALMEIDA DUARTE</t>
+  </si>
+  <si>
+    <t>maxsegur@maxsegur.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127756451 - JOSE BERNARDINO ALVES SILVA</t>
+  </si>
+  <si>
+    <t>mrc@mrcseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127765073 - ADRIANA FERREIRA SANTOS MOURA</t>
+  </si>
+  <si>
+    <t>blindage@blindageseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127805925 - GABRIELE DE GODOI HEILIG</t>
+  </si>
+  <si>
+    <t>zanattaseguros@zanattaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128120174 - SERGIO LUIZ PIMENTEL MARTINS</t>
+  </si>
+  <si>
+    <t>global@triagroseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128532262 - ELIAS BRAZ VENUTI</t>
+  </si>
+  <si>
+    <t>antonio@ouropretoseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129430889 - RONILTON BAGIO DE SOUZA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129400697 - DANIEL AUGUSTO ALVIM NUNES PEREIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126738041 - JOAO DAMAS EVANGELISTA</t>
+  </si>
+  <si>
+    <t>valeria@sulpelotas.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126749322 - MARCIO KARNOPP DEGAR</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126756390 - WANDERLEY ANDRADE DE FREITAS</t>
+  </si>
+  <si>
+    <t>maximo@maximocorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126980826 - DANIEL NEVES HENRIQUES</t>
+  </si>
+  <si>
+    <t>atendimento@domaia.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127087232 - MAURICIO SANTOS ARAUJO</t>
+  </si>
+  <si>
+    <t>backofficeseguros@vwfs.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127356821 - MONICA DE JESUS TEIXEIRA ALBUQUERQUE PEREIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127421352 - SILVIO VINICIUS JARDIM RODRIGUES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127408001 - ADRIANA MARTINELLI CATELLI DE SOUZA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127413169 - RAFAEL WEBER MULLER</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127438855 - SILAS NUNES LYRA</t>
+  </si>
+  <si>
+    <t>joseronaldo@ccseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127696983 - PATRICK CELSO MAXIMO NETTO</t>
+  </si>
+  <si>
+    <t>vendas@americachaves.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127737684 - REGINA MARIA BARBOSA ALVES VARALDA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127757897 - FLAVIA REGINA BARBOSA</t>
+  </si>
+  <si>
+    <t>aderli@agamo.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128115362 - JEAN MICHEL DOS SANTOS</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128329710 - JORGE LUIZ DOS SANTOS SILVA</t>
+  </si>
+  <si>
+    <t>leandro@cabreraseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128432351 - LUANA PARIS DA SILVA AIELLO</t>
+  </si>
+  <si>
+    <t>administrativo@rfcorretoradeseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128452176 - GABRIELA GATTASS FABI DE TOLEDO JORGE</t>
+  </si>
+  <si>
+    <t>senadocorretoraseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128494322 - LUIZ FELIPE AGOSTINI DE SEQUEIRA</t>
+  </si>
+  <si>
+    <t>sergio.gaspar@sg3seguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128491711 - MARCELO REZENDE RAINHO TEIXEIRA</t>
+  </si>
+  <si>
+    <t>masfseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128504665 - ROBERTO PEREIRA DE SOUZA</t>
+  </si>
+  <si>
+    <t>suellen.golcalves@wtwco.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128519584 - JAQUELINE COUTO AZEVEDO</t>
+  </si>
+  <si>
+    <t>fabio@milaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128883766 - FATIMA BARBARA MORETI DE ABREU</t>
+  </si>
+  <si>
+    <t>gerencia@radarseguros.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128977197 - KAROLINE KOECH BRATI THIBES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128997002 - DANILO RIBEIRO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127618797 - ANA BEATRIZ DE ALMEIDA SILVA</t>
+  </si>
+  <si>
+    <t>conteg@contegseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129821988 - JOANA SALETE FONTANA DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129846270 - RAFAEL CASTELLANO TOCHETTO</t>
   </si>
 </sst>
 </file>
@@ -812,10 +1097,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
         <v>23</v>
-      </c>
-      <c r="B3" t="s">
-        <v>24</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -823,10 +1108,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -834,10 +1119,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" t="s">
         <v>26</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -845,7 +1130,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
@@ -911,10 +1196,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" t="s">
         <v>39</v>
-      </c>
-      <c r="B12" t="s">
-        <v>40</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -922,10 +1207,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -933,7 +1218,7 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
         <v>42</v>
@@ -944,10 +1229,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -955,10 +1240,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="B16" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -966,10 +1251,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -977,10 +1262,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -988,10 +1273,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="B19" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -999,10 +1284,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -1010,10 +1295,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -1021,10 +1306,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -1032,10 +1317,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>6</v>
+        <v>56</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -1043,164 +1328,164 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>8</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>82</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>11</v>
@@ -1208,120 +1493,120 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>78</v>
+        <v>18</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>17</v>
+        <v>90</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>10</v>
+        <v>98</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
+        <v>102</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>13</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>92</v>
+        <v>104</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>14</v>
@@ -1329,10 +1614,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>14</v>
@@ -1340,32 +1625,32 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>19</v>
+        <v>108</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>96</v>
+        <v>109</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>99</v>
+        <v>112</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>100</v>
+        <v>113</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>15</v>
@@ -1373,195 +1658,587 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>101</v>
+        <v>114</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C55" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>118</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>8</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>121</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>123</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56"/>
-    </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57"/>
-    </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58"/>
-    </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59"/>
-    </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60"/>
+      <c r="B60" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>6</v>
+      </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61"/>
+      <c r="A61" t="s">
+        <v>8</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62"/>
+      <c r="A62" t="s">
+        <v>127</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A63"/>
+      <c r="A63" t="s">
+        <v>12</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70"/>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71"/>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73"/>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74"/>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75"/>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77"/>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78"/>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79"/>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80"/>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81"/>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A82"/>
-    </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A83"/>
-    </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A84"/>
-    </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A85"/>
-    </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A86"/>
-    </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A87"/>
-    </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A88"/>
-    </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A89"/>
-    </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A90"/>
-    </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A91"/>
-    </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A92"/>
-    </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A93"/>
-    </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A94"/>
-    </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A95"/>
-    </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A96"/>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97"/>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98"/>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99"/>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A100"/>
-    </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A101"/>
-    </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A102"/>
-    </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A103"/>
-    </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A104"/>
-    </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>130</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>132</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>134</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>136</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>138</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>12</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>12</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>142</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>144</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>146</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>148</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>150</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>152</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>68</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>72</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>156</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>9</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>159</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>161</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>163</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>16</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>16</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>163</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>9</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>169</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>171</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>9</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>174</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>9</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>177</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>179</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>181</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>183</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>185</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>187</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>189</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>191</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>9</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>19</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>195</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>174</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112"/>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E8F180-2D7A-484F-A23C-3FA126D361E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F37F49-42E7-496F-98AA-CB427A666FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="14640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="124">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -53,256 +53,22 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>lilian.sudati@allianz.com.br</t>
-  </si>
-  <si>
-    <t>daiane.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12755661900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>kaue.silva@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13032572200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>thais.pessoto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12875207400000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>rosthiane.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13031307800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>lucas.almeida@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12995523700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
     <t>priscila.sousa@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13030051300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>vanessa.penatti@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13031376800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
     <t>priscila.santana@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13032559700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>elisangela.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13032567000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>lidiane.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-28262204000110 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>fernando.freitas@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13005754100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>mayara.sampaio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12785626900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>afonso.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13029984300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13032597900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>luciana.belisario@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13032588800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>eduardo.marques@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13032587900000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13032598600000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>saulo.santiago@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11274338600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>gustavo.correa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12944791800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>andreia.cardias@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13009207200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>bruno.rosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13032577600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13032594700000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>pamela.burige@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13029817200000 Nota 741 - Inspeção veicular-exclusivo Operações</t>
-  </si>
-  <si>
     <t>flavia.costa@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13032584500000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>daniele.beck@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11795989100000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>claudia.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13032588500000 Nota 595 - ERRO PDF Proposta</t>
-  </si>
-  <si>
-    <t>raullison.castro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13032600800000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12858648600000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12955176400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13016811600000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13029891500000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13029935400000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13030113100000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13030453100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13030514700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13031043600000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13031093000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13031282200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13031542000000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13031563400000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13031627600000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13032952400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13033170900000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13033203000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
     <t>dimas.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13028072000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>rogerio.souza@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12616527500000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>lucidene.santana@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12697918300000 Nota 167 - Retorno Cobrança op53</t>
-  </si>
-  <si>
-    <t>aline.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12998169900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>mauricio.santo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12468296800000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>jaqueline.nicacio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12809511000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>adm@segurotranquilo.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126766500 - NADIA MARCELLINO CANDIDO</t>
   </si>
   <si>
     <t>Prezado(a), 
@@ -314,22 +80,7 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>karen@schneidseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126789863 - KAREN BORGES SCHNEID</t>
-  </si>
-  <si>
-    <t>diamantinaseguros@diamantinaseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126810122 - GISLAINE APARECIDA DA CRUZ OLIVEIRA</t>
-  </si>
-  <si>
     <t>backoffice.corretora@yamaha-motor.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127164862 - ISAQUE GALDINO DE CARVALHO</t>
   </si>
   <si>
     <t>Prezado(a), 
@@ -341,22 +92,7 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>manoeljr@atolseg.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127146836 - SUZANA MASUR</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127146764 - PAULO AUGUSTO DO NASCIMENTO LIMA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127128696 - PAULO HENRIQUE ALVES SILVA</t>
-  </si>
-  <si>
     <t>renovacaoseguros@honda.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127232755 - LUDMILLA DA SILVA CAMARAO CABRAL</t>
   </si>
   <si>
     <t>Prezado(a), 
@@ -368,64 +104,10 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>alliancaseguros1@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127442123 - RAFAELA DANTAS DINIZ MORAES</t>
-  </si>
-  <si>
-    <t>segkarla@terra.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127457462 - DIRCEU ADOLFO DIRK</t>
-  </si>
-  <si>
     <t>backofficecorretora@segurostoyota.com.br</t>
   </si>
   <si>
-    <t>Captura de parcela rejeitada - Apólice 127464677 - CPMX CONSULTORIA IMOBILIARIA LTDA ME</t>
-  </si>
-  <si>
     <t>suporte.vvd@vwfs.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127456694 - ELIZABETH DA SILVA LOPES</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127497712 - GERSON FERREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>npseguros@uol.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127498372 - SILVIA MARIA MAGALHAES DE SOUZA</t>
-  </si>
-  <si>
-    <t>thiago.freitas@haganaseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127775030 - VALDEMIR CUNHA</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>atendimento@wacor.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127791365 - FLAVIA MARIA DE LIMA CAVALCANTE</t>
-  </si>
-  <si>
-    <t>camilo@riosegon.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127946229 - JOSE LUIS BUENO DE CAMPOS</t>
   </si>
   <si>
     <t>Prezado(a), 
@@ -437,33 +119,6 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>contato@foster.seg.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127968835 - ROSA LIANE KLEIN STANKOWSKI</t>
-  </si>
-  <si>
-    <t>bhrseguros@bhr.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128080004 - ROSEMEIRE APARECIDA PICORELI DE SOUZA</t>
-  </si>
-  <si>
-    <t>pendencia@vilavelha.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128162982 - MONICA MARIA DO NASCIMENTO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128079849 - EDMILTON SIMOES DUARTE</t>
-  </si>
-  <si>
-    <t>renovacao@volantseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128588263 - NEYRISLAINE LOURES FERREIRA</t>
-  </si>
-  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -473,15 +128,6 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>Captura de parcela rejeitada - Apólice 128542576 - SERGIO ANTONIO BASSIT</t>
-  </si>
-  <si>
-    <t>atendimento@piaseg.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129029440 - ANA LUCIA MARRAN</t>
-  </si>
-  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -491,18 +137,6 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>reinaldo.alves@carmais.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129045964 - CRISTOVAM PEREIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>atendimento@yelli.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129462427 - VITOR EDISON DE SOUZA MAIA</t>
-  </si>
-  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 3 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -512,163 +146,10 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>esperanto@esperantoseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129512938 - ROSENILTON DE MATTOS CARVALHO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129492511 - ANTONIO CARLOS SOARES</t>
-  </si>
-  <si>
-    <t>barralife.contato@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126548932 - CASSIA MAYARA CASTRO CARVALHO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126799723 - JOAQUIM RUDRIGUES VIEIRA</t>
-  </si>
-  <si>
-    <t>mdangelis@mdangelis.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126830896 - MAURO LEME</t>
-  </si>
-  <si>
-    <t>aline@bianchiseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126833772 - ILSA TERESINHA RAMOS</t>
-  </si>
-  <si>
-    <t>seguros@cresol.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126833829 - LUCAS LELIS SILVA VICENTE</t>
-  </si>
-  <si>
-    <t>contato@diretaseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126835432 - ANGELICA CRISTIANE SOARES PROENCA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126815269 - SARKIS BORGES BUCALEN</t>
-  </si>
-  <si>
-    <t>seghura@seghura.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127047198 - PAULO CESAR ESCOBAR</t>
-  </si>
-  <si>
-    <t>protecta@protectaseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127097186 - SILVIA ALVES DE OLIVEIRA GEHRING</t>
-  </si>
-  <si>
-    <t>allianz@allianz123.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127136477 - MARINA DE OLIVEIRA MORAES</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127146638 - MARILIA SIQUEIRA D ALBUQUERQUE</t>
-  </si>
-  <si>
-    <t>carolina@norcor.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127470955 - AMANDA GLOWECKA MACHADO DIAS</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127480165 - JOSE NUNES DOS SANTOS</t>
-  </si>
-  <si>
-    <t>contigo@contigoseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127750363 - WYLLAMS CELESTINO DA SILVA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127779435 - FABRICIO LUCIANO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>atendimento@lexseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127788832 - MARIA APARECIDA PEREIRA DIAS</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127792885 - SANDRA SANTOS VAILANTE</t>
-  </si>
-  <si>
-    <t>seguromais@seguromais.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128012040 - FERNANDO SANCHEZ BENGUELLA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128071521 - JULIANA PEREIRA VIDELA</t>
-  </si>
-  <si>
-    <t>cadastro@hehcorretora.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128097490 - RODRIGO DE ALENCAR PIRES</t>
-  </si>
-  <si>
-    <t>controleseguros@gruposaga.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128145701 - ROSILENE DE SOUZA E SILVA RIBEIRO</t>
-  </si>
-  <si>
-    <t>patricia@portescorretora.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128511740 - CLAUDIA DE MORAES MARTINS PEREIRA</t>
-  </si>
-  <si>
-    <t>aoseguros@aoseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128524953 - BRUNO BRANDAO MOREIRA</t>
-  </si>
-  <si>
-    <t>lidercorretora@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129025666 - SOL CONSTRUCOES E TRANSPORTES LTDA EPP</t>
-  </si>
-  <si>
-    <t>automovel@mdsinsure.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129026731 - LUIS FERNANDO LARREA PARRA</t>
-  </si>
-  <si>
     <t>atendimento@projacseg.com.br</t>
   </si>
   <si>
-    <t>Captura de parcela rejeitada - Apólice 129337453 - DOUGLAS FREITAS CAITANO</t>
-  </si>
-  <si>
-    <t>anilton@mamadicorretoradeseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129386764 - EDER ALVES DA SILVA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129360098 - CELSO MANOEL DA COSTA</t>
-  </si>
-  <si>
     <t>seguros@grupovia1.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129936269 - GABRIEL HENRIQUE DA SILVA</t>
   </si>
   <si>
     <t>Prezado(a), 
@@ -680,10 +161,304 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>iara@durvalseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129808575 - ARLETE FRANCISCA DE OLIVEIRA</t>
+    <t>crislaine.trindade@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12929383500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>matheus.gomes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13032558100000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12902804200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>rosiane.honorato@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13032569700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>danillo.boem@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13035387200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>daniel.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13032615000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>fausto.reis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12850609700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13035410600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13020836000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>sonia.bortoleto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13035055600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>caroline.wojciechowski@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13030776900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>andriele.pala@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13032563800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>adonias.brito@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11701026899 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>noadia.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13030625600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>nilcea.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13030405300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13032596600000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>bruna.teixeira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13033749200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>renata.melo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13034154100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12628725600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13024618900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>fernando.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13030629800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13032584500000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13034037000000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13034152200000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13034763200000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13034816400000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13035244500000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12672721200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>cristiane.konrad@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12765949500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>carla.nascimento@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13028602300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>daniela.gois@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13033805100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>fabiola.caixeta@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13034221700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>carla.catalani@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13014555300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>eloiza.felippe@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13021532200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126745981 - FERNANDA VIANA DE ALBUQUERQUE</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126844788 - SIMONE CORREA PEREIRA</t>
+  </si>
+  <si>
+    <t>allianz@redelojacorr.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126864273 - MARCIELE DE FATIMA MARCHIORI</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126860084 - PAULA ANDRESSA MANCIO GABARDO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127159852 - TATIANE DE FATIMA BONTORIN</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127176386 - NATALIA RIBEIRO DOREA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127172276 - KARLA ROBERTA BEZERRA DA SILVA SANTOS</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127184539 - MARA NAIARA CABRAL DA COSTA ASSIS</t>
+  </si>
+  <si>
+    <t>corretora@costaecarminati.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127159306 - FABIO FOLLADOR MURTA</t>
+  </si>
+  <si>
+    <t>faleconosco@mapma.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127386311 - GUAJARINA GUALBERTO DA SILVA</t>
+  </si>
+  <si>
+    <t>administrativo@g4c.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127455371 - JOAO BOSCO NASCIMENTO DE SOUZA SANTOS</t>
+  </si>
+  <si>
+    <t>contate@gebramseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128129685 - CLAUDIO BERGAMO</t>
+  </si>
+  <si>
+    <t>pendencia@seguralta.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128497887 - ADRIANA FONSECA AZEVEDO</t>
+  </si>
+  <si>
+    <t>ritaromero@romeroedavid.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128975006 - MANDIOFER FERRO E ACO LTDA ME</t>
+  </si>
+  <si>
+    <t>allianz1@allianz1.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129046949 - GILSON OLIVEIRA MOREIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129044413 - MARIANA GABRIELLE PAIM CARVALHO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129057162 - PAULO MARCOLINO DA SILVA NETO</t>
+  </si>
+  <si>
+    <t>jlcs@jlcs.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129019279 - RUBIANE DIZ LUIZ</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129066551 - ALESSANDRA CAROLINE FERREIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129014461 - LUANA CRISTINA BORSATO</t>
+  </si>
+  <si>
+    <t>essegseguros@essegseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129468129 - VICTOR AGUIAR DE OLIVEIRA GOULART</t>
+  </si>
+  <si>
+    <t>joseronaldo@ccseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126900575 - GUILHERME MOREIRA CONCILIO</t>
+  </si>
+  <si>
+    <t>pedrabranca.eduardo@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129504444 - GISELE GOULARTE DE FREITAS</t>
+  </si>
+  <si>
+    <t>pendencias@rbmseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129830066 - SPEL ADMINISTRACAO DE BENS PROPRIOS LTDA</t>
+  </si>
+  <si>
+    <t>adm@liberoseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129804605 - LUZIA LIDINEIA BOSA</t>
+  </si>
+  <si>
+    <t>agillizeseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129904559 - MARCIO ARAUJO SOUSA</t>
+  </si>
+  <si>
+    <t>fernanda@marcheseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129928743 - MONICA JOANA COUTO</t>
+  </si>
+  <si>
+    <t>financeiro@wsdcorretoradeseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129928306 - SELMA MARIA HADAS DOS SANTOS</t>
   </si>
 </sst>
 </file>
@@ -1083,10 +858,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -1094,10 +869,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -1105,10 +880,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -1116,10 +891,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -1127,10 +902,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -1138,10 +913,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -1149,10 +924,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -1160,10 +935,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -1171,10 +946,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -1182,10 +957,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -1193,10 +968,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -1204,10 +979,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="B13" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -1215,10 +990,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="B14" t="s">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -1226,10 +1001,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="B15" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -1237,10 +1012,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -1248,10 +1023,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -1259,10 +1034,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -1270,10 +1045,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B19" t="s">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -1281,10 +1056,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>40</v>
+        <v>56</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -1292,10 +1067,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -1303,10 +1078,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -1314,10 +1089,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -1325,10 +1100,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>46</v>
+        <v>8</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
@@ -1336,10 +1111,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -1347,10 +1122,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>50</v>
+        <v>8</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
@@ -1358,10 +1133,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>52</v>
+        <v>8</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>53</v>
+        <v>64</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -1369,10 +1144,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>3</v>
@@ -1380,10 +1155,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>56</v>
+        <v>9</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>3</v>
@@ -1391,10 +1166,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>3</v>
@@ -1402,10 +1177,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>3</v>
@@ -1413,10 +1188,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>3</v>
@@ -1424,10 +1199,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>3</v>
@@ -1435,10 +1210,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>56</v>
+        <v>75</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>3</v>
@@ -1446,10 +1221,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>63</v>
+        <v>78</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>3</v>
@@ -1457,825 +1232,457 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>56</v>
+        <v>21</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>64</v>
+        <v>79</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>67</v>
+        <v>83</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>56</v>
+        <v>15</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>70</v>
+        <v>86</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>56</v>
+        <v>13</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>56</v>
+        <v>90</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>3</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>84</v>
+        <v>11</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>3</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>86</v>
+        <v>13</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>91</v>
+        <v>15</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>88</v>
+        <v>19</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>93</v>
+        <v>16</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>95</v>
+        <v>19</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>95</v>
+        <v>20</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>102</v>
+        <v>23</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>102</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>105</v>
+        <v>118</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>102</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>107</v>
+        <v>120</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>102</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>102</v>
+        <v>23</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>100</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C64" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>112</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>114</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>117</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>119</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="C68" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>122</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C69" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>124</v>
-      </c>
-      <c r="B70" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="C70" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>126</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C71" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>107</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C72" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>129</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>107</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A75" t="s">
-        <v>133</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A76" t="s">
-        <v>136</v>
-      </c>
-      <c r="B76" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C76" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>138</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C77" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>141</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C78" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
-        <v>91</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A80" t="s">
-        <v>144</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>109</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>147</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83" t="s">
-        <v>149</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84" t="s">
-        <v>151</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85" t="s">
-        <v>153</v>
-      </c>
-      <c r="B85" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86" t="s">
-        <v>107</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87" t="s">
-        <v>156</v>
-      </c>
-      <c r="B87" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88" t="s">
-        <v>158</v>
-      </c>
-      <c r="B88" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C88" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89" t="s">
-        <v>160</v>
-      </c>
-      <c r="B89" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C89" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90" t="s">
-        <v>109</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91" t="s">
-        <v>163</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92" t="s">
-        <v>100</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C92" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93" t="s">
-        <v>166</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94" t="s">
-        <v>158</v>
-      </c>
-      <c r="B94" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95" t="s">
-        <v>169</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96" t="s">
-        <v>100</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A97" t="s">
-        <v>172</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A98" t="s">
-        <v>107</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>175</v>
-      </c>
-      <c r="B99" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>177</v>
-      </c>
-      <c r="B100" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A101" t="s">
-        <v>179</v>
-      </c>
-      <c r="B101" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A102" t="s">
-        <v>181</v>
-      </c>
-      <c r="B102" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A103" t="s">
-        <v>183</v>
-      </c>
-      <c r="B103" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A104" t="s">
-        <v>185</v>
-      </c>
-      <c r="B104" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C104" s="2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A105" t="s">
-        <v>187</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C105" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A106" t="s">
-        <v>189</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C106" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A107" t="s">
-        <v>107</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C107" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A108" t="s">
-        <v>192</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A109" t="s">
-        <v>195</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C109" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64"/>
+    </row>
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65"/>
+    </row>
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66"/>
+    </row>
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67"/>
+    </row>
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68"/>
+    </row>
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69"/>
+    </row>
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70"/>
+    </row>
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A71"/>
+    </row>
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A72"/>
+    </row>
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A73"/>
+    </row>
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A74"/>
+    </row>
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A75"/>
+    </row>
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A76"/>
+    </row>
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A77"/>
+    </row>
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A78"/>
+    </row>
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A79"/>
+    </row>
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A80"/>
+    </row>
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A81"/>
+    </row>
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A82"/>
+    </row>
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A83"/>
+    </row>
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A84"/>
+    </row>
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A85"/>
+    </row>
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A86"/>
+    </row>
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A87"/>
+    </row>
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A88"/>
+    </row>
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A89"/>
+    </row>
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A90"/>
+    </row>
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A91"/>
+    </row>
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A92"/>
+    </row>
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A93"/>
+    </row>
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A94"/>
+    </row>
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A95"/>
+    </row>
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96"/>
+    </row>
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A97"/>
+    </row>
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A98"/>
+    </row>
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A99"/>
+    </row>
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A100"/>
+    </row>
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A101"/>
+    </row>
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A102"/>
+    </row>
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A103"/>
+    </row>
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A104"/>
+    </row>
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A105"/>
+    </row>
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A106"/>
+    </row>
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A107"/>
+    </row>
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A108"/>
+    </row>
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A109"/>
+    </row>
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110"/>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111"/>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112"/>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6F37F49-42E7-496F-98AA-CB427A666FDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2289C072-81B6-4895-9A1F-CF4D49535AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="14640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="142">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -53,22 +53,13 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>kaue.silva@allianz.com.br</t>
-  </si>
-  <si>
     <t>priscila.sousa@allianz.com.br</t>
   </si>
   <si>
     <t>priscila.santana@allianz.com.br</t>
   </si>
   <si>
-    <t>flavia.costa@allianz.com.br</t>
-  </si>
-  <si>
     <t>gabriela.logrado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>dimas.soares@allianz.com.br</t>
   </si>
   <si>
     <t>Prezado(a), 
@@ -80,9 +71,6 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>backoffice.corretora@yamaha-motor.com.br</t>
-  </si>
-  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 9 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -92,9 +80,6 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>renovacaoseguros@honda.com.br</t>
-  </si>
-  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 8 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -146,12 +131,6 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>atendimento@projacseg.com.br</t>
-  </si>
-  <si>
-    <t>seguros@grupovia1.com.br</t>
-  </si>
-  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 2 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -161,304 +140,385 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>crislaine.trindade@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12929383500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>matheus.gomes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13032558100000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12902804200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>rosiane.honorato@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13032569700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>danillo.boem@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13035387200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>daniel.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13032615000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
     <t>fausto.reis@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12850609700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13035410600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13020836000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
     <t>sonia.bortoleto@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13035055600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>caroline.wojciechowski@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13030776900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>andriele.pala@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13032563800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
     <t>adonias.brito@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-11701026899 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>noadia.rodrigues@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13030625600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>nilcea.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13030405300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13032596600000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>bruna.teixeira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13033749200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>renata.melo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13034154100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12628725600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13024618900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>fernando.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13030629800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13032584500000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13034037000000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13034152200000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13034763200000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13034816400000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13035244500000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12672721200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>cristiane.konrad@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12765949500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>carla.nascimento@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13028602300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>daniela.gois@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13033805100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>fabiola.caixeta@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13034221700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>carla.catalani@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13014555300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>eloiza.felippe@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13021532200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126745981 - FERNANDA VIANA DE ALBUQUERQUE</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126844788 - SIMONE CORREA PEREIRA</t>
-  </si>
-  <si>
-    <t>allianz@redelojacorr.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126864273 - MARCIELE DE FATIMA MARCHIORI</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126860084 - PAULA ANDRESSA MANCIO GABARDO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127159852 - TATIANE DE FATIMA BONTORIN</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127176386 - NATALIA RIBEIRO DOREA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127172276 - KARLA ROBERTA BEZERRA DA SILVA SANTOS</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127184539 - MARA NAIARA CABRAL DA COSTA ASSIS</t>
-  </si>
-  <si>
-    <t>corretora@costaecarminati.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127159306 - FABIO FOLLADOR MURTA</t>
-  </si>
-  <si>
-    <t>faleconosco@mapma.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127386311 - GUAJARINA GUALBERTO DA SILVA</t>
-  </si>
-  <si>
-    <t>administrativo@g4c.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127455371 - JOAO BOSCO NASCIMENTO DE SOUZA SANTOS</t>
-  </si>
-  <si>
-    <t>contate@gebramseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128129685 - CLAUDIO BERGAMO</t>
-  </si>
-  <si>
-    <t>pendencia@seguralta.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128497887 - ADRIANA FONSECA AZEVEDO</t>
-  </si>
-  <si>
-    <t>ritaromero@romeroedavid.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128975006 - MANDIOFER FERRO E ACO LTDA ME</t>
-  </si>
-  <si>
-    <t>allianz1@allianz1.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129046949 - GILSON OLIVEIRA MOREIRA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129044413 - MARIANA GABRIELLE PAIM CARVALHO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129057162 - PAULO MARCOLINO DA SILVA NETO</t>
-  </si>
-  <si>
-    <t>jlcs@jlcs.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129019279 - RUBIANE DIZ LUIZ</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129066551 - ALESSANDRA CAROLINE FERREIRA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129014461 - LUANA CRISTINA BORSATO</t>
-  </si>
-  <si>
-    <t>essegseguros@essegseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129468129 - VICTOR AGUIAR DE OLIVEIRA GOULART</t>
-  </si>
-  <si>
-    <t>joseronaldo@ccseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126900575 - GUILHERME MOREIRA CONCILIO</t>
-  </si>
-  <si>
-    <t>pedrabranca.eduardo@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129504444 - GISELE GOULARTE DE FREITAS</t>
-  </si>
-  <si>
     <t>pendencias@rbmseguros.com.br</t>
   </si>
   <si>
-    <t>Captura de parcela rejeitada - Apólice 129830066 - SPEL ADMINISTRACAO DE BENS PROPRIOS LTDA</t>
-  </si>
-  <si>
-    <t>adm@liberoseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129804605 - LUZIA LIDINEIA BOSA</t>
-  </si>
-  <si>
-    <t>agillizeseguros@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129904559 - MARCIO ARAUJO SOUSA</t>
-  </si>
-  <si>
-    <t>fernanda@marcheseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129928743 - MONICA JOANA COUTO</t>
-  </si>
-  <si>
-    <t>financeiro@wsdcorretoradeseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129928306 - SELMA MARIA HADAS DOS SANTOS</t>
+    <t>lilian.sudati@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12755661900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>tadeu.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13028436300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>erica.cassandre@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13031009200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>thais.pessoto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12663279100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>alessandra.araujo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13033677800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12610468400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>tatiany.macedo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12927975500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13026009200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13035277700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13028814800000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13034502100000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13036852000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13037098500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13037167300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>juliana.assis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12684870700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>mayara.sampaio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12834201500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13034152400000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13034613700000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>andre.gouvea@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13038795400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>everton.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12975849900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13034300600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13037045900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>douglas.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12967216300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>vitor.mattos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13036972100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>andreia.cardias@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12932078700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>laiane.martins@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12877710100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>daniel.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12933765500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>daniele.beck@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13037939100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>gustavo.arruda@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12793201300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>raullison.castro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13037649700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13032243100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13033979400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13034256300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13034345200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13034363700000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13035078000000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13035146900000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13035444700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13035465600000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13036187800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13036204200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13036404400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13037106800000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13037316500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13037326300000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13037347200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13037385800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>bruna.carneiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12973703600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>daniella.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12971830900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13024723500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>thays.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13037297300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13037318700000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>enriete.saucedo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13016259600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rosemeire.faria@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12595910200000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>carolina.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12604618400000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>rogerio.souza@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12901709800000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>lucidene.santana@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13017492400000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>claudenice.barbosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13035297600000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126866523 - CRISTINA BRONZATO BUENO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127176963 - HUELIGTON PEREIRA DE MELO</t>
+  </si>
+  <si>
+    <t>rogerio@bw4seguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127173235 - DAYANE DA SILVA RODRIGUES DAMACENO</t>
+  </si>
+  <si>
+    <t>jeferson.beltran@beltrancorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127276115 - SUELEN STEIL GEMERASCA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127480986 - VALMIR BARZAN</t>
+  </si>
+  <si>
+    <t>dalviseguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127493243 - NIVEA CRISTINA SENA COSTA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127499979 - ALBERTO GONCALVES BRASIL FILHO</t>
+  </si>
+  <si>
+    <t>tecnico1@centrosulseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127797733 - LEODECIO BRAZ DA SILVA SEGUNDO</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>jair@jnss.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127823704 - LARISSA USBERTI SOTTO FABIANO</t>
+  </si>
+  <si>
+    <t>nossacorretoraseg@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127824046 - VITORIA REGIA DA COSTA NETO PALLOTTINO</t>
+  </si>
+  <si>
+    <t>reinaldo.alves@carmais.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128093132 - JOSE HAMISTERDAN DE LEMOS FELIX</t>
+  </si>
+  <si>
+    <t>daitxseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128199787 - ANA LUCIA DUTRA RODRIGUES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128199600 - ANA LUCIA DUTRA RODRIGUES</t>
+  </si>
+  <si>
+    <t>suzi@v12corretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128202610 - JULIO CESAR FERREIRA</t>
+  </si>
+  <si>
+    <t>agseguros@terra.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128552375 - WAGNER JOSE CORAZZARI FILHO</t>
+  </si>
+  <si>
+    <t>gripp@grippseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128952973 - JAYME EDUARDO JUNQUEIRA VENTURATO</t>
+  </si>
+  <si>
+    <t>relacionamento@gpnc.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129029349 - JOSE LEVI PEREIRA MONTEBELO</t>
+  </si>
+  <si>
+    <t>divisaseguros@terra.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129069417 - NILSON SERGIO TRAVALINI</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129386173 - MERICIA FONSECA DE CARVALHO</t>
+  </si>
+  <si>
+    <t>joaocorretordeseguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129791315 - CARLA ZANDAVALLI</t>
   </si>
 </sst>
 </file>
@@ -858,10 +918,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -869,10 +929,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -880,10 +940,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -891,10 +951,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" t="s">
         <v>29</v>
-      </c>
-      <c r="B5" t="s">
-        <v>30</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -902,10 +962,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B6" t="s">
         <v>31</v>
-      </c>
-      <c r="B6" t="s">
-        <v>32</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -913,10 +973,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -924,10 +984,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -935,10 +995,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -946,10 +1006,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -957,10 +1017,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>39</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -968,10 +1028,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -979,10 +1039,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -990,10 +1050,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -1001,10 +1061,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>47</v>
+        <v>5</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -1012,10 +1072,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="B16" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -1023,10 +1083,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B17" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -1034,10 +1094,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="B18" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -1045,10 +1105,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="B19" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -1056,10 +1116,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -1067,10 +1127,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -1078,10 +1138,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -1089,10 +1149,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -1100,10 +1160,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
@@ -1111,10 +1171,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -1122,10 +1182,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>8</v>
+        <v>58</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
@@ -1133,10 +1193,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -1144,10 +1204,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>8</v>
+        <v>62</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>3</v>
@@ -1155,10 +1215,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>3</v>
@@ -1166,10 +1226,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>68</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>3</v>
@@ -1177,10 +1237,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>3</v>
@@ -1188,10 +1248,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>71</v>
+        <v>6</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>3</v>
@@ -1199,10 +1259,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>73</v>
+        <v>6</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>3</v>
@@ -1210,10 +1270,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>75</v>
+        <v>6</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>3</v>
@@ -1221,10 +1281,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>3</v>
@@ -1232,409 +1292,553 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>81</v>
+        <v>6</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>88</v>
+        <v>6</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>90</v>
+        <v>6</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>92</v>
+        <v>6</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>94</v>
+        <v>6</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>17</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>96</v>
+        <v>6</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>11</v>
+        <v>89</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>16</v>
+        <v>97</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>115</v>
+        <v>25</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>23</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>120</v>
+        <v>10</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>121</v>
+        <v>107</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>10</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>109</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>111</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>21</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>114</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>11</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>117</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>120</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
         <v>122</v>
       </c>
-      <c r="B63" s="2" t="s">
+      <c r="B71" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A64"/>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68"/>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69"/>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70"/>
-    </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A71"/>
-    </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A72"/>
-    </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A73"/>
-    </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A74"/>
-    </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A75"/>
-    </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A76"/>
-    </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A77"/>
-    </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A78"/>
-    </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A79"/>
-    </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A80"/>
-    </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A81"/>
-    </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="C71" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>124</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>126</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>126</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>129</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>131</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>133</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>135</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>137</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>10</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>140</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96"/>
     </row>
     <row r="97" spans="1:1" x14ac:dyDescent="0.25">

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2289C072-81B6-4895-9A1F-CF4D49535AAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0A4FC01-B04B-42DC-8948-79A4D5BC64CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="28920" windowHeight="14640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="180">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -53,13 +53,70 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>priscila.sousa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>priscila.santana@allianz.com.br</t>
-  </si>
-  <si>
     <t>gabriela.logrado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>sonia.bortoleto@allianz.com.br</t>
+  </si>
+  <si>
+    <t>raullison.castro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>lucidene.santana@allianz.com.br</t>
+  </si>
+  <si>
+    <t>diogo.junior@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13036805100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>yuri.santos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13035349400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12722447300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>armando.filho@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12892718400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13041214100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13028941800000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>laila.steil@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13033265100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>ivone.jesus@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12826963300000 Nota 167 - Retorno Cobrança op53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13026861400000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>nelma.xavier@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12898534200000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>vbsegs@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126844850 - LUIS CLAUDIO MATOS DA MOTA</t>
   </si>
   <si>
     <t>Prezado(a), 
@@ -71,6 +128,30 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
+    <t>bellia@bellia.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126870550 - REGINA TEREZA CAPRA CAVION</t>
+  </si>
+  <si>
+    <t>contato@unifisaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126883216 - ANA CAROLINA TOLEDO BAYER</t>
+  </si>
+  <si>
+    <t>aferbrasil@aferbrasil.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126864149 - CAMILA ALBUQUERQUE LINHARES ROMEIRO</t>
+  </si>
+  <si>
+    <t>backofficecorretora@segurostoyota.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127173239 - ADRIANA DE LOURDES PIRES COELHO</t>
+  </si>
+  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 9 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -80,6 +161,33 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
+    <t>Captura de parcela rejeitada - Apólice 127212741 - JOSE DA SILVA MOTTA</t>
+  </si>
+  <si>
+    <t>suporte.vvd@vwfs.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127214571 - FLAVIO WAKED DE MORAES REGO</t>
+  </si>
+  <si>
+    <t>renovacaoseguros@honda.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127216564 - SOLARCHIO PARTICIPACOES LTDA</t>
+  </si>
+  <si>
+    <t>info@plataformaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127216197 - BRUNO SOARES DA SILVA</t>
+  </si>
+  <si>
+    <t>casullo@casulloseguros.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127523311 - NATALIA COSTA REGHINI</t>
+  </si>
+  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 8 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -89,10 +197,25 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>backofficecorretora@segurostoyota.com.br</t>
-  </si>
-  <si>
-    <t>suporte.vvd@vwfs.com</t>
+    <t>renova@procede.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127784824 - RODOLFO POLCARO SAENZ</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>tinoduarte@porthalseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128201115 - ALAN AUGUSTO MARINO</t>
   </si>
   <si>
     <t>Prezado(a), 
@@ -104,6 +227,27 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
+    <t>Captura de parcela rejeitada - Apólice 128198489 - RAQUEL RODRIGUES DE PAIVA LEITE</t>
+  </si>
+  <si>
+    <t>diamantinaseguros@diamantinaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128222524 - GEILSON BARBOSA SILVEIRA</t>
+  </si>
+  <si>
+    <t>norteemissao@nortecorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128224312 - CELESTE PIMENTEL FAYAL</t>
+  </si>
+  <si>
+    <t>pendencias@jlcf.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128545549 - CRISTIANE JANOTTI CERQUEIRA LEITE</t>
+  </si>
+  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -113,6 +257,60 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
+    <t>roberto@susanseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128558559 - EDUARDO ZANETTI BUECKMANN</t>
+  </si>
+  <si>
+    <t>canastraseguro@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128641769 - ANTONIO VANDERCI DURAN</t>
+  </si>
+  <si>
+    <t>operacional@abcorseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128668250 - ANDRE ANVERSA</t>
+  </si>
+  <si>
+    <t>backoffice.corretora@yamaha-motor.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128677186 - CICERO GALDINO DA SILVA</t>
+  </si>
+  <si>
+    <t>sicoobcorretora@sicoobcorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128681804 - IZOLETE KRUGER KERBER</t>
+  </si>
+  <si>
+    <t>daninseguros@uol.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128660405 - PATRICIA DE JESUS CARLOS LIGEIRO BARBOSA</t>
+  </si>
+  <si>
+    <t>vendas@americachaves.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127737684 - REGINA MARIA BARBOSA ALVES VARALDA</t>
+  </si>
+  <si>
+    <t>reinaldo.alves@carmais.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128656851 - GILBERTO FREITAS DE OLIVEIRA JUNIOR</t>
+  </si>
+  <si>
+    <t>rebecanfc@yahoo.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129096219 - REBECA NUNES FONSECA DA CUNHA</t>
+  </si>
+  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -122,6 +320,12 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
+    <t>seguros@iconecorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129391959 - MARCELO MARQUES DE MIRANDA</t>
+  </si>
+  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 3 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -131,6 +335,15 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
+    <t>Captura de parcela rejeitada - Apólice 129543809 - ANGELICA SOUZA CENCI</t>
+  </si>
+  <si>
+    <t>afonsecaseguros@sercomtel.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 130001669 - JOSE BRENO FERRAZ JUNIOR</t>
+  </si>
+  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 2 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -140,385 +353,286 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>fausto.reis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>sonia.bortoleto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>adonias.brito@allianz.com.br</t>
-  </si>
-  <si>
-    <t>noadia.rodrigues@allianz.com.br</t>
+    <t>supervisor1.corretora@grupoleauto.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127113578 - PALOMA MENDES VIEIRA</t>
+  </si>
+  <si>
+    <t>gian@gianfseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127153318 - TAISSA MACAFERRI LICATTI</t>
+  </si>
+  <si>
+    <t>desenho@desenhoseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127185596 - JANE MARIA DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127179429 - SEMIRAMIS OLIVEIRA ROSADO DINIZ</t>
+  </si>
+  <si>
+    <t>landim@landimcorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127359207 - SILVIO FERREIRA GOMES JUNIOR</t>
+  </si>
+  <si>
+    <t>anderson@a2l2.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127459858 - FERNANDA DINIZ VASCONCELOS</t>
+  </si>
+  <si>
+    <t>contigo@contigoseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127817719 - NAAMA PEGADO FERREIRA</t>
+  </si>
+  <si>
+    <t>renata.guedes@adtsa.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127828136 - MARIA ROSALIA DA SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127843551 - PAULO VICTOR CAMPELO COSTA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127720469 - REALINO MARQUES TABANEZ</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127853956 - ROSIMERE FERREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>emissao@willistowerswatson.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128567164 - KARINA DE FATIMA LOPES FREITAS</t>
+  </si>
+  <si>
+    <t>operacional@resguardeseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128534128 - SANDRA CAMARA DA CRUZ</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128648856 - SONIA DO NASCIMENTO DA CUNHA</t>
+  </si>
+  <si>
+    <t>fenix@corretorafenix.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128530501 - JULIANA STOFFELLA ZATTAR COELHO</t>
+  </si>
+  <si>
+    <t>pendencia@seguralta.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128660884 - PHRSYSTEM CONSTRUTORA LTDA ME</t>
+  </si>
+  <si>
+    <t>cintaxiseguros@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128639265 - JOSE LEONARDO SILVA DE JESUS</t>
+  </si>
+  <si>
+    <t>comercial@mercanteseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128637804 - TIAGO GOMES PEIXOTO</t>
+  </si>
+  <si>
+    <t>chsseguros@outlook.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128670043 - VILMA ALVIM DE CARVALHO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128605697 - MARTA CALDEIRA DE OLIVEIRA KALK</t>
+  </si>
+  <si>
+    <t>essegseguros@essegseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128549807 - EDUARDO HENRIQUE DA SILVA</t>
+  </si>
+  <si>
+    <t>azecor@azecor.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129027092 - KERLI CRISTINA VIGLIOTTI SILVESTRE</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129134301 - MARCELA MARIA DE MELO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129133312 - JOAO SOUZA SANTOS JUNIOR</t>
+  </si>
+  <si>
+    <t>sanyuu@sanyuu.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129104624 - DEFFY TECNOLOGIA EM SEGUROS E SERVICOS LTDA E</t>
+  </si>
+  <si>
+    <t>backoffice.mds04@altio-op.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129055364 - MOACY BARBOSA DA SILVA JUNIOR</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129124183 - ITALO CORDEIRO DE BARROS IZAIAS</t>
+  </si>
+  <si>
+    <t>luciane.monteiro@idealvr.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129119258 - ELZA FERNANDES DA SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129460039 - SUELAINE OLIVEIRA LUCIANO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129493649 - JOSIELMO APARECIDO ANTUNES ALVES</t>
+  </si>
+  <si>
+    <t>melrioseguros@globo.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129886530 - MAGNO ALEXANDRE NETO</t>
+  </si>
+  <si>
+    <t>inaldo@ialcorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126877683 - WANDERSON STEWART PARREIRA MIRANDA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126883392 - KELLY ANTUNES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126861536 - MARIA DAS GRACAS ZENI DE SOUZA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127163191 - MIRELLA ALBUQUERQUE SOUSA</t>
+  </si>
+  <si>
+    <t>protecta@protectaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127161511 - RAYZA OLIVEIRA ECHEVERRIA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127201032 - GILMAR GUEDES MORAIS JUNIOR</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127158524 - MIRIAM YAMAZAKI PEZZOTTA</t>
+  </si>
+  <si>
+    <t>contato@economicaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127354724 - NATALIA GOMES MILANI</t>
+  </si>
+  <si>
+    <t>qualities.seguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127500888 - DANIEL DE ANDRADE FERNANDES</t>
+  </si>
+  <si>
+    <t>allianz@redelojacorr.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127824531 - RODRIGO LEANDRO COSTA</t>
+  </si>
+  <si>
+    <t>corretora@pessego.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128158034 - DUILIO DANTAS BRITO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128209675 - MARCOS ANTONIO GUEDES DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128209743 - LUANA DOS SANTOS SILVA NOGUEIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128210020 - DARIO GOMES DE CASTRO</t>
   </si>
   <si>
     <t>pendencias@rbmseguros.com.br</t>
   </si>
   <si>
-    <t>lilian.sudati@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12755661900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>tadeu.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13028436300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>erica.cassandre@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13031009200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>thais.pessoto@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12663279100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>alessandra.araujo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13033677800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12610468400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>tatiany.macedo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12927975500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13026009200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13035277700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13028814800000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13034502100000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13036852000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13037098500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13037167300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>juliana.assis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12684870700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>mayara.sampaio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12834201500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13034152400000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13034613700000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>andre.gouvea@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13038795400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>everton.silva1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12975849900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13034300600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13037045900000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>douglas.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12967216300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>vitor.mattos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13036972100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>andreia.cardias@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12932078700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>laiane.martins@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12877710100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>daniel.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12933765500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daniele.beck@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13037939100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>gustavo.arruda@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12793201300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>raullison.castro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13037649700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13032243100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13033979400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13034256300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13034345200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13034363700000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13035078000000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13035146900000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13035444700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13035465600000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13036187800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13036204200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13036404400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13037106800000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13037316500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13037326300000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13037347200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13037385800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>bruna.carneiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12973703600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daniella.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12971830900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13024723500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>thays.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13037297300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13037318700000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>enriete.saucedo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13016259600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>rosemeire.faria@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12595910200000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>carolina.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12604618400000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>rogerio.souza@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12901709800000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>lucidene.santana@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13017492400000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>claudenice.barbosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13035297600000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126866523 - CRISTINA BRONZATO BUENO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127176963 - HUELIGTON PEREIRA DE MELO</t>
-  </si>
-  <si>
-    <t>rogerio@bw4seguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127173235 - DAYANE DA SILVA RODRIGUES DAMACENO</t>
-  </si>
-  <si>
-    <t>jeferson.beltran@beltrancorretora.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127276115 - SUELEN STEIL GEMERASCA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127480986 - VALMIR BARZAN</t>
-  </si>
-  <si>
-    <t>dalviseguros@hotmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127493243 - NIVEA CRISTINA SENA COSTA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127499979 - ALBERTO GONCALVES BRASIL FILHO</t>
-  </si>
-  <si>
-    <t>tecnico1@centrosulseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127797733 - LEODECIO BRAZ DA SILVA SEGUNDO</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>jair@jnss.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127823704 - LARISSA USBERTI SOTTO FABIANO</t>
-  </si>
-  <si>
-    <t>nossacorretoraseg@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127824046 - VITORIA REGIA DA COSTA NETO PALLOTTINO</t>
-  </si>
-  <si>
-    <t>reinaldo.alves@carmais.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128093132 - JOSE HAMISTERDAN DE LEMOS FELIX</t>
-  </si>
-  <si>
-    <t>daitxseguros@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128199787 - ANA LUCIA DUTRA RODRIGUES</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128199600 - ANA LUCIA DUTRA RODRIGUES</t>
-  </si>
-  <si>
-    <t>suzi@v12corretora.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128202610 - JULIO CESAR FERREIRA</t>
-  </si>
-  <si>
-    <t>agseguros@terra.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128552375 - WAGNER JOSE CORAZZARI FILHO</t>
-  </si>
-  <si>
-    <t>gripp@grippseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128952973 - JAYME EDUARDO JUNQUEIRA VENTURATO</t>
-  </si>
-  <si>
-    <t>relacionamento@gpnc.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129029349 - JOSE LEVI PEREIRA MONTEBELO</t>
-  </si>
-  <si>
-    <t>divisaseguros@terra.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129069417 - NILSON SERGIO TRAVALINI</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129386173 - MERICIA FONSECA DE CARVALHO</t>
-  </si>
-  <si>
-    <t>joaocorretordeseguros@hotmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129791315 - CARLA ZANDAVALLI</t>
+    <t>Captura de parcela rejeitada - Apólice 128518354 - LUCIA REGINA DA SILVEIRA SANTOS</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128559200 - ERIKA BARBOSA TEIXEIRA DE SOUSA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128601566 - ANDREY FERNANDE DE MEDEIROS</t>
+  </si>
+  <si>
+    <t>barralife.contato@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126548932 - CASSIA MAYARA CASTRO CARVALHO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128618656 - ROBERTA MARIA ARAUJO GADELHA</t>
+  </si>
+  <si>
+    <t>maria_gomes@ajg.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128628210 - SILVIA QUINTAO NADALINI</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129006215 - ALMIR DE ALMEIDA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129093203 - JOSE SOBREIRO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129102405 - CICERO DA SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129068349 - CARILE FERRO MENEGHELI</t>
+  </si>
+  <si>
+    <t>backofficeseguros@vwfs.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129479452 - ANTONIA ANELIZIA DE CASTRO MAIA CHAVES</t>
+  </si>
+  <si>
+    <t>auto@moxuaraseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129489722 - FLAVIA CRISTINA DE CASTRO SARMENGHI</t>
+  </si>
+  <si>
+    <t>atendimentoemissao@brcorretorafoz.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129507749 - RAPHAEL DE PAULA BARTHOLO</t>
+  </si>
+  <si>
+    <t>magno@wiseseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129948045 - DANIELA ASSAFF LEAL MOBARAK</t>
+  </si>
+  <si>
+    <t>junior@viamultipla.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126976940 - LEONORIO LOURENCAO FILHO</t>
   </si>
 </sst>
 </file>
@@ -918,10 +1032,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -929,10 +1043,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -940,10 +1054,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -951,10 +1065,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -962,10 +1076,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -973,10 +1087,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -984,10 +1098,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -995,10 +1109,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -1006,10 +1120,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B10" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -1017,10 +1131,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -1028,865 +1142,1009 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="B13" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="B14" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="B15" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B18" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>3</v>
+        <v>51</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>3</v>
+        <v>51</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>3</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>3</v>
+        <v>51</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>6</v>
+        <v>68</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>71</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>3</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>3</v>
+        <v>81</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>3</v>
+        <v>81</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>6</v>
+        <v>83</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>3</v>
+        <v>85</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="B40" s="2" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>6</v>
+        <v>33</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>81</v>
+        <v>92</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>3</v>
+        <v>35</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>6</v>
+        <v>97</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>6</v>
+        <v>99</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>6</v>
+        <v>66</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>86</v>
+        <v>101</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>89</v>
+        <v>39</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>3</v>
+        <v>48</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>92</v>
+        <v>106</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>95</v>
+        <v>109</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>96</v>
+        <v>110</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>70</v>
+        <v>121</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>3</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>3</v>
+        <v>78</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>7</v>
+        <v>78</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>8</v>
+        <v>78</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>8</v>
+        <v>78</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>9</v>
+        <v>78</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>11</v>
+        <v>120</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>9</v>
+        <v>81</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>117</v>
+        <v>53</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>119</v>
+        <v>85</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>119</v>
+        <v>26</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>124</v>
+        <v>39</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>125</v>
+        <v>139</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>126</v>
+        <v>39</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>127</v>
+        <v>140</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>126</v>
+        <v>33</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>129</v>
+        <v>142</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>12</v>
+        <v>35</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>131</v>
+        <v>33</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>132</v>
+        <v>144</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>14</v>
+        <v>35</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>14</v>
+        <v>45</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>10</v>
+        <v>150</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A82"/>
+      <c r="A82" t="s">
+        <v>74</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A83"/>
+      <c r="A83" t="s">
+        <v>39</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A84"/>
+      <c r="A84" t="s">
+        <v>74</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>51</v>
+      </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A85"/>
+      <c r="A85" t="s">
+        <v>157</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A86"/>
+      <c r="A86" t="s">
+        <v>39</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A87"/>
+      <c r="A87" t="s">
+        <v>33</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A88"/>
+      <c r="A88" t="s">
+        <v>161</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A89"/>
+      <c r="A89" t="s">
+        <v>39</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A90"/>
+      <c r="A90" t="s">
+        <v>164</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A91"/>
+      <c r="A91" t="s">
+        <v>41</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A92"/>
+      <c r="A92" t="s">
+        <v>111</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A93"/>
+      <c r="A93" t="s">
+        <v>66</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A94"/>
+      <c r="A94" t="s">
+        <v>39</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A95"/>
+      <c r="A95" t="s">
+        <v>170</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A96"/>
-    </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A97"/>
-    </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A98"/>
-    </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A99"/>
-    </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>172</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>174</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>176</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>178</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112"/>
     </row>
     <row r="113" spans="1:1" x14ac:dyDescent="0.25">
@@ -2048,31 +2306,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAzNTMxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MzAvMTIvMjAyMCAxMTo0NTo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAzMC8xMi8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAzNTMxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MzAvMTIvMjAyMCAxMTo0NTo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAzMC8xMi8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DBFCB3-53E5-4527-B13D-DC7A854D4B55}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41A8E509-6991-4B84-B1B5-13851E156C6A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DBFCB3-53E5-4527-B13D-DC7A854D4B55}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CA3DF5A-975F-48C3-9E84-64E1C369407A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83B5AE3-DEC9-4D01-914A-950E4DDD30A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28800" windowHeight="14670" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envio Robô" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="67">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -56,19 +56,121 @@
     <t>yuri.santos@allianz.com.br</t>
   </si>
   <si>
-    <t>ivone.jesus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 10 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>backofficecorretora@segurostoyota.com.br</t>
+    <t>juliano.guimaraes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>fausto.reis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12610468400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>crislaine.trindade@allianz.com.br</t>
+  </si>
+  <si>
+    <t>daniel.lourenco@allianz.com.br</t>
+  </si>
+  <si>
+    <t>viviane.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>noadia.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>saulo.santiago@allianz.com.br</t>
+  </si>
+  <si>
+    <t>talita.meneses@allianz.com.br</t>
+  </si>
+  <si>
+    <t>viviane.corbari@allianz.com.br</t>
+  </si>
+  <si>
+    <t>andrea.duarte@allianz.com.br</t>
+  </si>
+  <si>
+    <t>cassia.souza@allianz.com.br</t>
+  </si>
+  <si>
+    <t>raullison.castro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>gabriela.logrado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>rodrigo.nascimento@allianz.com.br</t>
+  </si>
+  <si>
+    <t>rafael.leite@allianz.com.br</t>
+  </si>
+  <si>
+    <t>nicole.demori@allianz.com.br</t>
+  </si>
+  <si>
+    <t>cristiane.lozano@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13002364100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13041677500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13042857600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13045258200000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12996617000000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12684310500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12998324000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12674894100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13020157100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13043297300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12671449200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12672039000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13044957700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13029848400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13044524900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12720344200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13044849900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13034501200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13039072400000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>lucas@pracatu.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127120111 - NIVALDO ANDREAZZI</t>
   </si>
   <si>
     <t>Prezado(a), 
@@ -80,19 +182,43 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>suporte.vvd@vwfs.com</t>
-  </si>
-  <si>
-    <t>renovacaoseguros@honda.com.br</t>
+    <t>backofficecorretora@segurostoyota.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127200392 - PATRICIA DE MORAES SILVA</t>
+  </si>
+  <si>
+    <t>operacional@durangocorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127491198 - CAIO CRUZ MENEZES VITORIO</t>
   </si>
   <si>
     <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Identificamos uma falha na tentativa de captura da parcela 8 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
 Pedimos desculpas pelo transtorno causado.
 Att.
 Departamento de Cobrança
 "Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>nilsonfilho@nillmorseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127524663 - JUSCELINO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127545522 - FILIPE MARCEL BRITO DE SOUZA</t>
+  </si>
+  <si>
+    <t>renovacaoseguros@honda.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127552928 - HORACIO BATISTA DOS SANTOS JUNIOR</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128252495 - LUDMILA VIANA SILVA E SILVA</t>
   </si>
   <si>
     <t>Prezado(a), 
@@ -104,19 +230,28 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>diamantinaseguros@diamantinaseguros.com.br</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>backoffice.corretora@yamaha-motor.com.br</t>
+    <t>prontocar@prontocarseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128252321 - CRISTIANE DE OLIVEIRA SANTANA</t>
+  </si>
+  <si>
+    <t>reinaldo.alves@carmais.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128255047 - NAGELA MARIA SILVA DA ROCHA DE ANDRADE</t>
+  </si>
+  <si>
+    <t>administrativo@wagonseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128263248 - GLAUCIA DE JORGE CARVALHO PESSANHA</t>
+  </si>
+  <si>
+    <t>adriana.faria@jorlan.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129134133 - EDMEA CARNEIRO MARIANO CUNHA</t>
   </si>
   <si>
     <t>Prezado(a), 
@@ -128,277 +263,7 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 3 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>pendencia@seguralta.com.br</t>
-  </si>
-  <si>
-    <t>lilian.sudati@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12755661900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>matheus.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13034478400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>juliano.guimaraes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13040965400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>samuel.martins@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12704095300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>danillo.boem@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13035387200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>jaciely.dias@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13024477900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>flavio.cesar@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13041850600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>fausto.reis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12610468400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13035595000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>elisangela.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13041397300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>mayara.sampaio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13041512500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>leandro.gonzaga@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12996163300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>erineuza.monzillo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13019937400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daiane.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12997228300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>aline.carpes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13028371900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13043269900000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13043269900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>adautina.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13041929200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13042472000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>cristiane.konrad@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13042310400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>daniella.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13036265500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>eduardo.santos1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13032576400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12796729000000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>rosemeire.faria@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13022632600000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>claudenice.barbosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>anderson.menezes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13028915100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>carlos.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-2000482000000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11353935000000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12743335400000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>segurarty@segurarty.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126792067 - ANA TEREZA FLORES CARVALHO</t>
-  </si>
-  <si>
-    <t>cnlo.seg@uol.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126877020 - MARCOS AURELIO FERNANDES MARTINS</t>
-  </si>
-  <si>
-    <t>chasecorretora@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126867748 - ALEXANDRE OLIMPIO CAVALCANTI</t>
-  </si>
-  <si>
-    <t>contato@ethicalbrasil.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126891849 - MARIA APARECIDA PINTO ANCORA DA LUZ</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127227451 - RUAN ADEODATO ALENCAR</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127181924 - DAVID LUCAS DE ALMEIDA SOUSA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127847254 - SHIRLEY CAROLINA RODRIGUES WERNECK</t>
-  </si>
-  <si>
-    <t>emissao@rodobens.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128207062 - HELOISA GREGIANINI</t>
-  </si>
-  <si>
-    <t>jb@reidoseguro.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128239215 - ALESSANDRA CRISTINA FERRARI SOARES</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128245135 - GUSTAVO QUEMEL ALVES</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128246208 - JOSE SILVEIRA</t>
-  </si>
-  <si>
-    <t>seguros@bancorbras.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128696637 - SHEILA SANDRA CANDIDA VIANA</t>
-  </si>
-  <si>
-    <t>contato@ricknewseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128685455 - CHRISTIANO FERREIRA CAMPOS</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128712623 - THAYNAH MARIA SANTOS PAIVA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128633372 - CARLOS HENRIQUE DE SENA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128922475 - ANTONIO VENANCIO DE VASCONCELOS</t>
-  </si>
-  <si>
-    <t>corujaseguros@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128965335 - OZIAS PONCIANO DE AZEREDO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128995139 - JONAS FILGUEIRAS DE MELO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129012469 - ALESSANDRA TOMAL</t>
-  </si>
-  <si>
-    <t>juliana@centroseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129144984 - ERIKA ANTONIA DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>ouro@vidadeouro.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129154145 - LEONARDO DE SOUZA MERCEDO CAMANZI</t>
-  </si>
-  <si>
-    <t>seguros@inredeseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129116738 - LUCIANA SASSAKI DE JESUS</t>
-  </si>
-  <si>
-    <t>laysa.camargos@grupolider.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129530810 - ALINE BROZEGUINI CUNHA TRAGINO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129574712 - ADELINO JOSE FRANCISCO</t>
+    <t>Captura de parcela rejeitada - Apólice 129148480 - DAYANE MENEZES DOS SANTOS ALBUQUERQUE</t>
   </si>
 </sst>
 </file>
@@ -798,10 +663,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -809,10 +674,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -820,10 +685,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -831,7 +696,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>26</v>
@@ -842,10 +707,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -853,10 +718,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -864,10 +729,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -875,10 +740,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -886,10 +751,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -897,10 +762,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -908,10 +773,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -919,10 +784,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -930,10 +795,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>42</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -941,10 +806,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -952,10 +817,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>17</v>
       </c>
       <c r="B16" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -963,10 +828,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="B17" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -974,10 +839,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>44</v>
+        <v>19</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -985,10 +850,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="B19" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -996,10 +861,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -1007,10 +872,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>53</v>
+        <v>22</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -1018,395 +883,228 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>3</v>
+        <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>3</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>6</v>
+        <v>56</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>6</v>
+        <v>65</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>6</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>75</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>6</v>
-      </c>
+      <c r="A34"/>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A35"/>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>9</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="A36"/>
+      <c r="B36" s="3"/>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>10</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A37"/>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>80</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="A38"/>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>82</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="A39"/>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>10</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="A40"/>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>9</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="A41"/>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>86</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="A42"/>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>88</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="A43"/>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="A44"/>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>13</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="A45"/>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46" t="s">
-        <v>7</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="A46"/>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47" t="s">
-        <v>93</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>16</v>
-      </c>
+      <c r="A47"/>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>7</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>7</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>97</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>99</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>101</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>103</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>18</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A49"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A50"/>
+    </row>
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A51"/>
+    </row>
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A52"/>
+    </row>
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A53"/>
+    </row>
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A54"/>
+    </row>
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55"/>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56"/>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57"/>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58"/>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59"/>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60"/>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61"/>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62"/>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63"/>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64"/>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">
@@ -1712,31 +1410,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
+  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAzNTMxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MzAvMTIvMjAyMCAxMTo0NTo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAzMC8xMi8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
+</WrappedLabelHistory>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
   <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
 </sisl>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
-  <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAzNTMxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MzAvMTIvMjAyMCAxMTo0NTo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAzMC8xMi8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
-</WrappedLabelHistory>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DBFCB3-53E5-4527-B13D-DC7A854D4B55}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41A8E509-6991-4B84-B1B5-13851E156C6A}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DBFCB3-53E5-4527-B13D-DC7A854D4B55}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C83B5AE3-DEC9-4D01-914A-950E4DDD30A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1368CA97-EF61-4F99-B7D9-D9F907B5E0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="122">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -53,124 +53,13 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>yuri.santos@allianz.com.br</t>
-  </si>
-  <si>
     <t>juliano.guimaraes@allianz.com.br</t>
   </si>
   <si>
-    <t>fausto.reis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12610468400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>crislaine.trindade@allianz.com.br</t>
-  </si>
-  <si>
-    <t>daniel.lourenco@allianz.com.br</t>
-  </si>
-  <si>
-    <t>viviane.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>noadia.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>saulo.santiago@allianz.com.br</t>
-  </si>
-  <si>
-    <t>talita.meneses@allianz.com.br</t>
-  </si>
-  <si>
-    <t>viviane.corbari@allianz.com.br</t>
-  </si>
-  <si>
-    <t>andrea.duarte@allianz.com.br</t>
-  </si>
-  <si>
-    <t>cassia.souza@allianz.com.br</t>
-  </si>
-  <si>
-    <t>raullison.castro@allianz.com.br</t>
-  </si>
-  <si>
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
-    <t>rodrigo.nascimento@allianz.com.br</t>
-  </si>
-  <si>
     <t>rafael.leite@allianz.com.br</t>
-  </si>
-  <si>
-    <t>nicole.demori@allianz.com.br</t>
-  </si>
-  <si>
-    <t>cristiane.lozano@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13002364100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13041677500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13042857600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13045258200000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12996617000000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12684310500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12998324000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12674894100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13020157100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13043297300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12671449200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12672039000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13044957700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13029848400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13044524900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12720344200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13044849900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13034501200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13039072400000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>lucas@pracatu.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127120111 - NIVALDO ANDREAZZI</t>
   </si>
   <si>
     <t>Prezado(a), 
@@ -185,15 +74,6 @@
     <t>backofficecorretora@segurostoyota.com.br</t>
   </si>
   <si>
-    <t>Captura de parcela rejeitada - Apólice 127200392 - PATRICIA DE MORAES SILVA</t>
-  </si>
-  <si>
-    <t>operacional@durangocorretora.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127491198 - CAIO CRUZ MENEZES VITORIO</t>
-  </si>
-  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 8 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -203,22 +83,7 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>nilsonfilho@nillmorseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127524663 - JUSCELINO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127545522 - FILIPE MARCEL BRITO DE SOUZA</t>
-  </si>
-  <si>
     <t>renovacaoseguros@honda.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127552928 - HORACIO BATISTA DOS SANTOS JUNIOR</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128252495 - LUDMILA VIANA SILVA E SILVA</t>
   </si>
   <si>
     <t>Prezado(a), 
@@ -230,30 +95,6 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>prontocar@prontocarseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128252321 - CRISTIANE DE OLIVEIRA SANTANA</t>
-  </si>
-  <si>
-    <t>reinaldo.alves@carmais.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128255047 - NAGELA MARIA SILVA DA ROCHA DE ANDRADE</t>
-  </si>
-  <si>
-    <t>administrativo@wagonseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128263248 - GLAUCIA DE JORGE CARVALHO PESSANHA</t>
-  </si>
-  <si>
-    <t>adriana.faria@jorlan.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129134133 - EDMEA CARNEIRO MARIANO CUNHA</t>
-  </si>
-  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -263,7 +104,361 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>Captura de parcela rejeitada - Apólice 129148480 - DAYANE MENEZES DOS SANTOS ALBUQUERQUE</t>
+    <t>luiz.inocente@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12988469600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13023953700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>valeria.palhares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13036913300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>claudia.magalhaes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13023828900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-1336749000177 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rosthiane.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13047561600000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>jaciely.dias@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13037220400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>flavio.cesar@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13045961500000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>daniela.leal@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12978314100008 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>karina.barros@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13044104300000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>kaue.medeiros@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12611255200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>tatiana.monis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13045664600000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>juliana.diniz@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-33800148854 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>mayara.sampaio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13045525100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>douglas.pereira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12928910900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>vitor.mattos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13010683300000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>debora.sanches@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13030201200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>pamela.burige@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13031809800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>flavia.costa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13046783200000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13039856300000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13045445100000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13048078000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>lucas.monteiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12763686300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13045486500000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13045646700000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>fabiola.caixeta@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13046615200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>carolina.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12647994100000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>guilherme.teodoro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13033219400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13035879900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>carlos.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-10739609900000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12527663500000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12629853000000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>junior@inoveseguro.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126911560 - JULIANI CRISTINA CAPOCCI</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 10 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>mesegurosourobranco@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126842632 - ADALBERTO MATOS MONTEIRO JUNIOR</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126923281 - DERICK OLIVEIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126922986 - SAMUEL PEREIRA DOS SANTOS</t>
+  </si>
+  <si>
+    <t>financeiro@komunseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126899324 - YAN MOHR LANGE</t>
+  </si>
+  <si>
+    <t>seguradora@minutoseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127226979 - MUCIO MACEDO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>seguros@atuanaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127241899 - GABRIELA FERNANDA DA SILVA</t>
+  </si>
+  <si>
+    <t>mrc@mrcseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127247397 - FABIO LUIZ COBRA MEDA</t>
+  </si>
+  <si>
+    <t>segurosconclusiva@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127238141 - HELENICE TEIXEIRA FIALHO VINHA</t>
+  </si>
+  <si>
+    <t>prevenceseguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127222606 - EDINALDO RODRIGUES DA SILVA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127427410 - ROSELI APARECIDA PEREIRA DINIZ</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127540732 - LIEGES CARVALHO RODRIGUES</t>
+  </si>
+  <si>
+    <t>suporte.vvd@vwfs.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127563860 - MARIA APARECIDA MACIEL GONCALVES FRANCISCO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127567458 - MARIA DE FATIMA DANTAS ROCHA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127874001 - ALBERTO DA SILVA LEITE</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127861805 - CASSIO DE OLIVEIRA CARNEIRO</t>
+  </si>
+  <si>
+    <t>administrativo@focovix.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127885887 - EDILSON PASTORE CUNHA</t>
+  </si>
+  <si>
+    <t>sidneyseguros1@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127889228 - CANDIDA MENDES MARQUEZ</t>
+  </si>
+  <si>
+    <t>comercial@maresseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127889063 - LUIZ BESSA MIRANDA</t>
+  </si>
+  <si>
+    <t>admcorretora@tribancoseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128153796 - MARY APARECIDA DE LIMA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127765073 - ADRIANA FERREIRA SANTOS MOURA</t>
+  </si>
+  <si>
+    <t>contato@fckseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128686155 - SILVIA JURANE MARINHO MENEZES</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>ldr@ldrseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128710144 - ADRIANA ALVES DA SILVA</t>
+  </si>
+  <si>
+    <t>rejaseg@rejasegseguros.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128927184 - ANTONIO CARLOS JESUS REIS</t>
+  </si>
+  <si>
+    <t>abens@abensseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129143483 - TERUKI HIMORO</t>
+  </si>
+  <si>
+    <t>meuguia@yahoo.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129162839 - ALESSANDRA XAVIER FERNANDES</t>
+  </si>
+  <si>
+    <t>right@right.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129175637 - AVELINO WALTRICH FILHO</t>
+  </si>
+  <si>
+    <t>contato@limasclass.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129550389 - LEILA FERREIRA RIBEIRO</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 3 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>toninho@eloseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 130042986 - FERNANDO PACIELLO VIEIRA</t>
+  </si>
+  <si>
+    <t>Prezado(a), 
+Identificamos uma falha na tentativa de captura da parcela 2 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
+Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
+Pedimos desculpas pelo transtorno causado.
+Att.
+Departamento de Cobrança
+"Este e-mail é um envio automático, favor não responder.”</t>
   </si>
 </sst>
 </file>
@@ -663,10 +858,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -674,10 +869,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -685,10 +880,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -696,10 +891,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -707,10 +902,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -718,10 +913,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="B7" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -729,10 +924,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -740,10 +935,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -751,10 +946,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -762,10 +957,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -773,7 +968,7 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
@@ -784,10 +979,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -795,10 +990,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -806,10 +1001,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="B15" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -817,10 +1012,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="B16" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -828,10 +1023,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>41</v>
       </c>
       <c r="B17" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -839,10 +1034,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="B18" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -850,10 +1045,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>45</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -861,10 +1056,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -872,10 +1067,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -883,112 +1078,112 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>42</v>
+        <v>5</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>44</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>49</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>49</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>49</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>49</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>56</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -996,115 +1191,346 @@
         <v>63</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>65</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>66</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>65</v>
+        <v>3</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34"/>
+      <c r="A34" t="s">
+        <v>67</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35"/>
+      <c r="A35" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36"/>
-      <c r="B36" s="3"/>
+      <c r="A36" t="s">
+        <v>10</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37"/>
+      <c r="A37" t="s">
+        <v>10</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38"/>
+      <c r="A38" t="s">
+        <v>74</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>69</v>
+      </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39"/>
+      <c r="A39" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40"/>
+      <c r="A40" t="s">
+        <v>78</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41"/>
+      <c r="A41" t="s">
+        <v>80</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A42"/>
+      <c r="A42" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A43"/>
+      <c r="A43" t="s">
+        <v>84</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A44"/>
+      <c r="A44" t="s">
+        <v>8</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A45"/>
+      <c r="A45" t="s">
+        <v>10</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A46"/>
+      <c r="A46" t="s">
+        <v>88</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A47"/>
+      <c r="A47" t="s">
+        <v>10</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A48"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49"/>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A50"/>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A51"/>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A52"/>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A53"/>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A54"/>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A55"/>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A56"/>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A57"/>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A58"/>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A59"/>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A60"/>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A61"/>
-    </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A62"/>
-    </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>8</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>8</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>94</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>96</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>98</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>100</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>80</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>103</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>106</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>108</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>110</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>112</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>114</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>116</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>119</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64"/>
     </row>
     <row r="65" spans="1:1" x14ac:dyDescent="0.25">

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1368CA97-EF61-4F99-B7D9-D9F907B5E0CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33E3ECF8-5019-4D53-B855-CDFFE46B929F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28800" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envio Robô" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="103">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -51,15 +51,6 @@
   </si>
   <si>
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
-  </si>
-  <si>
-    <t>juliano.guimaraes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>gabriela.logrado@allianz.com.br</t>
-  </si>
-  <si>
-    <t>rafael.leite@allianz.com.br</t>
   </si>
   <si>
     <t>Prezado(a), 
@@ -104,172 +95,16 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>luiz.inocente@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12988469600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13023953700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
     <t>valeria.palhares@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13036913300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>claudia.magalhaes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13023828900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-1336749000177 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>rosthiane.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13047561600000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
     <t>jaciely.dias@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13037220400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>flavio.cesar@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13045961500000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>daniela.leal@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12978314100008 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>karina.barros@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13044104300000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>kaue.medeiros@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12611255200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>tatiana.monis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13045664600000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>juliana.diniz@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-33800148854 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>mayara.sampaio@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13045525100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>douglas.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12928910900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>vitor.mattos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13010683300000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>debora.sanches@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13030201200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>pamela.burige@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13031809800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>flavia.costa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13046783200000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13039856300000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13045445100000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13048078000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
     <t>lucas.monteiro@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12763686300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13045486500000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13045646700000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>fabiola.caixeta@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13046615200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
     <t>carolina.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12647994100000 Nota 167 - Retorno Cobrança OP53</t>
-  </si>
-  <si>
-    <t>guilherme.teodoro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13033219400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13035879900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>carlos.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-10739609900000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12527663500000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12629853000000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>junior@inoveseguro.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126911560 - JULIANI CRISTINA CAPOCCI</t>
   </si>
   <si>
     <t>Prezado(a), 
@@ -281,70 +116,7 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>mesegurosourobranco@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126842632 - ADALBERTO MATOS MONTEIRO JUNIOR</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126923281 - DERICK OLIVEIRA DA SILVA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126922986 - SAMUEL PEREIRA DOS SANTOS</t>
-  </si>
-  <si>
-    <t>financeiro@komunseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126899324 - YAN MOHR LANGE</t>
-  </si>
-  <si>
-    <t>seguradora@minutoseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127226979 - MUCIO MACEDO DE OLIVEIRA</t>
-  </si>
-  <si>
-    <t>seguros@atuanaseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127241899 - GABRIELA FERNANDA DA SILVA</t>
-  </si>
-  <si>
-    <t>mrc@mrcseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127247397 - FABIO LUIZ COBRA MEDA</t>
-  </si>
-  <si>
-    <t>segurosconclusiva@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127238141 - HELENICE TEIXEIRA FIALHO VINHA</t>
-  </si>
-  <si>
-    <t>prevenceseguros@hotmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127222606 - EDINALDO RODRIGUES DA SILVA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127427410 - ROSELI APARECIDA PEREIRA DINIZ</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127540732 - LIEGES CARVALHO RODRIGUES</t>
-  </si>
-  <si>
     <t>suporte.vvd@vwfs.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127563860 - MARIA APARECIDA MACIEL GONCALVES FRANCISCO</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127567458 - MARIA DE FATIMA DANTAS ROCHA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127874001 - ALBERTO DA SILVA LEITE</t>
   </si>
   <si>
     <t>Prezado(a), 
@@ -356,42 +128,6 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>Captura de parcela rejeitada - Apólice 127861805 - CASSIO DE OLIVEIRA CARNEIRO</t>
-  </si>
-  <si>
-    <t>administrativo@focovix.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127885887 - EDILSON PASTORE CUNHA</t>
-  </si>
-  <si>
-    <t>sidneyseguros1@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127889228 - CANDIDA MENDES MARQUEZ</t>
-  </si>
-  <si>
-    <t>comercial@maresseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127889063 - LUIZ BESSA MIRANDA</t>
-  </si>
-  <si>
-    <t>admcorretora@tribancoseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128153796 - MARY APARECIDA DE LIMA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127765073 - ADRIANA FERREIRA SANTOS MOURA</t>
-  </si>
-  <si>
-    <t>contato@fckseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128686155 - SILVIA JURANE MARINHO MENEZES</t>
-  </si>
-  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -401,42 +137,6 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>ldr@ldrseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128710144 - ADRIANA ALVES DA SILVA</t>
-  </si>
-  <si>
-    <t>rejaseg@rejasegseguros.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128927184 - ANTONIO CARLOS JESUS REIS</t>
-  </si>
-  <si>
-    <t>abens@abensseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129143483 - TERUKI HIMORO</t>
-  </si>
-  <si>
-    <t>meuguia@yahoo.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129162839 - ALESSANDRA XAVIER FERNANDES</t>
-  </si>
-  <si>
-    <t>right@right.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129175637 - AVELINO WALTRICH FILHO</t>
-  </si>
-  <si>
-    <t>contato@limasclass.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129550389 - LEILA FERREIRA RIBEIRO</t>
-  </si>
-  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 3 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -446,12 +146,6 @@
 "Este e-mail é um envio automático, favor não responder.”</t>
   </si>
   <si>
-    <t>toninho@eloseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 130042986 - FERNANDO PACIELLO VIEIRA</t>
-  </si>
-  <si>
     <t>Prezado(a), 
 Identificamos uma falha na tentativa de captura da parcela 2 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
 Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
@@ -459,6 +153,255 @@
 Att.
 Departamento de Cobrança
 "Este e-mail é um envio automático, favor não responder.”</t>
+  </si>
+  <si>
+    <t>ana.brito@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12857053900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12687219700000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>fabio.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13047468100000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13045429200000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>lucas.almeida@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13039178700000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13047681000000 Nota 595 - ERRO PDF Retono</t>
+  </si>
+  <si>
+    <t>gisele.mazzucco@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-36993774828 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>gisele.cardoso1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13047720500000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>andre.gouvea@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13048103100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>talita.meneses@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13026378900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>andreia.brixner@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13043885500000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>fernanda.carneiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13047797600000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>julianna.printes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13047935700000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>monica.plassa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12713603400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13039686100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13048318200000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>elaine.sousa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13047384000000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>leticia.bezerra@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13047302000000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>ivone.jesus@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12989442800000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13043283200000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>carla.catalani@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12969826400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>karina.vieira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12340783000000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>sandra.mikari@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12650341900000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126906119 - JULIO CESAR LISBOA GOMES</t>
+  </si>
+  <si>
+    <t>corretora@camedseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126880155 - TAMIRES CAMARA BRITO</t>
+  </si>
+  <si>
+    <t>paessanna.corretor@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126930140 - MARCIO DE CASTRO JUNIOR</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126932991 - MARCELA SILVA DA GUIA</t>
+  </si>
+  <si>
+    <t>agnseguros@hotmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 126640291 - SAYMON SILVA GOMES DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127261325 - MARCELA MONTEIRO SOARES</t>
+  </si>
+  <si>
+    <t>carlos@gomescorretoradeseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127554650 - DARIO AZEVEDO DOS SANTOS FILHO</t>
+  </si>
+  <si>
+    <t>nilsonfilho@nillmorseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127565909 - SANDRA ARANTES FELIPE</t>
+  </si>
+  <si>
+    <t>cmrpontual@gmail.com</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127817691 - MARCO ANTONIO NEVES</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127898883 - NELSON MOREIRA DA SILVA</t>
+  </si>
+  <si>
+    <t>protecta@protectaseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 127902481 - LOURDES MENOTI DE CARVALHO</t>
+  </si>
+  <si>
+    <t>gerenciador@ei-seguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128258374 - EVA ROSALINA DA SILVA</t>
+  </si>
+  <si>
+    <t>manicaseg@manica.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128264636 - JACQUELINE BERVIAN</t>
+  </si>
+  <si>
+    <t>maristela@coliseoseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128295211 - SERGIO OLIVEIRA MENDES</t>
+  </si>
+  <si>
+    <t>pendencia@seguralta.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128244777 - FABRICIO OLIVEIRA SILVA</t>
+  </si>
+  <si>
+    <t>lcr@lcrseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128628749 - WAGNER APARECIDO DE OLIVEIRA</t>
+  </si>
+  <si>
+    <t>segurarty@segurarty.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128533153 - ISOLETE CATARINA TEIXEIRA</t>
+  </si>
+  <si>
+    <t>georgia@foxseguros.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128696313 - MICHELLE RODRIGUES ALVES LIMA ROCHA</t>
+  </si>
+  <si>
+    <t>emissao@segurosarinos.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128678503 - LORENA TELLES MARTINS</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128608077 - VERA LUCIA QUINHONES GUIDOLIN</t>
+  </si>
+  <si>
+    <t>atendimento@douraseg.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128672980 - LILIANE RODRIGUES CONGRO DA ROCHA</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 128704577 - JOSE DE FRANCA SOUZA</t>
+  </si>
+  <si>
+    <t>fernandacunha@vivacorretora.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129188590 - BRUNO OLIVEIRA RAMOS</t>
+  </si>
+  <si>
+    <t>allianz1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 129627278 - MARCO ANTONIO DE ARAUJO</t>
+  </si>
+  <si>
+    <t>Captura de parcela rejeitada - Apólice 130033710 - PAULA CRISTINA OLIVEIRA SOUSA</t>
   </si>
 </sst>
 </file>
@@ -858,10 +801,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -869,10 +812,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -880,10 +823,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -891,10 +834,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -902,10 +845,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -913,10 +856,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B7" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -924,10 +867,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -935,10 +878,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -946,10 +889,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -957,10 +900,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -968,10 +911,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -979,10 +922,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -990,10 +933,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="B14" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -1001,10 +944,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -1012,10 +955,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>39</v>
+        <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -1023,10 +966,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="B17" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -1034,10 +977,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="B18" t="s">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -1045,318 +988,318 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B19" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>48</v>
+      <c r="A20" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" t="s">
+        <v>52</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="A21" t="s">
+        <v>13</v>
+      </c>
+      <c r="B21" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>54</v>
+      </c>
+      <c r="B22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>56</v>
+      </c>
+      <c r="B23" t="s">
+        <v>57</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>58</v>
+      </c>
+      <c r="B24" t="s">
+        <v>59</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="B25" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>63</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>63</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>66</v>
+        <v>73</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>74</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>68</v>
+        <v>7</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>75</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>70</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>71</v>
+        <v>76</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>69</v>
+        <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>10</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>72</v>
+        <v>78</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>79</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>69</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>10</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>73</v>
+        <v>80</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>81</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>69</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>74</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>75</v>
+        <v>82</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>83</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>69</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>76</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>77</v>
+        <v>84</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>85</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>78</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>79</v>
+        <v>86</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>87</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>80</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>81</v>
+        <v>88</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>89</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>82</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>83</v>
+        <v>90</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>91</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>84</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>85</v>
+        <v>92</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>93</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>8</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>86</v>
+        <v>78</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>94</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>10</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>87</v>
+        <v>95</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>96</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>88</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>89</v>
+        <v>84</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>10</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>90</v>
+        <v>98</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>99</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>9</v>
@@ -1364,168 +1307,77 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>8</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>91</v>
+        <v>100</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>101</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>92</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>8</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>93</v>
+        <v>84</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>102</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>92</v>
+        <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>94</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="A50"/>
+      <c r="B50" s="3"/>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>96</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="A51"/>
+      <c r="B51" s="3"/>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>98</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>92</v>
-      </c>
+      <c r="A52"/>
+      <c r="B52" s="3"/>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>100</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C53" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A53"/>
+      <c r="B53" s="3"/>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>80</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="A54"/>
+      <c r="B54" s="3"/>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>103</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>105</v>
-      </c>
+      <c r="A55"/>
+      <c r="B55" s="3"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>106</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>105</v>
-      </c>
+      <c r="A56"/>
+      <c r="B56" s="3"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A57" t="s">
-        <v>108</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="A57"/>
+      <c r="B57" s="3"/>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>110</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C58" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="A58"/>
+      <c r="B58" s="3"/>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A59" t="s">
-        <v>112</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="C59" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="A59"/>
+      <c r="B59" s="3"/>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A60" t="s">
-        <v>114</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="C60" s="2" t="s">
-        <v>12</v>
-      </c>
+      <c r="A60"/>
+      <c r="B60" s="3"/>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>116</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C61" s="2" t="s">
-        <v>118</v>
-      </c>
+      <c r="A61"/>
+      <c r="B61" s="3"/>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A62" t="s">
-        <v>119</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C62" s="2" t="s">
-        <v>121</v>
-      </c>
+      <c r="A62"/>
+      <c r="B62" s="3"/>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63"/>

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703BC5EF-B5D0-46B4-AC49-D0C4CAD705E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D3E3D0-B603-4760-8D87-66CDAE7907A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="28800" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Envio Robô" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="123" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -53,298 +53,124 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>backofficecorretora@segurostoyota.com.br</t>
-  </si>
-  <si>
-    <t>renovacaoseguros@honda.com.br</t>
-  </si>
-  <si>
-    <t>suporte.vvd@vwfs.com</t>
-  </si>
-  <si>
     <t>ana.brito@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12857053900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>mariana.dolence@allianz.com.br</t>
-  </si>
-  <si>
-    <t>renato.faillace@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12614513600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>denise@riscalli.com.br</t>
-  </si>
-  <si>
-    <t>pendencias@rbmseguros.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-3397060826 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>danillo.boem@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-10984178000178 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-28758086000135 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>jaciely.dias@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13048538000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>ana.alves1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12892900100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>tatiana.monis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12726763100000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
     <t>sonia.bortoleto@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12743432300000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13050323000000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>gisele.cardoso1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13041153900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>william.rosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12967920100018 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>viviane.corbari@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13040785200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>gustavo.correa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12714185000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>raullison.castro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13048999900000 Nota 595 - ERRO PDF RETORNO</t>
-  </si>
-  <si>
-    <t>patricia.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13046632100000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>cristiane.lozano@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12903047800000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
     <t>carlos.neves@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-12504787400000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>mafraseguros@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126976136 - MATEUS HENRIQUE ARAUJO SILVEIRA</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 10 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 126973352 - GISELE CANDIDO LANDI</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127265158 - ANA LUCIA BORLOT FALCAO</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 9 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127282765 - VALDETE MIRANDA MARCILIO</t>
-  </si>
-  <si>
-    <t>fernandacunha@vivacorretora.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127292767 - MARCONY GIORDANI MIRANDA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127294627 - FRANCISCO JEAN RODRIGUES FERREIRA</t>
-  </si>
-  <si>
-    <t>sbcor@sbcor.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127297829 - EDINA DE FATIMA RODRIGUES</t>
-  </si>
-  <si>
-    <t>diretoria@lapisbellus.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127618797 - LEONARDO BORGES DE ALMEIDA</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 8 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>bacellarseguros@bacellarseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127602548 - FRANCISCO PRETE PAZETO</t>
-  </si>
-  <si>
-    <t>andradecorretoraseguros@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127593533 - WANESSA PARREIRA SERAFIM CARDOSO</t>
-  </si>
-  <si>
-    <t>chasecorretora@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 127892803 - ADRIANA PERAZZA DA SILVA</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 7 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128325433 - EDILSON ANDRADE DE MELO</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 6 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128328510 - DESIREE MONTEIRO VERGINIO NETTO</t>
-  </si>
-  <si>
-    <t>pedro@riscoseguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128717610 - EDIMAR PAULINO DA SILVA</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 5 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128752543 - GILDA TEPEDINO DE SOUZA LIMA</t>
-  </si>
-  <si>
-    <t>comercial@condorcorretora.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128813260 - ROGERIO ALVES DA SILVA</t>
-  </si>
-  <si>
-    <t>filipe@f2seguros.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 128790822 - THIAGO HENRIQUE DE ALMEIDA ESPINHARA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129231517 - DIEREMY KIAK LISKA</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 4 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>thaysa@guararapescorretora.com.br</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 129228657 - AMANDA CAROLINE NEGREIRO DE ALMEIDA</t>
-  </si>
-  <si>
-    <t>nelsonjrneto8@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 130108349 - LUIZ CARLOS DE OLIVEIRA ARAUJO</t>
-  </si>
-  <si>
-    <t>Prezado(a), 
-Identificamos uma falha na tentativa de captura da parcela 2 da apólice em questão, para não penalizar o segurado com cobrança de juros, emitimos novo boleto que encontra-se indexado na Ficha Gestão da apólice, por favor encaminhá-lo ao pagador.
-Caso o cliente já tenha realizado o pagamento, pedimos que desconsidere o boleto ou entre em contato conosco através do gestor de operações na opção "Cobrança Indevida".
-Pedimos desculpas pelo transtorno causado.
-Att.
-Departamento de Cobrança
-"Este e-mail é um envio automático, favor não responder.”</t>
-  </si>
-  <si>
-    <t>novaterraempreendimentos@gmail.com</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 130119669 - NOVA TERRA EMPREENDIMENTOS LTDA</t>
-  </si>
-  <si>
-    <t>Captura de parcela rejeitada - Apólice 130131148 - PEDRO AUGUSTO NUNES SANTOS</t>
+    <t>lilian.sudati@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13050694000000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>valdirene.barbosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13041513400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>erica.cassandre@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13046892100000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>otto.lopes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13050107800000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>samuel.martins@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13046847000000 Nota 595 - ERRO PDF RETORNO</t>
+  </si>
+  <si>
+    <t>marco.schiabel@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12829704600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>raquel.sech@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13046972000000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>gleison.ferreira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13050676000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13048573700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>priscila.rubio@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12954972700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>claudia.pires@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12982203300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>monica.prates@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13049312200000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>dayane.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13046638200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>andrea.farias1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13040340000000 Nota 738 - Erro Voucher - exclusivo Operações</t>
+  </si>
+  <si>
+    <t>eudmila.tassara@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12815581000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rafael.leite@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13045646700000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>eduardo.santos1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13048539600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>cassia.silveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-83429720000102 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12980315100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12629853000000 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -394,14 +220,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -758,7 +581,7 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -766,10 +589,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -777,10 +600,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -788,10 +611,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -799,10 +622,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -810,10 +633,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -821,10 +644,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -832,10 +655,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -843,10 +666,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -854,10 +677,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -865,10 +688,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -876,10 +699,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -887,10 +710,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -898,10 +721,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>34</v>
+      </c>
+      <c r="B16" t="s">
         <v>35</v>
-      </c>
-      <c r="B16" t="s">
-        <v>36</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -909,10 +732,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>36</v>
+      </c>
+      <c r="B17" t="s">
         <v>37</v>
-      </c>
-      <c r="B17" t="s">
-        <v>38</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -920,10 +743,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" t="s">
         <v>39</v>
-      </c>
-      <c r="B18" t="s">
-        <v>40</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -931,10 +754,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" t="s">
         <v>41</v>
-      </c>
-      <c r="B19" t="s">
-        <v>42</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -942,265 +765,105 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>44</v>
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>42</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>45</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>46</v>
+        <v>6</v>
+      </c>
+      <c r="B21" t="s">
+        <v>43</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>45</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>48</v>
-      </c>
+      <c r="A22"/>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>48</v>
-      </c>
+      <c r="A23"/>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>50</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>48</v>
-      </c>
+      <c r="A24"/>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>48</v>
-      </c>
+      <c r="A25"/>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>53</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>48</v>
-      </c>
+      <c r="A26"/>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>55</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="A27"/>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="A28"/>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>60</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="A29"/>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>62</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>64</v>
-      </c>
+      <c r="A30"/>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>4</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>66</v>
-      </c>
+      <c r="A31"/>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>13</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>68</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>13</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>72</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>74</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>12</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>78</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>80</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>83</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>6</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A36"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A41"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42"/>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43"/>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44"/>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45"/>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46"/>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47"/>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48"/>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.25">

--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF48FFA9-3A92-43C6-BBC9-38B7517C608F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FD1569-6ED0-4EA0-BA2B-1721FB9D94AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="107">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -53,265 +53,313 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
+    <t>patricia.reis@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13105642600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>caroline.wojciechowski@allianz.com.br</t>
+  </si>
+  <si>
+    <t>lilian.sudati@allianz.com.br</t>
+  </si>
+  <si>
+    <t>juliano.guimaraes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>rodrigo.kuguyama@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11304671100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>bruno.rosa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>priscila.santana@allianz.com.br</t>
+  </si>
+  <si>
+    <t>laiane.martins@allianz.com.br</t>
+  </si>
+  <si>
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
-    <t>rosemeire.faria@allianz.com.br</t>
-  </si>
-  <si>
-    <t>claudia.assuncao@allianz.com.br</t>
-  </si>
-  <si>
-    <t>crislaine.trindade@allianz.com.br</t>
-  </si>
-  <si>
-    <t>nilcea.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>daniel.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>daniele.beck@allianz.com.br</t>
-  </si>
-  <si>
-    <t>dayane.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>lais.xavier@allianz.com.br</t>
-  </si>
-  <si>
-    <t>ana.rodrigues@allianz.com.br</t>
-  </si>
-  <si>
-    <t>claudenice.barbosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>nathalie.carmo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13044184900000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>silvia.taschetti@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12940825800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13027096000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>renato.lopes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13088001800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>patricia.reis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13080328000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>juliano.guimaraes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13079020300000 Nota 595 - ERRO PDF retorno</t>
+    <t>adautina.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>cassia.silveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>fabiana.moura@allianz.com.br</t>
+  </si>
+  <si>
+    <t>andreia.brixner@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13107458400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11745882900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>matheus.gomes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13097986300000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>caroline.falcao@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12651740700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13044204100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13112038900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13099778800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13100822100000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13100857700000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13100877300000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13100989100000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13107363100000 Nota 595 - ERRO PDF retorno</t>
   </si>
   <si>
     <t>thais.oliveira@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13094561600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>renata.matheus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12636043000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>wagner.simon@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12678588500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>marina.melo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13087663300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>everton.silva1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13089396800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>danilo.ruas@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12893824200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13084638500000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12910866100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>douglas.pereira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12567809100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12880384200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>bruna.teixeira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13094221600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13088878400000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>renato.faillace@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13082983800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13090208500000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13030091600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13086584600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13087627700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13087909600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13089263400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13090836800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13091823000000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13092033400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13092289000000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13094145700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>lucas.monteiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13073803000000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>elaine.sousa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12888760500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>bruna.carneiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13086349800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>daniela.carvalho@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13092545000000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13004856700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>thays.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13092807600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12793875600000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13062614600000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13063619200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13073597300000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13077228500000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13078769600000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13079915500000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13079928000000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13082947700000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13084435900000 Nota 472 - Reentrada OK Produto</t>
-  </si>
-  <si>
-    <t>anderson.menezes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-2183774000120 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>rosana.pessoa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12682380600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13080315400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>fabiana.moura@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13080805800000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>thomaz.jesus@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12302937300000 Nota 242 - Retorno Cobrança</t>
-  </si>
-  <si>
-    <t>jose.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12504787400000 Nota 242 - Retorno Cobrança</t>
+    <t>Retorno de GO referência-12331803900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>alessandra.araujo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12756682900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13096463400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>vanessa.campos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13107596500000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>fernando.martins1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13106438600000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13050614200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>allan.soares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13095684200000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>lidiane.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13108127800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13097485000000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>viviane.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13089295800000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>barbara.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13101289400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>luiz.sanchetta@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13108019600000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>daiane.soares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13094391500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>andreia.cardias@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13107414900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>rosilene.nogueira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13103675100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>fabio.ribeiro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13087978600000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13108354200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13110623500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13110638100000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13107064200000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13107166300000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13109256200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13110022200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13110706200000 Nota 595 - ERRO PDF</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13111026300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13111151300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13111221600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13111225100000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13111725600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13111820300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13111993900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13112154300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13112156100000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13112795400000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>ivana.freitas@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13103998800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>leticia.bezerra@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11230308000140 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>edmar.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13113755700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13113780700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13113813600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13113834800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13113865800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13113890500000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13113911900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13113939200000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13113955300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>leinny.amorim@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13097128400000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>enriete.saucedo@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12893248800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-73952583049 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12689136800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13100135700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13100257300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13100273600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13101377300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13101533700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>barbara.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11825312800000 Nota 167 - Retorno Cobrança op53</t>
   </si>
 </sst>
 </file>
@@ -684,7 +732,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:C54"/>
+  <dimension ref="A1:C70"/>
   <sheetFormatPr defaultColWidth="9.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="35.7265625" style="2" bestFit="1" customWidth="1"/>
@@ -708,10 +756,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B2" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -719,10 +767,10 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -730,10 +778,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B4" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -741,10 +789,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -752,10 +800,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -763,10 +811,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -774,10 +822,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" t="s">
         <v>26</v>
-      </c>
-      <c r="B8" t="s">
-        <v>27</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -785,10 +833,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -796,10 +844,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
         <v>28</v>
-      </c>
-      <c r="B10" t="s">
-        <v>29</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -807,10 +855,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -818,10 +866,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -829,10 +877,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -840,10 +888,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -851,10 +899,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B15" t="s">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -862,10 +910,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -873,10 +921,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B17" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -884,10 +932,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="B18" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -895,10 +943,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B19" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -906,10 +954,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -917,10 +965,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="B21" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -928,10 +976,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>43</v>
       </c>
       <c r="B22" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -939,10 +987,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="B23" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -950,10 +998,10 @@
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
@@ -961,10 +1009,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="B25" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -972,10 +1020,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
@@ -983,7 +1031,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>4</v>
+        <v>52</v>
       </c>
       <c r="B27" t="s">
         <v>53</v>
@@ -994,10 +1042,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>4</v>
+        <v>54</v>
       </c>
       <c r="B28" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>3</v>
@@ -1005,10 +1053,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>4</v>
+        <v>56</v>
       </c>
       <c r="B29" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>3</v>
@@ -1016,10 +1064,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>4</v>
+        <v>58</v>
       </c>
       <c r="B30" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>3</v>
@@ -1027,10 +1075,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="B31" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>3</v>
@@ -1038,10 +1086,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>4</v>
+        <v>60</v>
       </c>
       <c r="B32" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>3</v>
@@ -1049,10 +1097,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="B33" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>3</v>
@@ -1060,10 +1108,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B34" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>3</v>
@@ -1071,10 +1119,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>63</v>
+        <v>15</v>
       </c>
       <c r="B35" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>3</v>
@@ -1082,7 +1130,7 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="B36" t="s">
         <v>66</v>
@@ -1093,7 +1141,7 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B37" t="s">
         <v>67</v>
@@ -1104,10 +1152,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
+        <v>14</v>
+      </c>
+      <c r="B38" t="s">
         <v>68</v>
-      </c>
-      <c r="B38" t="s">
-        <v>69</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>3</v>
@@ -1115,10 +1163,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B39" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>3</v>
@@ -1126,10 +1174,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B40" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>3</v>
@@ -1140,7 +1188,7 @@
         <v>14</v>
       </c>
       <c r="B41" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>3</v>
@@ -1148,10 +1196,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B42" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>3</v>
@@ -1159,10 +1207,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B43" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>3</v>
@@ -1170,10 +1218,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B44" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>3</v>
@@ -1181,10 +1229,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B45" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>3</v>
@@ -1192,10 +1240,10 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B46" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C46" s="2" t="s">
         <v>3</v>
@@ -1203,10 +1251,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B47" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>3</v>
@@ -1214,10 +1262,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B48" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>3</v>
@@ -1225,10 +1273,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="B49" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>3</v>
@@ -1236,10 +1284,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B50" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>3</v>
@@ -1250,7 +1298,7 @@
         <v>82</v>
       </c>
       <c r="B51" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>3</v>
@@ -1258,10 +1306,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
+        <v>84</v>
+      </c>
+      <c r="B52" t="s">
         <v>85</v>
-      </c>
-      <c r="B52" t="s">
-        <v>86</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>3</v>
@@ -1269,10 +1317,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B53" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>3</v>
@@ -1280,12 +1328,188 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
+        <v>84</v>
+      </c>
+      <c r="B54" t="s">
+        <v>87</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>84</v>
+      </c>
+      <c r="B55" t="s">
+        <v>88</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>84</v>
+      </c>
+      <c r="B56" t="s">
         <v>89</v>
       </c>
-      <c r="B54" t="s">
+      <c r="C56" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>84</v>
+      </c>
+      <c r="B57" t="s">
         <v>90</v>
       </c>
-      <c r="C54" s="2" t="s">
+      <c r="C57" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>84</v>
+      </c>
+      <c r="B58" t="s">
+        <v>91</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>84</v>
+      </c>
+      <c r="B59" t="s">
+        <v>92</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>84</v>
+      </c>
+      <c r="B60" t="s">
+        <v>93</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>94</v>
+      </c>
+      <c r="B61" t="s">
+        <v>95</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>96</v>
+      </c>
+      <c r="B62" t="s">
+        <v>97</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>16</v>
+      </c>
+      <c r="B63" t="s">
+        <v>98</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>17</v>
+      </c>
+      <c r="B64" t="s">
+        <v>99</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>17</v>
+      </c>
+      <c r="B65" t="s">
+        <v>100</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>17</v>
+      </c>
+      <c r="B66" t="s">
+        <v>101</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A67" t="s">
+        <v>17</v>
+      </c>
+      <c r="B67" t="s">
+        <v>102</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A68" t="s">
+        <v>17</v>
+      </c>
+      <c r="B68" t="s">
+        <v>103</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A69" t="s">
+        <v>17</v>
+      </c>
+      <c r="B69" t="s">
+        <v>104</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A70" t="s">
+        <v>105</v>
+      </c>
+      <c r="B70" t="s">
+        <v>106</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1301,31 +1525,31 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
+  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
+</sisl>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <WrappedLabelHistory xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory">
   <Value>PD94bWwgdmVyc2lvbj0iMS4wIiBlbmNvZGluZz0idXMtYXNjaWkiPz48bGFiZWxIaXN0b3J5IHhtbG5zOnhzZD0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEiIHhtbG5zOnhzaT0iaHR0cDovL3d3dy53My5vcmcvMjAwMS9YTUxTY2hlbWEtaW5zdGFuY2UiIHhtbG5zPSJodHRwOi8vd3d3LmJvbGRvbmphbWVzLmNvbS8yMDE2LzAyL0NsYXNzaWZpZXIvaW50ZXJuYWwvbGFiZWxIaXN0b3J5Ij48aXRlbT48c2lzbCBzaXNsVmVyc2lvbj0iMCIgcG9saWN5PSJkZDIwZDIzOS1hN2U2LTRjNDktODc3Yy00NWI3YjQzMzU5Y2IiIG9yaWdpbj0idXNlclNlbGVjdGVkIj48ZWxlbWVudCB1aWQ9IjNiY2U0YTYzLTM2NzYtNDkzMS04MDlkLTNkNzI3YzZmNDMyNCIgdmFsdWU9IiIgeG1sbnM9Imh0dHA6Ly93d3cuYm9sZG9uamFtZXMuY29tLzIwMDgvMDEvc2llL2ludGVybmFsL2xhYmVsIiAvPjwvc2lzbD48VXNlck5hbWU+QUxMSUFOWlxCRTAzNTMxPC9Vc2VyTmFtZT48RGF0ZVRpbWU+MzAvMTIvMjAyMCAxMTo0NTo1NzwvRGF0ZVRpbWU+PExhYmVsU3RyaW5nPiAgICAgICAzMC8xMi8yMDIwICBQJiN4REE7QkxJQ08gIDwvTGFiZWxTdHJpbmc+PC9pdGVtPjwvbGFiZWxIaXN0b3J5Pg==</Value>
 </WrappedLabelHistory>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<sisl xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns="http://www.boldonjames.com/2008/01/sie/internal/label" sislVersion="0" policy="dd20d239-a7e6-4c49-877c-45b7b43359cb" origin="userSelected">
-  <element uid="3bce4a63-3676-4931-809d-3d727c6f4324" value=""/>
-</sisl>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41A8E509-6991-4B84-B1B5-13851E156C6A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{94DBFCB3-53E5-4527-B13D-DC7A854D4B55}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://www.boldonjames.com/2016/02/Classifier/internal/wrappedLabelHistory"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{41A8E509-6991-4B84-B1B5-13851E156C6A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://www.boldonjames.com/2008/01/sie/internal/label"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
+++ b/Treinamento/Envio de e-mail retorno GO - Planilha Padrão.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\ntxnas1\brasil\DIRETORIAS\DIR EXE OPERACOES\GESTAO OPERACIONAL\BACK-OFFICE\Dados e Relatórios\Envio de e-mail retorno GO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9FD1569-6ED0-4EA0-BA2B-1721FB9D94AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095FC317-B156-4D5E-986F-91CE07391684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="88">
   <si>
     <t>Campo Assunto</t>
   </si>
@@ -53,313 +53,256 @@
     <t>Prezado (a), existe uma tarefa no GO! Pendente de análise. Por favor, acesse seu painel para validação e retorno. "Este e-mail é um envio automático, favor não responder. Att."</t>
   </si>
   <si>
-    <t>patricia.reis@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13105642600000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>caroline.wojciechowski@allianz.com.br</t>
-  </si>
-  <si>
     <t>lilian.sudati@allianz.com.br</t>
   </si>
   <si>
     <t>juliano.guimaraes@allianz.com.br</t>
   </si>
   <si>
-    <t>rodrigo.kuguyama@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11304671100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>bruno.rosa@allianz.com.br</t>
-  </si>
-  <si>
-    <t>priscila.santana@allianz.com.br</t>
-  </si>
-  <si>
-    <t>laiane.martins@allianz.com.br</t>
-  </si>
-  <si>
     <t>gabriela.logrado@allianz.com.br</t>
   </si>
   <si>
-    <t>adautina.neves@allianz.com.br</t>
-  </si>
-  <si>
-    <t>cassia.silveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>fabiana.moura@allianz.com.br</t>
-  </si>
-  <si>
     <t>andreia.brixner@allianz.com.br</t>
   </si>
   <si>
-    <t>Retorno de GO referência-13107458400000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11745882900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>matheus.gomes@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13097986300000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>caroline.falcao@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12651740700000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13044204100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13112038900000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13099778800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13100822100000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13100857700000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13100877300000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13100989100000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13107363100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>thais.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12331803900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>alessandra.araujo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12756682900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13096463400000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>vanessa.campos@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13107596500000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>fernando.martins1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13106438600000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13050614200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>allan.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13095684200000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>lidiane.oliveira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13108127800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13097485000000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>viviane.lima@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13089295800000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>barbara.silva1@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13101289400000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>luiz.sanchetta@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13108019600000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>daiane.soares@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13094391500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>andreia.cardias@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13107414900000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>rosilene.nogueira@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13103675100000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>fabio.ribeiro@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13087978600000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13108354200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13110623500000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13110638100000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13107064200000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13107166300000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13109256200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13110022200000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13110706200000 Nota 595 - ERRO PDF</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13111026300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13111151300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13111221600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13111225100000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13111725600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13111820300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13111993900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13112154300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13112156100000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13112795400000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>ivana.freitas@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13103998800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
     <t>leticia.bezerra@allianz.com.br</t>
   </si>
   <si>
     <t>Retorno de GO referência-11230308000140 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
   </si>
   <si>
-    <t>edmar.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13113755700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13113780700000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13113813600000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13113834800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13113865800000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13113890500000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13113911900000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13113939200000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13113955300000 Nota 595 - ERRO PDF retorno</t>
-  </si>
-  <si>
-    <t>leinny.amorim@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13097128400000 Nota 595 - ERRO PDF Retorno</t>
-  </si>
-  <si>
-    <t>enriete.saucedo@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12893248800000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-73952583049 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-12689136800000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13100135700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13100257300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13100273600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13101377300000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-13101533700000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
-  </si>
-  <si>
-    <t>barbara.silva@allianz.com.br</t>
-  </si>
-  <si>
-    <t>Retorno de GO referência-11825312800000 Nota 167 - Retorno Cobrança op53</t>
+    <t>Retorno de GO referência-13024574300000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13064907400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>eliana.pedroso@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12674016200000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13113098700000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>edirilsa.bastos@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13112578500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13102551400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13107342800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>daniel.iarrocheski@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13102172300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>karina.barros@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12251796600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13104246000000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>leandro.pires@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12690699000000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12692429300000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>kaue.medeiros@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13115573100000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>juliana.diniz@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12786534000000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>renata.magalhaes@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13103354600000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>gustavo.correa@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13101065300000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13108959200000 Nota 742 - Reanalise vistoria Aceitável-exclus Operações</t>
+  </si>
+  <si>
+    <t>bruna.teixeira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13044486100000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>ana.cunha@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13102761400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>everton.silva1@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13104244900000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>raphael.callado@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12806788000000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>raullison.castro@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13028159500000 Nota 736 - Dispensa vistoria prévia -exclusivo Operações</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13109557500000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13110300900000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13111854800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13111919100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13112583600000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13112733800000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13113031700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13113052000000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13113094000000 Nota 595 - ERRO PDF Retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13113342700000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13113570200000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13113727300000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13113732100000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>roberta.oliveira@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-9150620703 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>patricia.soares@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13107893600000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>thays.silva@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12757858400000 Nota 595 - ERRO PDF retorno</t>
+  </si>
+  <si>
+    <t>lais.xavier@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13106723500000 Nota 743 - Reanalise vistoria Recusável-exclu. Operações</t>
+  </si>
+  <si>
+    <t>daniella.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-62072080134 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>marli.rocha@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12674016200000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>ana.rodrigues@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-12995744900000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>carolina.lima@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13094022000000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>rosemeire.faria@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13096968000000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>lucidene.santana@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13101273000000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13108331300000 Nota 472 - Reentrada OK Produto</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13111352000000 Nota 167 - Retorno Cobrança op53</t>
+  </si>
+  <si>
+    <t>renata.scarpino@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13030423600000 Nota 167 - Retorno Cobrança OP53</t>
+  </si>
+  <si>
+    <t>adriana.abreu@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-13093962100000 Nota 7027 - NOTIFICAÇÃO DE RECUSA MANUAL</t>
+  </si>
+  <si>
+    <t>carlos.neves@allianz.com.br</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-10867327600000 Nota 242 - Retorno Cobrança</t>
+  </si>
+  <si>
+    <t>Retorno de GO referência-11842570700000 Nota 242 - Retorno Cobrança</t>
   </si>
 </sst>
 </file>
@@ -756,10 +699,10 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>3</v>
@@ -770,7 +713,7 @@
         <v>7</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>3</v>
@@ -778,10 +721,10 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>3</v>
@@ -789,10 +732,10 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>3</v>
@@ -800,10 +743,10 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>3</v>
@@ -811,10 +754,10 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>3</v>
@@ -822,10 +765,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>3</v>
@@ -833,10 +776,10 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>3</v>
@@ -844,10 +787,10 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>3</v>
@@ -855,10 +798,10 @@
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>3</v>
@@ -866,10 +809,10 @@
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>3</v>
@@ -877,10 +820,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>3</v>
@@ -888,10 +831,10 @@
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>3</v>
@@ -899,10 +842,10 @@
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="B15" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>3</v>
@@ -910,10 +853,10 @@
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>3</v>
@@ -921,10 +864,10 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>3</v>
@@ -932,10 +875,10 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="B18" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>3</v>
@@ -943,10 +886,10 @@
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>3</v>
@@ -954,10 +897,10 @@
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>3</v>
@@ -965,10 +908,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>3</v>
@@ -976,10 +919,10 @@
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>42</v>
+      </c>
+      <c r="B22" t="s">
         <v>43</v>
-      </c>
-      <c r="B22" t="s">
-        <v>44</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>3</v>
@@ -987,10 +930,10 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>44</v>
+      </c>
+      <c r="B23" t="s">
         <v>45</v>
-      </c>
-      <c r="B23" t="s">
-        <v>46</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>3</v>
@@ -1001,7 +944,7 @@
         <v>6</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>3</v>
@@ -1009,10 +952,10 @@
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>3</v>
@@ -1020,10 +963,10 @@
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="B26" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>3</v>
@@ -1031,10 +974,10 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>6</v>
       </c>
       <c r="B27" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>3</v>
@@ -1042,10 +985,10 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>3</v>
@@ -1053,10 +996,10 @@
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>56</v>
+        <v>6</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>3</v>
@@ -1064,10 +1007,10 @@
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>58</v>
+        <v>6</v>
       </c>
       <c r="B30" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>3</v>
@@ -1075,10 +1018,10 @@
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="B31" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>3</v>
@@ -1086,10 +1029,10 @@
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="B32" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>3</v>
@@ -1097,10 +1040,10 @@
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B33" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>3</v>
@@ -1108,10 +1051,10 @@
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>3</v>
@@ -1119,10 +1062,10 @@
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B35" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="C35" s="2" t="s">
         <v>3</v>
@@ -1130,10 +1073,10 @@
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>3</v>
@@ -1141,10 +1084,10 @@
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>14</v>
+        <v>59</v>
       </c>
       <c r="B37" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>3</v>
@@ -1152,10 +1095,10 @@
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>14</v>
+        <v>61</v>
       </c>
       <c r="B38" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>3</v>
@@ -1163,10 +1106,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B39" t="s">
-        <v>69</v>
+        <v>9</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>3</v>
@@ -1174,10 +1117,10 @@
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>14</v>
+        <v>63</v>
       </c>
       <c r="B40" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="C40" s="2" t="s">
         <v>3</v>
@@ -1185,10 +1128,10 @@
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="B41" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>3</v>
@@ -1196,10 +1139,10 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>14</v>
+        <v>67</v>
       </c>
       <c r="B42" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>3</v>
@@ -1207,10 +1150,10 @@
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="B43" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>3</v>
@@ -1218,10 +1161,10 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>14</v>
+        <v>71</v>
       </c>
       <c r="B44" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>3</v>
@@ -1229,10 +1172,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>14</v>
+        <v>73</v>
       </c>
       <c r="B45" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C45" s="2" t="s">
         <v>3</v>
@@ -1240,7 +1183,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="B46" t="s">
         <v>76</v>
@@ -1251,10 +1194,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>14</v>
+        <v>77</v>
       </c>
       <c r="B47" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>3</v>
@@ -1262,10 +1205,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>14</v>
+        <v>69</v>
       </c>
       <c r="B48" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>3</v>
@@ -1273,10 +1216,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>14</v>
+        <v>75</v>
       </c>
       <c r="B49" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>3</v>
@@ -1284,10 +1227,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B50" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C50" s="2" t="s">
         <v>3</v>
@@ -1295,10 +1238,10 @@
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B51" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C51" s="2" t="s">
         <v>3</v>
@@ -1306,10 +1249,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B52" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>3</v>
@@ -1317,201 +1260,82 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B53" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>84</v>
-      </c>
-      <c r="B54" t="s">
-        <v>87</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A54"/>
+      <c r="B54"/>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>84</v>
-      </c>
-      <c r="B55" t="s">
-        <v>88</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A55"/>
+      <c r="B55"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>84</v>
-      </c>
-      <c r="B56" t="s">
-        <v>89</v>
-      </c>
-      <c r="C56" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A56"/>
+      <c r="B56"/>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>84</v>
-      </c>
-      <c r="B57" t="s">
-        <v>90</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>